--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G43">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G62">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G80">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G116">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G129">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G132">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G135">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G145">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G152">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G158">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G171">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G176">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G197">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G206">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G208">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G223">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G267">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G268">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G269">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G291">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G292">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G295">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G302">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G304">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G311">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G312">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G313">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G314">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G315">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G319">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G321">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G323">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G332">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G333">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G340">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G341">
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G342">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G343">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G28">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sisaket United</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-09-12 08:00:00</t>
+          <t>2026-09-12 07:00:00</t>
         </is>
       </c>
     </row>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sisaket United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,68 +5195,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,68 +5358,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G38">
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pattani</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-12 08:30:00</t>
+          <t>2026-09-12 08:00:00</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Pattani</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="G52">
@@ -8781,68 +8781,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-12 08:35:00</t>
+          <t>2026-09-12 08:30:00</t>
         </is>
       </c>
     </row>
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="G53">
@@ -8944,68 +8944,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-09-12 08:45:00</t>
+          <t>2026-09-12 08:35:00</t>
         </is>
       </c>
     </row>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rasi Salai United</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-09-12 09:00:00</t>
+          <t>2026-09-12 08:45:00</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Rasi Salai United</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G63">
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G69">
@@ -11672,27 +11672,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G70">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-09-12 09:15:00</t>
+          <t>2026-09-12 09:00:00</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G71">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G72">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-09-12 09:45:00</t>
+          <t>2026-09-12 09:15:00</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G73">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-09-12 10:00:00</t>
+          <t>2026-09-12 09:45:00</t>
         </is>
       </c>
     </row>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G99">
@@ -16562,27 +16562,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-09-12 10:15:00</t>
+          <t>2026-09-12 10:00:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-09-12 10:30:00</t>
+          <t>2026-09-12 10:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-09-12 10:30:00</t>
+          <t>2026-09-12 10:15:00</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G111">
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-09-12 11:00:00</t>
+          <t>2026-09-12 10:30:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-12 11:00:00</t>
+          <t>2026-09-12 10:30:00</t>
         </is>
       </c>
     </row>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G155">
@@ -25695,7 +25695,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G156">
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G158">
@@ -26184,7 +26184,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G159">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O160">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P160">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26510,22 +26510,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,22 +26673,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26836,22 +26836,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G163">
@@ -26994,27 +26994,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G164">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-09-12 11:15:00</t>
+          <t>2026-09-12 11:00:00</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O165">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P165">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27243,10 +27243,10 @@
         <v>0</v>
       </c>
       <c r="AA165">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB165">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC165">
         <v>0</v>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-09-12 11:15:00</t>
+          <t>2026-09-12 11:00:00</t>
         </is>
       </c>
     </row>
@@ -27320,12 +27320,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G166">
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-09-12 11:30:00</t>
+          <t>2026-09-12 11:15:00</t>
         </is>
       </c>
     </row>
@@ -27483,12 +27483,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-09-12 11:30:00</t>
+          <t>2026-09-12 11:15:00</t>
         </is>
       </c>
     </row>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G168">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G169">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G170">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G172">
@@ -28466,7 +28466,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G173">
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G174">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-09-12 12:00:00</t>
+          <t>2026-09-12 11:30:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G175">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-09-12 12:00:00</t>
+          <t>2026-09-12 11:30:00</t>
         </is>
       </c>
     </row>
@@ -28950,12 +28950,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G176">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-09-12 12:00:00</t>
+          <t>2026-09-12 11:30:00</t>
         </is>
       </c>
     </row>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,22 +29607,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G180">
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G181">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-09-12 12:15:00</t>
+          <t>2026-09-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -29928,12 +29928,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G182">
@@ -30079,7 +30079,7 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>2026-09-12 12:15:00</t>
+          <t>2026-09-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30091,27 +30091,27 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G183">
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-09-12 12:30:00</t>
+          <t>2026-09-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30254,27 +30254,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G184">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-09-12 12:30:00</t>
+          <t>2026-09-12 12:15:00</t>
         </is>
       </c>
     </row>
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-09-12 12:30:00</t>
+          <t>2026-09-12 12:15:00</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G186">
@@ -30748,22 +30748,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G187">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G188">
@@ -31074,22 +31074,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G191">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G193">
@@ -31884,12 +31884,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G194">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>2026-09-12 12:45:00</t>
+          <t>2026-09-12 12:30:00</t>
         </is>
       </c>
     </row>
@@ -32047,12 +32047,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G195">
@@ -32198,7 +32198,7 @@
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>2026-09-12 12:50:00</t>
+          <t>2026-09-12 12:30:00</t>
         </is>
       </c>
     </row>
@@ -32210,12 +32210,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G196">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>2026-09-12 13:00:00</t>
+          <t>2026-09-12 12:30:00</t>
         </is>
       </c>
     </row>
@@ -32373,12 +32373,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G197">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-09-12 13:00:00</t>
+          <t>2026-09-12 12:45:00</t>
         </is>
       </c>
     </row>
@@ -32536,12 +32536,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-09-12 13:00:00</t>
+          <t>2026-09-12 12:50:00</t>
         </is>
       </c>
     </row>
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G199">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,22 +33193,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O213">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P213">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35067,10 +35067,10 @@
         <v>0</v>
       </c>
       <c r="AA213">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB213">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC213">
         <v>0</v>
@@ -35144,12 +35144,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-09-12 13:15:00</t>
+          <t>2026-09-12 13:00:00</t>
         </is>
       </c>
     </row>
@@ -35307,12 +35307,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-09-12 13:15:00</t>
+          <t>2026-09-12 13:00:00</t>
         </is>
       </c>
     </row>
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35556,10 +35556,10 @@
         <v>0</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC216">
         <v>0</v>
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:00</t>
+          <t>2026-09-12 13:00:00</t>
         </is>
       </c>
     </row>
@@ -35633,12 +35633,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G217">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:00</t>
+          <t>2026-09-12 13:15:00</t>
         </is>
       </c>
     </row>
@@ -35796,12 +35796,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G218">
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:00</t>
+          <t>2026-09-12 13:15:00</t>
         </is>
       </c>
     </row>
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O219">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P219">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36045,10 +36045,10 @@
         <v>0</v>
       </c>
       <c r="AA219">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB219">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC219">
         <v>0</v>
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G220">
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G221">
@@ -36448,12 +36448,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G222">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-09-12 13:45:00</t>
+          <t>2026-09-12 13:30:00</t>
         </is>
       </c>
     </row>
@@ -36611,12 +36611,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36697,10 +36697,10 @@
         <v>0</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC223">
         <v>0</v>
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-09-12 13:45:00</t>
+          <t>2026-09-12 13:30:00</t>
         </is>
       </c>
     </row>
@@ -36774,12 +36774,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G224">
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>2026-09-12 13:45:00</t>
+          <t>2026-09-12 13:30:00</t>
         </is>
       </c>
     </row>
@@ -36937,12 +36937,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G225">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>2026-09-12 14:00:00</t>
+          <t>2026-09-12 13:30:00</t>
         </is>
       </c>
     </row>
@@ -37100,12 +37100,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G226">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-09-12 14:00:00</t>
+          <t>2026-09-12 13:45:00</t>
         </is>
       </c>
     </row>
@@ -37263,12 +37263,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G227">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-09-12 14:00:00</t>
+          <t>2026-09-12 13:45:00</t>
         </is>
       </c>
     </row>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-09-12 14:00:00</t>
+          <t>2026-09-12 13:45:00</t>
         </is>
       </c>
     </row>
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G229">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G230">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G231">
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G235">
@@ -38730,12 +38730,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G236">
@@ -38881,7 +38881,7 @@
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>2026-09-12 14:30:00</t>
+          <t>2026-09-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -38893,12 +38893,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G237">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>2026-09-12 14:30:00</t>
+          <t>2026-09-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -39056,12 +39056,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G238">
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-09-12 14:30:00</t>
+          <t>2026-09-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -39219,12 +39219,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G239">
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-09-12 14:45:00</t>
+          <t>2026-09-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -39382,12 +39382,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G240">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-09-12 15:00:00</t>
+          <t>2026-09-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -39545,12 +39545,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G241">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-09-12 15:00:00</t>
+          <t>2026-09-12 14:30:00</t>
         </is>
       </c>
     </row>
@@ -39708,27 +39708,27 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G242">
@@ -39859,7 +39859,7 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>2026-09-12 15:00:00</t>
+          <t>2026-09-12 14:30:00</t>
         </is>
       </c>
     </row>
@@ -39871,12 +39871,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-09-12 15:00:00</t>
+          <t>2026-09-12 14:30:00</t>
         </is>
       </c>
     </row>
@@ -40034,27 +40034,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G244">
@@ -40185,7 +40185,7 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>2026-09-12 15:00:00</t>
+          <t>2026-09-12 14:45:00</t>
         </is>
       </c>
     </row>
@@ -40202,22 +40202,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G246">
@@ -40528,22 +40528,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,22 +40854,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,22 +41017,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,22 +41180,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G251">
@@ -41338,12 +41338,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G252">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-09-12 15:15:00</t>
+          <t>2026-09-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G253">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-09-12 15:15:00</t>
+          <t>2026-09-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -41664,12 +41664,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-09-12 15:15:00</t>
+          <t>2026-09-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -41827,27 +41827,27 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G255">
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:00</t>
+          <t>2026-09-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -41990,12 +41990,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G256">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:00</t>
+          <t>2026-09-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -42153,12 +42153,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G257">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:00</t>
+          <t>2026-09-12 15:15:00</t>
         </is>
       </c>
     </row>
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:00</t>
+          <t>2026-09-12 15:15:00</t>
         </is>
       </c>
     </row>
@@ -42479,27 +42479,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G259">
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:00</t>
+          <t>2026-09-12 15:15:00</t>
         </is>
       </c>
     </row>
@@ -42642,12 +42642,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G260">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -42805,27 +42805,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -42968,27 +42968,27 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43131,12 +43131,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G263">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G264">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43457,27 +43457,27 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G265">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G266">
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -44272,12 +44272,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G270">
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -44435,27 +44435,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O271">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P271">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44521,10 +44521,10 @@
         <v>0</v>
       </c>
       <c r="AA271">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB271">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC271">
         <v>0</v>
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -44598,27 +44598,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O272">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P272">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44684,10 +44684,10 @@
         <v>0</v>
       </c>
       <c r="AA272">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB272">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC272">
         <v>0</v>
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,22 +45092,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,22 +45418,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.16</v>
+        <v>2.25</v>
       </c>
       <c r="O277">
-        <v>7.93</v>
+        <v>3.3</v>
       </c>
       <c r="P277">
-        <v>13.61</v>
+        <v>3.3</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45499,10 +45499,10 @@
         <v>0</v>
       </c>
       <c r="AA277">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AB277">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC277">
         <v>0</v>
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45662,10 +45662,10 @@
         <v>0</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC278">
         <v>0</v>
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,22 +45907,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G280">
@@ -46065,12 +46065,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O281">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P281">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46151,10 +46151,10 @@
         <v>0</v>
       </c>
       <c r="AA281">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB281">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC281">
         <v>0</v>
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-09-12 17:00:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46228,27 +46228,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-09-12 17:00:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>7.93</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>13.61</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46477,10 +46477,10 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC283">
         <v>0</v>
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-09-12 17:00:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46554,27 +46554,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G284">
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-09-12 17:00:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46717,27 +46717,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-09-12 17:00:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46880,27 +46880,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-09-12 18:15:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -47043,27 +47043,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O287">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P287">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47129,10 +47129,10 @@
         <v>0</v>
       </c>
       <c r="AA287">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB287">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC287">
         <v>0</v>
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-09-12 18:30:00</t>
+          <t>2026-09-12 16:30:00</t>
         </is>
       </c>
     </row>
@@ -47206,12 +47206,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30:00</t>
+          <t>2026-09-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47369,12 +47369,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30:00</t>
+          <t>2026-09-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47532,27 +47532,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47695,12 +47695,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G291">
@@ -47846,7 +47846,7 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47858,12 +47858,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G292">
@@ -48009,7 +48009,7 @@
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -48021,12 +48021,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G293">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 18:15:00</t>
         </is>
       </c>
     </row>
@@ -48184,12 +48184,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -48270,10 +48270,10 @@
         <v>0</v>
       </c>
       <c r="AA294">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB294">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC294">
         <v>0</v>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 18:30:00</t>
         </is>
       </c>
     </row>
@@ -48347,12 +48347,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G295">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 19:30:00</t>
         </is>
       </c>
     </row>
@@ -48510,12 +48510,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G296">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 19:30:00</t>
         </is>
       </c>
     </row>
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G297">
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G298">
@@ -48922,10 +48922,10 @@
         <v>0</v>
       </c>
       <c r="AA298">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB298">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC298">
         <v>0</v>
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G300">
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G301">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49488,12 +49488,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G303">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49814,12 +49814,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G304">
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -49977,27 +49977,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G305">
@@ -50063,10 +50063,10 @@
         <v>0</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC305">
         <v>0</v>
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O306">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P306">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50226,10 +50226,10 @@
         <v>0</v>
       </c>
       <c r="AA306">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB306">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC306">
         <v>0</v>
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -50303,27 +50303,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G307">
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -50466,27 +50466,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G308">
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -50629,27 +50629,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G309">
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -50792,27 +50792,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G310">
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -50955,27 +50955,27 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G311">
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G312">
@@ -51286,22 +51286,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51367,10 +51367,10 @@
         <v>0</v>
       </c>
       <c r="AA313">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB313">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC313">
         <v>0</v>
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G314">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G315">
@@ -51775,22 +51775,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G316">
@@ -51938,22 +51938,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G317">
@@ -52101,22 +52101,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G322">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G323">
@@ -53079,7 +53079,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G324">
@@ -53242,22 +53242,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G325">
@@ -53405,22 +53405,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G326">
@@ -53568,22 +53568,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G332">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G333">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G99">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G113">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G120">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G137">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G156">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G160">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G174">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G201">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G261">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G262">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G267">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G268">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G269">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G298">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G299">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G300">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G302">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G108">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G118">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G156">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G215">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G299">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G300">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G301">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G309">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G310">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G311">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G151">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G156">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU345"/>
+  <dimension ref="A1:AU339"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G314">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G315">
@@ -51775,22 +51775,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G316">
@@ -51938,22 +51938,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G317">
@@ -52101,22 +52101,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G321">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G322">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G323">
@@ -53079,7 +53079,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G324">
@@ -53242,22 +53242,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G325">
@@ -53405,22 +53405,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G326">
@@ -53568,22 +53568,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G327">
@@ -53726,27 +53726,27 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G328">
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 21:30:00</t>
         </is>
       </c>
     </row>
@@ -53889,27 +53889,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G329">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 21:30:00</t>
         </is>
       </c>
     </row>
@@ -54052,27 +54052,27 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G330">
@@ -54203,7 +54203,7 @@
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 21:30:00</t>
         </is>
       </c>
     </row>
@@ -54215,27 +54215,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G331">
@@ -54366,7 +54366,7 @@
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 21:45:00</t>
         </is>
       </c>
     </row>
@@ -54378,27 +54378,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G332">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 22:30:00</t>
         </is>
       </c>
     </row>
@@ -54541,27 +54541,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 22:30:00</t>
         </is>
       </c>
     </row>
@@ -54704,12 +54704,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G334">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-09-12 21:30:00</t>
+          <t>2026-09-12 23:00:00</t>
         </is>
       </c>
     </row>
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-09-12 21:30:00</t>
+          <t>2026-09-12 23:00:00</t>
         </is>
       </c>
     </row>
@@ -55030,12 +55030,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G336">
@@ -55181,7 +55181,7 @@
       </c>
       <c r="AU336" t="inlineStr">
         <is>
-          <t>2026-09-12 21:30:00</t>
+          <t>2026-09-12 23:00:00</t>
         </is>
       </c>
     </row>
@@ -55193,12 +55193,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G337">
@@ -55344,7 +55344,7 @@
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>2026-09-12 21:45:00</t>
+          <t>2026-09-12 23:00:00</t>
         </is>
       </c>
     </row>
@@ -55356,7 +55356,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G338">
@@ -55507,7 +55507,7 @@
       </c>
       <c r="AU338" t="inlineStr">
         <is>
-          <t>2026-09-12 22:30:00</t>
+          <t>2026-09-12 23:30:00</t>
         </is>
       </c>
     </row>
@@ -55519,7 +55519,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G339">
@@ -55669,984 +55669,6 @@
         <v>0</v>
       </c>
       <c r="AU339" t="inlineStr">
-        <is>
-          <t>2026-09-12 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>Sacramento Republic</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>Detroit City FC</t>
-        </is>
-      </c>
-      <c r="G340">
-        <v>0</v>
-      </c>
-      <c r="H340">
-        <v>0</v>
-      </c>
-      <c r="I340">
-        <v>0</v>
-      </c>
-      <c r="J340">
-        <v>0</v>
-      </c>
-      <c r="K340">
-        <v>0</v>
-      </c>
-      <c r="L340">
-        <v>0</v>
-      </c>
-      <c r="M340" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N340">
-        <v>0</v>
-      </c>
-      <c r="O340">
-        <v>0</v>
-      </c>
-      <c r="P340">
-        <v>0</v>
-      </c>
-      <c r="Q340">
-        <v>0</v>
-      </c>
-      <c r="R340">
-        <v>0</v>
-      </c>
-      <c r="S340">
-        <v>0</v>
-      </c>
-      <c r="T340">
-        <v>0</v>
-      </c>
-      <c r="U340">
-        <v>0</v>
-      </c>
-      <c r="V340">
-        <v>0</v>
-      </c>
-      <c r="W340">
-        <v>0</v>
-      </c>
-      <c r="X340">
-        <v>0</v>
-      </c>
-      <c r="Y340">
-        <v>0</v>
-      </c>
-      <c r="Z340">
-        <v>0</v>
-      </c>
-      <c r="AA340">
-        <v>0</v>
-      </c>
-      <c r="AB340">
-        <v>0</v>
-      </c>
-      <c r="AC340">
-        <v>0</v>
-      </c>
-      <c r="AD340">
-        <v>0</v>
-      </c>
-      <c r="AE340">
-        <v>0</v>
-      </c>
-      <c r="AF340">
-        <v>0</v>
-      </c>
-      <c r="AG340">
-        <v>0</v>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI340" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ340">
-        <v>0</v>
-      </c>
-      <c r="AK340">
-        <v>0</v>
-      </c>
-      <c r="AL340">
-        <v>0</v>
-      </c>
-      <c r="AM340">
-        <v>-1</v>
-      </c>
-      <c r="AN340">
-        <v>-1</v>
-      </c>
-      <c r="AO340">
-        <v>-1</v>
-      </c>
-      <c r="AP340">
-        <v>-1</v>
-      </c>
-      <c r="AQ340">
-        <v>0</v>
-      </c>
-      <c r="AR340">
-        <v>0</v>
-      </c>
-      <c r="AS340">
-        <v>0</v>
-      </c>
-      <c r="AT340">
-        <v>0</v>
-      </c>
-      <c r="AU340" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks</t>
-        </is>
-      </c>
-      <c r="G341">
-        <v>0</v>
-      </c>
-      <c r="H341">
-        <v>0</v>
-      </c>
-      <c r="I341">
-        <v>0</v>
-      </c>
-      <c r="J341">
-        <v>0</v>
-      </c>
-      <c r="K341">
-        <v>0</v>
-      </c>
-      <c r="L341">
-        <v>0</v>
-      </c>
-      <c r="M341" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N341">
-        <v>0</v>
-      </c>
-      <c r="O341">
-        <v>0</v>
-      </c>
-      <c r="P341">
-        <v>0</v>
-      </c>
-      <c r="Q341">
-        <v>0</v>
-      </c>
-      <c r="R341">
-        <v>0</v>
-      </c>
-      <c r="S341">
-        <v>0</v>
-      </c>
-      <c r="T341">
-        <v>0</v>
-      </c>
-      <c r="U341">
-        <v>0</v>
-      </c>
-      <c r="V341">
-        <v>0</v>
-      </c>
-      <c r="W341">
-        <v>0</v>
-      </c>
-      <c r="X341">
-        <v>0</v>
-      </c>
-      <c r="Y341">
-        <v>0</v>
-      </c>
-      <c r="Z341">
-        <v>0</v>
-      </c>
-      <c r="AA341">
-        <v>0</v>
-      </c>
-      <c r="AB341">
-        <v>0</v>
-      </c>
-      <c r="AC341">
-        <v>0</v>
-      </c>
-      <c r="AD341">
-        <v>0</v>
-      </c>
-      <c r="AE341">
-        <v>0</v>
-      </c>
-      <c r="AF341">
-        <v>0</v>
-      </c>
-      <c r="AG341">
-        <v>0</v>
-      </c>
-      <c r="AH341" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI341" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ341">
-        <v>0</v>
-      </c>
-      <c r="AK341">
-        <v>0</v>
-      </c>
-      <c r="AL341">
-        <v>0</v>
-      </c>
-      <c r="AM341">
-        <v>-1</v>
-      </c>
-      <c r="AN341">
-        <v>-1</v>
-      </c>
-      <c r="AO341">
-        <v>-1</v>
-      </c>
-      <c r="AP341">
-        <v>-1</v>
-      </c>
-      <c r="AQ341">
-        <v>0</v>
-      </c>
-      <c r="AR341">
-        <v>0</v>
-      </c>
-      <c r="AS341">
-        <v>0</v>
-      </c>
-      <c r="AT341">
-        <v>0</v>
-      </c>
-      <c r="AU341" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>Las Vegas Lights</t>
-        </is>
-      </c>
-      <c r="G342">
-        <v>0</v>
-      </c>
-      <c r="H342">
-        <v>0</v>
-      </c>
-      <c r="I342">
-        <v>0</v>
-      </c>
-      <c r="J342">
-        <v>0</v>
-      </c>
-      <c r="K342">
-        <v>0</v>
-      </c>
-      <c r="L342">
-        <v>0</v>
-      </c>
-      <c r="M342" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N342">
-        <v>0</v>
-      </c>
-      <c r="O342">
-        <v>0</v>
-      </c>
-      <c r="P342">
-        <v>0</v>
-      </c>
-      <c r="Q342">
-        <v>0</v>
-      </c>
-      <c r="R342">
-        <v>0</v>
-      </c>
-      <c r="S342">
-        <v>0</v>
-      </c>
-      <c r="T342">
-        <v>0</v>
-      </c>
-      <c r="U342">
-        <v>0</v>
-      </c>
-      <c r="V342">
-        <v>0</v>
-      </c>
-      <c r="W342">
-        <v>0</v>
-      </c>
-      <c r="X342">
-        <v>0</v>
-      </c>
-      <c r="Y342">
-        <v>0</v>
-      </c>
-      <c r="Z342">
-        <v>0</v>
-      </c>
-      <c r="AA342">
-        <v>0</v>
-      </c>
-      <c r="AB342">
-        <v>0</v>
-      </c>
-      <c r="AC342">
-        <v>0</v>
-      </c>
-      <c r="AD342">
-        <v>0</v>
-      </c>
-      <c r="AE342">
-        <v>0</v>
-      </c>
-      <c r="AF342">
-        <v>0</v>
-      </c>
-      <c r="AG342">
-        <v>0</v>
-      </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI342" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ342">
-        <v>0</v>
-      </c>
-      <c r="AK342">
-        <v>0</v>
-      </c>
-      <c r="AL342">
-        <v>0</v>
-      </c>
-      <c r="AM342">
-        <v>-1</v>
-      </c>
-      <c r="AN342">
-        <v>-1</v>
-      </c>
-      <c r="AO342">
-        <v>-1</v>
-      </c>
-      <c r="AP342">
-        <v>-1</v>
-      </c>
-      <c r="AQ342">
-        <v>0</v>
-      </c>
-      <c r="AR342">
-        <v>0</v>
-      </c>
-      <c r="AS342">
-        <v>0</v>
-      </c>
-      <c r="AT342">
-        <v>0</v>
-      </c>
-      <c r="AU342" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>Lexington</t>
-        </is>
-      </c>
-      <c r="G343">
-        <v>0</v>
-      </c>
-      <c r="H343">
-        <v>0</v>
-      </c>
-      <c r="I343">
-        <v>0</v>
-      </c>
-      <c r="J343">
-        <v>0</v>
-      </c>
-      <c r="K343">
-        <v>0</v>
-      </c>
-      <c r="L343">
-        <v>0</v>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N343">
-        <v>0</v>
-      </c>
-      <c r="O343">
-        <v>0</v>
-      </c>
-      <c r="P343">
-        <v>0</v>
-      </c>
-      <c r="Q343">
-        <v>0</v>
-      </c>
-      <c r="R343">
-        <v>0</v>
-      </c>
-      <c r="S343">
-        <v>0</v>
-      </c>
-      <c r="T343">
-        <v>0</v>
-      </c>
-      <c r="U343">
-        <v>0</v>
-      </c>
-      <c r="V343">
-        <v>0</v>
-      </c>
-      <c r="W343">
-        <v>0</v>
-      </c>
-      <c r="X343">
-        <v>0</v>
-      </c>
-      <c r="Y343">
-        <v>0</v>
-      </c>
-      <c r="Z343">
-        <v>0</v>
-      </c>
-      <c r="AA343">
-        <v>0</v>
-      </c>
-      <c r="AB343">
-        <v>0</v>
-      </c>
-      <c r="AC343">
-        <v>0</v>
-      </c>
-      <c r="AD343">
-        <v>0</v>
-      </c>
-      <c r="AE343">
-        <v>0</v>
-      </c>
-      <c r="AF343">
-        <v>0</v>
-      </c>
-      <c r="AG343">
-        <v>0</v>
-      </c>
-      <c r="AH343" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI343" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ343">
-        <v>0</v>
-      </c>
-      <c r="AK343">
-        <v>0</v>
-      </c>
-      <c r="AL343">
-        <v>0</v>
-      </c>
-      <c r="AM343">
-        <v>-1</v>
-      </c>
-      <c r="AN343">
-        <v>-1</v>
-      </c>
-      <c r="AO343">
-        <v>-1</v>
-      </c>
-      <c r="AP343">
-        <v>-1</v>
-      </c>
-      <c r="AQ343">
-        <v>0</v>
-      </c>
-      <c r="AR343">
-        <v>0</v>
-      </c>
-      <c r="AS343">
-        <v>0</v>
-      </c>
-      <c r="AT343">
-        <v>0</v>
-      </c>
-      <c r="AU343" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="G344">
-        <v>0</v>
-      </c>
-      <c r="H344">
-        <v>0</v>
-      </c>
-      <c r="I344">
-        <v>0</v>
-      </c>
-      <c r="J344">
-        <v>0</v>
-      </c>
-      <c r="K344">
-        <v>0</v>
-      </c>
-      <c r="L344">
-        <v>0</v>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N344">
-        <v>0</v>
-      </c>
-      <c r="O344">
-        <v>0</v>
-      </c>
-      <c r="P344">
-        <v>0</v>
-      </c>
-      <c r="Q344">
-        <v>0</v>
-      </c>
-      <c r="R344">
-        <v>0</v>
-      </c>
-      <c r="S344">
-        <v>0</v>
-      </c>
-      <c r="T344">
-        <v>0</v>
-      </c>
-      <c r="U344">
-        <v>0</v>
-      </c>
-      <c r="V344">
-        <v>0</v>
-      </c>
-      <c r="W344">
-        <v>0</v>
-      </c>
-      <c r="X344">
-        <v>0</v>
-      </c>
-      <c r="Y344">
-        <v>0</v>
-      </c>
-      <c r="Z344">
-        <v>0</v>
-      </c>
-      <c r="AA344">
-        <v>0</v>
-      </c>
-      <c r="AB344">
-        <v>0</v>
-      </c>
-      <c r="AC344">
-        <v>0</v>
-      </c>
-      <c r="AD344">
-        <v>0</v>
-      </c>
-      <c r="AE344">
-        <v>0</v>
-      </c>
-      <c r="AF344">
-        <v>0</v>
-      </c>
-      <c r="AG344">
-        <v>0</v>
-      </c>
-      <c r="AH344" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI344" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ344">
-        <v>0</v>
-      </c>
-      <c r="AK344">
-        <v>0</v>
-      </c>
-      <c r="AL344">
-        <v>0</v>
-      </c>
-      <c r="AM344">
-        <v>-1</v>
-      </c>
-      <c r="AN344">
-        <v>-1</v>
-      </c>
-      <c r="AO344">
-        <v>-1</v>
-      </c>
-      <c r="AP344">
-        <v>-1</v>
-      </c>
-      <c r="AQ344">
-        <v>0</v>
-      </c>
-      <c r="AR344">
-        <v>0</v>
-      </c>
-      <c r="AS344">
-        <v>0</v>
-      </c>
-      <c r="AT344">
-        <v>0</v>
-      </c>
-      <c r="AU344" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="G345">
-        <v>0</v>
-      </c>
-      <c r="H345">
-        <v>0</v>
-      </c>
-      <c r="I345">
-        <v>0</v>
-      </c>
-      <c r="J345">
-        <v>0</v>
-      </c>
-      <c r="K345">
-        <v>0</v>
-      </c>
-      <c r="L345">
-        <v>0</v>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N345">
-        <v>0</v>
-      </c>
-      <c r="O345">
-        <v>0</v>
-      </c>
-      <c r="P345">
-        <v>0</v>
-      </c>
-      <c r="Q345">
-        <v>0</v>
-      </c>
-      <c r="R345">
-        <v>0</v>
-      </c>
-      <c r="S345">
-        <v>0</v>
-      </c>
-      <c r="T345">
-        <v>0</v>
-      </c>
-      <c r="U345">
-        <v>0</v>
-      </c>
-      <c r="V345">
-        <v>0</v>
-      </c>
-      <c r="W345">
-        <v>0</v>
-      </c>
-      <c r="X345">
-        <v>0</v>
-      </c>
-      <c r="Y345">
-        <v>0</v>
-      </c>
-      <c r="Z345">
-        <v>0</v>
-      </c>
-      <c r="AA345">
-        <v>0</v>
-      </c>
-      <c r="AB345">
-        <v>0</v>
-      </c>
-      <c r="AC345">
-        <v>0</v>
-      </c>
-      <c r="AD345">
-        <v>0</v>
-      </c>
-      <c r="AE345">
-        <v>0</v>
-      </c>
-      <c r="AF345">
-        <v>0</v>
-      </c>
-      <c r="AG345">
-        <v>0</v>
-      </c>
-      <c r="AH345" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI345" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ345">
-        <v>0</v>
-      </c>
-      <c r="AK345">
-        <v>0</v>
-      </c>
-      <c r="AL345">
-        <v>0</v>
-      </c>
-      <c r="AM345">
-        <v>-1</v>
-      </c>
-      <c r="AN345">
-        <v>-1</v>
-      </c>
-      <c r="AO345">
-        <v>-1</v>
-      </c>
-      <c r="AP345">
-        <v>-1</v>
-      </c>
-      <c r="AQ345">
-        <v>0</v>
-      </c>
-      <c r="AR345">
-        <v>0</v>
-      </c>
-      <c r="AS345">
-        <v>0</v>
-      </c>
-      <c r="AT345">
-        <v>0</v>
-      </c>
-      <c r="AU345" t="inlineStr">
         <is>
           <t>2026-09-12 23:30:00</t>
         </is>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G113">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G116">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G118">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G124">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G136">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G147">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G152">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G156">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G158">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G201">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G236">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G261">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G262">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G297">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G298">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G299">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G301">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G316">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G321">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G338">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G339">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU339"/>
+  <dimension ref="A1:AU336"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G118">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G124">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G127">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G137">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G154">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G155">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G174">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G261">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G262">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G274">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G275">
@@ -53237,27 +53237,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G325">
@@ -53388,7 +53388,7 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 21:30:00</t>
         </is>
       </c>
     </row>
@@ -53400,27 +53400,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G326">
@@ -53551,7 +53551,7 @@
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 21:30:00</t>
         </is>
       </c>
     </row>
@@ -53563,27 +53563,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G327">
@@ -53714,7 +53714,7 @@
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 21:30:00</t>
         </is>
       </c>
     </row>
@@ -53726,12 +53726,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G328">
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>2026-09-12 21:30:00</t>
+          <t>2026-09-12 21:45:00</t>
         </is>
       </c>
     </row>
@@ -53889,7 +53889,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G329">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>2026-09-12 21:30:00</t>
+          <t>2026-09-12 22:30:00</t>
         </is>
       </c>
     </row>
@@ -54052,7 +54052,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G330">
@@ -54203,7 +54203,7 @@
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>2026-09-12 21:30:00</t>
+          <t>2026-09-12 22:30:00</t>
         </is>
       </c>
     </row>
@@ -54215,12 +54215,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G331">
@@ -54366,7 +54366,7 @@
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>2026-09-12 21:45:00</t>
+          <t>2026-09-12 23:00:00</t>
         </is>
       </c>
     </row>
@@ -54378,12 +54378,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G332">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-09-12 22:30:00</t>
+          <t>2026-09-12 23:00:00</t>
         </is>
       </c>
     </row>
@@ -54541,12 +54541,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-09-12 22:30:00</t>
+          <t>2026-09-12 23:00:00</t>
         </is>
       </c>
     </row>
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G334">
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-09-12 23:00:00</t>
+          <t>2026-09-12 23:30:00</t>
         </is>
       </c>
     </row>
@@ -55030,12 +55030,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G336">
@@ -55180,495 +55180,6 @@
         <v>0</v>
       </c>
       <c r="AU336" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Lexington</t>
-        </is>
-      </c>
-      <c r="G337">
-        <v>0</v>
-      </c>
-      <c r="H337">
-        <v>0</v>
-      </c>
-      <c r="I337">
-        <v>0</v>
-      </c>
-      <c r="J337">
-        <v>0</v>
-      </c>
-      <c r="K337">
-        <v>0</v>
-      </c>
-      <c r="L337">
-        <v>0</v>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N337">
-        <v>0</v>
-      </c>
-      <c r="O337">
-        <v>0</v>
-      </c>
-      <c r="P337">
-        <v>0</v>
-      </c>
-      <c r="Q337">
-        <v>0</v>
-      </c>
-      <c r="R337">
-        <v>0</v>
-      </c>
-      <c r="S337">
-        <v>0</v>
-      </c>
-      <c r="T337">
-        <v>0</v>
-      </c>
-      <c r="U337">
-        <v>0</v>
-      </c>
-      <c r="V337">
-        <v>0</v>
-      </c>
-      <c r="W337">
-        <v>0</v>
-      </c>
-      <c r="X337">
-        <v>0</v>
-      </c>
-      <c r="Y337">
-        <v>0</v>
-      </c>
-      <c r="Z337">
-        <v>0</v>
-      </c>
-      <c r="AA337">
-        <v>0</v>
-      </c>
-      <c r="AB337">
-        <v>0</v>
-      </c>
-      <c r="AC337">
-        <v>0</v>
-      </c>
-      <c r="AD337">
-        <v>0</v>
-      </c>
-      <c r="AE337">
-        <v>0</v>
-      </c>
-      <c r="AF337">
-        <v>0</v>
-      </c>
-      <c r="AG337">
-        <v>0</v>
-      </c>
-      <c r="AH337" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI337" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ337">
-        <v>0</v>
-      </c>
-      <c r="AK337">
-        <v>0</v>
-      </c>
-      <c r="AL337">
-        <v>0</v>
-      </c>
-      <c r="AM337">
-        <v>-1</v>
-      </c>
-      <c r="AN337">
-        <v>-1</v>
-      </c>
-      <c r="AO337">
-        <v>-1</v>
-      </c>
-      <c r="AP337">
-        <v>-1</v>
-      </c>
-      <c r="AQ337">
-        <v>0</v>
-      </c>
-      <c r="AR337">
-        <v>0</v>
-      </c>
-      <c r="AS337">
-        <v>0</v>
-      </c>
-      <c r="AT337">
-        <v>0</v>
-      </c>
-      <c r="AU337" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Seattle Sounders</t>
-        </is>
-      </c>
-      <c r="G338">
-        <v>0</v>
-      </c>
-      <c r="H338">
-        <v>0</v>
-      </c>
-      <c r="I338">
-        <v>0</v>
-      </c>
-      <c r="J338">
-        <v>0</v>
-      </c>
-      <c r="K338">
-        <v>0</v>
-      </c>
-      <c r="L338">
-        <v>0</v>
-      </c>
-      <c r="M338" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N338">
-        <v>0</v>
-      </c>
-      <c r="O338">
-        <v>0</v>
-      </c>
-      <c r="P338">
-        <v>0</v>
-      </c>
-      <c r="Q338">
-        <v>0</v>
-      </c>
-      <c r="R338">
-        <v>0</v>
-      </c>
-      <c r="S338">
-        <v>0</v>
-      </c>
-      <c r="T338">
-        <v>0</v>
-      </c>
-      <c r="U338">
-        <v>0</v>
-      </c>
-      <c r="V338">
-        <v>0</v>
-      </c>
-      <c r="W338">
-        <v>0</v>
-      </c>
-      <c r="X338">
-        <v>0</v>
-      </c>
-      <c r="Y338">
-        <v>0</v>
-      </c>
-      <c r="Z338">
-        <v>0</v>
-      </c>
-      <c r="AA338">
-        <v>0</v>
-      </c>
-      <c r="AB338">
-        <v>0</v>
-      </c>
-      <c r="AC338">
-        <v>0</v>
-      </c>
-      <c r="AD338">
-        <v>0</v>
-      </c>
-      <c r="AE338">
-        <v>0</v>
-      </c>
-      <c r="AF338">
-        <v>0</v>
-      </c>
-      <c r="AG338">
-        <v>0</v>
-      </c>
-      <c r="AH338" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI338" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ338">
-        <v>0</v>
-      </c>
-      <c r="AK338">
-        <v>0</v>
-      </c>
-      <c r="AL338">
-        <v>0</v>
-      </c>
-      <c r="AM338">
-        <v>-1</v>
-      </c>
-      <c r="AN338">
-        <v>-1</v>
-      </c>
-      <c r="AO338">
-        <v>-1</v>
-      </c>
-      <c r="AP338">
-        <v>-1</v>
-      </c>
-      <c r="AQ338">
-        <v>0</v>
-      </c>
-      <c r="AR338">
-        <v>0</v>
-      </c>
-      <c r="AS338">
-        <v>0</v>
-      </c>
-      <c r="AT338">
-        <v>0</v>
-      </c>
-      <c r="AU338" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="G339">
-        <v>0</v>
-      </c>
-      <c r="H339">
-        <v>0</v>
-      </c>
-      <c r="I339">
-        <v>0</v>
-      </c>
-      <c r="J339">
-        <v>0</v>
-      </c>
-      <c r="K339">
-        <v>0</v>
-      </c>
-      <c r="L339">
-        <v>0</v>
-      </c>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N339">
-        <v>0</v>
-      </c>
-      <c r="O339">
-        <v>0</v>
-      </c>
-      <c r="P339">
-        <v>0</v>
-      </c>
-      <c r="Q339">
-        <v>0</v>
-      </c>
-      <c r="R339">
-        <v>0</v>
-      </c>
-      <c r="S339">
-        <v>0</v>
-      </c>
-      <c r="T339">
-        <v>0</v>
-      </c>
-      <c r="U339">
-        <v>0</v>
-      </c>
-      <c r="V339">
-        <v>0</v>
-      </c>
-      <c r="W339">
-        <v>0</v>
-      </c>
-      <c r="X339">
-        <v>0</v>
-      </c>
-      <c r="Y339">
-        <v>0</v>
-      </c>
-      <c r="Z339">
-        <v>0</v>
-      </c>
-      <c r="AA339">
-        <v>0</v>
-      </c>
-      <c r="AB339">
-        <v>0</v>
-      </c>
-      <c r="AC339">
-        <v>0</v>
-      </c>
-      <c r="AD339">
-        <v>0</v>
-      </c>
-      <c r="AE339">
-        <v>0</v>
-      </c>
-      <c r="AF339">
-        <v>0</v>
-      </c>
-      <c r="AG339">
-        <v>0</v>
-      </c>
-      <c r="AH339" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI339" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ339">
-        <v>0</v>
-      </c>
-      <c r="AK339">
-        <v>0</v>
-      </c>
-      <c r="AL339">
-        <v>0</v>
-      </c>
-      <c r="AM339">
-        <v>-1</v>
-      </c>
-      <c r="AN339">
-        <v>-1</v>
-      </c>
-      <c r="AO339">
-        <v>-1</v>
-      </c>
-      <c r="AP339">
-        <v>-1</v>
-      </c>
-      <c r="AQ339">
-        <v>0</v>
-      </c>
-      <c r="AR339">
-        <v>0</v>
-      </c>
-      <c r="AS339">
-        <v>0</v>
-      </c>
-      <c r="AT339">
-        <v>0</v>
-      </c>
-      <c r="AU339" t="inlineStr">
         <is>
           <t>2026-09-12 23:30:00</t>
         </is>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU336"/>
+  <dimension ref="A1:AU337"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G34">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G58">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G86">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G92">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G106">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G147">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G155">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G156">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,7 +29933,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,22 +30096,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G183">
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G184">
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-09-12 12:15:00</t>
+          <t>2026-09-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G185">
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-09-12 12:15:00</t>
+          <t>2026-09-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30580,27 +30580,27 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G186">
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-09-12 12:30:00</t>
+          <t>2026-09-12 12:00:00</t>
         </is>
       </c>
     </row>
@@ -30743,27 +30743,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G187">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-09-12 12:30:00</t>
+          <t>2026-09-12 12:15:00</t>
         </is>
       </c>
     </row>
@@ -30906,12 +30906,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G188">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>2026-09-12 12:30:00</t>
+          <t>2026-09-12 12:15:00</t>
         </is>
       </c>
     </row>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,22 +31237,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G191">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G193">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G195">
@@ -32215,7 +32215,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G196">
@@ -32373,12 +32373,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G197">
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-09-12 12:45:00</t>
+          <t>2026-09-12 12:30:00</t>
         </is>
       </c>
     </row>
@@ -32536,12 +32536,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G198">
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-09-12 12:50:00</t>
+          <t>2026-09-12 12:30:00</t>
         </is>
       </c>
     </row>
@@ -32699,12 +32699,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G199">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>2026-09-12 13:00:00</t>
+          <t>2026-09-12 12:30:00</t>
         </is>
       </c>
     </row>
@@ -32862,12 +32862,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G200">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>2026-09-12 13:00:00</t>
+          <t>2026-09-12 12:45:00</t>
         </is>
       </c>
     </row>
@@ -33025,12 +33025,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G201">
@@ -33176,7 +33176,7 @@
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>2026-09-12 13:00:00</t>
+          <t>2026-09-12 12:50:00</t>
         </is>
       </c>
     </row>
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,7 +33519,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,22 +34171,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G209">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G213">
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G214">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G215">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O216">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P216">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35556,10 +35556,10 @@
         <v>0</v>
       </c>
       <c r="AA216">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB216">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC216">
         <v>0</v>
@@ -35633,12 +35633,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G217">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>2026-09-12 13:15:00</t>
+          <t>2026-09-12 13:00:00</t>
         </is>
       </c>
     </row>
@@ -35796,12 +35796,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G218">
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-09-12 13:15:00</t>
+          <t>2026-09-12 13:00:00</t>
         </is>
       </c>
     </row>
@@ -35959,12 +35959,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36045,10 +36045,10 @@
         <v>0</v>
       </c>
       <c r="AA219">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB219">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC219">
         <v>0</v>
@@ -36110,7 +36110,7 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:00</t>
+          <t>2026-09-12 13:00:00</t>
         </is>
       </c>
     </row>
@@ -36122,12 +36122,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G220">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:00</t>
+          <t>2026-09-12 13:15:00</t>
         </is>
       </c>
     </row>
@@ -36285,12 +36285,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G221">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:00</t>
+          <t>2026-09-12 13:15:00</t>
         </is>
       </c>
     </row>
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O223">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="P223">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36697,10 +36697,10 @@
         <v>0</v>
       </c>
       <c r="AA223">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB223">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC223">
         <v>0</v>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G225">
@@ -37100,12 +37100,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37186,10 +37186,10 @@
         <v>0</v>
       </c>
       <c r="AA226">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB226">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC226">
         <v>0</v>
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-09-12 13:45:00</t>
+          <t>2026-09-12 13:30:00</t>
         </is>
       </c>
     </row>
@@ -37263,12 +37263,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G227">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-09-12 13:45:00</t>
+          <t>2026-09-12 13:30:00</t>
         </is>
       </c>
     </row>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-09-12 13:45:00</t>
+          <t>2026-09-12 13:30:00</t>
         </is>
       </c>
     </row>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G229">
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-09-12 14:00:00</t>
+          <t>2026-09-12 13:45:00</t>
         </is>
       </c>
     </row>
@@ -37752,12 +37752,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-09-12 14:00:00</t>
+          <t>2026-09-12 13:45:00</t>
         </is>
       </c>
     </row>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G231">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-09-12 14:00:00</t>
+          <t>2026-09-12 13:45:00</t>
         </is>
       </c>
     </row>
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G235">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="G236">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G238">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G240">
@@ -39545,12 +39545,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G241">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-09-12 14:30:00</t>
+          <t>2026-09-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -39708,12 +39708,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G242">
@@ -39859,7 +39859,7 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>2026-09-12 14:30:00</t>
+          <t>2026-09-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -39871,12 +39871,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-09-12 14:30:00</t>
+          <t>2026-09-12 14:00:00</t>
         </is>
       </c>
     </row>
@@ -40034,12 +40034,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G244">
@@ -40185,7 +40185,7 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>2026-09-12 14:45:00</t>
+          <t>2026-09-12 14:30:00</t>
         </is>
       </c>
     </row>
@@ -40197,12 +40197,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G245">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>2026-09-12 15:00:00</t>
+          <t>2026-09-12 14:30:00</t>
         </is>
       </c>
     </row>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G246">
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>2026-09-12 15:00:00</t>
+          <t>2026-09-12 14:30:00</t>
         </is>
       </c>
     </row>
@@ -40523,27 +40523,27 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G247">
@@ -40674,7 +40674,7 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>2026-09-12 15:00:00</t>
+          <t>2026-09-12 14:45:00</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,22 +40854,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,22 +41343,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G252">
@@ -41506,22 +41506,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G253">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,22 +41995,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G256">
@@ -42153,12 +42153,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G257">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-09-12 15:15:00</t>
+          <t>2026-09-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -42316,12 +42316,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G258">
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-09-12 15:15:00</t>
+          <t>2026-09-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -42479,27 +42479,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G259">
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-09-12 15:15:00</t>
+          <t>2026-09-12 15:00:00</t>
         </is>
       </c>
     </row>
@@ -42642,12 +42642,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G260">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:00</t>
+          <t>2026-09-12 15:15:00</t>
         </is>
       </c>
     </row>
@@ -42805,27 +42805,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:00</t>
+          <t>2026-09-12 15:15:00</t>
         </is>
       </c>
     </row>
@@ -42968,27 +42968,27 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G262">
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-09-12 15:30:00</t>
+          <t>2026-09-12 15:15:00</t>
         </is>
       </c>
     </row>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,22 +43299,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G265">
@@ -43620,12 +43620,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -43946,27 +43946,27 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G268">
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-09-12 15:45:00</t>
+          <t>2026-09-12 15:30:00</t>
         </is>
       </c>
     </row>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G269">
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G272">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G273">
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -44924,12 +44924,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G274">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -45087,12 +45087,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G275">
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-09-12 16:00:00</t>
+          <t>2026-09-12 15:45:00</t>
         </is>
       </c>
     </row>
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,22 +45418,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O277">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P277">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45499,10 +45499,10 @@
         <v>0</v>
       </c>
       <c r="AA277">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB277">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC277">
         <v>0</v>
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O278">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P278">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45662,10 +45662,10 @@
         <v>0</v>
       </c>
       <c r="AA278">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB278">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC278">
         <v>0</v>
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -45988,10 +45988,10 @@
         <v>0</v>
       </c>
       <c r="AA280">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB280">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC280">
         <v>0</v>
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46151,10 +46151,10 @@
         <v>0</v>
       </c>
       <c r="AA281">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB281">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC281">
         <v>0</v>
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G282">
@@ -46396,22 +46396,22 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O283">
-        <v>7.93</v>
+        <v>0</v>
       </c>
       <c r="P283">
-        <v>13.61</v>
+        <v>0</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46477,10 +46477,10 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB283">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC283">
         <v>0</v>
@@ -46559,22 +46559,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>7.93</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>13.61</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -46966,10 +46966,10 @@
         <v>0</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC286">
         <v>0</v>
@@ -47043,12 +47043,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-09-12 16:30:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -47206,27 +47206,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O288">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P288">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB288">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-09-12 17:00:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -47369,27 +47369,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-09-12 17:00:00</t>
+          <t>2026-09-12 16:00:00</t>
         </is>
       </c>
     </row>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-09-12 17:00:00</t>
+          <t>2026-09-12 16:30:00</t>
         </is>
       </c>
     </row>
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47781,10 +47781,10 @@
         <v>0</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC291">
         <v>0</v>
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="G292">
@@ -48021,27 +48021,27 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G293">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>2026-09-12 18:15:00</t>
+          <t>2026-09-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -48184,12 +48184,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O294">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P294">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -48270,10 +48270,10 @@
         <v>0</v>
       </c>
       <c r="AA294">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB294">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC294">
         <v>0</v>
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-09-12 18:30:00</t>
+          <t>2026-09-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -48347,12 +48347,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G295">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30:00</t>
+          <t>2026-09-12 17:00:00</t>
         </is>
       </c>
     </row>
@@ -48510,12 +48510,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G296">
@@ -48661,7 +48661,7 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>2026-09-12 19:30:00</t>
+          <t>2026-09-12 18:15:00</t>
         </is>
       </c>
     </row>
@@ -48673,12 +48673,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O297">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P297">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48759,10 +48759,10 @@
         <v>0</v>
       </c>
       <c r="AA297">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB297">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC297">
         <v>0</v>
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 18:30:00</t>
         </is>
       </c>
     </row>
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 19:30:00</t>
         </is>
       </c>
     </row>
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-09-12 20:00:00</t>
+          <t>2026-09-12 19:30:00</t>
         </is>
       </c>
     </row>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G300">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G302">
@@ -49656,7 +49656,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G304">
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G305">
@@ -50063,10 +50063,10 @@
         <v>0</v>
       </c>
       <c r="AA305">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB305">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC305">
         <v>0</v>
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G306">
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -50303,12 +50303,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G307">
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-09-12 20:30:00</t>
+          <t>2026-09-12 20:00:00</t>
         </is>
       </c>
     </row>
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G308">
@@ -50552,10 +50552,10 @@
         <v>0</v>
       </c>
       <c r="AA308">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB308">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC308">
         <v>0</v>
@@ -50634,7 +50634,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G309">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G310">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G311">
@@ -51118,27 +51118,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G312">
@@ -51269,7 +51269,7 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -51281,12 +51281,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O313">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P313">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51367,10 +51367,10 @@
         <v>0</v>
       </c>
       <c r="AA313">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB313">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC313">
         <v>0</v>
@@ -51432,7 +51432,7 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -51444,27 +51444,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G314">
@@ -51595,7 +51595,7 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>2026-09-12 21:00:00</t>
+          <t>2026-09-12 20:30:00</t>
         </is>
       </c>
     </row>
@@ -51612,7 +51612,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G315">
@@ -51775,7 +51775,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G316">
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O316">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P316">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q316">
         <v>0</v>
@@ -51856,10 +51856,10 @@
         <v>0</v>
       </c>
       <c r="AA316">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB316">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC316">
         <v>0</v>
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G319">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G320">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G321">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G323">
@@ -53079,7 +53079,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G324">
@@ -53237,12 +53237,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G325">
@@ -53388,7 +53388,7 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>2026-09-12 21:30:00</t>
+          <t>2026-09-12 21:00:00</t>
         </is>
       </c>
     </row>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G326">
@@ -53726,12 +53726,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G328">
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>2026-09-12 21:45:00</t>
+          <t>2026-09-12 21:30:00</t>
         </is>
       </c>
     </row>
@@ -53889,12 +53889,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G329">
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>2026-09-12 22:30:00</t>
+          <t>2026-09-12 21:45:00</t>
         </is>
       </c>
     </row>
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G330">
@@ -54215,12 +54215,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G331">
@@ -54366,7 +54366,7 @@
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>2026-09-12 23:00:00</t>
+          <t>2026-09-12 22:30:00</t>
         </is>
       </c>
     </row>
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G332">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G333">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G334">
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G335">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-09-12 23:30:00</t>
+          <t>2026-09-12 23:00:00</t>
         </is>
       </c>
     </row>
@@ -55045,141 +55045,304 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="G336">
+        <v>0</v>
+      </c>
+      <c r="H336">
+        <v>0</v>
+      </c>
+      <c r="I336">
+        <v>0</v>
+      </c>
+      <c r="J336">
+        <v>0</v>
+      </c>
+      <c r="K336">
+        <v>0</v>
+      </c>
+      <c r="L336">
+        <v>0</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N336">
+        <v>0</v>
+      </c>
+      <c r="O336">
+        <v>0</v>
+      </c>
+      <c r="P336">
+        <v>0</v>
+      </c>
+      <c r="Q336">
+        <v>0</v>
+      </c>
+      <c r="R336">
+        <v>0</v>
+      </c>
+      <c r="S336">
+        <v>0</v>
+      </c>
+      <c r="T336">
+        <v>0</v>
+      </c>
+      <c r="U336">
+        <v>0</v>
+      </c>
+      <c r="V336">
+        <v>0</v>
+      </c>
+      <c r="W336">
+        <v>0</v>
+      </c>
+      <c r="X336">
+        <v>0</v>
+      </c>
+      <c r="Y336">
+        <v>0</v>
+      </c>
+      <c r="Z336">
+        <v>0</v>
+      </c>
+      <c r="AA336">
+        <v>0</v>
+      </c>
+      <c r="AB336">
+        <v>0</v>
+      </c>
+      <c r="AC336">
+        <v>0</v>
+      </c>
+      <c r="AD336">
+        <v>0</v>
+      </c>
+      <c r="AE336">
+        <v>0</v>
+      </c>
+      <c r="AF336">
+        <v>0</v>
+      </c>
+      <c r="AG336">
+        <v>0</v>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ336">
+        <v>0</v>
+      </c>
+      <c r="AK336">
+        <v>0</v>
+      </c>
+      <c r="AL336">
+        <v>0</v>
+      </c>
+      <c r="AM336">
+        <v>-1</v>
+      </c>
+      <c r="AN336">
+        <v>-1</v>
+      </c>
+      <c r="AO336">
+        <v>-1</v>
+      </c>
+      <c r="AP336">
+        <v>-1</v>
+      </c>
+      <c r="AQ336">
+        <v>0</v>
+      </c>
+      <c r="AR336">
+        <v>0</v>
+      </c>
+      <c r="AS336">
+        <v>0</v>
+      </c>
+      <c r="AT336">
+        <v>0</v>
+      </c>
+      <c r="AU336" t="inlineStr">
+        <is>
+          <t>2026-09-12 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
           <t>SJ Earthquakes</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
+      <c r="F337" t="inlineStr">
         <is>
           <t>Houston Dynamo</t>
         </is>
       </c>
-      <c r="G336">
-        <v>0</v>
-      </c>
-      <c r="H336">
-        <v>0</v>
-      </c>
-      <c r="I336">
-        <v>0</v>
-      </c>
-      <c r="J336">
-        <v>0</v>
-      </c>
-      <c r="K336">
-        <v>0</v>
-      </c>
-      <c r="L336">
-        <v>0</v>
-      </c>
-      <c r="M336" t="inlineStr">
+      <c r="G337">
+        <v>0</v>
+      </c>
+      <c r="H337">
+        <v>0</v>
+      </c>
+      <c r="I337">
+        <v>0</v>
+      </c>
+      <c r="J337">
+        <v>0</v>
+      </c>
+      <c r="K337">
+        <v>0</v>
+      </c>
+      <c r="L337">
+        <v>0</v>
+      </c>
+      <c r="M337" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N336">
-        <v>0</v>
-      </c>
-      <c r="O336">
-        <v>0</v>
-      </c>
-      <c r="P336">
-        <v>0</v>
-      </c>
-      <c r="Q336">
-        <v>0</v>
-      </c>
-      <c r="R336">
-        <v>0</v>
-      </c>
-      <c r="S336">
-        <v>0</v>
-      </c>
-      <c r="T336">
-        <v>0</v>
-      </c>
-      <c r="U336">
-        <v>0</v>
-      </c>
-      <c r="V336">
-        <v>0</v>
-      </c>
-      <c r="W336">
-        <v>0</v>
-      </c>
-      <c r="X336">
-        <v>0</v>
-      </c>
-      <c r="Y336">
-        <v>0</v>
-      </c>
-      <c r="Z336">
-        <v>0</v>
-      </c>
-      <c r="AA336">
-        <v>0</v>
-      </c>
-      <c r="AB336">
-        <v>0</v>
-      </c>
-      <c r="AC336">
-        <v>0</v>
-      </c>
-      <c r="AD336">
-        <v>0</v>
-      </c>
-      <c r="AE336">
-        <v>0</v>
-      </c>
-      <c r="AF336">
-        <v>0</v>
-      </c>
-      <c r="AG336">
-        <v>0</v>
-      </c>
-      <c r="AH336" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI336" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ336">
-        <v>0</v>
-      </c>
-      <c r="AK336">
-        <v>0</v>
-      </c>
-      <c r="AL336">
-        <v>0</v>
-      </c>
-      <c r="AM336">
-        <v>-1</v>
-      </c>
-      <c r="AN336">
-        <v>-1</v>
-      </c>
-      <c r="AO336">
-        <v>-1</v>
-      </c>
-      <c r="AP336">
-        <v>-1</v>
-      </c>
-      <c r="AQ336">
-        <v>0</v>
-      </c>
-      <c r="AR336">
-        <v>0</v>
-      </c>
-      <c r="AS336">
-        <v>0</v>
-      </c>
-      <c r="AT336">
-        <v>0</v>
-      </c>
-      <c r="AU336" t="inlineStr">
+      <c r="N337">
+        <v>0</v>
+      </c>
+      <c r="O337">
+        <v>0</v>
+      </c>
+      <c r="P337">
+        <v>0</v>
+      </c>
+      <c r="Q337">
+        <v>0</v>
+      </c>
+      <c r="R337">
+        <v>0</v>
+      </c>
+      <c r="S337">
+        <v>0</v>
+      </c>
+      <c r="T337">
+        <v>0</v>
+      </c>
+      <c r="U337">
+        <v>0</v>
+      </c>
+      <c r="V337">
+        <v>0</v>
+      </c>
+      <c r="W337">
+        <v>0</v>
+      </c>
+      <c r="X337">
+        <v>0</v>
+      </c>
+      <c r="Y337">
+        <v>0</v>
+      </c>
+      <c r="Z337">
+        <v>0</v>
+      </c>
+      <c r="AA337">
+        <v>0</v>
+      </c>
+      <c r="AB337">
+        <v>0</v>
+      </c>
+      <c r="AC337">
+        <v>0</v>
+      </c>
+      <c r="AD337">
+        <v>0</v>
+      </c>
+      <c r="AE337">
+        <v>0</v>
+      </c>
+      <c r="AF337">
+        <v>0</v>
+      </c>
+      <c r="AG337">
+        <v>0</v>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ337">
+        <v>0</v>
+      </c>
+      <c r="AK337">
+        <v>0</v>
+      </c>
+      <c r="AL337">
+        <v>0</v>
+      </c>
+      <c r="AM337">
+        <v>-1</v>
+      </c>
+      <c r="AN337">
+        <v>-1</v>
+      </c>
+      <c r="AO337">
+        <v>-1</v>
+      </c>
+      <c r="AP337">
+        <v>-1</v>
+      </c>
+      <c r="AQ337">
+        <v>0</v>
+      </c>
+      <c r="AR337">
+        <v>0</v>
+      </c>
+      <c r="AS337">
+        <v>0</v>
+      </c>
+      <c r="AT337">
+        <v>0</v>
+      </c>
+      <c r="AU337" t="inlineStr">
         <is>
           <t>2026-09-12 23:30:00</t>
         </is>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -9935,10 +9935,10 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S59">
         <v>0</v>
@@ -9947,10 +9947,10 @@
         <v>0</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W59">
         <v>0</v>
@@ -9959,31 +9959,31 @@
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>0</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10913,34 +10913,34 @@
         <v>2.84</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA65">
         <v>1.9</v>
@@ -10949,19 +10949,19 @@
         <v>1.9</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>0</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -16618,55 +16618,55 @@
         <v>0</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G105">
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G118">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q141">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R141">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S141">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T141">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U141">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V141">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W141">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X141">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y141">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z141">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA141">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB141">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC141">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD141">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE141">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF141">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK141">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T145">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U145">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V145">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X145">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y145">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z145">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC145">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD145">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF145">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK145">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S146">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T146">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U146">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V146">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W146">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X146">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z146">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE146">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF146">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG146">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK146">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V147">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X147">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S157">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T157">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U157">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V157">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W157">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y157">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z157">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE157">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF157">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG157">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK157">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26724,55 +26724,55 @@
         <v>4.05</v>
       </c>
       <c r="Q162">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R162">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S162">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T162">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U162">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V162">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W162">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X162">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z162">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD162">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE162">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF162">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG162">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK162">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,64 +26878,64 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,64 +27041,64 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q164">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R164">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S164">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T164">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U164">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V164">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W164">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X164">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y164">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z164">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA164">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB164">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC164">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD164">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE164">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF164">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG164">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK164">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27539,34 +27539,34 @@
         <v>4.43</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U167">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="V167">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W167">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z167">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA167">
         <v>2.1</v>
@@ -27575,19 +27575,19 @@
         <v>1.72</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE167">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK167">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X169">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q171">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R171">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S171">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T171">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U171">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V171">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W171">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X171">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y171">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z171">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA171">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC171">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD171">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE171">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF171">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG171">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK171">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G179">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X198">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S210">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T210">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U210">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V210">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W210">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X210">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z210">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA210">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD210">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE210">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG210">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK210">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T215">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W215">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X215">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S216">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T216">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U216">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V216">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W216">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X216">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y216">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z216">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC216">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD216">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG216">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK216">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35689,55 +35689,55 @@
         <v>0</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S217">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T217">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U217">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V217">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W217">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X217">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y217">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z217">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC217">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD217">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG217">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK217">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35852,55 +35852,55 @@
         <v>0</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U218">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V218">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W218">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y218">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z218">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36015,34 +36015,34 @@
         <v>2.06</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U219">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V219">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W219">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y219">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z219">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AA219">
         <v>2.2</v>
@@ -36051,19 +36051,19 @@
         <v>1.66</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG219">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK219">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36821,64 +36821,64 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X225">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA225">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37156,34 +37156,34 @@
         <v>5.84</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S226">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T226">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U226">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V226">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X226">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y226">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z226">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA226">
         <v>1.8</v>
@@ -37192,19 +37192,19 @@
         <v>2</v>
       </c>
       <c r="AC226">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD226">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG226">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK226">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T240">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V240">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X240">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y240">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z240">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE240">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF240">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG240">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AK240">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T246">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U246">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V246">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W246">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X246">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y246">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z246">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE246">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG246">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -42363,64 +42363,64 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S258">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T258">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V258">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W258">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X258">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y258">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z258">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC258">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD258">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE258">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF258">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG258">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK258">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -43015,64 +43015,64 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL262">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="O5">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>4.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>3.41</v>
       </c>
       <c r="R5">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S5">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="U5">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="AA5">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC5">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE5">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG5">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>2.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="O6">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="P6">
-        <v>2.4</v>
+        <v>4.35</v>
       </c>
       <c r="Q6">
-        <v>3.41</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="T6">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="AA6">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC6">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AD6">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK6">
-        <v>1.36</v>
+        <v>2.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q90">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="R90">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="S90">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T90">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="U90">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V90">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W90">
         <v>1.06</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z90">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="AA90">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB90">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AC90">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AD90">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE90">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG90">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK90">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="O91">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P91">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="Q91">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="R91">
+        <v>2.47</v>
+      </c>
+      <c r="S91">
+        <v>1.3</v>
+      </c>
+      <c r="T91">
+        <v>3.28</v>
+      </c>
+      <c r="U91">
+        <v>2.34</v>
+      </c>
+      <c r="V91">
+        <v>1.51</v>
+      </c>
+      <c r="W91">
+        <v>1.12</v>
+      </c>
+      <c r="X91">
+        <v>1.01</v>
+      </c>
+      <c r="Y91">
+        <v>1.2</v>
+      </c>
+      <c r="Z91">
+        <v>4.2</v>
+      </c>
+      <c r="AA91">
+        <v>1.62</v>
+      </c>
+      <c r="AB91">
         <v>2.2</v>
       </c>
-      <c r="S91">
-        <v>1.38</v>
-      </c>
-      <c r="T91">
-        <v>2.74</v>
-      </c>
-      <c r="U91">
-        <v>2.75</v>
-      </c>
-      <c r="V91">
-        <v>1.43</v>
-      </c>
-      <c r="W91">
-        <v>1.06</v>
-      </c>
-      <c r="X91">
-        <v>1.02</v>
-      </c>
-      <c r="Y91">
-        <v>1.25</v>
-      </c>
-      <c r="Z91">
-        <v>3.6</v>
-      </c>
-      <c r="AA91">
-        <v>1.79</v>
-      </c>
-      <c r="AB91">
-        <v>1.93</v>
-      </c>
       <c r="AC91">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD91">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AE91">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF91">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG91">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK91">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q92">
         <v>2</v>
       </c>
       <c r="R92">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="S92">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T92">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U92">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V92">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z92">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="AA92">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AB92">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AC92">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD92">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE92">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG92">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK92">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,19 +18076,19 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.8</v>
+        <v>2.17</v>
       </c>
       <c r="O109">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P109">
-        <v>1.63</v>
+        <v>2.62</v>
       </c>
       <c r="Q109">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="R109">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S109">
         <v>1.22</v>
@@ -18097,43 +18097,43 @@
         <v>4.05</v>
       </c>
       <c r="U109">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V109">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W109">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X109">
         <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z109">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="AA109">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB109">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AC109">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD109">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AE109">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF109">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AG109">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="AK109">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="O110">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P110">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q110">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="R110">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="S110">
+        <v>1.28</v>
+      </c>
+      <c r="T110">
+        <v>3.5</v>
+      </c>
+      <c r="U110">
+        <v>2.21</v>
+      </c>
+      <c r="V110">
+        <v>1.63</v>
+      </c>
+      <c r="W110">
+        <v>1.15</v>
+      </c>
+      <c r="X110">
+        <v>1.03</v>
+      </c>
+      <c r="Y110">
+        <v>1.18</v>
+      </c>
+      <c r="Z110">
+        <v>4.75</v>
+      </c>
+      <c r="AA110">
+        <v>1.57</v>
+      </c>
+      <c r="AB110">
+        <v>2.38</v>
+      </c>
+      <c r="AC110">
+        <v>2.4</v>
+      </c>
+      <c r="AD110">
+        <v>1.55</v>
+      </c>
+      <c r="AE110">
         <v>1.22</v>
       </c>
-      <c r="T110">
-        <v>4.05</v>
-      </c>
-      <c r="U110">
-        <v>2.05</v>
-      </c>
-      <c r="V110">
-        <v>1.8</v>
-      </c>
-      <c r="W110">
-        <v>1.21</v>
-      </c>
-      <c r="X110">
-        <v>1.02</v>
-      </c>
-      <c r="Y110">
-        <v>1.12</v>
-      </c>
-      <c r="Z110">
-        <v>5.95</v>
-      </c>
-      <c r="AA110">
-        <v>1.4</v>
-      </c>
-      <c r="AB110">
-        <v>2.84</v>
-      </c>
-      <c r="AC110">
-        <v>2.02</v>
-      </c>
-      <c r="AD110">
-        <v>1.84</v>
-      </c>
-      <c r="AE110">
-        <v>1.31</v>
-      </c>
       <c r="AF110">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AG110">
-        <v>3.04</v>
+        <v>2.3</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK110">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
+        <v>2.02</v>
+      </c>
+      <c r="O111">
+        <v>3.9</v>
+      </c>
+      <c r="P111">
+        <v>3.4</v>
+      </c>
+      <c r="Q111">
+        <v>2.5</v>
+      </c>
+      <c r="R111">
+        <v>2.41</v>
+      </c>
+      <c r="S111">
+        <v>1.25</v>
+      </c>
+      <c r="T111">
+        <v>4</v>
+      </c>
+      <c r="U111">
+        <v>2.19</v>
+      </c>
+      <c r="V111">
         <v>1.7</v>
       </c>
-      <c r="O111">
-        <v>4</v>
-      </c>
-      <c r="P111">
-        <v>4.4</v>
-      </c>
-      <c r="Q111">
-        <v>2.24</v>
-      </c>
-      <c r="R111">
-        <v>2.42</v>
-      </c>
-      <c r="S111">
-        <v>1.28</v>
-      </c>
-      <c r="T111">
-        <v>3.5</v>
-      </c>
-      <c r="U111">
+      <c r="W111">
+        <v>1.17</v>
+      </c>
+      <c r="X111">
+        <v>1.02</v>
+      </c>
+      <c r="Y111">
+        <v>1.11</v>
+      </c>
+      <c r="Z111">
+        <v>4.95</v>
+      </c>
+      <c r="AA111">
+        <v>1.5</v>
+      </c>
+      <c r="AB111">
+        <v>2.66</v>
+      </c>
+      <c r="AC111">
         <v>2.21</v>
       </c>
-      <c r="V111">
-        <v>1.63</v>
-      </c>
-      <c r="W111">
-        <v>1.15</v>
-      </c>
-      <c r="X111">
-        <v>1.03</v>
-      </c>
-      <c r="Y111">
-        <v>1.18</v>
-      </c>
-      <c r="Z111">
-        <v>4.75</v>
-      </c>
-      <c r="AA111">
-        <v>1.57</v>
-      </c>
-      <c r="AB111">
-        <v>2.38</v>
-      </c>
-      <c r="AC111">
-        <v>2.4</v>
-      </c>
       <c r="AD111">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AE111">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF111">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG111">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK111">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.02</v>
+        <v>3.8</v>
       </c>
       <c r="O112">
+        <v>4.1</v>
+      </c>
+      <c r="P112">
+        <v>1.63</v>
+      </c>
+      <c r="Q112">
         <v>3.9</v>
       </c>
-      <c r="P112">
-        <v>3.4</v>
-      </c>
-      <c r="Q112">
+      <c r="R112">
         <v>2.5</v>
       </c>
-      <c r="R112">
-        <v>2.41</v>
-      </c>
       <c r="S112">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U112">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="V112">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W112">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X112">
         <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z112">
-        <v>4.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA112">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB112">
         <v>2.66</v>
       </c>
       <c r="AC112">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AD112">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AE112">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF112">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG112">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AK112">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O117">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P117">
-        <v>2.47</v>
+        <v>3.28</v>
       </c>
       <c r="Q117">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R117">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S117">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T117">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="U117">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="V117">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W117">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z117">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA117">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AB117">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="AC117">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="AD117">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AE117">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF117">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AG117">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
+        <v>2.27</v>
+      </c>
+      <c r="O118">
+        <v>3.58</v>
+      </c>
+      <c r="P118">
+        <v>2.47</v>
+      </c>
+      <c r="Q118">
+        <v>3</v>
+      </c>
+      <c r="R118">
         <v>2.2</v>
       </c>
-      <c r="O118">
+      <c r="S118">
+        <v>1.28</v>
+      </c>
+      <c r="T118">
         <v>3.35</v>
       </c>
-      <c r="P118">
-        <v>3.28</v>
-      </c>
-      <c r="Q118">
-        <v>2.5</v>
-      </c>
-      <c r="R118">
-        <v>2.11</v>
-      </c>
-      <c r="S118">
-        <v>1.41</v>
-      </c>
-      <c r="T118">
-        <v>2.9</v>
-      </c>
       <c r="U118">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="V118">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W118">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y118">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z118">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA118">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB118">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AC118">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD118">
+        <v>1.52</v>
+      </c>
+      <c r="AE118">
+        <v>1.18</v>
+      </c>
+      <c r="AF118">
+        <v>1.51</v>
+      </c>
+      <c r="AG118">
+        <v>2.42</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
         <v>1.33</v>
       </c>
-      <c r="AE118">
-        <v>1.05</v>
-      </c>
-      <c r="AF118">
-        <v>1.73</v>
-      </c>
-      <c r="AG118">
-        <v>2</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.3</v>
-      </c>
       <c r="AK118">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="O119">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="P119">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q119">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="R119">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S119">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T119">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="U119">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="V119">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W119">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X119">
         <v>1</v>
       </c>
       <c r="Y119">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z119">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AA119">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB119">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC119">
         <v>3.25</v>
       </c>
       <c r="AD119">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE119">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG119">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK119">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="O120">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="P120">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q120">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="R120">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S120">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T120">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="U120">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="V120">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W120">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X120">
         <v>1</v>
       </c>
       <c r="Y120">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z120">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="AA120">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB120">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC120">
         <v>3.25</v>
       </c>
       <c r="AD120">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE120">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF120">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG120">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK120">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O122">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P122">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>2.59</v>
+        <v>10.1</v>
       </c>
       <c r="R122">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S122">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T122">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="U122">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="V122">
         <v>1.46</v>
       </c>
       <c r="W122">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y122">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z122">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA122">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AB122">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC122">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AD122">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE122">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF122">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AG122">
-        <v>2.18</v>
+        <v>1.62</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK122">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q123">
-        <v>10.1</v>
+        <v>2.67</v>
       </c>
       <c r="R123">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="S123">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="U123">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V123">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W123">
         <v>1.1</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y123">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z123">
         <v>4.1</v>
       </c>
       <c r="AA123">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AB123">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AC123">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="AD123">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE123">
         <v>1.13</v>
       </c>
       <c r="AF123">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="AG123">
-        <v>1.62</v>
+        <v>2.31</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK123">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="O124">
         <v>3.4</v>
       </c>
       <c r="P124">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q124">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="R124">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="S124">
         <v>1.29</v>
       </c>
       <c r="T124">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U124">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="V124">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W124">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X124">
         <v>1.03</v>
       </c>
       <c r="Y124">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z124">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA124">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AB124">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="AC124">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="AD124">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AE124">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF124">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG124">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK124">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="O126">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P126">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q126">
-        <v>3.64</v>
+        <v>1.98</v>
       </c>
       <c r="R126">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="S126">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T126">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U126">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W126">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z126">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA126">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB126">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AC126">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="AD126">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE126">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF126">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AG126">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK126">
-        <v>1.36</v>
+        <v>2.47</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.43</v>
+        <v>2.7</v>
       </c>
       <c r="O127">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P127">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q127">
-        <v>1.98</v>
+        <v>3.64</v>
       </c>
       <c r="R127">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="S127">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T127">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U127">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="V127">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z127">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA127">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB127">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="AC127">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="AD127">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE127">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF127">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AG127">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK127">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="O130">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P130">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="Q130">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R130">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="S130">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T130">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U130">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="V130">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="W130">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y130">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Z130">
-        <v>3.34</v>
+        <v>3.03</v>
       </c>
       <c r="AA130">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AB130">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AC130">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AD130">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AE130">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF130">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AG130">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK130">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
+        <v>3</v>
+      </c>
+      <c r="O131">
+        <v>3.6</v>
+      </c>
+      <c r="P131">
+        <v>2.15</v>
+      </c>
+      <c r="Q131">
+        <v>3.5</v>
+      </c>
+      <c r="R131">
+        <v>2.25</v>
+      </c>
+      <c r="S131">
+        <v>1.32</v>
+      </c>
+      <c r="T131">
+        <v>3.1</v>
+      </c>
+      <c r="U131">
         <v>2.44</v>
       </c>
-      <c r="O131">
-        <v>3.15</v>
-      </c>
-      <c r="P131">
-        <v>2.54</v>
-      </c>
-      <c r="Q131">
-        <v>3.3</v>
-      </c>
-      <c r="R131">
-        <v>2.11</v>
-      </c>
-      <c r="S131">
-        <v>1.4</v>
-      </c>
-      <c r="T131">
-        <v>2.62</v>
-      </c>
-      <c r="U131">
-        <v>3.2</v>
-      </c>
       <c r="V131">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="W131">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X131">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z131">
-        <v>3.03</v>
+        <v>3.72</v>
       </c>
       <c r="AA131">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AB131">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AC131">
-        <v>4.2</v>
+        <v>2.78</v>
       </c>
       <c r="AD131">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AE131">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF131">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AG131">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK131">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,43 +21825,43 @@
         </is>
       </c>
       <c r="N132">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O132">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P132">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q132">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R132">
         <v>2.25</v>
       </c>
       <c r="S132">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T132">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="U132">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V132">
         <v>1.47</v>
       </c>
       <c r="W132">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z132">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="AA132">
         <v>1.73</v>
@@ -21870,19 +21870,19 @@
         <v>2</v>
       </c>
       <c r="AC132">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD132">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE132">
         <v>1.14</v>
       </c>
       <c r="AF132">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG132">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="O133">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="P133">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="Q133">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R133">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S133">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T133">
-        <v>3.27</v>
+        <v>3.44</v>
       </c>
       <c r="U133">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="V133">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W133">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z133">
-        <v>4.1</v>
+        <v>4.42</v>
       </c>
       <c r="AA133">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB133">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC133">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AD133">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE133">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF133">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AG133">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>1.73</v>
+        <v>2.31</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,58 +22151,58 @@
         </is>
       </c>
       <c r="N134">
-        <v>3.25</v>
+        <v>2.23</v>
       </c>
       <c r="O134">
         <v>3.5</v>
       </c>
       <c r="P134">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q134">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="R134">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S134">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T134">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U134">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="V134">
         <v>1.41</v>
       </c>
       <c r="W134">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X134">
         <v>1</v>
       </c>
       <c r="Y134">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z134">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="AA134">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB134">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC134">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD134">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE134">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF134">
         <v>1.67</v>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AK134">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="O135">
         <v>3.5</v>
       </c>
       <c r="P135">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q135">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="R135">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T135">
         <v>3</v>
       </c>
       <c r="U135">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="V135">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W135">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
         <v>1</v>
       </c>
       <c r="Y135">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z135">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AA135">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB135">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC135">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AD135">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE135">
         <v>1.07</v>
       </c>
       <c r="AF135">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG135">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AK135">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O136">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="Q136">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="R136">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="T136">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="U136">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="V136">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W136">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z136">
-        <v>4.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA136">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AB136">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC136">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="AD136">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE136">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG136">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>2.31</v>
+        <v>1.58</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="O143">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P143">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="Q143">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="R143">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="S143">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T143">
-        <v>3.5</v>
+        <v>2.47</v>
       </c>
       <c r="U143">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="V143">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="W143">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X143">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y143">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z143">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="AA143">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AB143">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AC143">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="AD143">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AE143">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF143">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AG143">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK143">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,65 +23781,65 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="O144">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P144">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q144">
+        <v>3.2</v>
+      </c>
+      <c r="R144">
+        <v>2.1</v>
+      </c>
+      <c r="S144">
+        <v>1.39</v>
+      </c>
+      <c r="T144">
+        <v>2.77</v>
+      </c>
+      <c r="U144">
+        <v>2.89</v>
+      </c>
+      <c r="V144">
+        <v>1.39</v>
+      </c>
+      <c r="W144">
+        <v>1.03</v>
+      </c>
+      <c r="X144">
+        <v>1.03</v>
+      </c>
+      <c r="Y144">
+        <v>1.33</v>
+      </c>
+      <c r="Z144">
+        <v>3.3</v>
+      </c>
+      <c r="AA144">
+        <v>1.92</v>
+      </c>
+      <c r="AB144">
+        <v>1.8</v>
+      </c>
+      <c r="AC144">
+        <v>3.4</v>
+      </c>
+      <c r="AD144">
+        <v>1.3</v>
+      </c>
+      <c r="AE144">
+        <v>1.1</v>
+      </c>
+      <c r="AF144">
+        <v>1.71</v>
+      </c>
+      <c r="AG144">
         <v>2</v>
       </c>
-      <c r="R144">
-        <v>2.36</v>
-      </c>
-      <c r="S144">
-        <v>1.25</v>
-      </c>
-      <c r="T144">
-        <v>3.45</v>
-      </c>
-      <c r="U144">
-        <v>2.2</v>
-      </c>
-      <c r="V144">
-        <v>1.52</v>
-      </c>
-      <c r="W144">
-        <v>1.11</v>
-      </c>
-      <c r="X144">
-        <v>1.01</v>
-      </c>
-      <c r="Y144">
-        <v>1.14</v>
-      </c>
-      <c r="Z144">
-        <v>4.45</v>
-      </c>
-      <c r="AA144">
-        <v>1.54</v>
-      </c>
-      <c r="AB144">
-        <v>2.37</v>
-      </c>
-      <c r="AC144">
-        <v>2.45</v>
-      </c>
-      <c r="AD144">
-        <v>1.57</v>
-      </c>
-      <c r="AE144">
-        <v>1.18</v>
-      </c>
-      <c r="AF144">
-        <v>1.6</v>
-      </c>
-      <c r="AG144">
-        <v>2.19</v>
-      </c>
       <c r="AH144" t="inlineStr">
         <is>
           <t>[]</t>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AK144">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="O145">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="P145">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q145">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="R145">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="S145">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T145">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="U145">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="V145">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="W145">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X145">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z145">
-        <v>2.95</v>
+        <v>4.45</v>
       </c>
       <c r="AA145">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="AB145">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AC145">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="AD145">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AE145">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF145">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="O146">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P146">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="Q146">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="R146">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S146">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T146">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="U146">
-        <v>2.89</v>
+        <v>2.38</v>
       </c>
       <c r="V146">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W146">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X146">
         <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z146">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA146">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AB146">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC146">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD146">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE146">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF146">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG146">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK146">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O153">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P153">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q153">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R153">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S153">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T153">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U153">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="V153">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W153">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X153">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y153">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z153">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AA153">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC153">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD153">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE153">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF153">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG153">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK153">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,80 +25574,80 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.93</v>
+        <v>2.98</v>
       </c>
       <c r="O155">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="P155">
-        <v>3.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q155">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="R155">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S155">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T155">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U155">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="V155">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W155">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z155">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA155">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB155">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AC155">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="AD155">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE155">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF155">
+        <v>1.57</v>
+      </c>
+      <c r="AG155">
+        <v>2.25</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
         <v>1.73</v>
       </c>
-      <c r="AG155">
-        <v>2</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>1.23</v>
-      </c>
       <c r="AK155">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.98</v>
+        <v>1.84</v>
       </c>
       <c r="O156">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="P156">
-        <v>1.97</v>
+        <v>4</v>
       </c>
       <c r="Q156">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="R156">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S156">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T156">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U156">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="V156">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W156">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z156">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="AA156">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB156">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AC156">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="AD156">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE156">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF156">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.73</v>
+        <v>1.21</v>
       </c>
       <c r="AK156">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G177">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G178">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,61 +45949,61 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="O280">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P280">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q280">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="R280">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S280">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T280">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U280">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="V280">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W280">
+        <v>1.05</v>
+      </c>
+      <c r="X280">
+        <v>1.05</v>
+      </c>
+      <c r="Y280">
+        <v>1.34</v>
+      </c>
+      <c r="Z280">
+        <v>2.8</v>
+      </c>
+      <c r="AA280">
+        <v>2.25</v>
+      </c>
+      <c r="AB280">
+        <v>1.61</v>
+      </c>
+      <c r="AC280">
+        <v>3.94</v>
+      </c>
+      <c r="AD280">
+        <v>1.2</v>
+      </c>
+      <c r="AE280">
         <v>1.07</v>
       </c>
-      <c r="X280">
-        <v>1.04</v>
-      </c>
-      <c r="Y280">
-        <v>1.38</v>
-      </c>
-      <c r="Z280">
-        <v>3</v>
-      </c>
-      <c r="AA280">
-        <v>2.1</v>
-      </c>
-      <c r="AB280">
-        <v>1.7</v>
-      </c>
-      <c r="AC280">
-        <v>3.54</v>
-      </c>
-      <c r="AD280">
-        <v>1.22</v>
-      </c>
-      <c r="AE280">
-        <v>1.05</v>
-      </c>
       <c r="AF280">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG280">
         <v>1.85</v>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK280">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,61 +46112,61 @@
         </is>
       </c>
       <c r="N281">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="O281">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P281">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q281">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="R281">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S281">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T281">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U281">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="V281">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W281">
+        <v>1.07</v>
+      </c>
+      <c r="X281">
+        <v>1.04</v>
+      </c>
+      <c r="Y281">
+        <v>1.38</v>
+      </c>
+      <c r="Z281">
+        <v>3</v>
+      </c>
+      <c r="AA281">
+        <v>2.1</v>
+      </c>
+      <c r="AB281">
+        <v>1.7</v>
+      </c>
+      <c r="AC281">
+        <v>3.54</v>
+      </c>
+      <c r="AD281">
+        <v>1.22</v>
+      </c>
+      <c r="AE281">
         <v>1.05</v>
       </c>
-      <c r="X281">
-        <v>1.05</v>
-      </c>
-      <c r="Y281">
-        <v>1.34</v>
-      </c>
-      <c r="Z281">
-        <v>2.8</v>
-      </c>
-      <c r="AA281">
-        <v>2.25</v>
-      </c>
-      <c r="AB281">
-        <v>1.61</v>
-      </c>
-      <c r="AC281">
-        <v>3.94</v>
-      </c>
-      <c r="AD281">
-        <v>1.2</v>
-      </c>
-      <c r="AE281">
-        <v>1.07</v>
-      </c>
       <c r="AF281">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG281">
         <v>1.85</v>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK281">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G305">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q13">
-        <v>2.67</v>
+        <v>3.85</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T13">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
+        <v>1.41</v>
+      </c>
+      <c r="Z13">
+        <v>2.79</v>
+      </c>
+      <c r="AA13">
+        <v>2.35</v>
+      </c>
+      <c r="AB13">
+        <v>1.57</v>
+      </c>
+      <c r="AC13">
+        <v>4.1</v>
+      </c>
+      <c r="AD13">
+        <v>1.2</v>
+      </c>
+      <c r="AE13">
+        <v>1.01</v>
+      </c>
+      <c r="AF13">
+        <v>1.91</v>
+      </c>
+      <c r="AG13">
+        <v>1.76</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.27</v>
+      </c>
+      <c r="AK13">
         <v>1.25</v>
-      </c>
-      <c r="Z13">
-        <v>3.72</v>
-      </c>
-      <c r="AA13">
-        <v>1.81</v>
-      </c>
-      <c r="AB13">
-        <v>2</v>
-      </c>
-      <c r="AC13">
-        <v>2.95</v>
-      </c>
-      <c r="AD13">
-        <v>1.36</v>
-      </c>
-      <c r="AE13">
-        <v>1.11</v>
-      </c>
-      <c r="AF13">
-        <v>1.62</v>
-      </c>
-      <c r="AG13">
-        <v>2.1</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.22</v>
-      </c>
-      <c r="AK13">
-        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.85</v>
+        <v>2.67</v>
       </c>
       <c r="R14">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="U14">
+        <v>2.5</v>
+      </c>
+      <c r="V14">
+        <v>1.44</v>
+      </c>
+      <c r="W14">
+        <v>1.11</v>
+      </c>
+      <c r="X14">
+        <v>1.04</v>
+      </c>
+      <c r="Y14">
+        <v>1.25</v>
+      </c>
+      <c r="Z14">
+        <v>3.72</v>
+      </c>
+      <c r="AA14">
+        <v>1.81</v>
+      </c>
+      <c r="AB14">
+        <v>2</v>
+      </c>
+      <c r="AC14">
         <v>2.95</v>
       </c>
-      <c r="V14">
-        <v>1.31</v>
-      </c>
-      <c r="W14">
-        <v>1.06</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.41</v>
-      </c>
-      <c r="Z14">
-        <v>2.79</v>
-      </c>
-      <c r="AA14">
-        <v>2.35</v>
-      </c>
-      <c r="AB14">
-        <v>1.57</v>
-      </c>
-      <c r="AC14">
-        <v>4.1</v>
-      </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="O114">
-        <v>3.65</v>
+        <v>5.95</v>
       </c>
       <c r="P114">
-        <v>3.9</v>
+        <v>14</v>
       </c>
       <c r="Q114">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="R114">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="S114">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="T114">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="U114">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="V114">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="W114">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="Z114">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA114">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AB114">
-        <v>2.01</v>
+        <v>2.68</v>
       </c>
       <c r="AC114">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="AD114">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="AE114">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AF114">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG114">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK114">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
+        <v>1.44</v>
+      </c>
+      <c r="O115">
+        <v>4.9</v>
+      </c>
+      <c r="P115">
+        <v>6</v>
+      </c>
+      <c r="Q115">
+        <v>1.83</v>
+      </c>
+      <c r="R115">
+        <v>2.62</v>
+      </c>
+      <c r="S115">
         <v>1.22</v>
       </c>
-      <c r="O115">
-        <v>5.95</v>
-      </c>
-      <c r="P115">
-        <v>14</v>
-      </c>
-      <c r="Q115">
-        <v>1.57</v>
-      </c>
-      <c r="R115">
-        <v>2.88</v>
-      </c>
-      <c r="S115">
-        <v>1.2</v>
-      </c>
       <c r="T115">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U115">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V115">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W115">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z115">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA115">
         <v>1.4</v>
       </c>
       <c r="AB115">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="AC115">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD115">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AE115">
         <v>1.28</v>
       </c>
       <c r="AF115">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG115">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="O116">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="P116">
-        <v>6</v>
+        <v>3.28</v>
       </c>
       <c r="Q116">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R116">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="S116">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="T116">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="U116">
+        <v>2.75</v>
+      </c>
+      <c r="V116">
+        <v>1.4</v>
+      </c>
+      <c r="W116">
+        <v>1.05</v>
+      </c>
+      <c r="X116">
+        <v>1.01</v>
+      </c>
+      <c r="Y116">
+        <v>1.29</v>
+      </c>
+      <c r="Z116">
+        <v>3.05</v>
+      </c>
+      <c r="AA116">
         <v>2</v>
       </c>
-      <c r="V116">
+      <c r="AB116">
+        <v>1.85</v>
+      </c>
+      <c r="AC116">
+        <v>3.3</v>
+      </c>
+      <c r="AD116">
+        <v>1.33</v>
+      </c>
+      <c r="AE116">
+        <v>1.05</v>
+      </c>
+      <c r="AF116">
         <v>1.73</v>
       </c>
-      <c r="W116">
-        <v>1.18</v>
-      </c>
-      <c r="X116">
-        <v>1.02</v>
-      </c>
-      <c r="Y116">
-        <v>1.1</v>
-      </c>
-      <c r="Z116">
-        <v>6</v>
-      </c>
-      <c r="AA116">
-        <v>1.4</v>
-      </c>
-      <c r="AB116">
-        <v>2.85</v>
-      </c>
-      <c r="AC116">
-        <v>2.16</v>
-      </c>
-      <c r="AD116">
-        <v>1.72</v>
-      </c>
-      <c r="AE116">
-        <v>1.28</v>
-      </c>
-      <c r="AF116">
-        <v>1.57</v>
-      </c>
       <c r="AG116">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,80 +19380,80 @@
         </is>
       </c>
       <c r="N117">
+        <v>2.27</v>
+      </c>
+      <c r="O117">
+        <v>3.58</v>
+      </c>
+      <c r="P117">
+        <v>2.47</v>
+      </c>
+      <c r="Q117">
+        <v>3</v>
+      </c>
+      <c r="R117">
         <v>2.2</v>
       </c>
-      <c r="O117">
+      <c r="S117">
+        <v>1.28</v>
+      </c>
+      <c r="T117">
         <v>3.35</v>
       </c>
-      <c r="P117">
-        <v>3.28</v>
-      </c>
-      <c r="Q117">
-        <v>2.5</v>
-      </c>
-      <c r="R117">
-        <v>2.11</v>
-      </c>
-      <c r="S117">
-        <v>1.41</v>
-      </c>
-      <c r="T117">
-        <v>2.9</v>
-      </c>
       <c r="U117">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="V117">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X117">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA117">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB117">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AC117">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD117">
+        <v>1.52</v>
+      </c>
+      <c r="AE117">
+        <v>1.18</v>
+      </c>
+      <c r="AF117">
+        <v>1.51</v>
+      </c>
+      <c r="AG117">
+        <v>2.42</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ117">
         <v>1.33</v>
       </c>
-      <c r="AE117">
-        <v>1.05</v>
-      </c>
-      <c r="AF117">
-        <v>1.73</v>
-      </c>
-      <c r="AG117">
-        <v>2</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>1.3</v>
-      </c>
       <c r="AK117">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="O118">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P118">
-        <v>2.47</v>
+        <v>3.9</v>
       </c>
       <c r="Q118">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R118">
         <v>2.2</v>
       </c>
       <c r="S118">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T118">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="U118">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="V118">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W118">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X118">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z118">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA118">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB118">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="AC118">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD118">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AE118">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG118">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
+        <v>3</v>
+      </c>
+      <c r="O130">
+        <v>3.6</v>
+      </c>
+      <c r="P130">
+        <v>2.15</v>
+      </c>
+      <c r="Q130">
+        <v>3.5</v>
+      </c>
+      <c r="R130">
+        <v>2.25</v>
+      </c>
+      <c r="S130">
+        <v>1.32</v>
+      </c>
+      <c r="T130">
+        <v>3.1</v>
+      </c>
+      <c r="U130">
         <v>2.44</v>
       </c>
-      <c r="O130">
-        <v>3.15</v>
-      </c>
-      <c r="P130">
-        <v>2.54</v>
-      </c>
-      <c r="Q130">
-        <v>3.3</v>
-      </c>
-      <c r="R130">
-        <v>2.11</v>
-      </c>
-      <c r="S130">
-        <v>1.4</v>
-      </c>
-      <c r="T130">
-        <v>2.62</v>
-      </c>
-      <c r="U130">
-        <v>3.2</v>
-      </c>
       <c r="V130">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="W130">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X130">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z130">
-        <v>3.03</v>
+        <v>3.72</v>
       </c>
       <c r="AA130">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AB130">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AC130">
-        <v>4.2</v>
+        <v>2.78</v>
       </c>
       <c r="AD130">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AE130">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF130">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AG130">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK130">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,43 +21662,43 @@
         </is>
       </c>
       <c r="N131">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="O131">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P131">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q131">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R131">
         <v>2.25</v>
       </c>
       <c r="S131">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T131">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="U131">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V131">
         <v>1.47</v>
       </c>
       <c r="W131">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X131">
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z131">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="AA131">
         <v>1.73</v>
@@ -21707,19 +21707,19 @@
         <v>2</v>
       </c>
       <c r="AC131">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD131">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE131">
         <v>1.14</v>
       </c>
       <c r="AF131">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG131">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="O132">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="P132">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="Q132">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R132">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S132">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="T132">
-        <v>3.27</v>
+        <v>3.44</v>
       </c>
       <c r="U132">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="V132">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W132">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z132">
-        <v>4.1</v>
+        <v>4.42</v>
       </c>
       <c r="AA132">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB132">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC132">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="AD132">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE132">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF132">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AG132">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK132">
-        <v>1.73</v>
+        <v>2.31</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="O133">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="P133">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="Q133">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="R133">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S133">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="T133">
-        <v>3.44</v>
+        <v>2.62</v>
       </c>
       <c r="U133">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="V133">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="W133">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X133">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y133">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="Z133">
-        <v>4.42</v>
+        <v>3.03</v>
       </c>
       <c r="AA133">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB133">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC133">
-        <v>2.43</v>
+        <v>4.2</v>
       </c>
       <c r="AD133">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AE133">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AF133">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AG133">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AK133">
-        <v>2.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="O135">
         <v>3.5</v>
       </c>
       <c r="P135">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q135">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="R135">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S135">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T135">
         <v>3</v>
       </c>
       <c r="U135">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="V135">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W135">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X135">
         <v>1</v>
       </c>
       <c r="Y135">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z135">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AA135">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB135">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC135">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AD135">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE135">
         <v>1.07</v>
       </c>
       <c r="AF135">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG135">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q136">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="R136">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S136">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T136">
         <v>3</v>
       </c>
       <c r="U136">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="V136">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X136">
         <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z136">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AA136">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB136">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC136">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AD136">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE136">
         <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AK136">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,28 +23944,28 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="O145">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P145">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="Q145">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R145">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="S145">
         <v>1.25</v>
       </c>
       <c r="T145">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U145">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V145">
         <v>1.52</v>
@@ -23974,34 +23974,34 @@
         <v>1.11</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z145">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA145">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AB145">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC145">
         <v>2.45</v>
       </c>
       <c r="AD145">
+        <v>1.53</v>
+      </c>
+      <c r="AE145">
+        <v>1.16</v>
+      </c>
+      <c r="AF145">
         <v>1.57</v>
       </c>
-      <c r="AE145">
-        <v>1.18</v>
-      </c>
-      <c r="AF145">
-        <v>1.6</v>
-      </c>
       <c r="AG145">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK145">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,28 +24107,28 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="O146">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="P146">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Q146">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="R146">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="S146">
         <v>1.25</v>
       </c>
       <c r="T146">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U146">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V146">
         <v>1.52</v>
@@ -24137,34 +24137,34 @@
         <v>1.11</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z146">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA146">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AB146">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC146">
         <v>2.45</v>
       </c>
       <c r="AD146">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE146">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF146">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG146">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK146">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O151">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P151">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q151">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R151">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S151">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T151">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U151">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V151">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W151">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X151">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y151">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z151">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="AA151">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB151">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC151">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AD151">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE151">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF151">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG151">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK151">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G152">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O154">
+        <v>3.8</v>
+      </c>
+      <c r="P154">
+        <v>3.15</v>
+      </c>
+      <c r="Q154">
+        <v>2.45</v>
+      </c>
+      <c r="R154">
+        <v>2.48</v>
+      </c>
+      <c r="S154">
+        <v>1.25</v>
+      </c>
+      <c r="T154">
         <v>3.5</v>
       </c>
-      <c r="P154">
-        <v>3.75</v>
-      </c>
-      <c r="Q154">
-        <v>2.4</v>
-      </c>
-      <c r="R154">
-        <v>2.1</v>
-      </c>
-      <c r="S154">
-        <v>1.35</v>
-      </c>
-      <c r="T154">
-        <v>2.95</v>
-      </c>
       <c r="U154">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="V154">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W154">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X154">
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>3.3</v>
+        <v>4.79</v>
       </c>
       <c r="AA154">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AB154">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AC154">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="AD154">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AE154">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF154">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG154">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK154">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.98</v>
+        <v>1.93</v>
       </c>
       <c r="O155">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="P155">
-        <v>1.97</v>
+        <v>3.75</v>
       </c>
       <c r="Q155">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="R155">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S155">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T155">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U155">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="V155">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W155">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z155">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA155">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB155">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AC155">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="AD155">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE155">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF155">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG155">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="AK155">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.84</v>
+        <v>2.98</v>
       </c>
       <c r="O156">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="P156">
-        <v>4</v>
+        <v>1.97</v>
       </c>
       <c r="Q156">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="R156">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="S156">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T156">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U156">
-        <v>2.89</v>
+        <v>2.49</v>
       </c>
       <c r="V156">
+        <v>1.51</v>
+      </c>
+      <c r="W156">
+        <v>1.08</v>
+      </c>
+      <c r="X156">
+        <v>1.01</v>
+      </c>
+      <c r="Y156">
+        <v>1.18</v>
+      </c>
+      <c r="Z156">
+        <v>4.2</v>
+      </c>
+      <c r="AA156">
+        <v>1.65</v>
+      </c>
+      <c r="AB156">
+        <v>2.11</v>
+      </c>
+      <c r="AC156">
+        <v>2.57</v>
+      </c>
+      <c r="AD156">
         <v>1.4</v>
       </c>
-      <c r="W156">
-        <v>1.06</v>
-      </c>
-      <c r="X156">
-        <v>1.02</v>
-      </c>
-      <c r="Y156">
-        <v>1.26</v>
-      </c>
-      <c r="Z156">
-        <v>3.44</v>
-      </c>
-      <c r="AA156">
-        <v>1.85</v>
-      </c>
-      <c r="AB156">
-        <v>1.8</v>
-      </c>
-      <c r="AC156">
-        <v>3</v>
-      </c>
-      <c r="AD156">
-        <v>1.27</v>
-      </c>
       <c r="AE156">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF156">
+        <v>1.57</v>
+      </c>
+      <c r="AG156">
+        <v>2.25</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
         <v>1.73</v>
       </c>
-      <c r="AG156">
-        <v>1.9</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.21</v>
-      </c>
       <c r="AK156">
-        <v>1.89</v>
+        <v>1.29</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -39927,55 +39927,55 @@
         <v>0</v>
       </c>
       <c r="Q243">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R243">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S243">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T243">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U243">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V243">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W243">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X243">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y243">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z243">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA243">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB243">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC243">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD243">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE243">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF243">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG243">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G300">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G302">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G303">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G305">

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O105">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P105">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q105">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="R105">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="S105">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>3.18</v>
+        <v>2.7</v>
       </c>
       <c r="U105">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="V105">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W105">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z105">
-        <v>3.96</v>
+        <v>3.41</v>
       </c>
       <c r="AA105">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AB105">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC105">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="AD105">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE105">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF105">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG105">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O106">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P106">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q106">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="R106">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T106">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="U106">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V106">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W106">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X106">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z106">
-        <v>3.41</v>
+        <v>3.96</v>
       </c>
       <c r="AA106">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AB106">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC106">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AD106">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE106">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG106">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.02</v>
+        <v>3.8</v>
       </c>
       <c r="O111">
+        <v>4.1</v>
+      </c>
+      <c r="P111">
+        <v>1.63</v>
+      </c>
+      <c r="Q111">
         <v>3.9</v>
       </c>
-      <c r="P111">
-        <v>3.4</v>
-      </c>
-      <c r="Q111">
+      <c r="R111">
         <v>2.5</v>
       </c>
-      <c r="R111">
-        <v>2.41</v>
-      </c>
       <c r="S111">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T111">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U111">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="V111">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W111">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X111">
         <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z111">
-        <v>4.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA111">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB111">
         <v>2.66</v>
       </c>
       <c r="AC111">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AD111">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AE111">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF111">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG111">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AK111">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.8</v>
+        <v>1.22</v>
       </c>
       <c r="O112">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="P112">
-        <v>1.63</v>
+        <v>10.5</v>
       </c>
       <c r="Q112">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="R112">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S112">
+        <v>1.17</v>
+      </c>
+      <c r="T112">
+        <v>4.8</v>
+      </c>
+      <c r="U112">
+        <v>1.93</v>
+      </c>
+      <c r="V112">
+        <v>1.88</v>
+      </c>
+      <c r="W112">
         <v>1.22</v>
       </c>
-      <c r="T112">
-        <v>4.05</v>
-      </c>
-      <c r="U112">
-        <v>2.13</v>
-      </c>
-      <c r="V112">
-        <v>1.74</v>
-      </c>
-      <c r="W112">
-        <v>1.2</v>
-      </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z112">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AA112">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB112">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AC112">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD112">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE112">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AF112">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AG112">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK112">
-        <v>1.22</v>
+        <v>4.08</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="O113">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="P113">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q113">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="R113">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="S113">
+        <v>1.25</v>
+      </c>
+      <c r="T113">
+        <v>4</v>
+      </c>
+      <c r="U113">
+        <v>2.19</v>
+      </c>
+      <c r="V113">
+        <v>1.7</v>
+      </c>
+      <c r="W113">
         <v>1.17</v>
       </c>
-      <c r="T113">
-        <v>4.8</v>
-      </c>
-      <c r="U113">
-        <v>1.93</v>
-      </c>
-      <c r="V113">
-        <v>1.88</v>
-      </c>
-      <c r="W113">
-        <v>1.22</v>
-      </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z113">
-        <v>8</v>
+        <v>4.95</v>
       </c>
       <c r="AA113">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB113">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AC113">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="AD113">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AE113">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AF113">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AG113">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK113">
-        <v>4.08</v>
+        <v>1.73</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="O116">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P116">
-        <v>2.47</v>
+        <v>3.9</v>
       </c>
       <c r="Q116">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R116">
         <v>2.2</v>
       </c>
       <c r="S116">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T116">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="U116">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="V116">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W116">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X116">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z116">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA116">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB116">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="AC116">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD116">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AE116">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF116">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG116">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK116">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="O117">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P117">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="Q117">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R117">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S117">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T117">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U117">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V117">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W117">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z117">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AA117">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB117">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AC117">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AD117">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE117">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF117">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG117">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
+        <v>2.27</v>
+      </c>
+      <c r="O118">
+        <v>3.58</v>
+      </c>
+      <c r="P118">
+        <v>2.47</v>
+      </c>
+      <c r="Q118">
+        <v>3</v>
+      </c>
+      <c r="R118">
         <v>2.2</v>
       </c>
-      <c r="O118">
+      <c r="S118">
+        <v>1.28</v>
+      </c>
+      <c r="T118">
         <v>3.35</v>
       </c>
-      <c r="P118">
-        <v>3.28</v>
-      </c>
-      <c r="Q118">
-        <v>2.5</v>
-      </c>
-      <c r="R118">
-        <v>2.11</v>
-      </c>
-      <c r="S118">
-        <v>1.41</v>
-      </c>
-      <c r="T118">
-        <v>2.9</v>
-      </c>
       <c r="U118">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="V118">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W118">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y118">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z118">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA118">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB118">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AC118">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD118">
+        <v>1.52</v>
+      </c>
+      <c r="AE118">
+        <v>1.18</v>
+      </c>
+      <c r="AF118">
+        <v>1.51</v>
+      </c>
+      <c r="AG118">
+        <v>2.42</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
         <v>1.33</v>
       </c>
-      <c r="AE118">
-        <v>1.05</v>
-      </c>
-      <c r="AF118">
-        <v>1.73</v>
-      </c>
-      <c r="AG118">
-        <v>2</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.3</v>
-      </c>
       <c r="AK118">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,80 +21825,80 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="O132">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P132">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="Q132">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R132">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S132">
+        <v>1.39</v>
+      </c>
+      <c r="T132">
+        <v>2.7</v>
+      </c>
+      <c r="U132">
+        <v>2.69</v>
+      </c>
+      <c r="V132">
+        <v>1.41</v>
+      </c>
+      <c r="W132">
+        <v>1.06</v>
+      </c>
+      <c r="X132">
+        <v>1</v>
+      </c>
+      <c r="Y132">
+        <v>1.24</v>
+      </c>
+      <c r="Z132">
+        <v>3.34</v>
+      </c>
+      <c r="AA132">
+        <v>1.88</v>
+      </c>
+      <c r="AB132">
+        <v>1.87</v>
+      </c>
+      <c r="AC132">
+        <v>3.08</v>
+      </c>
+      <c r="AD132">
+        <v>1.29</v>
+      </c>
+      <c r="AE132">
+        <v>1.11</v>
+      </c>
+      <c r="AF132">
+        <v>1.67</v>
+      </c>
+      <c r="AG132">
+        <v>2.05</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ132">
         <v>1.4</v>
       </c>
-      <c r="T132">
-        <v>2.62</v>
-      </c>
-      <c r="U132">
-        <v>3.2</v>
-      </c>
-      <c r="V132">
-        <v>1.3</v>
-      </c>
-      <c r="W132">
-        <v>1.05</v>
-      </c>
-      <c r="X132">
-        <v>1.05</v>
-      </c>
-      <c r="Y132">
-        <v>1.36</v>
-      </c>
-      <c r="Z132">
-        <v>3.03</v>
-      </c>
-      <c r="AA132">
-        <v>2.15</v>
-      </c>
-      <c r="AB132">
-        <v>1.66</v>
-      </c>
-      <c r="AC132">
-        <v>4.2</v>
-      </c>
-      <c r="AD132">
-        <v>1.18</v>
-      </c>
-      <c r="AE132">
-        <v>1.04</v>
-      </c>
-      <c r="AF132">
-        <v>1.84</v>
-      </c>
-      <c r="AG132">
-        <v>1.86</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>1.44</v>
-      </c>
       <c r="AK132">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.62</v>
+        <v>1.6</v>
       </c>
       <c r="O133">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P133">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R133">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S133">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="T133">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="U133">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V133">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="W133">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z133">
-        <v>3.25</v>
+        <v>4.42</v>
       </c>
       <c r="AA133">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB133">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC133">
-        <v>3.55</v>
+        <v>2.43</v>
       </c>
       <c r="AD133">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AE133">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF133">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG133">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>1.44</v>
+        <v>2.31</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P135">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="Q135">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R135">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="S135">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T135">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U135">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="V135">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="W135">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Z135">
-        <v>3.34</v>
+        <v>3.03</v>
       </c>
       <c r="AA135">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AB135">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AC135">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="AD135">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AE135">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF135">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AG135">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK135">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,65 +22640,65 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.6</v>
+        <v>2.62</v>
       </c>
       <c r="O137">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P137">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="Q137">
+        <v>3</v>
+      </c>
+      <c r="R137">
+        <v>2.1</v>
+      </c>
+      <c r="S137">
+        <v>1.4</v>
+      </c>
+      <c r="T137">
+        <v>2.8</v>
+      </c>
+      <c r="U137">
+        <v>2.88</v>
+      </c>
+      <c r="V137">
+        <v>1.35</v>
+      </c>
+      <c r="W137">
+        <v>1.08</v>
+      </c>
+      <c r="X137">
+        <v>1.01</v>
+      </c>
+      <c r="Y137">
+        <v>1.33</v>
+      </c>
+      <c r="Z137">
+        <v>3.25</v>
+      </c>
+      <c r="AA137">
+        <v>2.03</v>
+      </c>
+      <c r="AB137">
+        <v>1.8</v>
+      </c>
+      <c r="AC137">
+        <v>3.55</v>
+      </c>
+      <c r="AD137">
+        <v>1.28</v>
+      </c>
+      <c r="AE137">
+        <v>1.04</v>
+      </c>
+      <c r="AF137">
+        <v>1.75</v>
+      </c>
+      <c r="AG137">
         <v>2</v>
       </c>
-      <c r="R137">
-        <v>2.3</v>
-      </c>
-      <c r="S137">
-        <v>1.26</v>
-      </c>
-      <c r="T137">
-        <v>3.44</v>
-      </c>
-      <c r="U137">
-        <v>2.23</v>
-      </c>
-      <c r="V137">
-        <v>1.57</v>
-      </c>
-      <c r="W137">
-        <v>1.12</v>
-      </c>
-      <c r="X137">
-        <v>1.02</v>
-      </c>
-      <c r="Y137">
-        <v>1.19</v>
-      </c>
-      <c r="Z137">
-        <v>4.42</v>
-      </c>
-      <c r="AA137">
-        <v>1.6</v>
-      </c>
-      <c r="AB137">
-        <v>2.2</v>
-      </c>
-      <c r="AC137">
-        <v>2.43</v>
-      </c>
-      <c r="AD137">
-        <v>1.45</v>
-      </c>
-      <c r="AE137">
-        <v>1.15</v>
-      </c>
-      <c r="AF137">
-        <v>1.66</v>
-      </c>
-      <c r="AG137">
-        <v>2.09</v>
-      </c>
       <c r="AH137" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK137">
-        <v>2.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O145">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="P145">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q145">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="R145">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="S145">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T145">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="U145">
+        <v>3.1</v>
+      </c>
+      <c r="V145">
+        <v>1.32</v>
+      </c>
+      <c r="W145">
+        <v>1.03</v>
+      </c>
+      <c r="X145">
+        <v>1.08</v>
+      </c>
+      <c r="Y145">
+        <v>1.36</v>
+      </c>
+      <c r="Z145">
+        <v>2.95</v>
+      </c>
+      <c r="AA145">
         <v>2.2</v>
       </c>
-      <c r="V145">
-        <v>1.52</v>
-      </c>
-      <c r="W145">
-        <v>1.11</v>
-      </c>
-      <c r="X145">
-        <v>1.01</v>
-      </c>
-      <c r="Y145">
-        <v>1.14</v>
-      </c>
-      <c r="Z145">
-        <v>4.45</v>
-      </c>
-      <c r="AA145">
-        <v>1.54</v>
-      </c>
       <c r="AB145">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="AC145">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="AD145">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AE145">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF145">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AG145">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK145">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="O146">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P146">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q146">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R146">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S146">
         <v>1.4</v>
       </c>
       <c r="T146">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="U146">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="V146">
+        <v>1.39</v>
+      </c>
+      <c r="W146">
+        <v>1.04</v>
+      </c>
+      <c r="X146">
+        <v>1.03</v>
+      </c>
+      <c r="Y146">
         <v>1.32</v>
       </c>
-      <c r="W146">
-        <v>1.03</v>
-      </c>
-      <c r="X146">
-        <v>1.08</v>
-      </c>
-      <c r="Y146">
-        <v>1.36</v>
-      </c>
       <c r="Z146">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AA146">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB146">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC146">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD146">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE146">
         <v>1.06</v>
       </c>
       <c r="AF146">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AG146">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>1.33</v>
       </c>
       <c r="AK146">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.87</v>
+        <v>1.61</v>
       </c>
       <c r="O147">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P147">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q147">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="R147">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="S147">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T147">
-        <v>2.73</v>
+        <v>3.45</v>
       </c>
       <c r="U147">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="V147">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W147">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X147">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z147">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="AA147">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AB147">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AC147">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD147">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE147">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF147">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AG147">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK147">
-        <v>1.39</v>
+        <v>2.25</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,31 +24433,31 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O148">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P148">
-        <v>3.15</v>
+        <v>3.38</v>
       </c>
       <c r="Q148">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R148">
         <v>2.3</v>
       </c>
       <c r="S148">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T148">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U148">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="V148">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W148">
         <v>1.12</v>
@@ -24466,31 +24466,31 @@
         <v>1.01</v>
       </c>
       <c r="Y148">
+        <v>1.16</v>
+      </c>
+      <c r="Z148">
+        <v>3.8</v>
+      </c>
+      <c r="AA148">
+        <v>1.65</v>
+      </c>
+      <c r="AB148">
+        <v>2.2</v>
+      </c>
+      <c r="AC148">
+        <v>2.59</v>
+      </c>
+      <c r="AD148">
+        <v>1.46</v>
+      </c>
+      <c r="AE148">
         <v>1.18</v>
       </c>
-      <c r="Z148">
-        <v>4.77</v>
-      </c>
-      <c r="AA148">
-        <v>1.6</v>
-      </c>
-      <c r="AB148">
-        <v>2.34</v>
-      </c>
-      <c r="AC148">
-        <v>2.36</v>
-      </c>
-      <c r="AD148">
-        <v>1.5</v>
-      </c>
-      <c r="AE148">
-        <v>1.16</v>
-      </c>
       <c r="AF148">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AG148">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK148">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="O149">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="P149">
-        <v>4.3</v>
+        <v>2.48</v>
       </c>
       <c r="Q149">
-        <v>2.14</v>
+        <v>2.87</v>
       </c>
       <c r="R149">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="S149">
+        <v>1.37</v>
+      </c>
+      <c r="T149">
+        <v>2.77</v>
+      </c>
+      <c r="U149">
+        <v>2.55</v>
+      </c>
+      <c r="V149">
+        <v>1.39</v>
+      </c>
+      <c r="W149">
+        <v>1.06</v>
+      </c>
+      <c r="X149">
+        <v>1.03</v>
+      </c>
+      <c r="Y149">
         <v>1.25</v>
       </c>
-      <c r="T149">
-        <v>3.6</v>
-      </c>
-      <c r="U149">
-        <v>2.2</v>
-      </c>
-      <c r="V149">
-        <v>1.6</v>
-      </c>
-      <c r="W149">
-        <v>1.13</v>
-      </c>
-      <c r="X149">
-        <v>1.01</v>
-      </c>
-      <c r="Y149">
-        <v>1.13</v>
-      </c>
       <c r="Z149">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA149">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB149">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AC149">
-        <v>2.35</v>
+        <v>3.24</v>
       </c>
       <c r="AD149">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AE149">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF149">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG149">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AK149">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="O150">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P150">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="Q150">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R150">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S150">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T150">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U150">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="V150">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W150">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X150">
         <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z150">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA150">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB150">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC150">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="AD150">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AE150">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF150">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AG150">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK150">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
+        <v>2.55</v>
+      </c>
+      <c r="O151">
+        <v>3.4</v>
+      </c>
+      <c r="P151">
         <v>2.35</v>
       </c>
-      <c r="O151">
-        <v>3.38</v>
-      </c>
-      <c r="P151">
-        <v>2.48</v>
-      </c>
       <c r="Q151">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="R151">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="S151">
         <v>1.37</v>
       </c>
       <c r="T151">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="U151">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="V151">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W151">
         <v>1.06</v>
       </c>
       <c r="X151">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z151">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AA151">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB151">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC151">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AD151">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE151">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF151">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG151">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK151">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,25 +25085,25 @@
         </is>
       </c>
       <c r="N152">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="O152">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P152">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="Q152">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="R152">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="S152">
         <v>1.25</v>
       </c>
       <c r="T152">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U152">
         <v>2.2</v>
@@ -25118,31 +25118,31 @@
         <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z152">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="AA152">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB152">
+        <v>2.4</v>
+      </c>
+      <c r="AC152">
         <v>2.35</v>
       </c>
-      <c r="AC152">
-        <v>2.44</v>
-      </c>
       <c r="AD152">
+        <v>1.57</v>
+      </c>
+      <c r="AE152">
+        <v>1.19</v>
+      </c>
+      <c r="AF152">
         <v>1.55</v>
       </c>
-      <c r="AE152">
-        <v>1.18</v>
-      </c>
-      <c r="AF152">
-        <v>1.5</v>
-      </c>
       <c r="AG152">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK152">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.98</v>
+        <v>1.84</v>
       </c>
       <c r="O153">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="P153">
-        <v>1.97</v>
+        <v>4</v>
       </c>
       <c r="Q153">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="R153">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="S153">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T153">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U153">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="V153">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W153">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X153">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z153">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="AA153">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB153">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AC153">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="AD153">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE153">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF153">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG153">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.73</v>
+        <v>1.21</v>
       </c>
       <c r="AK153">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,80 +25411,80 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.93</v>
+        <v>2.98</v>
       </c>
       <c r="O154">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="P154">
-        <v>3.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q154">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="R154">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S154">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U154">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="V154">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W154">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X154">
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA154">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB154">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AC154">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="AD154">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE154">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF154">
+        <v>1.57</v>
+      </c>
+      <c r="AG154">
+        <v>2.25</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ154">
         <v>1.73</v>
       </c>
-      <c r="AG154">
-        <v>2</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>1.23</v>
-      </c>
       <c r="AK154">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="O155">
+        <v>3.6</v>
+      </c>
+      <c r="P155">
+        <v>3.15</v>
+      </c>
+      <c r="Q155">
+        <v>2.4</v>
+      </c>
+      <c r="R155">
+        <v>2.3</v>
+      </c>
+      <c r="S155">
+        <v>1.29</v>
+      </c>
+      <c r="T155">
         <v>3.4</v>
       </c>
-      <c r="P155">
-        <v>2.35</v>
-      </c>
-      <c r="Q155">
-        <v>3.2</v>
-      </c>
-      <c r="R155">
-        <v>2.2</v>
-      </c>
-      <c r="S155">
-        <v>1.37</v>
-      </c>
-      <c r="T155">
-        <v>3.05</v>
-      </c>
       <c r="U155">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="V155">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W155">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z155">
-        <v>3.64</v>
+        <v>4.77</v>
       </c>
       <c r="AA155">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB155">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC155">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="AD155">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AE155">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF155">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG155">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK155">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="O156">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P156">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="Q156">
         <v>2.45</v>
       </c>
       <c r="R156">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="S156">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T156">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U156">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="V156">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W156">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X156">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z156">
-        <v>3.44</v>
+        <v>4.79</v>
       </c>
       <c r="AA156">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AB156">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC156">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="AD156">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="AE156">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF156">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG156">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.21</v>
       </c>
       <c r="AK156">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G215">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G225">
@@ -36987,61 +36987,61 @@
         <v>2.05</v>
       </c>
       <c r="O225">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P225">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q225">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="R225">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="S225">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="T225">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="U225">
-        <v>2.41</v>
+        <v>3.07</v>
       </c>
       <c r="V225">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W225">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X225">
         <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="Z225">
-        <v>4.05</v>
+        <v>3.12</v>
       </c>
       <c r="AA225">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AB225">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC225">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD225">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AE225">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF225">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG225">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>1.3</v>
       </c>
       <c r="AK225">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G226">
@@ -37150,61 +37150,61 @@
         <v>2.05</v>
       </c>
       <c r="O226">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P226">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q226">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="R226">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="S226">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="T226">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="U226">
-        <v>3.07</v>
+        <v>2.41</v>
       </c>
       <c r="V226">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W226">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X226">
         <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z226">
-        <v>3.12</v>
+        <v>4.05</v>
       </c>
       <c r="AA226">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AB226">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC226">
-        <v>4.2</v>
+        <v>2.48</v>
       </c>
       <c r="AD226">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AE226">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF226">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG226">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>1.3</v>
       </c>
       <c r="AK226">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,80 +39266,80 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q239">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="R239">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S239">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T239">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="U239">
         <v>2.75</v>
       </c>
       <c r="V239">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W239">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X239">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y239">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z239">
-        <v>3.24</v>
+        <v>3.51</v>
       </c>
       <c r="AA239">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AB239">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AC239">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AD239">
+        <v>1.29</v>
+      </c>
+      <c r="AE239">
+        <v>1.08</v>
+      </c>
+      <c r="AF239">
+        <v>1.67</v>
+      </c>
+      <c r="AG239">
+        <v>2.03</v>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ239">
         <v>1.24</v>
       </c>
-      <c r="AE239">
-        <v>1.05</v>
-      </c>
-      <c r="AF239">
-        <v>1.75</v>
-      </c>
-      <c r="AG239">
-        <v>1.95</v>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ239">
-        <v>1.38</v>
-      </c>
       <c r="AK239">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O240">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P240">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q240">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="R240">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S240">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T240">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="U240">
         <v>2.75</v>
       </c>
       <c r="V240">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W240">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X240">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y240">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z240">
-        <v>3.51</v>
+        <v>3.24</v>
       </c>
       <c r="AA240">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AB240">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AC240">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="AD240">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE240">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF240">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG240">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AK240">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G244">
@@ -40090,16 +40090,16 @@
         <v>0</v>
       </c>
       <c r="Q244">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="R244">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S244">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T244">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U244">
         <v>0</v>
@@ -40114,31 +40114,31 @@
         <v>0</v>
       </c>
       <c r="Y244">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z244">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA244">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB244">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC244">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD244">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE244">
         <v>0</v>
       </c>
       <c r="AF244">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG244">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK244">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G245">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G246">
@@ -40416,16 +40416,16 @@
         <v>0</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R246">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S246">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T246">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U246">
         <v>0</v>
@@ -40440,31 +40440,31 @@
         <v>0</v>
       </c>
       <c r="Y246">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z246">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC246">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD246">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE246">
         <v>0</v>
       </c>
       <c r="AF246">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG246">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK246">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,25 +44808,25 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O273">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="P273">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="Q273">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="R273">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="S273">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T273">
-        <v>3.01</v>
+        <v>2.81</v>
       </c>
       <c r="U273">
         <v>2.75</v>
@@ -44838,34 +44838,34 @@
         <v>1.06</v>
       </c>
       <c r="X273">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y273">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z273">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA273">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AB273">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC273">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AD273">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE273">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF273">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG273">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AK273">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O274">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="P274">
-        <v>2.44</v>
+        <v>2.77</v>
       </c>
       <c r="Q274">
         <v>3.1</v>
       </c>
       <c r="R274">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="S274">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T274">
-        <v>3.6</v>
+        <v>3.01</v>
       </c>
       <c r="U274">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="V274">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W274">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X274">
         <v>1.04</v>
       </c>
       <c r="Y274">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z274">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA274">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB274">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC274">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD274">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE274">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF274">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AG274">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AK274">
         <v>1.52</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O275">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P275">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q275">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="R275">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S275">
+        <v>1.29</v>
+      </c>
+      <c r="T275">
+        <v>3.6</v>
+      </c>
+      <c r="U275">
+        <v>2.51</v>
+      </c>
+      <c r="V275">
+        <v>1.53</v>
+      </c>
+      <c r="W275">
+        <v>1.11</v>
+      </c>
+      <c r="X275">
+        <v>1.04</v>
+      </c>
+      <c r="Y275">
+        <v>1.18</v>
+      </c>
+      <c r="Z275">
+        <v>4.1</v>
+      </c>
+      <c r="AA275">
+        <v>1.66</v>
+      </c>
+      <c r="AB275">
+        <v>2.2</v>
+      </c>
+      <c r="AC275">
+        <v>2.7</v>
+      </c>
+      <c r="AD275">
         <v>1.43</v>
       </c>
-      <c r="T275">
-        <v>2.81</v>
-      </c>
-      <c r="U275">
-        <v>2.75</v>
-      </c>
-      <c r="V275">
-        <v>1.4</v>
-      </c>
-      <c r="W275">
-        <v>1.06</v>
-      </c>
-      <c r="X275">
-        <v>1.03</v>
-      </c>
-      <c r="Y275">
-        <v>1.3</v>
-      </c>
-      <c r="Z275">
-        <v>3.1</v>
-      </c>
-      <c r="AA275">
-        <v>1.86</v>
-      </c>
-      <c r="AB275">
-        <v>1.9</v>
-      </c>
-      <c r="AC275">
-        <v>3</v>
-      </c>
-      <c r="AD275">
-        <v>1.3</v>
-      </c>
       <c r="AE275">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF275">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AG275">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AK275">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -49381,34 +49381,34 @@
         <v>5</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA301">
         <v>2.05</v>
@@ -49417,19 +49417,19 @@
         <v>1.75</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49707,55 +49707,55 @@
         <v>0</v>
       </c>
       <c r="Q303">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R303">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S303">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T303">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U303">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V303">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W303">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X303">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y303">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z303">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA303">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB303">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC303">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD303">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE303">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF303">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG303">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK303">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,64 +49861,64 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q304">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R304">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S304">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T304">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U304">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V304">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W304">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X304">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y304">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z304">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA304">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB304">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC304">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD304">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE304">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF304">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG304">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK304">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,64 +50024,64 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T305">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U305">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V305">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X305">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y305">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z305">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC305">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD305">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF305">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG305">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK305">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q306">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R306">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S306">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T306">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U306">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V306">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W306">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X306">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y306">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z306">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AA306">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB306">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC306">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD306">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE306">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF306">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG306">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK306">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q307">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R307">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S307">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T307">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U307">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V307">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W307">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X307">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y307">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z307">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA307">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB307">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC307">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD307">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE307">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF307">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG307">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK307">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P308">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q308">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="R308">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S308">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T308">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U308">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V308">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W308">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X308">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z308">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA308">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB308">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC308">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD308">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE308">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF308">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG308">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK308">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P309">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA309">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB309">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O310">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P310">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O311">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P311">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q311">
         <v>0</v>
@@ -51041,10 +51041,10 @@
         <v>0</v>
       </c>
       <c r="AA311">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB311">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC311">
         <v>0</v>
@@ -51174,34 +51174,34 @@
         <v>0</v>
       </c>
       <c r="Q312">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R312">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S312">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T312">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U312">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V312">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W312">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X312">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z312">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA312">
         <v>2</v>
@@ -51210,19 +51210,19 @@
         <v>1.8</v>
       </c>
       <c r="AC312">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AD312">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE312">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF312">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG312">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK312">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -52478,34 +52478,34 @@
         <v>2.95</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X320">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA320">
         <v>2</v>
@@ -52514,19 +52514,19 @@
         <v>1.8</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,64 +52632,64 @@
         </is>
       </c>
       <c r="N321">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O321">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P321">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q321">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R321">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S321">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T321">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U321">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V321">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W321">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X321">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y321">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z321">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA321">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB321">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC321">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD321">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE321">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF321">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG321">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK321">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O322">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P322">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="Q322">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R322">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S322">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T322">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U322">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V322">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W322">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X322">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y322">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z322">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AA322">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB322">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC322">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD322">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE322">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF322">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG322">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK322">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q323">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R323">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S323">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T323">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U323">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V323">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W323">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X323">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y323">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z323">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA323">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB323">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC323">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AD323">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE323">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF323">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG323">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK323">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q324">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R324">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S324">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T324">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U324">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V324">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W324">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X324">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y324">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z324">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA324">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB324">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC324">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD324">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE324">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF324">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG324">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK324">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O325">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P325">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q325">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R325">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S325">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T325">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U325">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V325">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W325">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X325">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y325">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z325">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA325">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB325">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC325">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD325">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE325">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF325">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG325">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK325">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,64 +53447,64 @@
         </is>
       </c>
       <c r="N326">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O326">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P326">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q326">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R326">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S326">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T326">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U326">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V326">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W326">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X326">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y326">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z326">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AA326">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB326">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC326">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD326">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE326">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF326">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG326">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK326">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O327">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P327">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q327">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R327">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S327">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T327">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U327">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V327">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W327">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X327">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y327">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z327">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA327">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB327">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC327">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD327">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE327">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF327">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG327">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK327">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O328">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P328">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q328">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R328">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S328">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T328">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U328">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V328">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W328">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X328">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y328">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z328">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA328">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB328">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC328">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AD328">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE328">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF328">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG328">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK328">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53945,55 +53945,55 @@
         <v>0</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S329">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T329">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U329">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V329">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W329">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X329">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA329">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB329">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC329">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD329">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE329">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF329">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG329">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK329">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G330">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G332">
@@ -54597,55 +54597,55 @@
         <v>0</v>
       </c>
       <c r="Q333">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R333">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S333">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T333">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U333">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V333">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W333">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X333">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y333">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z333">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA333">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB333">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC333">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD333">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE333">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF333">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG333">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
@@ -54658,10 +54658,10 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK333">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL333">
         <v>0</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,64 +55077,64 @@
         </is>
       </c>
       <c r="N336">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O336">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P336">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q336">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R336">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S336">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T336">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U336">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V336">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W336">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X336">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y336">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z336">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA336">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB336">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC336">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD336">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE336">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF336">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG336">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK336">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,64 +55240,64 @@
         </is>
       </c>
       <c r="N337">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O337">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P337">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q337">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R337">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S337">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T337">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U337">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V337">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W337">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X337">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y337">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z337">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA337">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB337">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC337">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD337">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE337">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF337">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG337">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK337">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,64 +55403,64 @@
         </is>
       </c>
       <c r="N338">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O338">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P338">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q338">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R338">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S338">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T338">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U338">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V338">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W338">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X338">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y338">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z338">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA338">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB338">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC338">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD338">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE338">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF338">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG338">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,10 +55473,10 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK338">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55566,64 +55566,64 @@
         </is>
       </c>
       <c r="N339">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O339">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P339">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q339">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R339">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S339">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T339">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U339">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V339">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W339">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X339">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y339">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z339">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AA339">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB339">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC339">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD339">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE339">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF339">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG339">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK339">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL339">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3.85</v>
+        <v>2.67</v>
       </c>
       <c r="R13">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="U13">
+        <v>2.5</v>
+      </c>
+      <c r="V13">
+        <v>1.44</v>
+      </c>
+      <c r="W13">
+        <v>1.11</v>
+      </c>
+      <c r="X13">
+        <v>1.04</v>
+      </c>
+      <c r="Y13">
+        <v>1.25</v>
+      </c>
+      <c r="Z13">
+        <v>3.72</v>
+      </c>
+      <c r="AA13">
+        <v>1.81</v>
+      </c>
+      <c r="AB13">
+        <v>2</v>
+      </c>
+      <c r="AC13">
         <v>2.95</v>
       </c>
-      <c r="V13">
-        <v>1.31</v>
-      </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>1.41</v>
-      </c>
-      <c r="Z13">
-        <v>2.79</v>
-      </c>
-      <c r="AA13">
-        <v>2.35</v>
-      </c>
-      <c r="AB13">
-        <v>1.57</v>
-      </c>
-      <c r="AC13">
-        <v>4.1</v>
-      </c>
       <c r="AD13">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q14">
-        <v>2.67</v>
+        <v>3.85</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
+        <v>1.41</v>
+      </c>
+      <c r="Z14">
+        <v>2.79</v>
+      </c>
+      <c r="AA14">
+        <v>2.35</v>
+      </c>
+      <c r="AB14">
+        <v>1.57</v>
+      </c>
+      <c r="AC14">
+        <v>4.1</v>
+      </c>
+      <c r="AD14">
+        <v>1.2</v>
+      </c>
+      <c r="AE14">
+        <v>1.01</v>
+      </c>
+      <c r="AF14">
+        <v>1.91</v>
+      </c>
+      <c r="AG14">
+        <v>1.76</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.27</v>
+      </c>
+      <c r="AK14">
         <v>1.25</v>
-      </c>
-      <c r="Z14">
-        <v>3.72</v>
-      </c>
-      <c r="AA14">
-        <v>1.81</v>
-      </c>
-      <c r="AB14">
-        <v>2</v>
-      </c>
-      <c r="AC14">
-        <v>2.95</v>
-      </c>
-      <c r="AD14">
-        <v>1.36</v>
-      </c>
-      <c r="AE14">
-        <v>1.11</v>
-      </c>
-      <c r="AF14">
-        <v>1.62</v>
-      </c>
-      <c r="AG14">
-        <v>2.1</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.22</v>
-      </c>
-      <c r="AK14">
-        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O50">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P50">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="Q50">
+        <v>3.62</v>
+      </c>
+      <c r="R50">
+        <v>2.05</v>
+      </c>
+      <c r="S50">
+        <v>1.38</v>
+      </c>
+      <c r="T50">
+        <v>2.81</v>
+      </c>
+      <c r="U50">
         <v>3</v>
       </c>
-      <c r="R50">
-        <v>2.13</v>
-      </c>
-      <c r="S50">
-        <v>1.34</v>
-      </c>
-      <c r="T50">
+      <c r="V50">
+        <v>1.33</v>
+      </c>
+      <c r="W50">
+        <v>1.04</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+      <c r="Y50">
+        <v>1.36</v>
+      </c>
+      <c r="Z50">
         <v>2.99</v>
       </c>
-      <c r="U50">
-        <v>2.6</v>
-      </c>
-      <c r="V50">
-        <v>1.45</v>
-      </c>
-      <c r="W50">
-        <v>1.07</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.25</v>
-      </c>
-      <c r="Z50">
-        <v>3.85</v>
-      </c>
       <c r="AA50">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC50">
-        <v>2.9</v>
+        <v>3.62</v>
       </c>
       <c r="AD50">
+        <v>1.22</v>
+      </c>
+      <c r="AE50">
+        <v>1.05</v>
+      </c>
+      <c r="AF50">
+        <v>1.8</v>
+      </c>
+      <c r="AG50">
+        <v>1.9</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.53</v>
+      </c>
+      <c r="AK50">
         <v>1.4</v>
-      </c>
-      <c r="AE50">
-        <v>1.1</v>
-      </c>
-      <c r="AF50">
-        <v>1.57</v>
-      </c>
-      <c r="AG50">
-        <v>2.25</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.41</v>
-      </c>
-      <c r="AK50">
-        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
+        <v>2.45</v>
+      </c>
+      <c r="O51">
+        <v>3.35</v>
+      </c>
+      <c r="P51">
+        <v>2.43</v>
+      </c>
+      <c r="Q51">
+        <v>3</v>
+      </c>
+      <c r="R51">
+        <v>2.13</v>
+      </c>
+      <c r="S51">
+        <v>1.34</v>
+      </c>
+      <c r="T51">
+        <v>2.99</v>
+      </c>
+      <c r="U51">
+        <v>2.6</v>
+      </c>
+      <c r="V51">
+        <v>1.45</v>
+      </c>
+      <c r="W51">
+        <v>1.07</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
+        <v>1.25</v>
+      </c>
+      <c r="Z51">
+        <v>3.85</v>
+      </c>
+      <c r="AA51">
+        <v>1.73</v>
+      </c>
+      <c r="AB51">
+        <v>2</v>
+      </c>
+      <c r="AC51">
         <v>2.9</v>
       </c>
-      <c r="O51">
-        <v>3.25</v>
-      </c>
-      <c r="P51">
-        <v>2.28</v>
-      </c>
-      <c r="Q51">
-        <v>3.62</v>
-      </c>
-      <c r="R51">
-        <v>2.05</v>
-      </c>
-      <c r="S51">
-        <v>1.38</v>
-      </c>
-      <c r="T51">
-        <v>2.81</v>
-      </c>
-      <c r="U51">
-        <v>3</v>
-      </c>
-      <c r="V51">
-        <v>1.33</v>
-      </c>
-      <c r="W51">
-        <v>1.04</v>
-      </c>
-      <c r="X51">
-        <v>1</v>
-      </c>
-      <c r="Y51">
-        <v>1.36</v>
-      </c>
-      <c r="Z51">
-        <v>2.99</v>
-      </c>
-      <c r="AA51">
-        <v>2.08</v>
-      </c>
-      <c r="AB51">
-        <v>1.74</v>
-      </c>
-      <c r="AC51">
-        <v>3.62</v>
-      </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AK51">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.8</v>
+        <v>1.22</v>
       </c>
       <c r="O111">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="P111">
-        <v>1.63</v>
+        <v>10.5</v>
       </c>
       <c r="Q111">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="R111">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S111">
+        <v>1.17</v>
+      </c>
+      <c r="T111">
+        <v>4.8</v>
+      </c>
+      <c r="U111">
+        <v>1.93</v>
+      </c>
+      <c r="V111">
+        <v>1.88</v>
+      </c>
+      <c r="W111">
         <v>1.22</v>
       </c>
-      <c r="T111">
-        <v>4.05</v>
-      </c>
-      <c r="U111">
-        <v>2.13</v>
-      </c>
-      <c r="V111">
-        <v>1.74</v>
-      </c>
-      <c r="W111">
-        <v>1.2</v>
-      </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z111">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AA111">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB111">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AC111">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD111">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE111">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AF111">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AG111">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK111">
-        <v>1.22</v>
+        <v>4.08</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="O112">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="P112">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q112">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="R112">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="S112">
+        <v>1.25</v>
+      </c>
+      <c r="T112">
+        <v>4</v>
+      </c>
+      <c r="U112">
+        <v>2.19</v>
+      </c>
+      <c r="V112">
+        <v>1.7</v>
+      </c>
+      <c r="W112">
         <v>1.17</v>
       </c>
-      <c r="T112">
-        <v>4.8</v>
-      </c>
-      <c r="U112">
-        <v>1.93</v>
-      </c>
-      <c r="V112">
-        <v>1.88</v>
-      </c>
-      <c r="W112">
-        <v>1.22</v>
-      </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z112">
-        <v>8</v>
+        <v>4.95</v>
       </c>
       <c r="AA112">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB112">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AC112">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="AD112">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AE112">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AF112">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AG112">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK112">
-        <v>4.08</v>
+        <v>1.73</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.02</v>
+        <v>3.8</v>
       </c>
       <c r="O113">
+        <v>4.1</v>
+      </c>
+      <c r="P113">
+        <v>1.63</v>
+      </c>
+      <c r="Q113">
         <v>3.9</v>
       </c>
-      <c r="P113">
-        <v>3.4</v>
-      </c>
-      <c r="Q113">
+      <c r="R113">
         <v>2.5</v>
       </c>
-      <c r="R113">
-        <v>2.41</v>
-      </c>
       <c r="S113">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U113">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="V113">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W113">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X113">
         <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z113">
-        <v>4.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA113">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB113">
         <v>2.66</v>
       </c>
       <c r="AC113">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="AD113">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AE113">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF113">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG113">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AK113">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q134">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="R134">
         <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T134">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U134">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V134">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W134">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z134">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA134">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AB134">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AC134">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AD134">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE134">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF134">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG134">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK134">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q136">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="R136">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T136">
         <v>3</v>
       </c>
       <c r="U136">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="V136">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W136">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
         <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z136">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AA136">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB136">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC136">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AD136">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE136">
         <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG136">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="O137">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q137">
+        <v>3.55</v>
+      </c>
+      <c r="R137">
+        <v>2.25</v>
+      </c>
+      <c r="S137">
+        <v>1.35</v>
+      </c>
+      <c r="T137">
         <v>3</v>
       </c>
-      <c r="R137">
-        <v>2.1</v>
-      </c>
-      <c r="S137">
-        <v>1.4</v>
-      </c>
-      <c r="T137">
-        <v>2.8</v>
-      </c>
       <c r="U137">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V137">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z137">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="AA137">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB137">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC137">
-        <v>3.55</v>
+        <v>2.97</v>
       </c>
       <c r="AD137">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE137">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG137">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AK137">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.87</v>
+        <v>1.61</v>
       </c>
       <c r="O146">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P146">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q146">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="R146">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="S146">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T146">
-        <v>2.73</v>
+        <v>3.45</v>
       </c>
       <c r="U146">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="V146">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W146">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z146">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="AA146">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AB146">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AC146">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD146">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE146">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF146">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AG146">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK146">
-        <v>1.39</v>
+        <v>2.25</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,65 +24270,65 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.61</v>
+        <v>2.87</v>
       </c>
       <c r="O147">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P147">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q147">
+        <v>3.4</v>
+      </c>
+      <c r="R147">
+        <v>2.07</v>
+      </c>
+      <c r="S147">
+        <v>1.4</v>
+      </c>
+      <c r="T147">
+        <v>2.73</v>
+      </c>
+      <c r="U147">
+        <v>2.85</v>
+      </c>
+      <c r="V147">
+        <v>1.39</v>
+      </c>
+      <c r="W147">
+        <v>1.04</v>
+      </c>
+      <c r="X147">
+        <v>1.03</v>
+      </c>
+      <c r="Y147">
+        <v>1.32</v>
+      </c>
+      <c r="Z147">
+        <v>3</v>
+      </c>
+      <c r="AA147">
+        <v>1.93</v>
+      </c>
+      <c r="AB147">
+        <v>1.8</v>
+      </c>
+      <c r="AC147">
+        <v>3.4</v>
+      </c>
+      <c r="AD147">
+        <v>1.28</v>
+      </c>
+      <c r="AE147">
+        <v>1.06</v>
+      </c>
+      <c r="AF147">
+        <v>1.74</v>
+      </c>
+      <c r="AG147">
         <v>2</v>
       </c>
-      <c r="R147">
-        <v>2.36</v>
-      </c>
-      <c r="S147">
-        <v>1.25</v>
-      </c>
-      <c r="T147">
-        <v>3.45</v>
-      </c>
-      <c r="U147">
-        <v>2.2</v>
-      </c>
-      <c r="V147">
-        <v>1.52</v>
-      </c>
-      <c r="W147">
-        <v>1.11</v>
-      </c>
-      <c r="X147">
-        <v>1.01</v>
-      </c>
-      <c r="Y147">
-        <v>1.14</v>
-      </c>
-      <c r="Z147">
-        <v>4.45</v>
-      </c>
-      <c r="AA147">
-        <v>1.54</v>
-      </c>
-      <c r="AB147">
-        <v>2.37</v>
-      </c>
-      <c r="AC147">
-        <v>2.45</v>
-      </c>
-      <c r="AD147">
-        <v>1.57</v>
-      </c>
-      <c r="AE147">
-        <v>1.18</v>
-      </c>
-      <c r="AF147">
-        <v>1.6</v>
-      </c>
-      <c r="AG147">
-        <v>2.19</v>
-      </c>
       <c r="AH147" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK147">
-        <v>2.25</v>
+        <v>1.39</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="O148">
-        <v>3.68</v>
+        <v>3.38</v>
       </c>
       <c r="P148">
-        <v>3.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q148">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="R148">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="S148">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T148">
+        <v>2.77</v>
+      </c>
+      <c r="U148">
+        <v>2.55</v>
+      </c>
+      <c r="V148">
+        <v>1.39</v>
+      </c>
+      <c r="W148">
+        <v>1.06</v>
+      </c>
+      <c r="X148">
+        <v>1.03</v>
+      </c>
+      <c r="Y148">
+        <v>1.25</v>
+      </c>
+      <c r="Z148">
         <v>3.3</v>
       </c>
-      <c r="U148">
-        <v>2.35</v>
-      </c>
-      <c r="V148">
-        <v>1.5</v>
-      </c>
-      <c r="W148">
-        <v>1.12</v>
-      </c>
-      <c r="X148">
-        <v>1.01</v>
-      </c>
-      <c r="Y148">
-        <v>1.16</v>
-      </c>
-      <c r="Z148">
-        <v>3.8</v>
-      </c>
       <c r="AA148">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB148">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AC148">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="AD148">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AE148">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AF148">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AG148">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK148">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="O149">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P149">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="Q149">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="R149">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="S149">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T149">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U149">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="V149">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W149">
         <v>1.06</v>
       </c>
       <c r="X149">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y149">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z149">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AA149">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB149">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC149">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AD149">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE149">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF149">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG149">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK149">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O150">
+        <v>3.8</v>
+      </c>
+      <c r="P150">
+        <v>3.15</v>
+      </c>
+      <c r="Q150">
+        <v>2.45</v>
+      </c>
+      <c r="R150">
+        <v>2.48</v>
+      </c>
+      <c r="S150">
+        <v>1.25</v>
+      </c>
+      <c r="T150">
         <v>3.5</v>
       </c>
-      <c r="P150">
-        <v>3.75</v>
-      </c>
-      <c r="Q150">
-        <v>2.4</v>
-      </c>
-      <c r="R150">
-        <v>2.1</v>
-      </c>
-      <c r="S150">
-        <v>1.35</v>
-      </c>
-      <c r="T150">
-        <v>2.95</v>
-      </c>
       <c r="U150">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="V150">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W150">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X150">
         <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z150">
-        <v>3.3</v>
+        <v>4.79</v>
       </c>
       <c r="AA150">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="AB150">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AC150">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="AD150">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AE150">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF150">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG150">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK150">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="O151">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P151">
-        <v>2.35</v>
+        <v>3.75</v>
       </c>
       <c r="Q151">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="R151">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S151">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T151">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="U151">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="V151">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W151">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z151">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="AA151">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB151">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC151">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="AD151">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE151">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF151">
         <v>1.73</v>
       </c>
       <c r="AG151">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK151">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.53</v>
+        <v>2.98</v>
       </c>
       <c r="O152">
-        <v>4.2</v>
+        <v>3.51</v>
       </c>
       <c r="P152">
-        <v>4.3</v>
+        <v>1.97</v>
       </c>
       <c r="Q152">
-        <v>2.14</v>
+        <v>3.65</v>
       </c>
       <c r="R152">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T152">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U152">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="V152">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W152">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X152">
         <v>1.01</v>
       </c>
       <c r="Y152">
+        <v>1.18</v>
+      </c>
+      <c r="Z152">
+        <v>4.2</v>
+      </c>
+      <c r="AA152">
+        <v>1.65</v>
+      </c>
+      <c r="AB152">
+        <v>2.11</v>
+      </c>
+      <c r="AC152">
+        <v>2.57</v>
+      </c>
+      <c r="AD152">
+        <v>1.4</v>
+      </c>
+      <c r="AE152">
         <v>1.13</v>
       </c>
-      <c r="Z152">
-        <v>4.75</v>
-      </c>
-      <c r="AA152">
-        <v>1.55</v>
-      </c>
-      <c r="AB152">
-        <v>2.4</v>
-      </c>
-      <c r="AC152">
-        <v>2.35</v>
-      </c>
-      <c r="AD152">
+      <c r="AF152">
         <v>1.57</v>
       </c>
-      <c r="AE152">
-        <v>1.19</v>
-      </c>
-      <c r="AF152">
-        <v>1.55</v>
-      </c>
       <c r="AG152">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AK152">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O153">
+        <v>3.6</v>
+      </c>
+      <c r="P153">
+        <v>3.15</v>
+      </c>
+      <c r="Q153">
+        <v>2.4</v>
+      </c>
+      <c r="R153">
+        <v>2.3</v>
+      </c>
+      <c r="S153">
+        <v>1.29</v>
+      </c>
+      <c r="T153">
         <v>3.4</v>
       </c>
-      <c r="P153">
-        <v>4</v>
-      </c>
-      <c r="Q153">
-        <v>2.45</v>
-      </c>
-      <c r="R153">
-        <v>2.09</v>
-      </c>
-      <c r="S153">
-        <v>1.36</v>
-      </c>
-      <c r="T153">
-        <v>2.88</v>
-      </c>
       <c r="U153">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="V153">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W153">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X153">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z153">
-        <v>3.44</v>
+        <v>4.77</v>
       </c>
       <c r="AA153">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB153">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AC153">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="AD153">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AE153">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF153">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG153">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK153">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.98</v>
+        <v>1.8</v>
       </c>
       <c r="O154">
-        <v>3.51</v>
+        <v>3.68</v>
       </c>
       <c r="P154">
-        <v>1.97</v>
+        <v>3.38</v>
       </c>
       <c r="Q154">
-        <v>3.65</v>
+        <v>2.25</v>
       </c>
       <c r="R154">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S154">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T154">
         <v>3.3</v>
       </c>
       <c r="U154">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V154">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W154">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X154">
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z154">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA154">
         <v>1.65</v>
       </c>
       <c r="AB154">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC154">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="AD154">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE154">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF154">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG154">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK154">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="O155">
+        <v>4.2</v>
+      </c>
+      <c r="P155">
+        <v>4.3</v>
+      </c>
+      <c r="Q155">
+        <v>2.14</v>
+      </c>
+      <c r="R155">
+        <v>2.6</v>
+      </c>
+      <c r="S155">
+        <v>1.25</v>
+      </c>
+      <c r="T155">
         <v>3.6</v>
       </c>
-      <c r="P155">
-        <v>3.15</v>
-      </c>
-      <c r="Q155">
-        <v>2.4</v>
-      </c>
-      <c r="R155">
-        <v>2.3</v>
-      </c>
-      <c r="S155">
-        <v>1.29</v>
-      </c>
-      <c r="T155">
-        <v>3.4</v>
-      </c>
       <c r="U155">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V155">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W155">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z155">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="AA155">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB155">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AC155">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AD155">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE155">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF155">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG155">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK155">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O156">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P156">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="Q156">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="R156">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="S156">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T156">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="U156">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="V156">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="W156">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X156">
         <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z156">
-        <v>4.79</v>
+        <v>3.64</v>
       </c>
       <c r="AA156">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AB156">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC156">
-        <v>2.44</v>
+        <v>3.18</v>
       </c>
       <c r="AD156">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AE156">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF156">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G215">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O233">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="P233">
-        <v>3</v>
+        <v>1.99</v>
       </c>
       <c r="Q233">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R233">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="S233">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T233">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="U233">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="V233">
+        <v>1.48</v>
+      </c>
+      <c r="W233">
+        <v>1.08</v>
+      </c>
+      <c r="X233">
+        <v>1.01</v>
+      </c>
+      <c r="Y233">
+        <v>1.23</v>
+      </c>
+      <c r="Z233">
+        <v>4.13</v>
+      </c>
+      <c r="AA233">
+        <v>1.75</v>
+      </c>
+      <c r="AB233">
+        <v>2.05</v>
+      </c>
+      <c r="AC233">
+        <v>2.71</v>
+      </c>
+      <c r="AD233">
         <v>1.36</v>
       </c>
-      <c r="W233">
-        <v>1.05</v>
-      </c>
-      <c r="X233">
-        <v>1.03</v>
-      </c>
-      <c r="Y233">
-        <v>1.33</v>
-      </c>
-      <c r="Z233">
-        <v>2.85</v>
-      </c>
-      <c r="AA233">
-        <v>2.2</v>
-      </c>
-      <c r="AB233">
-        <v>1.73</v>
-      </c>
-      <c r="AC233">
-        <v>3.62</v>
-      </c>
-      <c r="AD233">
-        <v>1.21</v>
-      </c>
       <c r="AE233">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF233">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AG233">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK233">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,80 +38451,80 @@
         </is>
       </c>
       <c r="N234">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O234">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="P234">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="Q234">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R234">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="S234">
+        <v>1.42</v>
+      </c>
+      <c r="T234">
+        <v>2.66</v>
+      </c>
+      <c r="U234">
+        <v>2.91</v>
+      </c>
+      <c r="V234">
+        <v>1.36</v>
+      </c>
+      <c r="W234">
+        <v>1.05</v>
+      </c>
+      <c r="X234">
+        <v>1.03</v>
+      </c>
+      <c r="Y234">
         <v>1.33</v>
       </c>
-      <c r="T234">
-        <v>3.25</v>
-      </c>
-      <c r="U234">
-        <v>2.53</v>
-      </c>
-      <c r="V234">
-        <v>1.48</v>
-      </c>
-      <c r="W234">
-        <v>1.08</v>
-      </c>
-      <c r="X234">
-        <v>1.01</v>
-      </c>
-      <c r="Y234">
-        <v>1.23</v>
-      </c>
       <c r="Z234">
-        <v>4.13</v>
+        <v>2.85</v>
       </c>
       <c r="AA234">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB234">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AC234">
-        <v>2.71</v>
+        <v>3.62</v>
       </c>
       <c r="AD234">
+        <v>1.21</v>
+      </c>
+      <c r="AE234">
+        <v>1.04</v>
+      </c>
+      <c r="AF234">
+        <v>1.84</v>
+      </c>
+      <c r="AG234">
+        <v>1.86</v>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ234">
         <v>1.36</v>
       </c>
-      <c r="AE234">
-        <v>1.11</v>
-      </c>
-      <c r="AF234">
-        <v>1.62</v>
-      </c>
-      <c r="AG234">
-        <v>2.15</v>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ234">
-        <v>1.26</v>
-      </c>
       <c r="AK234">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O274">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="P274">
-        <v>2.77</v>
+        <v>2.44</v>
       </c>
       <c r="Q274">
         <v>3.1</v>
       </c>
       <c r="R274">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S274">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T274">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="U274">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="V274">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W274">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X274">
         <v>1.04</v>
       </c>
       <c r="Y274">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z274">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA274">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB274">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC274">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD274">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AE274">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF274">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AG274">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AK274">
         <v>1.52</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="O275">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="P275">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="Q275">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="R275">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S275">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="T275">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="U275">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="V275">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W275">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X275">
         <v>1.04</v>
       </c>
       <c r="Y275">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z275">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AA275">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB275">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC275">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD275">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE275">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF275">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AG275">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK275">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="O276">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="P276">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="Q276">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="R276">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S276">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="T276">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="U276">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="V276">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W276">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X276">
         <v>1.04</v>
       </c>
       <c r="Y276">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z276">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA276">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB276">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC276">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD276">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE276">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF276">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG276">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK276">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O308">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="P308">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="Q308">
-        <v>4.97</v>
+        <v>4.26</v>
       </c>
       <c r="R308">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S308">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T308">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U308">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="V308">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W308">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X308">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y308">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z308">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AA308">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AB308">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC308">
-        <v>2.69</v>
+        <v>3.14</v>
       </c>
       <c r="AD308">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE308">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF308">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG308">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK308">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
+        <v>4.2</v>
+      </c>
+      <c r="O309">
+        <v>3.95</v>
+      </c>
+      <c r="P309">
+        <v>1.57</v>
+      </c>
+      <c r="Q309">
+        <v>4.97</v>
+      </c>
+      <c r="R309">
+        <v>2.39</v>
+      </c>
+      <c r="S309">
+        <v>1.29</v>
+      </c>
+      <c r="T309">
         <v>3.25</v>
       </c>
-      <c r="O309">
-        <v>3.25</v>
-      </c>
-      <c r="P309">
-        <v>1.98</v>
-      </c>
-      <c r="Q309">
-        <v>4.26</v>
-      </c>
-      <c r="R309">
-        <v>2.1</v>
-      </c>
-      <c r="S309">
-        <v>1.36</v>
-      </c>
-      <c r="T309">
-        <v>2.88</v>
-      </c>
       <c r="U309">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="V309">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W309">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X309">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y309">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z309">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AA309">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB309">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC309">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="AD309">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE309">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF309">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG309">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK309">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.36</v>
+        <v>1.96</v>
       </c>
       <c r="O322">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="P322">
-        <v>7.35</v>
+        <v>3.85</v>
       </c>
       <c r="Q322">
-        <v>1.86</v>
+        <v>2.68</v>
       </c>
       <c r="R322">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="S322">
+        <v>1.48</v>
+      </c>
+      <c r="T322">
+        <v>2.45</v>
+      </c>
+      <c r="U322">
+        <v>3</v>
+      </c>
+      <c r="V322">
         <v>1.28</v>
       </c>
-      <c r="T322">
-        <v>3.16</v>
-      </c>
-      <c r="U322">
-        <v>2.42</v>
-      </c>
-      <c r="V322">
-        <v>1.47</v>
-      </c>
       <c r="W322">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X322">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y322">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z322">
-        <v>3.79</v>
+        <v>2.66</v>
       </c>
       <c r="AA322">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AB322">
-        <v>2.01</v>
+        <v>1.58</v>
       </c>
       <c r="AC322">
-        <v>2.82</v>
+        <v>4.24</v>
       </c>
       <c r="AD322">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AE322">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF322">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AG322">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AK322">
-        <v>2.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.96</v>
+        <v>4.15</v>
       </c>
       <c r="O323">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P323">
-        <v>3.85</v>
+        <v>1.73</v>
       </c>
       <c r="Q323">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="R323">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="S323">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="T323">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U323">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="V323">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W323">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X323">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y323">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z323">
-        <v>2.66</v>
+        <v>3.52</v>
       </c>
       <c r="AA323">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="AB323">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AC323">
-        <v>4.24</v>
+        <v>2.91</v>
       </c>
       <c r="AD323">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AE323">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF323">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AG323">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK323">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>4.15</v>
+        <v>1.46</v>
       </c>
       <c r="O324">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P324">
-        <v>1.73</v>
+        <v>6.15</v>
       </c>
       <c r="Q324">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="R324">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="S324">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T324">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U324">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V324">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W324">
         <v>1.08</v>
       </c>
       <c r="X324">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y324">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z324">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AA324">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AB324">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AC324">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="AD324">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE324">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF324">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AG324">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK324">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,80 +53284,80 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="O325">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P325">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="Q325">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R325">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S325">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T325">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U325">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="V325">
+        <v>1.3</v>
+      </c>
+      <c r="W325">
+        <v>1.03</v>
+      </c>
+      <c r="X325">
+        <v>1.03</v>
+      </c>
+      <c r="Y325">
         <v>1.4</v>
       </c>
-      <c r="W325">
-        <v>1.08</v>
-      </c>
-      <c r="X325">
-        <v>1</v>
-      </c>
-      <c r="Y325">
-        <v>1.31</v>
-      </c>
       <c r="Z325">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="AA325">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AB325">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC325">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="AD325">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE325">
+        <v>1.02</v>
+      </c>
+      <c r="AF325">
+        <v>2.1</v>
+      </c>
+      <c r="AG325">
+        <v>1.62</v>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ325">
         <v>1.1</v>
       </c>
-      <c r="AF325">
-        <v>2.03</v>
-      </c>
-      <c r="AG325">
-        <v>1.69</v>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI325" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ325">
-        <v>1.22</v>
-      </c>
       <c r="AK325">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,65 +53447,65 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.59</v>
+        <v>3.65</v>
       </c>
       <c r="O326">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P326">
-        <v>6</v>
+        <v>2.02</v>
       </c>
       <c r="Q326">
-        <v>2.1</v>
+        <v>4.55</v>
       </c>
       <c r="R326">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S326">
         <v>1.45</v>
       </c>
       <c r="T326">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="U326">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="V326">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W326">
         <v>1.03</v>
       </c>
       <c r="X326">
+        <v>1.04</v>
+      </c>
+      <c r="Y326">
+        <v>1.38</v>
+      </c>
+      <c r="Z326">
+        <v>2.85</v>
+      </c>
+      <c r="AA326">
+        <v>2.23</v>
+      </c>
+      <c r="AB326">
+        <v>1.57</v>
+      </c>
+      <c r="AC326">
+        <v>4</v>
+      </c>
+      <c r="AD326">
+        <v>1.19</v>
+      </c>
+      <c r="AE326">
         <v>1.03</v>
       </c>
-      <c r="Y326">
-        <v>1.4</v>
-      </c>
-      <c r="Z326">
-        <v>2.84</v>
-      </c>
-      <c r="AA326">
-        <v>2.08</v>
-      </c>
-      <c r="AB326">
+      <c r="AF326">
+        <v>1.94</v>
+      </c>
+      <c r="AG326">
         <v>1.75</v>
       </c>
-      <c r="AC326">
-        <v>3.86</v>
-      </c>
-      <c r="AD326">
-        <v>1.2</v>
-      </c>
-      <c r="AE326">
-        <v>1.02</v>
-      </c>
-      <c r="AF326">
-        <v>2.1</v>
-      </c>
-      <c r="AG326">
-        <v>1.62</v>
-      </c>
       <c r="AH326" t="inlineStr">
         <is>
           <t>[]</t>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AK326">
-        <v>2.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="O327">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P327">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="Q327">
-        <v>4.55</v>
+        <v>3.51</v>
       </c>
       <c r="R327">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S327">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T327">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U327">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="V327">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W327">
         <v>1.03</v>
       </c>
       <c r="X327">
+        <v>1.08</v>
+      </c>
+      <c r="Y327">
+        <v>1.4</v>
+      </c>
+      <c r="Z327">
+        <v>2.65</v>
+      </c>
+      <c r="AA327">
+        <v>2.4</v>
+      </c>
+      <c r="AB327">
+        <v>1.6</v>
+      </c>
+      <c r="AC327">
+        <v>4.22</v>
+      </c>
+      <c r="AD327">
+        <v>1.2</v>
+      </c>
+      <c r="AE327">
         <v>1.04</v>
       </c>
-      <c r="Y327">
-        <v>1.38</v>
-      </c>
-      <c r="Z327">
-        <v>2.85</v>
-      </c>
-      <c r="AA327">
-        <v>2.23</v>
-      </c>
-      <c r="AB327">
-        <v>1.57</v>
-      </c>
-      <c r="AC327">
-        <v>4</v>
-      </c>
-      <c r="AD327">
-        <v>1.19</v>
-      </c>
-      <c r="AE327">
-        <v>1.03</v>
-      </c>
       <c r="AF327">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG327">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK327">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="O328">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="P328">
-        <v>2.55</v>
+        <v>7.35</v>
       </c>
       <c r="Q328">
-        <v>3.51</v>
+        <v>1.86</v>
       </c>
       <c r="R328">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="S328">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="T328">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="U328">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="V328">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="W328">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X328">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y328">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z328">
-        <v>2.65</v>
+        <v>3.79</v>
       </c>
       <c r="AA328">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB328">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="AC328">
-        <v>4.22</v>
+        <v>2.82</v>
       </c>
       <c r="AD328">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE328">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF328">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AG328">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK328">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="AL328">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="O7">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q13">
-        <v>2.67</v>
+        <v>3.85</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T13">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
+        <v>1.41</v>
+      </c>
+      <c r="Z13">
+        <v>2.79</v>
+      </c>
+      <c r="AA13">
+        <v>2.35</v>
+      </c>
+      <c r="AB13">
+        <v>1.57</v>
+      </c>
+      <c r="AC13">
+        <v>4.1</v>
+      </c>
+      <c r="AD13">
+        <v>1.2</v>
+      </c>
+      <c r="AE13">
+        <v>1.01</v>
+      </c>
+      <c r="AF13">
+        <v>1.91</v>
+      </c>
+      <c r="AG13">
+        <v>1.76</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.27</v>
+      </c>
+      <c r="AK13">
         <v>1.25</v>
-      </c>
-      <c r="Z13">
-        <v>3.72</v>
-      </c>
-      <c r="AA13">
-        <v>1.81</v>
-      </c>
-      <c r="AB13">
-        <v>2</v>
-      </c>
-      <c r="AC13">
-        <v>2.95</v>
-      </c>
-      <c r="AD13">
-        <v>1.36</v>
-      </c>
-      <c r="AE13">
-        <v>1.11</v>
-      </c>
-      <c r="AF13">
-        <v>1.62</v>
-      </c>
-      <c r="AG13">
-        <v>2.1</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.22</v>
-      </c>
-      <c r="AK13">
-        <v>1.62</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.85</v>
+        <v>2.67</v>
       </c>
       <c r="R14">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>2.6</v>
+        <v>2.91</v>
       </c>
       <c r="U14">
+        <v>2.5</v>
+      </c>
+      <c r="V14">
+        <v>1.44</v>
+      </c>
+      <c r="W14">
+        <v>1.11</v>
+      </c>
+      <c r="X14">
+        <v>1.04</v>
+      </c>
+      <c r="Y14">
+        <v>1.25</v>
+      </c>
+      <c r="Z14">
+        <v>3.72</v>
+      </c>
+      <c r="AA14">
+        <v>1.81</v>
+      </c>
+      <c r="AB14">
+        <v>2</v>
+      </c>
+      <c r="AC14">
         <v>2.95</v>
       </c>
-      <c r="V14">
-        <v>1.31</v>
-      </c>
-      <c r="W14">
-        <v>1.06</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.41</v>
-      </c>
-      <c r="Z14">
-        <v>2.79</v>
-      </c>
-      <c r="AA14">
-        <v>2.35</v>
-      </c>
-      <c r="AB14">
-        <v>1.57</v>
-      </c>
-      <c r="AC14">
-        <v>4.1</v>
-      </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
+        <v>2.45</v>
+      </c>
+      <c r="O50">
+        <v>3.35</v>
+      </c>
+      <c r="P50">
+        <v>2.43</v>
+      </c>
+      <c r="Q50">
+        <v>3</v>
+      </c>
+      <c r="R50">
+        <v>2.13</v>
+      </c>
+      <c r="S50">
+        <v>1.34</v>
+      </c>
+      <c r="T50">
+        <v>2.99</v>
+      </c>
+      <c r="U50">
+        <v>2.6</v>
+      </c>
+      <c r="V50">
+        <v>1.45</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1.01</v>
+      </c>
+      <c r="Y50">
+        <v>1.25</v>
+      </c>
+      <c r="Z50">
+        <v>3.85</v>
+      </c>
+      <c r="AA50">
+        <v>1.73</v>
+      </c>
+      <c r="AB50">
+        <v>2</v>
+      </c>
+      <c r="AC50">
         <v>2.9</v>
       </c>
-      <c r="O50">
-        <v>3.25</v>
-      </c>
-      <c r="P50">
-        <v>2.28</v>
-      </c>
-      <c r="Q50">
-        <v>3.62</v>
-      </c>
-      <c r="R50">
-        <v>2.05</v>
-      </c>
-      <c r="S50">
-        <v>1.38</v>
-      </c>
-      <c r="T50">
-        <v>2.81</v>
-      </c>
-      <c r="U50">
-        <v>3</v>
-      </c>
-      <c r="V50">
-        <v>1.33</v>
-      </c>
-      <c r="W50">
-        <v>1.04</v>
-      </c>
-      <c r="X50">
-        <v>1</v>
-      </c>
-      <c r="Y50">
-        <v>1.36</v>
-      </c>
-      <c r="Z50">
-        <v>2.99</v>
-      </c>
-      <c r="AA50">
-        <v>2.08</v>
-      </c>
-      <c r="AB50">
-        <v>1.74</v>
-      </c>
-      <c r="AC50">
-        <v>3.62</v>
-      </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="Q51">
+        <v>3.62</v>
+      </c>
+      <c r="R51">
+        <v>2.05</v>
+      </c>
+      <c r="S51">
+        <v>1.38</v>
+      </c>
+      <c r="T51">
+        <v>2.81</v>
+      </c>
+      <c r="U51">
         <v>3</v>
       </c>
-      <c r="R51">
-        <v>2.13</v>
-      </c>
-      <c r="S51">
-        <v>1.34</v>
-      </c>
-      <c r="T51">
+      <c r="V51">
+        <v>1.33</v>
+      </c>
+      <c r="W51">
+        <v>1.04</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51">
+        <v>1.36</v>
+      </c>
+      <c r="Z51">
         <v>2.99</v>
       </c>
-      <c r="U51">
-        <v>2.6</v>
-      </c>
-      <c r="V51">
-        <v>1.45</v>
-      </c>
-      <c r="W51">
-        <v>1.07</v>
-      </c>
-      <c r="X51">
-        <v>1.01</v>
-      </c>
-      <c r="Y51">
-        <v>1.25</v>
-      </c>
-      <c r="Z51">
-        <v>3.85</v>
-      </c>
       <c r="AA51">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC51">
-        <v>2.9</v>
+        <v>3.62</v>
       </c>
       <c r="AD51">
+        <v>1.22</v>
+      </c>
+      <c r="AE51">
+        <v>1.05</v>
+      </c>
+      <c r="AF51">
+        <v>1.8</v>
+      </c>
+      <c r="AG51">
+        <v>1.9</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.53</v>
+      </c>
+      <c r="AK51">
         <v>1.4</v>
-      </c>
-      <c r="AE51">
-        <v>1.1</v>
-      </c>
-      <c r="AF51">
-        <v>1.57</v>
-      </c>
-      <c r="AG51">
-        <v>2.25</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.41</v>
-      </c>
-      <c r="AK51">
-        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11559,13 +11559,13 @@
         <v>3.6</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
         <v>1.82</v>
       </c>
       <c r="Q69">
-        <v>4.58</v>
+        <v>4</v>
       </c>
       <c r="R69">
         <v>2.1</v>
@@ -11574,37 +11574,37 @@
         <v>1.36</v>
       </c>
       <c r="T69">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="U69">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="V69">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z69">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA69">
+        <v>1.92</v>
+      </c>
+      <c r="AB69">
         <v>1.87</v>
       </c>
-      <c r="AB69">
-        <v>1.82</v>
-      </c>
       <c r="AC69">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="AD69">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE69">
         <v>1.06</v>
@@ -11613,7 +11613,7 @@
         <v>1.74</v>
       </c>
       <c r="AG69">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.24</v>
       </c>
       <c r="AK69">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
+        <v>3.8</v>
+      </c>
+      <c r="O111">
+        <v>4.1</v>
+      </c>
+      <c r="P111">
+        <v>1.63</v>
+      </c>
+      <c r="Q111">
+        <v>3.9</v>
+      </c>
+      <c r="R111">
+        <v>2.5</v>
+      </c>
+      <c r="S111">
         <v>1.22</v>
       </c>
-      <c r="O111">
-        <v>6.5</v>
-      </c>
-      <c r="P111">
-        <v>10.5</v>
-      </c>
-      <c r="Q111">
-        <v>1.55</v>
-      </c>
-      <c r="R111">
-        <v>3</v>
-      </c>
-      <c r="S111">
-        <v>1.17</v>
-      </c>
       <c r="T111">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="U111">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="V111">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="W111">
+        <v>1.2</v>
+      </c>
+      <c r="X111">
+        <v>1.02</v>
+      </c>
+      <c r="Y111">
+        <v>1.07</v>
+      </c>
+      <c r="Z111">
+        <v>5.8</v>
+      </c>
+      <c r="AA111">
+        <v>1.36</v>
+      </c>
+      <c r="AB111">
+        <v>2.66</v>
+      </c>
+      <c r="AC111">
+        <v>2</v>
+      </c>
+      <c r="AD111">
+        <v>1.79</v>
+      </c>
+      <c r="AE111">
+        <v>1.27</v>
+      </c>
+      <c r="AF111">
+        <v>1.45</v>
+      </c>
+      <c r="AG111">
+        <v>2.62</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>2.1</v>
+      </c>
+      <c r="AK111">
         <v>1.22</v>
-      </c>
-      <c r="X111">
-        <v>1.01</v>
-      </c>
-      <c r="Y111">
-        <v>1.06</v>
-      </c>
-      <c r="Z111">
-        <v>8</v>
-      </c>
-      <c r="AA111">
-        <v>1.3</v>
-      </c>
-      <c r="AB111">
-        <v>3.14</v>
-      </c>
-      <c r="AC111">
-        <v>1.92</v>
-      </c>
-      <c r="AD111">
-        <v>1.85</v>
-      </c>
-      <c r="AE111">
-        <v>1.34</v>
-      </c>
-      <c r="AF111">
-        <v>1.78</v>
-      </c>
-      <c r="AG111">
-        <v>1.95</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>1.12</v>
-      </c>
-      <c r="AK111">
-        <v>4.08</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.8</v>
+        <v>1.22</v>
       </c>
       <c r="O113">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="P113">
-        <v>1.63</v>
+        <v>10.5</v>
       </c>
       <c r="Q113">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="R113">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S113">
+        <v>1.17</v>
+      </c>
+      <c r="T113">
+        <v>4.8</v>
+      </c>
+      <c r="U113">
+        <v>1.93</v>
+      </c>
+      <c r="V113">
+        <v>1.88</v>
+      </c>
+      <c r="W113">
         <v>1.22</v>
       </c>
-      <c r="T113">
-        <v>4.05</v>
-      </c>
-      <c r="U113">
-        <v>2.13</v>
-      </c>
-      <c r="V113">
-        <v>1.74</v>
-      </c>
-      <c r="W113">
-        <v>1.2</v>
-      </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z113">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AA113">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB113">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AC113">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD113">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE113">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AF113">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AG113">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK113">
-        <v>1.22</v>
+        <v>4.08</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
+        <v>1.6</v>
+      </c>
+      <c r="O132">
+        <v>4.33</v>
+      </c>
+      <c r="P132">
+        <v>5</v>
+      </c>
+      <c r="Q132">
+        <v>2</v>
+      </c>
+      <c r="R132">
+        <v>2.3</v>
+      </c>
+      <c r="S132">
+        <v>1.26</v>
+      </c>
+      <c r="T132">
+        <v>3.44</v>
+      </c>
+      <c r="U132">
         <v>2.23</v>
       </c>
-      <c r="O132">
-        <v>3.5</v>
-      </c>
-      <c r="P132">
-        <v>2.87</v>
-      </c>
-      <c r="Q132">
-        <v>3</v>
-      </c>
-      <c r="R132">
-        <v>2.06</v>
-      </c>
-      <c r="S132">
-        <v>1.39</v>
-      </c>
-      <c r="T132">
-        <v>2.7</v>
-      </c>
-      <c r="U132">
-        <v>2.69</v>
-      </c>
       <c r="V132">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W132">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X132">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z132">
-        <v>3.34</v>
+        <v>4.42</v>
       </c>
       <c r="AA132">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AB132">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AC132">
-        <v>3.08</v>
+        <v>2.43</v>
       </c>
       <c r="AD132">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AE132">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF132">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG132">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AK132">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,65 +21988,65 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.6</v>
+        <v>2.62</v>
       </c>
       <c r="O133">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="Q133">
+        <v>3</v>
+      </c>
+      <c r="R133">
+        <v>2.1</v>
+      </c>
+      <c r="S133">
+        <v>1.4</v>
+      </c>
+      <c r="T133">
+        <v>2.8</v>
+      </c>
+      <c r="U133">
+        <v>2.88</v>
+      </c>
+      <c r="V133">
+        <v>1.35</v>
+      </c>
+      <c r="W133">
+        <v>1.08</v>
+      </c>
+      <c r="X133">
+        <v>1.01</v>
+      </c>
+      <c r="Y133">
+        <v>1.33</v>
+      </c>
+      <c r="Z133">
+        <v>3.25</v>
+      </c>
+      <c r="AA133">
+        <v>2.03</v>
+      </c>
+      <c r="AB133">
+        <v>1.8</v>
+      </c>
+      <c r="AC133">
+        <v>3.55</v>
+      </c>
+      <c r="AD133">
+        <v>1.28</v>
+      </c>
+      <c r="AE133">
+        <v>1.04</v>
+      </c>
+      <c r="AF133">
+        <v>1.75</v>
+      </c>
+      <c r="AG133">
         <v>2</v>
       </c>
-      <c r="R133">
-        <v>2.3</v>
-      </c>
-      <c r="S133">
-        <v>1.26</v>
-      </c>
-      <c r="T133">
-        <v>3.44</v>
-      </c>
-      <c r="U133">
-        <v>2.23</v>
-      </c>
-      <c r="V133">
-        <v>1.57</v>
-      </c>
-      <c r="W133">
-        <v>1.12</v>
-      </c>
-      <c r="X133">
-        <v>1.02</v>
-      </c>
-      <c r="Y133">
-        <v>1.19</v>
-      </c>
-      <c r="Z133">
-        <v>4.42</v>
-      </c>
-      <c r="AA133">
-        <v>1.6</v>
-      </c>
-      <c r="AB133">
-        <v>2.2</v>
-      </c>
-      <c r="AC133">
-        <v>2.43</v>
-      </c>
-      <c r="AD133">
-        <v>1.45</v>
-      </c>
-      <c r="AE133">
-        <v>1.15</v>
-      </c>
-      <c r="AF133">
-        <v>1.66</v>
-      </c>
-      <c r="AG133">
-        <v>2.09</v>
-      </c>
       <c r="AH133" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK133">
-        <v>2.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
+        <v>2.1</v>
+      </c>
+      <c r="O134">
+        <v>3.5</v>
+      </c>
+      <c r="P134">
+        <v>3.2</v>
+      </c>
+      <c r="Q134">
         <v>2.62</v>
-      </c>
-      <c r="O134">
-        <v>3.4</v>
-      </c>
-      <c r="P134">
-        <v>2.6</v>
-      </c>
-      <c r="Q134">
-        <v>3</v>
       </c>
       <c r="R134">
         <v>2.1</v>
       </c>
       <c r="S134">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T134">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U134">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V134">
+        <v>1.42</v>
+      </c>
+      <c r="W134">
+        <v>1.07</v>
+      </c>
+      <c r="X134">
+        <v>1</v>
+      </c>
+      <c r="Y134">
+        <v>1.22</v>
+      </c>
+      <c r="Z134">
+        <v>3.6</v>
+      </c>
+      <c r="AA134">
+        <v>1.83</v>
+      </c>
+      <c r="AB134">
+        <v>1.93</v>
+      </c>
+      <c r="AC134">
+        <v>3</v>
+      </c>
+      <c r="AD134">
         <v>1.35</v>
       </c>
-      <c r="W134">
-        <v>1.08</v>
-      </c>
-      <c r="X134">
-        <v>1.01</v>
-      </c>
-      <c r="Y134">
-        <v>1.33</v>
-      </c>
-      <c r="Z134">
-        <v>3.25</v>
-      </c>
-      <c r="AA134">
-        <v>2.03</v>
-      </c>
-      <c r="AB134">
-        <v>1.8</v>
-      </c>
-      <c r="AC134">
-        <v>3.55</v>
-      </c>
-      <c r="AD134">
-        <v>1.28</v>
-      </c>
       <c r="AE134">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF134">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG134">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK134">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q136">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="R136">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S136">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T136">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U136">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V136">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X136">
         <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z136">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA136">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB136">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC136">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AD136">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF136">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK136">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="O145">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="P145">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q145">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="R145">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="S145">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T145">
-        <v>2.47</v>
+        <v>3.45</v>
       </c>
       <c r="U145">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="V145">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="W145">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X145">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y145">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z145">
-        <v>2.95</v>
+        <v>4.45</v>
       </c>
       <c r="AA145">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="AB145">
-        <v>1.63</v>
+        <v>2.37</v>
       </c>
       <c r="AC145">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="AD145">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AE145">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF145">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O146">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="P146">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="Q146">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="R146">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="S146">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T146">
-        <v>3.45</v>
+        <v>2.47</v>
       </c>
       <c r="U146">
+        <v>3.1</v>
+      </c>
+      <c r="V146">
+        <v>1.32</v>
+      </c>
+      <c r="W146">
+        <v>1.03</v>
+      </c>
+      <c r="X146">
+        <v>1.08</v>
+      </c>
+      <c r="Y146">
+        <v>1.36</v>
+      </c>
+      <c r="Z146">
+        <v>2.95</v>
+      </c>
+      <c r="AA146">
         <v>2.2</v>
       </c>
-      <c r="V146">
-        <v>1.52</v>
-      </c>
-      <c r="W146">
-        <v>1.11</v>
-      </c>
-      <c r="X146">
-        <v>1.01</v>
-      </c>
-      <c r="Y146">
-        <v>1.14</v>
-      </c>
-      <c r="Z146">
-        <v>4.45</v>
-      </c>
-      <c r="AA146">
-        <v>1.54</v>
-      </c>
       <c r="AB146">
-        <v>2.37</v>
+        <v>1.63</v>
       </c>
       <c r="AC146">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="AD146">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AE146">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF146">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AG146">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK146">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,34 +24759,34 @@
         </is>
       </c>
       <c r="N150">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="O150">
-        <v>3.8</v>
+        <v>3.51</v>
       </c>
       <c r="P150">
-        <v>3.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q150">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="R150">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="S150">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T150">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U150">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="V150">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W150">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X150">
         <v>1.01</v>
@@ -24795,28 +24795,28 @@
         <v>1.18</v>
       </c>
       <c r="Z150">
-        <v>4.79</v>
+        <v>4.2</v>
       </c>
       <c r="AA150">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AB150">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AC150">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="AD150">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AE150">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF150">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG150">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="AK150">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="O151">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P151">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="Q151">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R151">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S151">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T151">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U151">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="V151">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W151">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X151">
         <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z151">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA151">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB151">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AC151">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="AD151">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE151">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF151">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="AG151">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.98</v>
+        <v>1.53</v>
       </c>
       <c r="O152">
-        <v>3.51</v>
+        <v>4.2</v>
       </c>
       <c r="P152">
-        <v>1.97</v>
+        <v>4.3</v>
       </c>
       <c r="Q152">
-        <v>3.65</v>
+        <v>2.14</v>
       </c>
       <c r="R152">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="S152">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T152">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U152">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="V152">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="W152">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X152">
         <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z152">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AA152">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB152">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="AC152">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="AD152">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE152">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF152">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG152">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AK152">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O154">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P154">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="Q154">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="R154">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S154">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T154">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U154">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="V154">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W154">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X154">
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>3.8</v>
+        <v>4.79</v>
       </c>
       <c r="AA154">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AB154">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC154">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="AD154">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE154">
         <v>1.18</v>
       </c>
       <c r="AF154">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AG154">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK154">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="O155">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P155">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q155">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="R155">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S155">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T155">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="U155">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="V155">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W155">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z155">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA155">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AB155">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="AC155">
-        <v>2.35</v>
+        <v>2.99</v>
       </c>
       <c r="AD155">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AE155">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AF155">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG155">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK155">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="O206">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P206">
-        <v>3</v>
+        <v>4.01</v>
       </c>
       <c r="Q206">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="R206">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S206">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T206">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U206">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V206">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W206">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X206">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z206">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="AA206">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB206">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AC206">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AD206">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AE206">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF206">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG206">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK206">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,80 +34050,80 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="O207">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P207">
-        <v>4.01</v>
+        <v>3</v>
       </c>
       <c r="Q207">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="R207">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S207">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T207">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="U207">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V207">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W207">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X207">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z207">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="AA207">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB207">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AC207">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AD207">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AE207">
+        <v>1.29</v>
+      </c>
+      <c r="AF207">
+        <v>1.36</v>
+      </c>
+      <c r="AG207">
+        <v>3</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
         <v>1.25</v>
       </c>
-      <c r="AF207">
-        <v>1.45</v>
-      </c>
-      <c r="AG207">
-        <v>2.5</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.22</v>
-      </c>
       <c r="AK207">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,64 +52632,64 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="O321">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P321">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="Q321">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="R321">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S321">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T321">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U321">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V321">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W321">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X321">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y321">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z321">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AA321">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AB321">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC321">
-        <v>4.1</v>
+        <v>4.24</v>
       </c>
       <c r="AD321">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE321">
         <v>1.01</v>
       </c>
       <c r="AF321">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG321">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK321">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.96</v>
+        <v>4.15</v>
       </c>
       <c r="O322">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P322">
-        <v>3.85</v>
+        <v>1.73</v>
       </c>
       <c r="Q322">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="R322">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="S322">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="T322">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U322">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="V322">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W322">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X322">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y322">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z322">
-        <v>2.66</v>
+        <v>3.52</v>
       </c>
       <c r="AA322">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="AB322">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AC322">
-        <v>4.24</v>
+        <v>2.91</v>
       </c>
       <c r="AD322">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AE322">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF322">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="AG322">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK322">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>4.15</v>
+        <v>1.46</v>
       </c>
       <c r="O323">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P323">
-        <v>1.73</v>
+        <v>6.15</v>
       </c>
       <c r="Q323">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="R323">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="S323">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T323">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U323">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V323">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W323">
         <v>1.08</v>
       </c>
       <c r="X323">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y323">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z323">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AA323">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AB323">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AC323">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="AD323">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE323">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF323">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AG323">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK323">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,80 +53121,80 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="O324">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P324">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="Q324">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R324">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S324">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T324">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U324">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="V324">
+        <v>1.3</v>
+      </c>
+      <c r="W324">
+        <v>1.03</v>
+      </c>
+      <c r="X324">
+        <v>1.03</v>
+      </c>
+      <c r="Y324">
         <v>1.4</v>
       </c>
-      <c r="W324">
-        <v>1.08</v>
-      </c>
-      <c r="X324">
-        <v>1</v>
-      </c>
-      <c r="Y324">
-        <v>1.31</v>
-      </c>
       <c r="Z324">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="AA324">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="AB324">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC324">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="AD324">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE324">
+        <v>1.02</v>
+      </c>
+      <c r="AF324">
+        <v>2.1</v>
+      </c>
+      <c r="AG324">
+        <v>1.62</v>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ324">
         <v>1.1</v>
       </c>
-      <c r="AF324">
-        <v>2.03</v>
-      </c>
-      <c r="AG324">
-        <v>1.69</v>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI324" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ324">
-        <v>1.22</v>
-      </c>
       <c r="AK324">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,65 +53284,65 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.59</v>
+        <v>3.65</v>
       </c>
       <c r="O325">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P325">
-        <v>6</v>
+        <v>2.02</v>
       </c>
       <c r="Q325">
-        <v>2.1</v>
+        <v>4.55</v>
       </c>
       <c r="R325">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S325">
         <v>1.45</v>
       </c>
       <c r="T325">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="U325">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="V325">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W325">
         <v>1.03</v>
       </c>
       <c r="X325">
+        <v>1.04</v>
+      </c>
+      <c r="Y325">
+        <v>1.38</v>
+      </c>
+      <c r="Z325">
+        <v>2.85</v>
+      </c>
+      <c r="AA325">
+        <v>2.23</v>
+      </c>
+      <c r="AB325">
+        <v>1.57</v>
+      </c>
+      <c r="AC325">
+        <v>4</v>
+      </c>
+      <c r="AD325">
+        <v>1.19</v>
+      </c>
+      <c r="AE325">
         <v>1.03</v>
       </c>
-      <c r="Y325">
-        <v>1.4</v>
-      </c>
-      <c r="Z325">
-        <v>2.84</v>
-      </c>
-      <c r="AA325">
-        <v>2.08</v>
-      </c>
-      <c r="AB325">
+      <c r="AF325">
+        <v>1.94</v>
+      </c>
+      <c r="AG325">
         <v>1.75</v>
       </c>
-      <c r="AC325">
-        <v>3.86</v>
-      </c>
-      <c r="AD325">
-        <v>1.2</v>
-      </c>
-      <c r="AE325">
-        <v>1.02</v>
-      </c>
-      <c r="AF325">
-        <v>2.1</v>
-      </c>
-      <c r="AG325">
-        <v>1.62</v>
-      </c>
       <c r="AH325" t="inlineStr">
         <is>
           <t>[]</t>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AK325">
-        <v>2.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,64 +53447,64 @@
         </is>
       </c>
       <c r="N326">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="O326">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P326">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="Q326">
-        <v>4.55</v>
+        <v>3.51</v>
       </c>
       <c r="R326">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S326">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T326">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U326">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="V326">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W326">
         <v>1.03</v>
       </c>
       <c r="X326">
+        <v>1.08</v>
+      </c>
+      <c r="Y326">
+        <v>1.4</v>
+      </c>
+      <c r="Z326">
+        <v>2.65</v>
+      </c>
+      <c r="AA326">
+        <v>2.4</v>
+      </c>
+      <c r="AB326">
+        <v>1.6</v>
+      </c>
+      <c r="AC326">
+        <v>4.22</v>
+      </c>
+      <c r="AD326">
+        <v>1.2</v>
+      </c>
+      <c r="AE326">
         <v>1.04</v>
       </c>
-      <c r="Y326">
-        <v>1.38</v>
-      </c>
-      <c r="Z326">
-        <v>2.85</v>
-      </c>
-      <c r="AA326">
-        <v>2.23</v>
-      </c>
-      <c r="AB326">
-        <v>1.57</v>
-      </c>
-      <c r="AC326">
-        <v>4</v>
-      </c>
-      <c r="AD326">
-        <v>1.19</v>
-      </c>
-      <c r="AE326">
-        <v>1.03</v>
-      </c>
       <c r="AF326">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG326">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK326">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="O327">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="P327">
-        <v>2.55</v>
+        <v>7.35</v>
       </c>
       <c r="Q327">
-        <v>3.51</v>
+        <v>1.86</v>
       </c>
       <c r="R327">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="S327">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="T327">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="U327">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="V327">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="W327">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X327">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y327">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z327">
-        <v>2.65</v>
+        <v>3.79</v>
       </c>
       <c r="AA327">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB327">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="AC327">
-        <v>4.22</v>
+        <v>2.82</v>
       </c>
       <c r="AD327">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE327">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF327">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AG327">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK327">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
+        <v>1.77</v>
+      </c>
+      <c r="O328">
+        <v>3.3</v>
+      </c>
+      <c r="P328">
+        <v>4.45</v>
+      </c>
+      <c r="Q328">
+        <v>2.43</v>
+      </c>
+      <c r="R328">
+        <v>1.95</v>
+      </c>
+      <c r="S328">
+        <v>1.46</v>
+      </c>
+      <c r="T328">
+        <v>2.44</v>
+      </c>
+      <c r="U328">
+        <v>3.25</v>
+      </c>
+      <c r="V328">
+        <v>1.27</v>
+      </c>
+      <c r="W328">
+        <v>1.03</v>
+      </c>
+      <c r="X328">
+        <v>1.02</v>
+      </c>
+      <c r="Y328">
         <v>1.36</v>
       </c>
-      <c r="O328">
-        <v>4.35</v>
-      </c>
-      <c r="P328">
-        <v>7.35</v>
-      </c>
-      <c r="Q328">
-        <v>1.86</v>
-      </c>
-      <c r="R328">
-        <v>2.33</v>
-      </c>
-      <c r="S328">
-        <v>1.28</v>
-      </c>
-      <c r="T328">
-        <v>3.16</v>
-      </c>
-      <c r="U328">
-        <v>2.42</v>
-      </c>
-      <c r="V328">
-        <v>1.47</v>
-      </c>
-      <c r="W328">
-        <v>1.09</v>
-      </c>
-      <c r="X328">
-        <v>1.04</v>
-      </c>
-      <c r="Y328">
-        <v>1.21</v>
-      </c>
       <c r="Z328">
-        <v>3.79</v>
+        <v>2.77</v>
       </c>
       <c r="AA328">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AB328">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AC328">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD328">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AE328">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF328">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG328">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK328">
-        <v>2.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL328">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="O5">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="P5">
-        <v>2.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q5">
-        <v>3.41</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="T5">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="U5">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AB5">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC5">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AD5">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AE5">
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AG5">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,65 +1287,65 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.57</v>
+        <v>2.68</v>
       </c>
       <c r="O6">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>4.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>3.43</v>
       </c>
       <c r="R6">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.67</v>
+        <v>3.82</v>
       </c>
       <c r="AA6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB6">
+        <v>2.15</v>
+      </c>
+      <c r="AC6">
+        <v>2.6</v>
+      </c>
+      <c r="AD6">
+        <v>1.45</v>
+      </c>
+      <c r="AE6">
+        <v>1.16</v>
+      </c>
+      <c r="AF6">
+        <v>1.5</v>
+      </c>
+      <c r="AG6">
         <v>2.35</v>
       </c>
-      <c r="AC6">
-        <v>2.33</v>
-      </c>
-      <c r="AD6">
-        <v>1.49</v>
-      </c>
-      <c r="AE6">
-        <v>1.18</v>
-      </c>
-      <c r="AF6">
-        <v>1.6</v>
-      </c>
-      <c r="AG6">
-        <v>2.18</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AK6">
-        <v>2.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R21">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S21">
         <v>1.33</v>
@@ -3762,13 +3762,13 @@
         <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z21">
-        <v>3.51</v>
+        <v>3.46</v>
       </c>
       <c r="AA21">
         <v>1.9</v>
@@ -3777,13 +3777,13 @@
         <v>1.88</v>
       </c>
       <c r="AC21">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD21">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE21">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
         <v>1.7</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O22">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="P22">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q22">
-        <v>5.47</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>2.32</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V22">
         <v>1.43</v>
@@ -3928,19 +3928,19 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z22">
         <v>3.88</v>
       </c>
       <c r="AA22">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB22">
         <v>2.05</v>
       </c>
       <c r="AC22">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="AD22">
         <v>1.34</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>2.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5365,61 +5365,61 @@
         <v>2.19</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
+        <v>2.8</v>
+      </c>
+      <c r="Q31">
+        <v>2.41</v>
+      </c>
+      <c r="R31">
+        <v>2.1</v>
+      </c>
+      <c r="S31">
+        <v>1.35</v>
+      </c>
+      <c r="T31">
+        <v>3.13</v>
+      </c>
+      <c r="U31">
+        <v>2.7</v>
+      </c>
+      <c r="V31">
+        <v>1.44</v>
+      </c>
+      <c r="W31">
+        <v>1.07</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>1.25</v>
+      </c>
+      <c r="Z31">
+        <v>3.5</v>
+      </c>
+      <c r="AA31">
+        <v>1.77</v>
+      </c>
+      <c r="AB31">
+        <v>1.95</v>
+      </c>
+      <c r="AC31">
         <v>3</v>
       </c>
-      <c r="Q31">
-        <v>2.8</v>
-      </c>
-      <c r="R31">
-        <v>2.2</v>
-      </c>
-      <c r="S31">
-        <v>1.36</v>
-      </c>
-      <c r="T31">
-        <v>2.7</v>
-      </c>
-      <c r="U31">
-        <v>2.65</v>
-      </c>
-      <c r="V31">
-        <v>1.42</v>
-      </c>
-      <c r="W31">
-        <v>1.06</v>
-      </c>
-      <c r="X31">
-        <v>1.03</v>
-      </c>
-      <c r="Y31">
-        <v>1.29</v>
-      </c>
-      <c r="Z31">
-        <v>3.8</v>
-      </c>
-      <c r="AA31">
-        <v>1.91</v>
-      </c>
-      <c r="AB31">
-        <v>1.9</v>
-      </c>
-      <c r="AC31">
-        <v>3.13</v>
-      </c>
       <c r="AD31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF31">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG31">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O33">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S33">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V33">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
         <v>4.5</v>
       </c>
       <c r="AA33">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB33">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="AC33">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AD33">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG33">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="P34">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="R34">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W34">
         <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
         <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB34">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="AC34">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AD34">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>1.06</v>
       </c>
       <c r="Y45">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
         <v>3.2</v>
@@ -7701,7 +7701,7 @@
         <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="O46">
         <v>3.7</v>
       </c>
       <c r="P46">
-        <v>2.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q46">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z46">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="AA46">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB46">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AC46">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AD46">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AE46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="O47">
         <v>3.7</v>
       </c>
       <c r="P47">
-        <v>3.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q47">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X47">
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z47">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA47">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AC47">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AD47">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG47">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK47">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P50">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="Q50">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="R50">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="U50">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Z50">
-        <v>3.98</v>
+        <v>3.05</v>
       </c>
       <c r="AA50">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AC50">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AD50">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="O51">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q51">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="R51">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
+        <v>1.11</v>
+      </c>
+      <c r="X51">
         <v>1.05</v>
       </c>
-      <c r="X51">
-        <v>1.06</v>
-      </c>
       <c r="Y51">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Z51">
-        <v>3.05</v>
+        <v>3.98</v>
       </c>
       <c r="AA51">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AB51">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AK51">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="O53">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q53">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S53">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T53">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="U53">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="V53">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="W53">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z53">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA53">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB53">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC53">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AD53">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE53">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG53">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.28</v>
       </c>
       <c r="AK53">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9440,10 +9440,10 @@
         <v>1.51</v>
       </c>
       <c r="O56">
-        <v>4.26</v>
+        <v>3.8</v>
       </c>
       <c r="P56">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9630,7 +9630,7 @@
         <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y57">
         <v>1.29</v>
@@ -9639,13 +9639,13 @@
         <v>3.05</v>
       </c>
       <c r="AA57">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB57">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC57">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD57">
         <v>1.22</v>
@@ -9654,7 +9654,7 @@
         <v>1.06</v>
       </c>
       <c r="AF57">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG57">
         <v>1.85</v>
@@ -9781,46 +9781,46 @@
         <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U58">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="V58">
         <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X58">
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z58">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA58">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB58">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC58">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD58">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF58">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG58">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10750,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S64">
         <v>0</v>
@@ -10762,10 +10762,10 @@
         <v>0</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W64">
         <v>0</v>
@@ -10774,31 +10774,31 @@
         <v>0</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE64">
         <v>0</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11752,7 +11752,7 @@
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z70">
         <v>3.35</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK70">
         <v>1.27</v>
@@ -12220,13 +12220,13 @@
         <v>3.12</v>
       </c>
       <c r="R73">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S73">
         <v>1.35</v>
       </c>
       <c r="T73">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U73">
         <v>2.47</v>
@@ -12241,13 +12241,13 @@
         <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z73">
         <v>3.85</v>
       </c>
       <c r="AA73">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB73">
         <v>2</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK73">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
+        <v>1.56</v>
+      </c>
+      <c r="O90">
+        <v>4</v>
+      </c>
+      <c r="P90">
+        <v>4.95</v>
+      </c>
+      <c r="Q90">
         <v>2</v>
       </c>
-      <c r="O90">
-        <v>3.4</v>
-      </c>
-      <c r="P90">
-        <v>3.37</v>
-      </c>
-      <c r="Q90">
-        <v>2.64</v>
-      </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="S90">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T90">
-        <v>3.06</v>
+        <v>3.28</v>
       </c>
       <c r="U90">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="V90">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z90">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="AA90">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AB90">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AC90">
-        <v>3.15</v>
+        <v>2.43</v>
       </c>
       <c r="AD90">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF90">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="O91">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>4.95</v>
+        <v>3.37</v>
       </c>
       <c r="Q91">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="R91">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T91">
-        <v>3.28</v>
+        <v>3.06</v>
       </c>
       <c r="U91">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="V91">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W91">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z91">
-        <v>4.17</v>
+        <v>3.6</v>
       </c>
       <c r="AA91">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AB91">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AC91">
-        <v>2.43</v>
+        <v>3.15</v>
       </c>
       <c r="AD91">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AE91">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF91">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG91">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK91">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15806,7 +15806,7 @@
         <v>2.4</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S95">
         <v>1.3</v>
@@ -15827,25 +15827,25 @@
         <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z95">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA95">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB95">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC95">
         <v>2.6</v>
       </c>
       <c r="AD95">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE95">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF95">
         <v>1.57</v>
@@ -16621,10 +16621,10 @@
         <v>2.12</v>
       </c>
       <c r="R100">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S100">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T100">
         <v>3.35</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.22</v>
+        <v>2.3</v>
       </c>
       <c r="O111">
-        <v>6.65</v>
+        <v>4</v>
       </c>
       <c r="P111">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q111">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="R111">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="S111">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T111">
         <v>4.2</v>
       </c>
       <c r="U111">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V111">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="W111">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z111">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="AA111">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AB111">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AC111">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD111">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AE111">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="AG111">
-        <v>1.96</v>
+        <v>3.04</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AK111">
-        <v>4.15</v>
+        <v>1.57</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,80 +18565,80 @@
         </is>
       </c>
       <c r="N112">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="O112">
-        <v>4.33</v>
+        <v>6.65</v>
       </c>
       <c r="P112">
-        <v>1.75</v>
+        <v>10.5</v>
       </c>
       <c r="Q112">
+        <v>1.57</v>
+      </c>
+      <c r="R112">
+        <v>3</v>
+      </c>
+      <c r="S112">
+        <v>1.2</v>
+      </c>
+      <c r="T112">
+        <v>4.2</v>
+      </c>
+      <c r="U112">
+        <v>2.02</v>
+      </c>
+      <c r="V112">
+        <v>1.88</v>
+      </c>
+      <c r="W112">
+        <v>1.22</v>
+      </c>
+      <c r="X112">
+        <v>1.01</v>
+      </c>
+      <c r="Y112">
+        <v>1.06</v>
+      </c>
+      <c r="Z112">
+        <v>6.75</v>
+      </c>
+      <c r="AA112">
+        <v>1.29</v>
+      </c>
+      <c r="AB112">
+        <v>3.2</v>
+      </c>
+      <c r="AC112">
+        <v>1.92</v>
+      </c>
+      <c r="AD112">
+        <v>1.9</v>
+      </c>
+      <c r="AE112">
+        <v>1.4</v>
+      </c>
+      <c r="AF112">
+        <v>1.77</v>
+      </c>
+      <c r="AG112">
+        <v>1.96</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <v>1.12</v>
+      </c>
+      <c r="AK112">
         <v>4.15</v>
-      </c>
-      <c r="R112">
-        <v>2.5</v>
-      </c>
-      <c r="S112">
-        <v>1.22</v>
-      </c>
-      <c r="T112">
-        <v>4.05</v>
-      </c>
-      <c r="U112">
-        <v>2</v>
-      </c>
-      <c r="V112">
-        <v>1.79</v>
-      </c>
-      <c r="W112">
-        <v>1.2</v>
-      </c>
-      <c r="X112">
-        <v>1.02</v>
-      </c>
-      <c r="Y112">
-        <v>1.12</v>
-      </c>
-      <c r="Z112">
-        <v>7</v>
-      </c>
-      <c r="AA112">
-        <v>1.42</v>
-      </c>
-      <c r="AB112">
-        <v>2.88</v>
-      </c>
-      <c r="AC112">
-        <v>2</v>
-      </c>
-      <c r="AD112">
-        <v>1.83</v>
-      </c>
-      <c r="AE112">
-        <v>1.33</v>
-      </c>
-      <c r="AF112">
-        <v>1.45</v>
-      </c>
-      <c r="AG112">
-        <v>2.75</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>2.1</v>
-      </c>
-      <c r="AK112">
-        <v>1.26</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,31 +18728,31 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="O113">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P113">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q113">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="R113">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="S113">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U113">
         <v>2</v>
       </c>
       <c r="V113">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="W113">
         <v>1.2</v>
@@ -18764,28 +18764,28 @@
         <v>1.12</v>
       </c>
       <c r="Z113">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AA113">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB113">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AC113">
         <v>2</v>
       </c>
       <c r="AD113">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE113">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF113">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AG113">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AK113">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -20032,19 +20032,19 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q121">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="R121">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="S121">
         <v>1.22</v>
@@ -20059,7 +20059,7 @@
         <v>1.58</v>
       </c>
       <c r="W121">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X121">
         <v>1</v>
@@ -20071,7 +20071,7 @@
         <v>4.75</v>
       </c>
       <c r="AA121">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB121">
         <v>2.35</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q122">
         <v>10.1</v>
@@ -20210,13 +20210,13 @@
         <v>2.36</v>
       </c>
       <c r="S122">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T122">
         <v>3.02</v>
       </c>
       <c r="U122">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V122">
         <v>1.46</v>
@@ -20252,7 +20252,7 @@
         <v>2.14</v>
       </c>
       <c r="AG122">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>1.1</v>
       </c>
       <c r="AK122">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20361,7 +20361,7 @@
         <v>2.25</v>
       </c>
       <c r="O123">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P123">
         <v>2.7</v>
@@ -20391,19 +20391,19 @@
         <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z123">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="AA123">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB123">
         <v>2.05</v>
       </c>
       <c r="AC123">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="AD123">
         <v>1.44</v>
@@ -20557,7 +20557,7 @@
         <v>1.18</v>
       </c>
       <c r="Z124">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA124">
         <v>1.72</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,80 +21988,80 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="O133">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P133">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="R133">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S133">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T133">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="U133">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="V133">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W133">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X133">
         <v>1.03</v>
       </c>
       <c r="Y133">
+        <v>1.27</v>
+      </c>
+      <c r="Z133">
+        <v>3.64</v>
+      </c>
+      <c r="AA133">
+        <v>1.8</v>
+      </c>
+      <c r="AB133">
+        <v>1.91</v>
+      </c>
+      <c r="AC133">
+        <v>3.15</v>
+      </c>
+      <c r="AD133">
         <v>1.34</v>
       </c>
-      <c r="Z133">
-        <v>2.93</v>
-      </c>
-      <c r="AA133">
-        <v>2.02</v>
-      </c>
-      <c r="AB133">
-        <v>1.78</v>
-      </c>
-      <c r="AC133">
-        <v>3.42</v>
-      </c>
-      <c r="AD133">
+      <c r="AE133">
+        <v>1.09</v>
+      </c>
+      <c r="AF133">
+        <v>1.67</v>
+      </c>
+      <c r="AG133">
+        <v>2.05</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ133">
         <v>1.25</v>
       </c>
-      <c r="AE133">
-        <v>1.04</v>
-      </c>
-      <c r="AF133">
-        <v>1.8</v>
-      </c>
-      <c r="AG133">
-        <v>2</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>1.29</v>
-      </c>
       <c r="AK133">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,31 +22151,31 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O134">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P134">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="Q134">
+        <v>2.68</v>
+      </c>
+      <c r="R134">
+        <v>2.13</v>
+      </c>
+      <c r="S134">
+        <v>1.32</v>
+      </c>
+      <c r="T134">
         <v>3</v>
       </c>
-      <c r="R134">
-        <v>2.15</v>
-      </c>
-      <c r="S134">
-        <v>1.37</v>
-      </c>
-      <c r="T134">
-        <v>2.81</v>
-      </c>
       <c r="U134">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V134">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W134">
         <v>1.05</v>
@@ -22184,28 +22184,28 @@
         <v>1</v>
       </c>
       <c r="Y134">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z134">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA134">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB134">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC134">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD134">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE134">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG134">
         <v>2.05</v>
@@ -22224,7 +22224,7 @@
         <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,61 +22314,61 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O135">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P135">
-        <v>1.98</v>
+        <v>2.82</v>
       </c>
       <c r="Q135">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R135">
         <v>2.15</v>
       </c>
       <c r="S135">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T135">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="U135">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V135">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W135">
         <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y135">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z135">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="AA135">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB135">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC135">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AD135">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE135">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF135">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG135">
         <v>2.05</v>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,80 +22477,80 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O136">
         <v>3.25</v>
       </c>
       <c r="P136">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q136">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R136">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T136">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="U136">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="V136">
+        <v>1.38</v>
+      </c>
+      <c r="W136">
+        <v>1.03</v>
+      </c>
+      <c r="X136">
+        <v>1.03</v>
+      </c>
+      <c r="Y136">
+        <v>1.34</v>
+      </c>
+      <c r="Z136">
+        <v>2.93</v>
+      </c>
+      <c r="AA136">
+        <v>2.02</v>
+      </c>
+      <c r="AB136">
+        <v>1.78</v>
+      </c>
+      <c r="AC136">
+        <v>3.42</v>
+      </c>
+      <c r="AD136">
+        <v>1.25</v>
+      </c>
+      <c r="AE136">
+        <v>1.04</v>
+      </c>
+      <c r="AF136">
+        <v>1.8</v>
+      </c>
+      <c r="AG136">
+        <v>2</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ136">
         <v>1.29</v>
       </c>
-      <c r="W136">
-        <v>1.05</v>
-      </c>
-      <c r="X136">
-        <v>1.05</v>
-      </c>
-      <c r="Y136">
-        <v>1.32</v>
-      </c>
-      <c r="Z136">
-        <v>3.1</v>
-      </c>
-      <c r="AA136">
-        <v>2.16</v>
-      </c>
-      <c r="AB136">
-        <v>1.67</v>
-      </c>
-      <c r="AC136">
-        <v>3.75</v>
-      </c>
-      <c r="AD136">
-        <v>1.16</v>
-      </c>
-      <c r="AE136">
-        <v>1.07</v>
-      </c>
-      <c r="AF136">
-        <v>1.85</v>
-      </c>
-      <c r="AG136">
-        <v>1.85</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>1.3</v>
-      </c>
       <c r="AK136">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="O137">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P137">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="Q137">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="R137">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="S137">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="T137">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="U137">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="V137">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W137">
         <v>1.05</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y137">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z137">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA137">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="AB137">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC137">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AD137">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AE137">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG137">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>1.3</v>
       </c>
       <c r="AK137">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O138">
         <v>3.7</v>
@@ -22815,19 +22815,19 @@
         <v>2.2</v>
       </c>
       <c r="R138">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="S138">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T138">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="U138">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V138">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W138">
         <v>1.16</v>
@@ -22848,7 +22848,7 @@
         <v>2.7</v>
       </c>
       <c r="AC138">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AD138">
         <v>1.75</v>
@@ -22857,7 +22857,7 @@
         <v>1.27</v>
       </c>
       <c r="AF138">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG138">
         <v>2.75</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23325,13 +23325,13 @@
         <v>1.05</v>
       </c>
       <c r="Y141">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z141">
         <v>3.85</v>
       </c>
       <c r="AA141">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB141">
         <v>1.9</v>
@@ -23349,7 +23349,7 @@
         <v>1.64</v>
       </c>
       <c r="AG141">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>2.3</v>
       </c>
       <c r="O142">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P142">
         <v>2.9</v>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK142">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="O143">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P143">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="Q143">
         <v>3</v>
@@ -23657,7 +23657,7 @@
         <v>3.2</v>
       </c>
       <c r="AA143">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB143">
         <v>1.8</v>
@@ -23823,10 +23823,10 @@
         <v>1.62</v>
       </c>
       <c r="AB144">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC144">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AD144">
         <v>1.49</v>
@@ -23835,10 +23835,10 @@
         <v>1.18</v>
       </c>
       <c r="AF144">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG144">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.87</v>
+        <v>1.67</v>
       </c>
       <c r="O145">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="P145">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q145">
-        <v>3.35</v>
+        <v>2.05</v>
       </c>
       <c r="R145">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="S145">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T145">
-        <v>2.73</v>
+        <v>3.75</v>
       </c>
       <c r="U145">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="V145">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="W145">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X145">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y145">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="Z145">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="AA145">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AB145">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AC145">
-        <v>3.24</v>
+        <v>2.43</v>
       </c>
       <c r="AD145">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="AE145">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AF145">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG145">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK145">
-        <v>1.39</v>
+        <v>2.25</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24158,7 +24158,7 @@
         <v>1.2</v>
       </c>
       <c r="AE146">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF146">
         <v>1.84</v>
@@ -24180,7 +24180,7 @@
         <v>1.41</v>
       </c>
       <c r="AK146">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.61</v>
+        <v>2.84</v>
       </c>
       <c r="O147">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="P147">
-        <v>4.8</v>
+        <v>2.42</v>
       </c>
       <c r="Q147">
+        <v>3.35</v>
+      </c>
+      <c r="R147">
         <v>2.05</v>
       </c>
-      <c r="R147">
-        <v>2.5</v>
-      </c>
       <c r="S147">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T147">
-        <v>3.75</v>
+        <v>2.73</v>
       </c>
       <c r="U147">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="V147">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="W147">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X147">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="Z147">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AA147">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AB147">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC147">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="AD147">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AE147">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AF147">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG147">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AK147">
-        <v>2.25</v>
+        <v>1.39</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,64 +24596,64 @@
         </is>
       </c>
       <c r="N149">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="O149">
+        <v>3.8</v>
+      </c>
+      <c r="P149">
+        <v>3.4</v>
+      </c>
+      <c r="Q149">
+        <v>2.31</v>
+      </c>
+      <c r="R149">
+        <v>2.28</v>
+      </c>
+      <c r="S149">
+        <v>1.25</v>
+      </c>
+      <c r="T149">
         <v>3.5</v>
       </c>
-      <c r="P149">
-        <v>1.97</v>
-      </c>
-      <c r="Q149">
-        <v>3.65</v>
-      </c>
-      <c r="R149">
-        <v>2.16</v>
-      </c>
-      <c r="S149">
-        <v>1.35</v>
-      </c>
-      <c r="T149">
-        <v>2.86</v>
-      </c>
       <c r="U149">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V149">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="W149">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X149">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y149">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z149">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AA149">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AB149">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC149">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="AD149">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AE149">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF149">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG149">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK149">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="O150">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="P150">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q150">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="R150">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="S150">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T150">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="U150">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V150">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W150">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X150">
         <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z150">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA150">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB150">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC150">
-        <v>2.48</v>
+        <v>3.39</v>
       </c>
       <c r="AD150">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE150">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF150">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG150">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AK150">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="O151">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P151">
         <v>4</v>
       </c>
       <c r="Q151">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="R151">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S151">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T151">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="U151">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="V151">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W151">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X151">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z151">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA151">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="AB151">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AC151">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AD151">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AE151">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF151">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG151">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK151">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="O152">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P152">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q152">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="R152">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T152">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="U152">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="V152">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="W152">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X152">
         <v>1.03</v>
       </c>
       <c r="Y152">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z152">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA152">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AB152">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AC152">
-        <v>2.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD152">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AE152">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF152">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG152">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK152">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,31 +25248,31 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="O153">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P153">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Q153">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R153">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S153">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T153">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U153">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V153">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W153">
         <v>1.12</v>
@@ -25281,31 +25281,31 @@
         <v>1.01</v>
       </c>
       <c r="Y153">
+        <v>1.2</v>
+      </c>
+      <c r="Z153">
+        <v>3.7</v>
+      </c>
+      <c r="AA153">
+        <v>1.65</v>
+      </c>
+      <c r="AB153">
+        <v>2.25</v>
+      </c>
+      <c r="AC153">
+        <v>2.48</v>
+      </c>
+      <c r="AD153">
+        <v>1.43</v>
+      </c>
+      <c r="AE153">
         <v>1.18</v>
       </c>
-      <c r="Z153">
-        <v>4.2</v>
-      </c>
-      <c r="AA153">
-        <v>1.59</v>
-      </c>
-      <c r="AB153">
-        <v>2.17</v>
-      </c>
-      <c r="AC153">
-        <v>2.56</v>
-      </c>
-      <c r="AD153">
-        <v>1.49</v>
-      </c>
-      <c r="AE153">
-        <v>1.15</v>
-      </c>
       <c r="AF153">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG153">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK153">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.6</v>
+        <v>2.98</v>
       </c>
       <c r="O155">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P155">
-        <v>4.68</v>
+        <v>1.97</v>
       </c>
       <c r="Q155">
-        <v>2.14</v>
+        <v>3.65</v>
       </c>
       <c r="R155">
-        <v>2.64</v>
+        <v>2.16</v>
       </c>
       <c r="S155">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T155">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="U155">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V155">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="W155">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X155">
         <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z155">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AA155">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AB155">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC155">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="AD155">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AE155">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AF155">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG155">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="O156">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P156">
-        <v>2.55</v>
+        <v>4.68</v>
       </c>
       <c r="Q156">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="R156">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="S156">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T156">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="U156">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="V156">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W156">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X156">
         <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z156">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA156">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AB156">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AC156">
-        <v>3.39</v>
+        <v>2.12</v>
       </c>
       <c r="AD156">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AE156">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AF156">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG156">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK156">
-        <v>1.44</v>
+        <v>2.19</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -27062,10 +27062,10 @@
         <v>3</v>
       </c>
       <c r="U164">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V164">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W164">
         <v>1.08</v>
@@ -27074,10 +27074,10 @@
         <v>1.01</v>
       </c>
       <c r="Y164">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z164">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AA164">
         <v>1.76</v>
@@ -27092,10 +27092,10 @@
         <v>1.32</v>
       </c>
       <c r="AE164">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF164">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG164">
         <v>2.05</v>
@@ -27216,7 +27216,7 @@
         <v>2.65</v>
       </c>
       <c r="R165">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S165">
         <v>1.4</v>
@@ -27258,7 +27258,7 @@
         <v>1.06</v>
       </c>
       <c r="AF165">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG165">
         <v>1.95</v>
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK165">
         <v>1.47</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G178">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G179">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G180">
@@ -31442,16 +31442,16 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O191">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P191">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q191">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="R191">
         <v>2</v>
@@ -31466,40 +31466,40 @@
         <v>2.92</v>
       </c>
       <c r="V191">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W191">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y191">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z191">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA191">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AB191">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC191">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD191">
         <v>1.28</v>
       </c>
       <c r="AE191">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF191">
         <v>1.73</v>
       </c>
       <c r="AG191">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK191">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="O196">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P196">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q196">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="R196">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S196">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T196">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U196">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="V196">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W196">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X196">
         <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z196">
-        <v>4.63</v>
+        <v>4.8</v>
       </c>
       <c r="AA196">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB196">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AC196">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="AD196">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE196">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF196">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG196">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>1.13</v>
       </c>
       <c r="AK196">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>6.96</v>
+        <v>10</v>
       </c>
       <c r="O202">
-        <v>5.51</v>
+        <v>6.34</v>
       </c>
       <c r="P202">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S202">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T202">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U202">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V202">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W202">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X202">
         <v>0</v>
       </c>
       <c r="Y202">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z202">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA202">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB202">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC202">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD202">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE202">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG202">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK202">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,80 +33887,80 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="O206">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P206">
-        <v>4.01</v>
+        <v>3</v>
       </c>
       <c r="Q206">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="R206">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S206">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T206">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="U206">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V206">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W206">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X206">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y206">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z206">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="AA206">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB206">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AC206">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AD206">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AE206">
+        <v>1.29</v>
+      </c>
+      <c r="AF206">
+        <v>1.36</v>
+      </c>
+      <c r="AG206">
+        <v>3</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ206">
         <v>1.25</v>
       </c>
-      <c r="AF206">
-        <v>1.45</v>
-      </c>
-      <c r="AG206">
-        <v>2.5</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ206">
-        <v>1.22</v>
-      </c>
       <c r="AK206">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="O207">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P207">
-        <v>3</v>
+        <v>4.01</v>
       </c>
       <c r="Q207">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="R207">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S207">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T207">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U207">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V207">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W207">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X207">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y207">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z207">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="AA207">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB207">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AC207">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AD207">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AE207">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF207">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG207">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK207">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34376,25 +34376,25 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O209">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P209">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q209">
         <v>2.25</v>
       </c>
       <c r="R209">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S209">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T209">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="U209">
         <v>2.3</v>
@@ -34409,25 +34409,25 @@
         <v>1.04</v>
       </c>
       <c r="Y209">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z209">
         <v>4.2</v>
       </c>
       <c r="AA209">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB209">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC209">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AD209">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE209">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF209">
         <v>1.58</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK209">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,80 +35028,80 @@
         </is>
       </c>
       <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213">
+        <v>0</v>
+      </c>
+      <c r="P213">
+        <v>0</v>
+      </c>
+      <c r="Q213">
+        <v>3.08</v>
+      </c>
+      <c r="R213">
+        <v>1.92</v>
+      </c>
+      <c r="S213">
+        <v>1.44</v>
+      </c>
+      <c r="T213">
+        <v>2.63</v>
+      </c>
+      <c r="U213">
+        <v>3.14</v>
+      </c>
+      <c r="V213">
+        <v>1.28</v>
+      </c>
+      <c r="W213">
+        <v>1.01</v>
+      </c>
+      <c r="X213">
+        <v>1.02</v>
+      </c>
+      <c r="Y213">
+        <v>1.34</v>
+      </c>
+      <c r="Z213">
+        <v>2.78</v>
+      </c>
+      <c r="AA213">
+        <v>2.15</v>
+      </c>
+      <c r="AB213">
+        <v>1.61</v>
+      </c>
+      <c r="AC213">
+        <v>3.95</v>
+      </c>
+      <c r="AD213">
+        <v>1.17</v>
+      </c>
+      <c r="AE213">
+        <v>1.02</v>
+      </c>
+      <c r="AF213">
+        <v>1.84</v>
+      </c>
+      <c r="AG213">
+        <v>1.83</v>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ213">
+        <v>1.28</v>
+      </c>
+      <c r="AK213">
         <v>1.46</v>
-      </c>
-      <c r="O213">
-        <v>4.1</v>
-      </c>
-      <c r="P213">
-        <v>6.4</v>
-      </c>
-      <c r="Q213">
-        <v>0</v>
-      </c>
-      <c r="R213">
-        <v>0</v>
-      </c>
-      <c r="S213">
-        <v>0</v>
-      </c>
-      <c r="T213">
-        <v>0</v>
-      </c>
-      <c r="U213">
-        <v>0</v>
-      </c>
-      <c r="V213">
-        <v>0</v>
-      </c>
-      <c r="W213">
-        <v>0</v>
-      </c>
-      <c r="X213">
-        <v>0</v>
-      </c>
-      <c r="Y213">
-        <v>0</v>
-      </c>
-      <c r="Z213">
-        <v>0</v>
-      </c>
-      <c r="AA213">
-        <v>0</v>
-      </c>
-      <c r="AB213">
-        <v>0</v>
-      </c>
-      <c r="AC213">
-        <v>0</v>
-      </c>
-      <c r="AD213">
-        <v>0</v>
-      </c>
-      <c r="AE213">
-        <v>0</v>
-      </c>
-      <c r="AF213">
-        <v>0</v>
-      </c>
-      <c r="AG213">
-        <v>0</v>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ213">
-        <v>0</v>
-      </c>
-      <c r="AK213">
-        <v>0</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q214">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R214">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S214">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T214">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U214">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="V214">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W214">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X214">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y214">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z214">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA214">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB214">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC214">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD214">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE214">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF214">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG214">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK214">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G215">
@@ -35363,55 +35363,55 @@
         <v>0</v>
       </c>
       <c r="Q215">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="R215">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="S215">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T215">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U215">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="V215">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W215">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X215">
         <v>1.02</v>
       </c>
       <c r="Y215">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z215">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA215">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AB215">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AC215">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD215">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE215">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF215">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG215">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK215">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -38614,16 +38614,16 @@
         </is>
       </c>
       <c r="N235">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O235">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P235">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q235">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R235">
         <v>2.3</v>
@@ -38635,19 +38635,19 @@
         <v>3.08</v>
       </c>
       <c r="U235">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V235">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W235">
         <v>1.1</v>
       </c>
       <c r="X235">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y235">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z235">
         <v>3.88</v>
@@ -38662,16 +38662,16 @@
         <v>2.74</v>
       </c>
       <c r="AD235">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE235">
         <v>1.15</v>
       </c>
       <c r="AF235">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG235">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O239">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P239">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q239">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="R239">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S239">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T239">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="U239">
         <v>2.75</v>
       </c>
       <c r="V239">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W239">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X239">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y239">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z239">
-        <v>3.51</v>
+        <v>3.24</v>
       </c>
       <c r="AA239">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AB239">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AC239">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="AD239">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE239">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF239">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG239">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AK239">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,80 +39429,80 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q240">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="R240">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S240">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T240">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="U240">
         <v>2.75</v>
       </c>
       <c r="V240">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W240">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X240">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y240">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z240">
-        <v>3.24</v>
+        <v>3.51</v>
       </c>
       <c r="AA240">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AB240">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AC240">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AD240">
+        <v>1.29</v>
+      </c>
+      <c r="AE240">
+        <v>1.08</v>
+      </c>
+      <c r="AF240">
+        <v>1.67</v>
+      </c>
+      <c r="AG240">
+        <v>2.03</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ240">
         <v>1.24</v>
       </c>
-      <c r="AE240">
-        <v>1.05</v>
-      </c>
-      <c r="AF240">
-        <v>1.75</v>
-      </c>
-      <c r="AG240">
-        <v>1.95</v>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ240">
-        <v>1.38</v>
-      </c>
       <c r="AK240">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42200,64 +42200,64 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC257">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD257">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -43178,16 +43178,16 @@
         </is>
       </c>
       <c r="N263">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O263">
         <v>3.65</v>
       </c>
       <c r="P263">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="Q263">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R263">
         <v>2.4</v>
@@ -43199,43 +43199,43 @@
         <v>3.75</v>
       </c>
       <c r="U263">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="V263">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W263">
         <v>1.14</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y263">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z263">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA263">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AB263">
         <v>2.7</v>
       </c>
       <c r="AC263">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="AD263">
         <v>1.68</v>
       </c>
       <c r="AE263">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF263">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG263">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44645,28 +44645,28 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="O272">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P272">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q272">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R272">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S272">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T272">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="U272">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="V272">
         <v>1.4</v>
@@ -44675,31 +44675,31 @@
         <v>1.1</v>
       </c>
       <c r="X272">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y272">
         <v>1.28</v>
       </c>
       <c r="Z272">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="AA272">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB272">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC272">
         <v>2.97</v>
       </c>
       <c r="AD272">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE272">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF272">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG272">
         <v>2</v>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK272">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O274">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="P274">
-        <v>2.44</v>
+        <v>2.77</v>
       </c>
       <c r="Q274">
         <v>3.1</v>
       </c>
       <c r="R274">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="S274">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T274">
-        <v>3.6</v>
+        <v>3.01</v>
       </c>
       <c r="U274">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="V274">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W274">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X274">
         <v>1.04</v>
       </c>
       <c r="Y274">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z274">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA274">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB274">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC274">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD274">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE274">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF274">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AG274">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AK274">
         <v>1.52</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O275">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="P275">
-        <v>2.77</v>
+        <v>2.44</v>
       </c>
       <c r="Q275">
         <v>3.1</v>
       </c>
       <c r="R275">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S275">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T275">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="U275">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="V275">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W275">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X275">
         <v>1.04</v>
       </c>
       <c r="Y275">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z275">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA275">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB275">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC275">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD275">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AE275">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF275">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AG275">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AK275">
         <v>1.52</v>
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O284">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P284">
         <v>3.3</v>
       </c>
       <c r="Q284">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="R284">
         <v>2.05</v>
       </c>
       <c r="S284">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T284">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U284">
-        <v>3.15</v>
+        <v>2.91</v>
       </c>
       <c r="V284">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W284">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X284">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y284">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z284">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA284">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB284">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC284">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AD284">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE284">
         <v>1.07</v>
       </c>
       <c r="AF284">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG284">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>1.31</v>
       </c>
       <c r="AK284">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="O285">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P285">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q285">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="R285">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="S285">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T285">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="U285">
-        <v>2.94</v>
+        <v>3.07</v>
       </c>
       <c r="V285">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W285">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X285">
+        <v>1.02</v>
+      </c>
+      <c r="Y285">
+        <v>1.34</v>
+      </c>
+      <c r="Z285">
+        <v>2.99</v>
+      </c>
+      <c r="AA285">
+        <v>2.09</v>
+      </c>
+      <c r="AB285">
+        <v>1.78</v>
+      </c>
+      <c r="AC285">
+        <v>3.52</v>
+      </c>
+      <c r="AD285">
+        <v>1.25</v>
+      </c>
+      <c r="AE285">
         <v>1.04</v>
       </c>
-      <c r="Y285">
-        <v>1.38</v>
-      </c>
-      <c r="Z285">
-        <v>3</v>
-      </c>
-      <c r="AA285">
-        <v>2.1</v>
-      </c>
-      <c r="AB285">
-        <v>1.7</v>
-      </c>
-      <c r="AC285">
-        <v>3.54</v>
-      </c>
-      <c r="AD285">
-        <v>1.22</v>
-      </c>
-      <c r="AE285">
-        <v>1.05</v>
-      </c>
       <c r="AF285">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG285">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK285">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,80 +50187,80 @@
         </is>
       </c>
       <c r="N306">
-        <v>3.2</v>
+        <v>1.71</v>
       </c>
       <c r="O306">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P306">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q306">
-        <v>3.78</v>
+        <v>2.25</v>
       </c>
       <c r="R306">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="S306">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T306">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="U306">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="V306">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="W306">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X306">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y306">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z306">
-        <v>5.27</v>
+        <v>3.45</v>
       </c>
       <c r="AA306">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AB306">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="AC306">
-        <v>2.21</v>
+        <v>2.85</v>
       </c>
       <c r="AD306">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AE306">
+        <v>1.06</v>
+      </c>
+      <c r="AF306">
+        <v>1.8</v>
+      </c>
+      <c r="AG306">
+        <v>1.89</v>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ306">
         <v>1.21</v>
       </c>
-      <c r="AF306">
-        <v>1.46</v>
-      </c>
-      <c r="AG306">
-        <v>2.45</v>
-      </c>
-      <c r="AH306" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI306" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ306">
-        <v>1.19</v>
-      </c>
       <c r="AK306">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,19 +50350,19 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.71</v>
+        <v>3.25</v>
       </c>
       <c r="O307">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P307">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="Q307">
-        <v>2.25</v>
+        <v>4.26</v>
       </c>
       <c r="R307">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S307">
         <v>1.36</v>
@@ -50371,59 +50371,59 @@
         <v>2.88</v>
       </c>
       <c r="U307">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V307">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W307">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X307">
         <v>1.01</v>
       </c>
       <c r="Y307">
+        <v>1.3</v>
+      </c>
+      <c r="Z307">
+        <v>3.35</v>
+      </c>
+      <c r="AA307">
+        <v>1.89</v>
+      </c>
+      <c r="AB307">
+        <v>1.83</v>
+      </c>
+      <c r="AC307">
+        <v>3.14</v>
+      </c>
+      <c r="AD307">
+        <v>1.27</v>
+      </c>
+      <c r="AE307">
+        <v>1.1</v>
+      </c>
+      <c r="AF307">
+        <v>1.7</v>
+      </c>
+      <c r="AG307">
+        <v>2</v>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ307">
+        <v>1.24</v>
+      </c>
+      <c r="AK307">
         <v>1.23</v>
-      </c>
-      <c r="Z307">
-        <v>3.45</v>
-      </c>
-      <c r="AA307">
-        <v>1.85</v>
-      </c>
-      <c r="AB307">
-        <v>1.88</v>
-      </c>
-      <c r="AC307">
-        <v>2.85</v>
-      </c>
-      <c r="AD307">
-        <v>1.28</v>
-      </c>
-      <c r="AE307">
-        <v>1.06</v>
-      </c>
-      <c r="AF307">
-        <v>1.8</v>
-      </c>
-      <c r="AG307">
-        <v>1.89</v>
-      </c>
-      <c r="AH307" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI307" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ307">
-        <v>1.21</v>
-      </c>
-      <c r="AK307">
-        <v>1.86</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
+        <v>4.2</v>
+      </c>
+      <c r="O308">
+        <v>3.95</v>
+      </c>
+      <c r="P308">
+        <v>1.57</v>
+      </c>
+      <c r="Q308">
+        <v>4.97</v>
+      </c>
+      <c r="R308">
+        <v>2.39</v>
+      </c>
+      <c r="S308">
+        <v>1.29</v>
+      </c>
+      <c r="T308">
         <v>3.25</v>
       </c>
-      <c r="O308">
-        <v>3.25</v>
-      </c>
-      <c r="P308">
-        <v>1.98</v>
-      </c>
-      <c r="Q308">
-        <v>4.26</v>
-      </c>
-      <c r="R308">
-        <v>2.1</v>
-      </c>
-      <c r="S308">
-        <v>1.36</v>
-      </c>
-      <c r="T308">
-        <v>2.88</v>
-      </c>
       <c r="U308">
-        <v>2.9</v>
+        <v>2.52</v>
       </c>
       <c r="V308">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W308">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X308">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z308">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AA308">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AB308">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC308">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="AD308">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AE308">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF308">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG308">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK308">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="O309">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P309">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="Q309">
-        <v>4.97</v>
+        <v>3.78</v>
       </c>
       <c r="R309">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S309">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T309">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U309">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="V309">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W309">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X309">
         <v>1.02</v>
       </c>
       <c r="Y309">
+        <v>1.14</v>
+      </c>
+      <c r="Z309">
+        <v>5.27</v>
+      </c>
+      <c r="AA309">
+        <v>1.49</v>
+      </c>
+      <c r="AB309">
+        <v>2.33</v>
+      </c>
+      <c r="AC309">
+        <v>2.21</v>
+      </c>
+      <c r="AD309">
+        <v>1.59</v>
+      </c>
+      <c r="AE309">
         <v>1.21</v>
       </c>
-      <c r="Z309">
-        <v>4.1</v>
-      </c>
-      <c r="AA309">
-        <v>1.65</v>
-      </c>
-      <c r="AB309">
-        <v>2.2</v>
-      </c>
-      <c r="AC309">
-        <v>2.69</v>
-      </c>
-      <c r="AD309">
-        <v>1.42</v>
-      </c>
-      <c r="AE309">
-        <v>1.14</v>
-      </c>
       <c r="AF309">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AG309">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK309">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,64 +55077,64 @@
         </is>
       </c>
       <c r="N336">
+        <v>1.97</v>
+      </c>
+      <c r="O336">
+        <v>3.15</v>
+      </c>
+      <c r="P336">
+        <v>3.7</v>
+      </c>
+      <c r="Q336">
+        <v>2.64</v>
+      </c>
+      <c r="R336">
         <v>1.96</v>
       </c>
-      <c r="O336">
-        <v>3.3</v>
-      </c>
-      <c r="P336">
-        <v>3.25</v>
-      </c>
-      <c r="Q336">
+      <c r="S336">
+        <v>1.5</v>
+      </c>
+      <c r="T336">
         <v>2.52</v>
       </c>
-      <c r="R336">
-        <v>2.13</v>
-      </c>
-      <c r="S336">
-        <v>1.35</v>
-      </c>
-      <c r="T336">
-        <v>3</v>
-      </c>
       <c r="U336">
-        <v>2.66</v>
+        <v>3.18</v>
       </c>
       <c r="V336">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W336">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X336">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y336">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="Z336">
-        <v>3.28</v>
+        <v>2.68</v>
       </c>
       <c r="AA336">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AB336">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AC336">
-        <v>3.05</v>
+        <v>4.15</v>
       </c>
       <c r="AD336">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AE336">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF336">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG336">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK336">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,64 +55240,64 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="O337">
         <v>3.35</v>
       </c>
       <c r="P337">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="Q337">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="R337">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="S337">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="T337">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="U337">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="V337">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W337">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X337">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y337">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z337">
-        <v>3.75</v>
+        <v>3.57</v>
       </c>
       <c r="AA337">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB337">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC337">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AD337">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE337">
         <v>1.08</v>
       </c>
       <c r="AF337">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AG337">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK337">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,80 +55403,80 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="O338">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P338">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="Q338">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="R338">
+        <v>2.21</v>
+      </c>
+      <c r="S338">
+        <v>1.26</v>
+      </c>
+      <c r="T338">
+        <v>3.32</v>
+      </c>
+      <c r="U338">
+        <v>2.42</v>
+      </c>
+      <c r="V338">
+        <v>1.47</v>
+      </c>
+      <c r="W338">
+        <v>1.08</v>
+      </c>
+      <c r="X338">
+        <v>1.03</v>
+      </c>
+      <c r="Y338">
+        <v>1.22</v>
+      </c>
+      <c r="Z338">
+        <v>3.75</v>
+      </c>
+      <c r="AA338">
+        <v>1.75</v>
+      </c>
+      <c r="AB338">
         <v>1.96</v>
       </c>
-      <c r="S338">
-        <v>1.5</v>
-      </c>
-      <c r="T338">
-        <v>2.52</v>
-      </c>
-      <c r="U338">
-        <v>3.18</v>
-      </c>
-      <c r="V338">
-        <v>1.28</v>
-      </c>
-      <c r="W338">
-        <v>1.02</v>
-      </c>
-      <c r="X338">
-        <v>1.04</v>
-      </c>
-      <c r="Y338">
-        <v>1.45</v>
-      </c>
-      <c r="Z338">
-        <v>2.68</v>
-      </c>
-      <c r="AA338">
-        <v>2.29</v>
-      </c>
-      <c r="AB338">
+      <c r="AC338">
+        <v>2.8</v>
+      </c>
+      <c r="AD338">
+        <v>1.32</v>
+      </c>
+      <c r="AE338">
+        <v>1.08</v>
+      </c>
+      <c r="AF338">
+        <v>1.61</v>
+      </c>
+      <c r="AG338">
+        <v>2.16</v>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ338">
+        <v>1.22</v>
+      </c>
+      <c r="AK338">
         <v>1.55</v>
-      </c>
-      <c r="AC338">
-        <v>4.15</v>
-      </c>
-      <c r="AD338">
-        <v>1.16</v>
-      </c>
-      <c r="AE338">
-        <v>1.02</v>
-      </c>
-      <c r="AF338">
-        <v>2</v>
-      </c>
-      <c r="AG338">
-        <v>1.71</v>
-      </c>
-      <c r="AH338" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI338" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ338">
-        <v>1.24</v>
-      </c>
-      <c r="AK338">
-        <v>1.75</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,31 +55566,31 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="O339">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P339">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="Q339">
-        <v>2.94</v>
+        <v>2.52</v>
       </c>
       <c r="R339">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="S339">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T339">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U339">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V339">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W339">
         <v>1.06</v>
@@ -55599,31 +55599,31 @@
         <v>1.01</v>
       </c>
       <c r="Y339">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z339">
-        <v>3.57</v>
+        <v>3.28</v>
       </c>
       <c r="AA339">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AB339">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC339">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AD339">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE339">
         <v>1.08</v>
       </c>
       <c r="AF339">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG339">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK339">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AL339">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="R33">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V33">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
         <v>4.5</v>
       </c>
       <c r="AA33">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB33">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="AC33">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AD33">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O34">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S34">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V34">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
         <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
         <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB34">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="AC34">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AD34">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AG34">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="O50">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q50">
-        <v>3.35</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="V50">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
+        <v>1.11</v>
+      </c>
+      <c r="X50">
         <v>1.05</v>
       </c>
-      <c r="X50">
-        <v>1.06</v>
-      </c>
       <c r="Y50">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Z50">
-        <v>3.05</v>
+        <v>3.98</v>
       </c>
       <c r="AA50">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AB50">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AC50">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="AD50">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="Q51">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="R51">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="U51">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y51">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Z51">
-        <v>3.98</v>
+        <v>3.05</v>
       </c>
       <c r="AA51">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AC51">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="O61">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P61">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="Q61">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S61">
         <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U61">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
+        <v>1.53</v>
+      </c>
+      <c r="W61">
+        <v>1.1</v>
+      </c>
+      <c r="X61">
+        <v>1.03</v>
+      </c>
+      <c r="Y61">
+        <v>1.14</v>
+      </c>
+      <c r="Z61">
+        <v>4.33</v>
+      </c>
+      <c r="AA61">
         <v>1.57</v>
       </c>
-      <c r="W61">
-        <v>1.14</v>
-      </c>
-      <c r="X61">
-        <v>1.01</v>
-      </c>
-      <c r="Y61">
-        <v>1.13</v>
-      </c>
-      <c r="Z61">
-        <v>4.5</v>
-      </c>
-      <c r="AA61">
-        <v>1.5</v>
-      </c>
       <c r="AB61">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC61">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AD61">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AG61">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q62">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="R62">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="S62">
+        <v>1.28</v>
+      </c>
+      <c r="T62">
+        <v>3.15</v>
+      </c>
+      <c r="U62">
+        <v>2.5</v>
+      </c>
+      <c r="V62">
+        <v>1.5</v>
+      </c>
+      <c r="W62">
+        <v>1.11</v>
+      </c>
+      <c r="X62">
+        <v>1.04</v>
+      </c>
+      <c r="Y62">
+        <v>1.16</v>
+      </c>
+      <c r="Z62">
+        <v>4.05</v>
+      </c>
+      <c r="AA62">
+        <v>1.67</v>
+      </c>
+      <c r="AB62">
+        <v>2.1</v>
+      </c>
+      <c r="AC62">
+        <v>2.62</v>
+      </c>
+      <c r="AD62">
+        <v>1.38</v>
+      </c>
+      <c r="AE62">
+        <v>1.11</v>
+      </c>
+      <c r="AF62">
+        <v>1.54</v>
+      </c>
+      <c r="AG62">
+        <v>2.25</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.25</v>
       </c>
-      <c r="T62">
-        <v>3.5</v>
-      </c>
-      <c r="U62">
-        <v>2.2</v>
-      </c>
-      <c r="V62">
-        <v>1.53</v>
-      </c>
-      <c r="W62">
-        <v>1.1</v>
-      </c>
-      <c r="X62">
-        <v>1.03</v>
-      </c>
-      <c r="Y62">
-        <v>1.14</v>
-      </c>
-      <c r="Z62">
-        <v>4.33</v>
-      </c>
-      <c r="AA62">
-        <v>1.57</v>
-      </c>
-      <c r="AB62">
-        <v>2.25</v>
-      </c>
-      <c r="AC62">
-        <v>2.35</v>
-      </c>
-      <c r="AD62">
-        <v>1.47</v>
-      </c>
-      <c r="AE62">
-        <v>1.22</v>
-      </c>
-      <c r="AF62">
-        <v>1.48</v>
-      </c>
-      <c r="AG62">
-        <v>2.45</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.21</v>
-      </c>
       <c r="AK62">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P63">
+        <v>5</v>
+      </c>
+      <c r="Q63">
+        <v>2.14</v>
+      </c>
+      <c r="R63">
+        <v>2.4</v>
+      </c>
+      <c r="S63">
+        <v>1.25</v>
+      </c>
+      <c r="T63">
+        <v>3.28</v>
+      </c>
+      <c r="U63">
+        <v>2.26</v>
+      </c>
+      <c r="V63">
+        <v>1.57</v>
+      </c>
+      <c r="W63">
+        <v>1.14</v>
+      </c>
+      <c r="X63">
+        <v>1.01</v>
+      </c>
+      <c r="Y63">
+        <v>1.13</v>
+      </c>
+      <c r="Z63">
+        <v>4.5</v>
+      </c>
+      <c r="AA63">
+        <v>1.5</v>
+      </c>
+      <c r="AB63">
         <v>2.5</v>
       </c>
-      <c r="Q63">
-        <v>2.96</v>
-      </c>
-      <c r="R63">
-        <v>2.19</v>
-      </c>
-      <c r="S63">
-        <v>1.28</v>
-      </c>
-      <c r="T63">
-        <v>3.15</v>
-      </c>
-      <c r="U63">
-        <v>2.5</v>
-      </c>
-      <c r="V63">
-        <v>1.5</v>
-      </c>
-      <c r="W63">
-        <v>1.11</v>
-      </c>
-      <c r="X63">
-        <v>1.04</v>
-      </c>
-      <c r="Y63">
-        <v>1.16</v>
-      </c>
-      <c r="Z63">
-        <v>4.05</v>
-      </c>
-      <c r="AA63">
-        <v>1.67</v>
-      </c>
-      <c r="AB63">
-        <v>2.1</v>
-      </c>
       <c r="AC63">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="AD63">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AE63">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF63">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AG63">
+        <v>2.21</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>1.13</v>
+      </c>
+      <c r="AK63">
         <v>2.25</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.25</v>
-      </c>
-      <c r="AK63">
-        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
+        <v>4</v>
+      </c>
+      <c r="O112">
+        <v>4.33</v>
+      </c>
+      <c r="P112">
+        <v>1.75</v>
+      </c>
+      <c r="Q112">
+        <v>4.15</v>
+      </c>
+      <c r="R112">
+        <v>2.5</v>
+      </c>
+      <c r="S112">
         <v>1.22</v>
       </c>
-      <c r="O112">
-        <v>6.65</v>
-      </c>
-      <c r="P112">
-        <v>10.5</v>
-      </c>
-      <c r="Q112">
-        <v>1.57</v>
-      </c>
-      <c r="R112">
-        <v>3</v>
-      </c>
-      <c r="S112">
+      <c r="T112">
+        <v>4.05</v>
+      </c>
+      <c r="U112">
+        <v>2</v>
+      </c>
+      <c r="V112">
+        <v>1.79</v>
+      </c>
+      <c r="W112">
         <v>1.2</v>
       </c>
-      <c r="T112">
-        <v>4.2</v>
-      </c>
-      <c r="U112">
-        <v>2.02</v>
-      </c>
-      <c r="V112">
-        <v>1.88</v>
-      </c>
-      <c r="W112">
-        <v>1.22</v>
-      </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z112">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AA112">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AB112">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AC112">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AD112">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE112">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF112">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="AG112">
-        <v>1.96</v>
+        <v>2.75</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="AK112">
-        <v>4.15</v>
+        <v>1.26</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,80 +18728,80 @@
         </is>
       </c>
       <c r="N113">
-        <v>4</v>
+        <v>1.22</v>
       </c>
       <c r="O113">
-        <v>4.33</v>
+        <v>6.65</v>
       </c>
       <c r="P113">
-        <v>1.75</v>
+        <v>10.5</v>
       </c>
       <c r="Q113">
+        <v>1.57</v>
+      </c>
+      <c r="R113">
+        <v>3</v>
+      </c>
+      <c r="S113">
+        <v>1.2</v>
+      </c>
+      <c r="T113">
+        <v>4.2</v>
+      </c>
+      <c r="U113">
+        <v>2.02</v>
+      </c>
+      <c r="V113">
+        <v>1.88</v>
+      </c>
+      <c r="W113">
+        <v>1.22</v>
+      </c>
+      <c r="X113">
+        <v>1.01</v>
+      </c>
+      <c r="Y113">
+        <v>1.06</v>
+      </c>
+      <c r="Z113">
+        <v>6.75</v>
+      </c>
+      <c r="AA113">
+        <v>1.29</v>
+      </c>
+      <c r="AB113">
+        <v>3.2</v>
+      </c>
+      <c r="AC113">
+        <v>1.92</v>
+      </c>
+      <c r="AD113">
+        <v>1.9</v>
+      </c>
+      <c r="AE113">
+        <v>1.4</v>
+      </c>
+      <c r="AF113">
+        <v>1.77</v>
+      </c>
+      <c r="AG113">
+        <v>1.96</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
+        <v>1.12</v>
+      </c>
+      <c r="AK113">
         <v>4.15</v>
-      </c>
-      <c r="R113">
-        <v>2.5</v>
-      </c>
-      <c r="S113">
-        <v>1.22</v>
-      </c>
-      <c r="T113">
-        <v>4.05</v>
-      </c>
-      <c r="U113">
-        <v>2</v>
-      </c>
-      <c r="V113">
-        <v>1.79</v>
-      </c>
-      <c r="W113">
-        <v>1.2</v>
-      </c>
-      <c r="X113">
-        <v>1.02</v>
-      </c>
-      <c r="Y113">
-        <v>1.12</v>
-      </c>
-      <c r="Z113">
-        <v>7</v>
-      </c>
-      <c r="AA113">
-        <v>1.42</v>
-      </c>
-      <c r="AB113">
-        <v>2.88</v>
-      </c>
-      <c r="AC113">
-        <v>2</v>
-      </c>
-      <c r="AD113">
-        <v>1.83</v>
-      </c>
-      <c r="AE113">
-        <v>1.33</v>
-      </c>
-      <c r="AF113">
-        <v>1.45</v>
-      </c>
-      <c r="AG113">
-        <v>2.75</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>2.1</v>
-      </c>
-      <c r="AK113">
-        <v>1.26</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="O132">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="P132">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="Q132">
-        <v>2.03</v>
+        <v>2.68</v>
       </c>
       <c r="R132">
-        <v>2.52</v>
+        <v>2.13</v>
       </c>
       <c r="S132">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="T132">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="U132">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V132">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W132">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X132">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y132">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z132">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA132">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AB132">
-        <v>2.24</v>
+        <v>1.81</v>
       </c>
       <c r="AC132">
-        <v>2.43</v>
+        <v>3.25</v>
       </c>
       <c r="AD132">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE132">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF132">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG132">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,61 +21988,61 @@
         </is>
       </c>
       <c r="N133">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O133">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P133">
-        <v>1.98</v>
+        <v>2.82</v>
       </c>
       <c r="Q133">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R133">
         <v>2.15</v>
       </c>
       <c r="S133">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T133">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="U133">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V133">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W133">
         <v>1.05</v>
       </c>
       <c r="X133">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y133">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z133">
-        <v>3.64</v>
+        <v>3.34</v>
       </c>
       <c r="AA133">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB133">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC133">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AD133">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AE133">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF133">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG133">
         <v>2.05</v>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK133">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,58 +22151,58 @@
         </is>
       </c>
       <c r="N134">
+        <v>3.15</v>
+      </c>
+      <c r="O134">
+        <v>3.3</v>
+      </c>
+      <c r="P134">
+        <v>1.98</v>
+      </c>
+      <c r="Q134">
+        <v>3.85</v>
+      </c>
+      <c r="R134">
         <v>2.15</v>
       </c>
-      <c r="O134">
-        <v>3.6</v>
-      </c>
-      <c r="P134">
-        <v>3.15</v>
-      </c>
-      <c r="Q134">
-        <v>2.68</v>
-      </c>
-      <c r="R134">
-        <v>2.13</v>
-      </c>
       <c r="S134">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T134">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="U134">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="V134">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W134">
         <v>1.05</v>
       </c>
       <c r="X134">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z134">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AA134">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB134">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC134">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AD134">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE134">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF134">
         <v>1.67</v>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK134">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="O135">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P135">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="Q135">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R135">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S135">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T135">
-        <v>2.81</v>
+        <v>2.57</v>
       </c>
       <c r="U135">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="V135">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W135">
         <v>1.05</v>
       </c>
       <c r="X135">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z135">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AA135">
+        <v>2.16</v>
+      </c>
+      <c r="AB135">
+        <v>1.67</v>
+      </c>
+      <c r="AC135">
+        <v>3.75</v>
+      </c>
+      <c r="AD135">
+        <v>1.16</v>
+      </c>
+      <c r="AE135">
+        <v>1.07</v>
+      </c>
+      <c r="AF135">
         <v>1.85</v>
       </c>
-      <c r="AB135">
+      <c r="AG135">
         <v>1.85</v>
-      </c>
-      <c r="AC135">
-        <v>3.08</v>
-      </c>
-      <c r="AD135">
-        <v>1.28</v>
-      </c>
-      <c r="AE135">
-        <v>1.11</v>
-      </c>
-      <c r="AF135">
-        <v>1.68</v>
-      </c>
-      <c r="AG135">
-        <v>2.05</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.62</v>
+        <v>1.6</v>
       </c>
       <c r="O136">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="P136">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="Q136">
-        <v>3</v>
+        <v>2.03</v>
       </c>
       <c r="R136">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="S136">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="T136">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="U136">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V136">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W136">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X136">
         <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="Z136">
-        <v>2.93</v>
+        <v>4.4</v>
       </c>
       <c r="AA136">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AB136">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="AC136">
-        <v>3.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD136">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE136">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AF136">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG136">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK136">
-        <v>1.38</v>
+        <v>2.31</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O137">
         <v>3.25</v>
       </c>
       <c r="P137">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q137">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R137">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S137">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T137">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="U137">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="V137">
+        <v>1.38</v>
+      </c>
+      <c r="W137">
+        <v>1.03</v>
+      </c>
+      <c r="X137">
+        <v>1.03</v>
+      </c>
+      <c r="Y137">
+        <v>1.34</v>
+      </c>
+      <c r="Z137">
+        <v>2.93</v>
+      </c>
+      <c r="AA137">
+        <v>2.02</v>
+      </c>
+      <c r="AB137">
+        <v>1.78</v>
+      </c>
+      <c r="AC137">
+        <v>3.42</v>
+      </c>
+      <c r="AD137">
+        <v>1.25</v>
+      </c>
+      <c r="AE137">
+        <v>1.04</v>
+      </c>
+      <c r="AF137">
+        <v>1.8</v>
+      </c>
+      <c r="AG137">
+        <v>2</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
         <v>1.29</v>
       </c>
-      <c r="W137">
-        <v>1.05</v>
-      </c>
-      <c r="X137">
-        <v>1.05</v>
-      </c>
-      <c r="Y137">
-        <v>1.32</v>
-      </c>
-      <c r="Z137">
-        <v>3.1</v>
-      </c>
-      <c r="AA137">
-        <v>2.16</v>
-      </c>
-      <c r="AB137">
-        <v>1.67</v>
-      </c>
-      <c r="AC137">
-        <v>3.75</v>
-      </c>
-      <c r="AD137">
-        <v>1.16</v>
-      </c>
-      <c r="AE137">
-        <v>1.07</v>
-      </c>
-      <c r="AF137">
-        <v>1.85</v>
-      </c>
-      <c r="AG137">
-        <v>1.85</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.3</v>
-      </c>
       <c r="AK137">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="O146">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="P146">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="Q146">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="R146">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S146">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T146">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U146">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="V146">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W146">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z146">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA146">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AB146">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC146">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD146">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE146">
         <v>1.06</v>
       </c>
       <c r="AF146">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AG146">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AK146">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="O147">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="P147">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="Q147">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="R147">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S147">
+        <v>1.47</v>
+      </c>
+      <c r="T147">
+        <v>2.75</v>
+      </c>
+      <c r="U147">
+        <v>3.2</v>
+      </c>
+      <c r="V147">
+        <v>1.3</v>
+      </c>
+      <c r="W147">
+        <v>1.04</v>
+      </c>
+      <c r="X147">
+        <v>1.03</v>
+      </c>
+      <c r="Y147">
         <v>1.4</v>
       </c>
-      <c r="T147">
-        <v>2.73</v>
-      </c>
-      <c r="U147">
-        <v>2.85</v>
-      </c>
-      <c r="V147">
-        <v>1.39</v>
-      </c>
-      <c r="W147">
-        <v>1.05</v>
-      </c>
-      <c r="X147">
-        <v>1.01</v>
-      </c>
-      <c r="Y147">
-        <v>1.32</v>
-      </c>
       <c r="Z147">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA147">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB147">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC147">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD147">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE147">
         <v>1.06</v>
       </c>
       <c r="AF147">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AG147">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AK147">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,64 +24759,64 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="O150">
+        <v>3.7</v>
+      </c>
+      <c r="P150">
+        <v>4</v>
+      </c>
+      <c r="Q150">
+        <v>2.25</v>
+      </c>
+      <c r="R150">
+        <v>2.3</v>
+      </c>
+      <c r="S150">
+        <v>1.25</v>
+      </c>
+      <c r="T150">
         <v>3.3</v>
       </c>
-      <c r="P150">
-        <v>2.55</v>
-      </c>
-      <c r="Q150">
-        <v>2.85</v>
-      </c>
-      <c r="R150">
-        <v>2.1</v>
-      </c>
-      <c r="S150">
-        <v>1.37</v>
-      </c>
-      <c r="T150">
-        <v>2.9</v>
-      </c>
       <c r="U150">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="V150">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W150">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X150">
         <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z150">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA150">
-        <v>1.93</v>
+        <v>1.59</v>
       </c>
       <c r="AB150">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AC150">
-        <v>3.39</v>
+        <v>2.56</v>
       </c>
       <c r="AD150">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AE150">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF150">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG150">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AK150">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,31 +24922,31 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="O151">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P151">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Q151">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R151">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S151">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T151">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U151">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V151">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W151">
         <v>1.12</v>
@@ -24955,31 +24955,31 @@
         <v>1.01</v>
       </c>
       <c r="Y151">
+        <v>1.2</v>
+      </c>
+      <c r="Z151">
+        <v>3.7</v>
+      </c>
+      <c r="AA151">
+        <v>1.65</v>
+      </c>
+      <c r="AB151">
+        <v>2.25</v>
+      </c>
+      <c r="AC151">
+        <v>2.48</v>
+      </c>
+      <c r="AD151">
+        <v>1.43</v>
+      </c>
+      <c r="AE151">
         <v>1.18</v>
       </c>
-      <c r="Z151">
-        <v>4.2</v>
-      </c>
-      <c r="AA151">
-        <v>1.59</v>
-      </c>
-      <c r="AB151">
-        <v>2.17</v>
-      </c>
-      <c r="AC151">
-        <v>2.56</v>
-      </c>
-      <c r="AD151">
-        <v>1.49</v>
-      </c>
-      <c r="AE151">
-        <v>1.15</v>
-      </c>
       <c r="AF151">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG151">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK151">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="O152">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P152">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q152">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R152">
         <v>2.25</v>
       </c>
       <c r="S152">
+        <v>1.34</v>
+      </c>
+      <c r="T152">
+        <v>3.05</v>
+      </c>
+      <c r="U152">
+        <v>2.6</v>
+      </c>
+      <c r="V152">
+        <v>1.43</v>
+      </c>
+      <c r="W152">
+        <v>1.07</v>
+      </c>
+      <c r="X152">
+        <v>1.01</v>
+      </c>
+      <c r="Y152">
+        <v>1.22</v>
+      </c>
+      <c r="Z152">
+        <v>3.93</v>
+      </c>
+      <c r="AA152">
+        <v>1.8</v>
+      </c>
+      <c r="AB152">
+        <v>2</v>
+      </c>
+      <c r="AC152">
+        <v>2.71</v>
+      </c>
+      <c r="AD152">
         <v>1.36</v>
       </c>
-      <c r="T152">
-        <v>2.81</v>
-      </c>
-      <c r="U152">
-        <v>2.81</v>
-      </c>
-      <c r="V152">
-        <v>1.38</v>
-      </c>
-      <c r="W152">
-        <v>1.04</v>
-      </c>
-      <c r="X152">
-        <v>1.03</v>
-      </c>
-      <c r="Y152">
-        <v>1.3</v>
-      </c>
-      <c r="Z152">
-        <v>3.45</v>
-      </c>
-      <c r="AA152">
-        <v>1.9</v>
-      </c>
-      <c r="AB152">
-        <v>1.8</v>
-      </c>
-      <c r="AC152">
-        <v>3.34</v>
-      </c>
-      <c r="AD152">
-        <v>1.31</v>
-      </c>
       <c r="AE152">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF152">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG152">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>1.19</v>
       </c>
       <c r="AK152">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="O153">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P153">
-        <v>3.4</v>
+        <v>4.68</v>
       </c>
       <c r="Q153">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="R153">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="S153">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T153">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U153">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V153">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W153">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X153">
         <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z153">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AA153">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AB153">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC153">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="AD153">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AE153">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AF153">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG153">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK153">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,31 +25411,31 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.74</v>
+        <v>2.98</v>
       </c>
       <c r="O154">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P154">
-        <v>4.33</v>
+        <v>1.97</v>
       </c>
       <c r="Q154">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="R154">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S154">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T154">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="U154">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V154">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W154">
         <v>1.07</v>
@@ -25444,31 +25444,31 @@
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="AA154">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB154">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC154">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="AD154">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE154">
         <v>1.13</v>
       </c>
       <c r="AF154">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG154">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK154">
-        <v>1.98</v>
+        <v>1.29</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.98</v>
+        <v>1.83</v>
       </c>
       <c r="O155">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P155">
-        <v>1.97</v>
+        <v>4</v>
       </c>
       <c r="Q155">
-        <v>3.65</v>
+        <v>2.43</v>
       </c>
       <c r="R155">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S155">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T155">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="U155">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="V155">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W155">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X155">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y155">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z155">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AA155">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB155">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC155">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AD155">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE155">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG155">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK155">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="O156">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P156">
-        <v>4.68</v>
+        <v>2.55</v>
       </c>
       <c r="Q156">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="R156">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="S156">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T156">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="U156">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="V156">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W156">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X156">
         <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z156">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA156">
-        <v>1.47</v>
+        <v>1.93</v>
       </c>
       <c r="AB156">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AC156">
-        <v>2.12</v>
+        <v>3.39</v>
       </c>
       <c r="AD156">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AE156">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AF156">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AK156">
-        <v>2.19</v>
+        <v>1.44</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -31466,10 +31466,10 @@
         <v>2.92</v>
       </c>
       <c r="V191">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W191">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X191">
         <v>1.05</v>
@@ -31481,19 +31481,19 @@
         <v>3.2</v>
       </c>
       <c r="AA191">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AB191">
         <v>1.75</v>
       </c>
       <c r="AC191">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD191">
         <v>1.28</v>
       </c>
       <c r="AE191">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF191">
         <v>1.73</v>
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK191">
         <v>1.5</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="O206">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P206">
-        <v>3</v>
+        <v>4.01</v>
       </c>
       <c r="Q206">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="R206">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S206">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T206">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="U206">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V206">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W206">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X206">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z206">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="AA206">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB206">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AC206">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="AD206">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AE206">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF206">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG206">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK206">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,80 +34050,80 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="O207">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P207">
-        <v>4.01</v>
+        <v>3</v>
       </c>
       <c r="Q207">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="R207">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S207">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T207">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="U207">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V207">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W207">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X207">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z207">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="AA207">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB207">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AC207">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AD207">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AE207">
+        <v>1.29</v>
+      </c>
+      <c r="AF207">
+        <v>1.36</v>
+      </c>
+      <c r="AG207">
+        <v>3</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
         <v>1.25</v>
       </c>
-      <c r="AF207">
-        <v>1.45</v>
-      </c>
-      <c r="AG207">
-        <v>2.5</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.22</v>
-      </c>
       <c r="AK207">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O214">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P214">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q215">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R215">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S215">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T215">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U215">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="V215">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W215">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X215">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y215">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z215">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA215">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB215">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC215">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD215">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE215">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF215">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG215">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK215">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G225">
@@ -36987,61 +36987,61 @@
         <v>2.05</v>
       </c>
       <c r="O225">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P225">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q225">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="R225">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="S225">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="T225">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="U225">
-        <v>3.07</v>
+        <v>2.41</v>
       </c>
       <c r="V225">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W225">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X225">
         <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z225">
-        <v>3.12</v>
+        <v>4.05</v>
       </c>
       <c r="AA225">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AB225">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC225">
-        <v>4.2</v>
+        <v>2.48</v>
       </c>
       <c r="AD225">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AE225">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AF225">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG225">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>1.3</v>
       </c>
       <c r="AK225">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G226">
@@ -37150,61 +37150,61 @@
         <v>2.05</v>
       </c>
       <c r="O226">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P226">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q226">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="R226">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="S226">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="T226">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="U226">
-        <v>2.41</v>
+        <v>3.07</v>
       </c>
       <c r="V226">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W226">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X226">
         <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="Z226">
-        <v>4.05</v>
+        <v>3.12</v>
       </c>
       <c r="AA226">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AB226">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC226">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD226">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AE226">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF226">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG226">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>1.3</v>
       </c>
       <c r="AK226">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,80 +39266,80 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q239">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="R239">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S239">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T239">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="U239">
         <v>2.75</v>
       </c>
       <c r="V239">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W239">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X239">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y239">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z239">
-        <v>3.24</v>
+        <v>3.51</v>
       </c>
       <c r="AA239">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AB239">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AC239">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="AD239">
+        <v>1.29</v>
+      </c>
+      <c r="AE239">
+        <v>1.08</v>
+      </c>
+      <c r="AF239">
+        <v>1.67</v>
+      </c>
+      <c r="AG239">
+        <v>2.03</v>
+      </c>
+      <c r="AH239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ239">
         <v>1.24</v>
       </c>
-      <c r="AE239">
-        <v>1.05</v>
-      </c>
-      <c r="AF239">
-        <v>1.75</v>
-      </c>
-      <c r="AG239">
-        <v>1.95</v>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ239">
-        <v>1.38</v>
-      </c>
       <c r="AK239">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,64 +39429,64 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O240">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P240">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q240">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="R240">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S240">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T240">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="U240">
         <v>2.75</v>
       </c>
       <c r="V240">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W240">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X240">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y240">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z240">
-        <v>3.51</v>
+        <v>3.24</v>
       </c>
       <c r="AA240">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AB240">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AC240">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="AD240">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE240">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF240">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG240">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AK240">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -41711,64 +41711,64 @@
         </is>
       </c>
       <c r="N254">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="O254">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P254">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q254">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="R254">
         <v>2.15</v>
       </c>
       <c r="S254">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T254">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="U254">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="V254">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W254">
         <v>1.06</v>
       </c>
       <c r="X254">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y254">
         <v>1.28</v>
       </c>
       <c r="Z254">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA254">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB254">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC254">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AD254">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE254">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF254">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG254">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK254">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O274">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="P274">
-        <v>2.77</v>
+        <v>2.44</v>
       </c>
       <c r="Q274">
         <v>3.1</v>
       </c>
       <c r="R274">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S274">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T274">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="U274">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="V274">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W274">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X274">
         <v>1.04</v>
       </c>
       <c r="Y274">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z274">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA274">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB274">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC274">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD274">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AE274">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF274">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AG274">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AK274">
         <v>1.52</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="O275">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="P275">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="Q275">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="R275">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S275">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="T275">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="U275">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="V275">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W275">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X275">
         <v>1.04</v>
       </c>
       <c r="Y275">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z275">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AA275">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB275">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC275">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD275">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE275">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF275">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AG275">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK275">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="O276">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="P276">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="Q276">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="R276">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S276">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="T276">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="U276">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="V276">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W276">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X276">
         <v>1.04</v>
       </c>
       <c r="Y276">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z276">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA276">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB276">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC276">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD276">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE276">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF276">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG276">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK276">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,64 +50024,64 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="O305">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P305">
         <v>4.4</v>
       </c>
       <c r="Q305">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R305">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="S305">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T305">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U305">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="V305">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W305">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X305">
         <v>1.01</v>
       </c>
       <c r="Y305">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z305">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA305">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB305">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AC305">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="AD305">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AE305">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AF305">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG305">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK305">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.71</v>
+        <v>4.2</v>
       </c>
       <c r="O306">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P306">
-        <v>4.4</v>
+        <v>1.57</v>
       </c>
       <c r="Q306">
-        <v>2.25</v>
+        <v>4.97</v>
       </c>
       <c r="R306">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="S306">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T306">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U306">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="V306">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W306">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X306">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y306">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z306">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="AA306">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB306">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC306">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="AD306">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE306">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF306">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG306">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK306">
-        <v>1.86</v>
+        <v>1.12</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>4.2</v>
+        <v>1.56</v>
       </c>
       <c r="O308">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P308">
-        <v>1.57</v>
+        <v>4.4</v>
       </c>
       <c r="Q308">
-        <v>4.97</v>
+        <v>2</v>
       </c>
       <c r="R308">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S308">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T308">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U308">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="V308">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W308">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X308">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y308">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z308">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA308">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB308">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC308">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AD308">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AE308">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF308">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG308">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>1.16</v>
       </c>
       <c r="AK308">
-        <v>1.12</v>
+        <v>2.16</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="O325">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P325">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="Q325">
-        <v>4.55</v>
+        <v>3.51</v>
       </c>
       <c r="R325">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S325">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T325">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U325">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="V325">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W325">
         <v>1.03</v>
       </c>
       <c r="X325">
+        <v>1.08</v>
+      </c>
+      <c r="Y325">
+        <v>1.4</v>
+      </c>
+      <c r="Z325">
+        <v>2.65</v>
+      </c>
+      <c r="AA325">
+        <v>2.4</v>
+      </c>
+      <c r="AB325">
+        <v>1.6</v>
+      </c>
+      <c r="AC325">
+        <v>4.22</v>
+      </c>
+      <c r="AD325">
+        <v>1.2</v>
+      </c>
+      <c r="AE325">
         <v>1.04</v>
       </c>
-      <c r="Y325">
-        <v>1.38</v>
-      </c>
-      <c r="Z325">
-        <v>2.85</v>
-      </c>
-      <c r="AA325">
-        <v>2.23</v>
-      </c>
-      <c r="AB325">
-        <v>1.57</v>
-      </c>
-      <c r="AC325">
-        <v>4</v>
-      </c>
-      <c r="AD325">
-        <v>1.19</v>
-      </c>
-      <c r="AE325">
-        <v>1.03</v>
-      </c>
       <c r="AF325">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AG325">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK325">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,64 +53447,64 @@
         </is>
       </c>
       <c r="N326">
-        <v>2.7</v>
+        <v>1.36</v>
       </c>
       <c r="O326">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="P326">
-        <v>2.55</v>
+        <v>7.35</v>
       </c>
       <c r="Q326">
-        <v>3.51</v>
+        <v>1.86</v>
       </c>
       <c r="R326">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="S326">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="T326">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="U326">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="V326">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="W326">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X326">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y326">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z326">
-        <v>2.65</v>
+        <v>3.79</v>
       </c>
       <c r="AA326">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB326">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="AC326">
-        <v>4.22</v>
+        <v>2.82</v>
       </c>
       <c r="AD326">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE326">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF326">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AG326">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK326">
-        <v>1.4</v>
+        <v>2.83</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
+        <v>1.77</v>
+      </c>
+      <c r="O327">
+        <v>3.3</v>
+      </c>
+      <c r="P327">
+        <v>4.45</v>
+      </c>
+      <c r="Q327">
+        <v>2.43</v>
+      </c>
+      <c r="R327">
+        <v>1.95</v>
+      </c>
+      <c r="S327">
+        <v>1.46</v>
+      </c>
+      <c r="T327">
+        <v>2.44</v>
+      </c>
+      <c r="U327">
+        <v>3.25</v>
+      </c>
+      <c r="V327">
+        <v>1.27</v>
+      </c>
+      <c r="W327">
+        <v>1.03</v>
+      </c>
+      <c r="X327">
+        <v>1.02</v>
+      </c>
+      <c r="Y327">
         <v>1.36</v>
       </c>
-      <c r="O327">
-        <v>4.35</v>
-      </c>
-      <c r="P327">
-        <v>7.35</v>
-      </c>
-      <c r="Q327">
-        <v>1.86</v>
-      </c>
-      <c r="R327">
-        <v>2.33</v>
-      </c>
-      <c r="S327">
-        <v>1.28</v>
-      </c>
-      <c r="T327">
-        <v>3.16</v>
-      </c>
-      <c r="U327">
-        <v>2.42</v>
-      </c>
-      <c r="V327">
-        <v>1.47</v>
-      </c>
-      <c r="W327">
-        <v>1.09</v>
-      </c>
-      <c r="X327">
-        <v>1.04</v>
-      </c>
-      <c r="Y327">
-        <v>1.21</v>
-      </c>
       <c r="Z327">
-        <v>3.79</v>
+        <v>2.77</v>
       </c>
       <c r="AA327">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="AB327">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AC327">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD327">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AE327">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF327">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG327">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK327">
-        <v>2.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,43 +53773,43 @@
         </is>
       </c>
       <c r="N328">
-        <v>1.77</v>
+        <v>3.65</v>
       </c>
       <c r="O328">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P328">
-        <v>4.45</v>
+        <v>2.02</v>
       </c>
       <c r="Q328">
-        <v>2.43</v>
+        <v>4.55</v>
       </c>
       <c r="R328">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="S328">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T328">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U328">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="V328">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W328">
         <v>1.03</v>
       </c>
       <c r="X328">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y328">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z328">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="AA328">
         <v>2.23</v>
@@ -53818,19 +53818,19 @@
         <v>1.57</v>
       </c>
       <c r="AC328">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD328">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE328">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF328">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AG328">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK328">
-        <v>1.91</v>
+        <v>1.19</v>
       </c>
       <c r="AL328">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T2">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="U2">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R4">
+        <v>2.15</v>
+      </c>
+      <c r="S4">
+        <v>1.37</v>
+      </c>
+      <c r="T4">
+        <v>2.85</v>
+      </c>
+      <c r="U4">
+        <v>2.77</v>
+      </c>
+      <c r="V4">
+        <v>1.39</v>
+      </c>
+      <c r="W4">
+        <v>1.04</v>
+      </c>
+      <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>1.29</v>
+      </c>
+      <c r="Z4">
+        <v>3.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.9</v>
+      </c>
+      <c r="AB4">
+        <v>1.9</v>
+      </c>
+      <c r="AC4">
+        <v>3.2</v>
+      </c>
+      <c r="AD4">
+        <v>1.3</v>
+      </c>
+      <c r="AE4">
+        <v>1.11</v>
+      </c>
+      <c r="AF4">
+        <v>1.67</v>
+      </c>
+      <c r="AG4">
         <v>2.1</v>
       </c>
-      <c r="S4">
-        <v>1.42</v>
-      </c>
-      <c r="T4">
-        <v>2.65</v>
-      </c>
-      <c r="U4">
-        <v>2.99</v>
-      </c>
-      <c r="V4">
-        <v>1.34</v>
-      </c>
-      <c r="W4">
-        <v>1.02</v>
-      </c>
-      <c r="X4">
-        <v>1.06</v>
-      </c>
-      <c r="Y4">
-        <v>1.33</v>
-      </c>
-      <c r="Z4">
-        <v>3.1</v>
-      </c>
-      <c r="AA4">
-        <v>2</v>
-      </c>
-      <c r="AB4">
-        <v>1.73</v>
-      </c>
-      <c r="AC4">
-        <v>3.6</v>
-      </c>
-      <c r="AD4">
-        <v>1.25</v>
-      </c>
-      <c r="AE4">
-        <v>1.08</v>
-      </c>
-      <c r="AF4">
-        <v>1.75</v>
-      </c>
-      <c r="AG4">
-        <v>1.95</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>2.16</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P7">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.71</v>
+        <v>1.83</v>
       </c>
       <c r="O33">
+        <v>3.8</v>
+      </c>
+      <c r="P33">
+        <v>3.5</v>
+      </c>
+      <c r="Q33">
+        <v>2.36</v>
+      </c>
+      <c r="R33">
+        <v>2.29</v>
+      </c>
+      <c r="S33">
+        <v>1.26</v>
+      </c>
+      <c r="T33">
         <v>3.6</v>
       </c>
-      <c r="P33">
-        <v>2.17</v>
-      </c>
-      <c r="Q33">
-        <v>3</v>
-      </c>
-      <c r="R33">
-        <v>2.3</v>
-      </c>
-      <c r="S33">
-        <v>1.3</v>
-      </c>
-      <c r="T33">
-        <v>3.22</v>
-      </c>
       <c r="U33">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5727,10 +5727,10 @@
         <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB33">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC33">
         <v>2.45</v>
@@ -5739,13 +5739,13 @@
         <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF33">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG33">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.83</v>
+        <v>2.71</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="Q34">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U34">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5890,10 +5890,10 @@
         <v>4.6</v>
       </c>
       <c r="AA34">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
         <v>2.45</v>
@@ -5902,13 +5902,13 @@
         <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG34">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7327,10 +7327,10 @@
         <v>5.25</v>
       </c>
       <c r="Q43">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S43">
         <v>1.23</v>
@@ -7339,7 +7339,7 @@
         <v>3.42</v>
       </c>
       <c r="U43">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V43">
         <v>1.59</v>
@@ -7348,7 +7348,7 @@
         <v>1.12</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y43">
         <v>1.12</v>
@@ -7363,19 +7363,19 @@
         <v>2.33</v>
       </c>
       <c r="AC43">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD43">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE43">
         <v>1.17</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK43">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="O44">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="P44">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q44">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="R44">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="S44">
         <v>1.15</v>
@@ -7523,22 +7523,22 @@
         <v>1.28</v>
       </c>
       <c r="AB44">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AC44">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD44">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AE44">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AF44">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG44">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AK44">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="O46">
         <v>3.7</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T46">
-        <v>3.42</v>
+        <v>2.82</v>
       </c>
       <c r="U46">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
+        <v>1.07</v>
+      </c>
+      <c r="X46">
+        <v>1.04</v>
+      </c>
+      <c r="Y46">
+        <v>1.23</v>
+      </c>
+      <c r="Z46">
+        <v>3.85</v>
+      </c>
+      <c r="AA46">
+        <v>1.8</v>
+      </c>
+      <c r="AB46">
+        <v>2</v>
+      </c>
+      <c r="AC46">
+        <v>2.9</v>
+      </c>
+      <c r="AD46">
+        <v>1.36</v>
+      </c>
+      <c r="AE46">
         <v>1.13</v>
       </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>1.15</v>
-      </c>
-      <c r="Z46">
-        <v>4.3</v>
-      </c>
-      <c r="AA46">
-        <v>1.57</v>
-      </c>
-      <c r="AB46">
-        <v>2.17</v>
-      </c>
-      <c r="AC46">
-        <v>2.51</v>
-      </c>
-      <c r="AD46">
-        <v>1.47</v>
-      </c>
-      <c r="AE46">
-        <v>1.18</v>
-      </c>
       <c r="AF46">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="O47">
         <v>3.7</v>
       </c>
       <c r="P47">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q47">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="T47">
-        <v>2.82</v>
+        <v>3.42</v>
       </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AA47">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB47">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC47">
-        <v>2.9</v>
+        <v>2.51</v>
       </c>
       <c r="AD47">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG47">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK47">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="O50">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Q50">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S50">
+        <v>1.29</v>
+      </c>
+      <c r="T50">
+        <v>3.3</v>
+      </c>
+      <c r="U50">
+        <v>2.64</v>
+      </c>
+      <c r="V50">
+        <v>1.44</v>
+      </c>
+      <c r="W50">
+        <v>1.08</v>
+      </c>
+      <c r="X50">
+        <v>1.05</v>
+      </c>
+      <c r="Y50">
+        <v>1.24</v>
+      </c>
+      <c r="Z50">
+        <v>3.98</v>
+      </c>
+      <c r="AA50">
+        <v>1.78</v>
+      </c>
+      <c r="AB50">
+        <v>2</v>
+      </c>
+      <c r="AC50">
+        <v>2.76</v>
+      </c>
+      <c r="AD50">
         <v>1.39</v>
       </c>
-      <c r="T50">
-        <v>2.65</v>
-      </c>
-      <c r="U50">
-        <v>2.95</v>
-      </c>
-      <c r="V50">
-        <v>1.33</v>
-      </c>
-      <c r="W50">
-        <v>1.05</v>
-      </c>
-      <c r="X50">
-        <v>1.06</v>
-      </c>
-      <c r="Y50">
-        <v>1.37</v>
-      </c>
-      <c r="Z50">
-        <v>2.94</v>
-      </c>
-      <c r="AA50">
-        <v>2.1</v>
-      </c>
-      <c r="AB50">
-        <v>1.7</v>
-      </c>
-      <c r="AC50">
-        <v>3.78</v>
-      </c>
-      <c r="AD50">
-        <v>1.19</v>
-      </c>
       <c r="AE50">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="Q51">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="R51">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="U51">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y51">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Z51">
-        <v>3.98</v>
+        <v>2.94</v>
       </c>
       <c r="AA51">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC51">
-        <v>2.76</v>
+        <v>3.78</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AE51">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>0</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11559,22 +11559,22 @@
         <v>3.6</v>
       </c>
       <c r="O69">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P69">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q69">
-        <v>4</v>
+        <v>4.72</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S69">
         <v>1.36</v>
       </c>
       <c r="T69">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U69">
         <v>2.85</v>
@@ -11583,7 +11583,7 @@
         <v>1.36</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
         <v>1.05</v>
@@ -11607,10 +11607,10 @@
         <v>1.32</v>
       </c>
       <c r="AE69">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF69">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG69">
         <v>2</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,22 +11728,22 @@
         <v>2.18</v>
       </c>
       <c r="Q70">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R70">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U70">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="V70">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
         <v>1.06</v>
@@ -11773,10 +11773,10 @@
         <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG70">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="AK70">
         <v>1.3</v>
@@ -13678,55 +13678,55 @@
         <v>3.2</v>
       </c>
       <c r="O82">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P82">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="Q82">
-        <v>3.4</v>
+        <v>4.18</v>
       </c>
       <c r="R82">
         <v>2</v>
       </c>
       <c r="S82">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="T82">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="U82">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="V82">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W82">
         <v>1.03</v>
       </c>
       <c r="X82">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y82">
         <v>1.35</v>
       </c>
       <c r="Z82">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AA82">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB82">
         <v>1.6</v>
       </c>
       <c r="AC82">
-        <v>4.33</v>
+        <v>3.74</v>
       </c>
       <c r="AD82">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE82">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF82">
         <v>1.91</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AK82">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
         <v>3.1</v>
@@ -13847,19 +13847,19 @@
         <v>3</v>
       </c>
       <c r="Q83">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R83">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T83">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U83">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="V83">
         <v>1.35</v>
@@ -13877,25 +13877,25 @@
         <v>3.12</v>
       </c>
       <c r="AA83">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AB83">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC83">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="AD83">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE83">
         <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG83">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,58 +14001,58 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="O84">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P84">
-        <v>3.99</v>
+        <v>4.05</v>
       </c>
       <c r="Q84">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R84">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T84">
         <v>2.7</v>
       </c>
       <c r="U84">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="V84">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W84">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y84">
         <v>1.36</v>
       </c>
       <c r="Z84">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AA84">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB84">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC84">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD84">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE84">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF84">
         <v>1.85</v>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
         <v>1.75</v>
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O85">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P85">
         <v>2.6</v>
@@ -14185,13 +14185,13 @@
         <v>2.53</v>
       </c>
       <c r="U85">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V85">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W85">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X85">
         <v>1.01</v>
@@ -14221,7 +14221,7 @@
         <v>1.81</v>
       </c>
       <c r="AG85">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14336,16 +14336,16 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="R86">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S86">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T86">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="U86">
         <v>2.8</v>
@@ -14354,7 +14354,7 @@
         <v>1.35</v>
       </c>
       <c r="W86">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X86">
         <v>1.02</v>
@@ -14372,19 +14372,19 @@
         <v>1.7</v>
       </c>
       <c r="AC86">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD86">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE86">
         <v>1.04</v>
       </c>
       <c r="AF86">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG86">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -16120,37 +16120,37 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O97">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P97">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q97">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R97">
         <v>1.98</v>
       </c>
       <c r="S97">
+        <v>1.4</v>
+      </c>
+      <c r="T97">
+        <v>2.71</v>
+      </c>
+      <c r="U97">
+        <v>2.75</v>
+      </c>
+      <c r="V97">
         <v>1.36</v>
       </c>
-      <c r="T97">
-        <v>2.88</v>
-      </c>
-      <c r="U97">
-        <v>2.8</v>
-      </c>
-      <c r="V97">
-        <v>1.33</v>
-      </c>
       <c r="W97">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
         <v>1.29</v>
@@ -16159,25 +16159,25 @@
         <v>3.04</v>
       </c>
       <c r="AA97">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB97">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC97">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD97">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE97">
         <v>1.04</v>
       </c>
       <c r="AF97">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG97">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.27</v>
       </c>
       <c r="AK97">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="O98">
         <v>3.2</v>
       </c>
       <c r="P98">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q98">
+        <v>3.38</v>
+      </c>
+      <c r="R98">
+        <v>2</v>
+      </c>
+      <c r="S98">
+        <v>1.38</v>
+      </c>
+      <c r="T98">
+        <v>2.67</v>
+      </c>
+      <c r="U98">
         <v>2.88</v>
       </c>
-      <c r="R98">
-        <v>2.1</v>
-      </c>
-      <c r="S98">
-        <v>1.36</v>
-      </c>
-      <c r="T98">
-        <v>2.75</v>
-      </c>
-      <c r="U98">
-        <v>2.79</v>
-      </c>
       <c r="V98">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W98">
         <v>1.03</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z98">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA98">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AB98">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC98">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD98">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE98">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF98">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AG98">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK98">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,19 +16446,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O99">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P99">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q99">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="R99">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S99">
         <v>1.4</v>
@@ -16467,43 +16467,43 @@
         <v>2.75</v>
       </c>
       <c r="U99">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="V99">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
         <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z99">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AA99">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AB99">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC99">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AD99">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE99">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF99">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG99">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK99">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16621,7 +16621,7 @@
         <v>2.12</v>
       </c>
       <c r="R100">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S100">
         <v>1.28</v>
@@ -16630,13 +16630,13 @@
         <v>3.35</v>
       </c>
       <c r="U100">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V100">
         <v>1.55</v>
       </c>
       <c r="W100">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
         <v>1.02</v>
@@ -16663,10 +16663,10 @@
         <v>1.15</v>
       </c>
       <c r="AF100">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AG100">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK100">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -18076,61 +18076,61 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="O109">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="P109">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q109">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="R109">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S109">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
         <v>3.58</v>
       </c>
       <c r="U109">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V109">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W109">
         <v>1.15</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z109">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AA109">
         <v>1.53</v>
       </c>
       <c r="AB109">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC109">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AD109">
         <v>1.57</v>
       </c>
       <c r="AE109">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF109">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG109">
         <v>2.3</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="O110">
         <v>3.9</v>
       </c>
       <c r="P110">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q110">
         <v>2.38</v>
@@ -18257,43 +18257,43 @@
         <v>1.2</v>
       </c>
       <c r="T110">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U110">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V110">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W110">
         <v>1.15</v>
       </c>
       <c r="X110">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z110">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA110">
         <v>1.5</v>
       </c>
       <c r="AB110">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC110">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD110">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE110">
         <v>1.25</v>
       </c>
       <c r="AF110">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG110">
         <v>2.6</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
+        <v>2.3</v>
+      </c>
+      <c r="O111">
+        <v>3.9</v>
+      </c>
+      <c r="P111">
+        <v>2.69</v>
+      </c>
+      <c r="Q111">
+        <v>2.7</v>
+      </c>
+      <c r="R111">
+        <v>2.45</v>
+      </c>
+      <c r="S111">
+        <v>1.21</v>
+      </c>
+      <c r="T111">
         <v>4</v>
       </c>
-      <c r="O111">
-        <v>4.1</v>
-      </c>
-      <c r="P111">
-        <v>1.75</v>
-      </c>
-      <c r="Q111">
-        <v>4.37</v>
-      </c>
-      <c r="R111">
-        <v>2.5</v>
-      </c>
-      <c r="S111">
-        <v>1.2</v>
-      </c>
-      <c r="T111">
-        <v>4.33</v>
-      </c>
       <c r="U111">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V111">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="W111">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z111">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA111">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB111">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC111">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD111">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AE111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF111">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AG111">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AK111">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="O112">
-        <v>3.9</v>
+        <v>4.16</v>
       </c>
       <c r="P112">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q112">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="R112">
         <v>2.5</v>
       </c>
       <c r="S112">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U112">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V112">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W112">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X112">
         <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z112">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA112">
         <v>1.4</v>
       </c>
       <c r="AB112">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AC112">
         <v>1.95</v>
       </c>
       <c r="AD112">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE112">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF112">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AG112">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18731,13 +18731,13 @@
         <v>1.23</v>
       </c>
       <c r="O113">
-        <v>6.65</v>
+        <v>6.9</v>
       </c>
       <c r="P113">
-        <v>10.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q113">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R113">
         <v>3.1</v>
@@ -18752,34 +18752,34 @@
         <v>2.02</v>
       </c>
       <c r="V113">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="W113">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z113">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA113">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB113">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AC113">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AD113">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AE113">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF113">
         <v>1.77</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK113">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.44</v>
+        <v>2.84</v>
       </c>
       <c r="O126">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="P126">
-        <v>6.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q126">
-        <v>1.93</v>
+        <v>3.23</v>
       </c>
       <c r="R126">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S126">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T126">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="U126">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="V126">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W126">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X126">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z126">
-        <v>3.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA126">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AB126">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
       <c r="AC126">
-        <v>3.06</v>
+        <v>3.65</v>
       </c>
       <c r="AD126">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE126">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF126">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG126">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="AK126">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.84</v>
+        <v>1.44</v>
       </c>
       <c r="O127">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="P127">
-        <v>2.33</v>
+        <v>6.25</v>
       </c>
       <c r="Q127">
-        <v>3.23</v>
+        <v>1.93</v>
       </c>
       <c r="R127">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S127">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T127">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U127">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="V127">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W127">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y127">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z127">
-        <v>2.97</v>
+        <v>3.95</v>
       </c>
       <c r="AA127">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AB127">
-        <v>1.71</v>
+        <v>2.03</v>
       </c>
       <c r="AC127">
-        <v>3.65</v>
+        <v>3.06</v>
       </c>
       <c r="AD127">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE127">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF127">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AG127">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="AK127">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="O132">
+        <v>3.6</v>
+      </c>
+      <c r="P132">
         <v>3.2</v>
       </c>
-      <c r="P132">
-        <v>2.9</v>
-      </c>
       <c r="Q132">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="R132">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S132">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T132">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="U132">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V132">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W132">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X132">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z132">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA132">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB132">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC132">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD132">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE132">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF132">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG132">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="O133">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P133">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="R133">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S133">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T133">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="U133">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="V133">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W133">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X133">
         <v>1.06</v>
       </c>
       <c r="Y133">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z133">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA133">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AB133">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC133">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD133">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE133">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF133">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG133">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="O134">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="P134">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="Q134">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="R134">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="S134">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T134">
-        <v>2.57</v>
+        <v>3.44</v>
       </c>
       <c r="U134">
-        <v>3.22</v>
+        <v>2.23</v>
       </c>
       <c r="V134">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="W134">
+        <v>1.11</v>
+      </c>
+      <c r="X134">
         <v>1.01</v>
       </c>
-      <c r="X134">
-        <v>1.06</v>
-      </c>
       <c r="Y134">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z134">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA134">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="AB134">
+        <v>2.2</v>
+      </c>
+      <c r="AC134">
+        <v>2.6</v>
+      </c>
+      <c r="AD134">
+        <v>1.47</v>
+      </c>
+      <c r="AE134">
+        <v>1.18</v>
+      </c>
+      <c r="AF134">
         <v>1.65</v>
       </c>
-      <c r="AC134">
-        <v>3.9</v>
-      </c>
-      <c r="AD134">
-        <v>1.18</v>
-      </c>
-      <c r="AE134">
-        <v>1.06</v>
-      </c>
-      <c r="AF134">
-        <v>1.85</v>
-      </c>
       <c r="AG134">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK134">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.15</v>
+        <v>2.37</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P135">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q135">
-        <v>3.52</v>
+        <v>2.87</v>
       </c>
       <c r="R135">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S135">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T135">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="U135">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="V135">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W135">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X135">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y135">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z135">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA135">
         <v>1.85</v>
       </c>
       <c r="AB135">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC135">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD135">
+        <v>1.33</v>
+      </c>
+      <c r="AE135">
+        <v>1.12</v>
+      </c>
+      <c r="AF135">
+        <v>1.73</v>
+      </c>
+      <c r="AG135">
+        <v>2.1</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
         <v>1.3</v>
       </c>
-      <c r="AE135">
-        <v>1.07</v>
-      </c>
-      <c r="AF135">
-        <v>1.75</v>
-      </c>
-      <c r="AG135">
-        <v>2.05</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.29</v>
-      </c>
       <c r="AK135">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,61 +22477,61 @@
         </is>
       </c>
       <c r="N136">
+        <v>3.15</v>
+      </c>
+      <c r="O136">
+        <v>3.5</v>
+      </c>
+      <c r="P136">
         <v>2.15</v>
       </c>
-      <c r="O136">
-        <v>3.6</v>
-      </c>
-      <c r="P136">
-        <v>3.2</v>
-      </c>
       <c r="Q136">
-        <v>2.63</v>
+        <v>3.52</v>
       </c>
       <c r="R136">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T136">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="U136">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="V136">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
         <v>1.05</v>
       </c>
       <c r="X136">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z136">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA136">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB136">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC136">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD136">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE136">
         <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
         <v>2.05</v>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK136">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.6</v>
+        <v>2.47</v>
       </c>
       <c r="O137">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P137">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="Q137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R137">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="S137">
+        <v>1.36</v>
+      </c>
+      <c r="T137">
+        <v>2.63</v>
+      </c>
+      <c r="U137">
+        <v>2.9</v>
+      </c>
+      <c r="V137">
+        <v>1.37</v>
+      </c>
+      <c r="W137">
+        <v>1.06</v>
+      </c>
+      <c r="X137">
+        <v>1.06</v>
+      </c>
+      <c r="Y137">
+        <v>1.33</v>
+      </c>
+      <c r="Z137">
+        <v>3.1</v>
+      </c>
+      <c r="AA137">
+        <v>2.02</v>
+      </c>
+      <c r="AB137">
+        <v>1.78</v>
+      </c>
+      <c r="AC137">
+        <v>3.6</v>
+      </c>
+      <c r="AD137">
         <v>1.25</v>
       </c>
-      <c r="T137">
-        <v>3.44</v>
-      </c>
-      <c r="U137">
-        <v>2.23</v>
-      </c>
-      <c r="V137">
-        <v>1.57</v>
-      </c>
-      <c r="W137">
-        <v>1.11</v>
-      </c>
-      <c r="X137">
-        <v>1.01</v>
-      </c>
-      <c r="Y137">
-        <v>1.2</v>
-      </c>
-      <c r="Z137">
-        <v>4.2</v>
-      </c>
-      <c r="AA137">
-        <v>1.65</v>
-      </c>
-      <c r="AB137">
-        <v>2.2</v>
-      </c>
-      <c r="AC137">
-        <v>2.6</v>
-      </c>
-      <c r="AD137">
-        <v>1.47</v>
-      </c>
       <c r="AE137">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AF137">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG137">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK137">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23295,25 +23295,25 @@
         <v>3.7</v>
       </c>
       <c r="O141">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P141">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q141">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="R141">
         <v>2.75</v>
       </c>
       <c r="S141">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T141">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U141">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="V141">
         <v>1.78</v>
@@ -23346,7 +23346,7 @@
         <v>1.35</v>
       </c>
       <c r="AF141">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AG141">
         <v>2.9</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
+        <v>1.91</v>
+      </c>
+      <c r="O151">
+        <v>3.6</v>
+      </c>
+      <c r="P151">
+        <v>3.35</v>
+      </c>
+      <c r="Q151">
+        <v>2.37</v>
+      </c>
+      <c r="R151">
+        <v>2.2</v>
+      </c>
+      <c r="S151">
+        <v>1.29</v>
+      </c>
+      <c r="T151">
+        <v>3.4</v>
+      </c>
+      <c r="U151">
+        <v>2.4</v>
+      </c>
+      <c r="V151">
         <v>1.53</v>
       </c>
-      <c r="O151">
-        <v>4</v>
-      </c>
-      <c r="P151">
-        <v>4.3</v>
-      </c>
-      <c r="Q151">
-        <v>2.15</v>
-      </c>
-      <c r="R151">
-        <v>2.63</v>
-      </c>
-      <c r="S151">
-        <v>1.25</v>
-      </c>
-      <c r="T151">
-        <v>3.5</v>
-      </c>
-      <c r="U151">
-        <v>2.19</v>
-      </c>
-      <c r="V151">
-        <v>1.62</v>
-      </c>
       <c r="W151">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X151">
         <v>1.03</v>
       </c>
       <c r="Y151">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z151">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA151">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AB151">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AC151">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="AD151">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AE151">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF151">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG151">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK151">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
+        <v>2.6</v>
+      </c>
+      <c r="O152">
         <v>3.3</v>
       </c>
-      <c r="O152">
-        <v>3.6</v>
-      </c>
       <c r="P152">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="Q152">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="R152">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="S152">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T152">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="U152">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="V152">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W152">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X152">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z152">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AA152">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AB152">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC152">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="AD152">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE152">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF152">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG152">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>1.25</v>
       </c>
       <c r="AK152">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O153">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P153">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="Q153">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="R153">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S153">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T153">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="U153">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V153">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W153">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X153">
         <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z153">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA153">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AB153">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC153">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="AD153">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AE153">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF153">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG153">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK153">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="O154">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P154">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="Q154">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="R154">
-        <v>2.06</v>
+        <v>2.63</v>
       </c>
       <c r="S154">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T154">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="U154">
-        <v>2.73</v>
+        <v>2.19</v>
       </c>
       <c r="V154">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W154">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X154">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z154">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA154">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="AB154">
-        <v>1.85</v>
+        <v>2.44</v>
       </c>
       <c r="AC154">
-        <v>3.4</v>
+        <v>2.12</v>
       </c>
       <c r="AD154">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AE154">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF154">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG154">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK154">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="O156">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P156">
-        <v>3.52</v>
+        <v>1.97</v>
       </c>
       <c r="Q156">
-        <v>2.32</v>
+        <v>3.47</v>
       </c>
       <c r="R156">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="S156">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T156">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="U156">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="V156">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y156">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z156">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA156">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB156">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC156">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="AD156">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE156">
         <v>1.11</v>
       </c>
       <c r="AF156">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG156">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK156">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26754,10 +26754,10 @@
         <v>0</v>
       </c>
       <c r="AA162">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB162">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC162">
         <v>0</v>
@@ -26878,19 +26878,19 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O163">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P163">
-        <v>3.93</v>
+        <v>3.85</v>
       </c>
       <c r="Q163">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="R163">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="S163">
         <v>1.2</v>
@@ -26899,40 +26899,40 @@
         <v>4.1</v>
       </c>
       <c r="U163">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="V163">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W163">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X163">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y163">
         <v>1.07</v>
       </c>
       <c r="Z163">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AA163">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AB163">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AC163">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD163">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE163">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AF163">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG163">
         <v>2.7</v>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK163">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q164">
         <v>2.35</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.37</v>
+        <v>1.87</v>
       </c>
       <c r="O165">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P165">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="Q165">
         <v>2.9</v>
@@ -27225,10 +27225,10 @@
         <v>3</v>
       </c>
       <c r="U165">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V165">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W165">
         <v>1.08</v>
@@ -27237,7 +27237,7 @@
         <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z165">
         <v>3.65</v>
@@ -27246,7 +27246,7 @@
         <v>1.76</v>
       </c>
       <c r="AB165">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC165">
         <v>3</v>
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK165">
         <v>1.54</v>
@@ -27367,16 +27367,16 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="O166">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P166">
         <v>2.82</v>
       </c>
       <c r="Q166">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="R166">
         <v>2.1</v>
@@ -27437,7 +27437,7 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK166">
         <v>1.5</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB167">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T170">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V170">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X170">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y170">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z170">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG170">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK170">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -30986,10 +30986,10 @@
         <v>1.04</v>
       </c>
       <c r="Y188">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z188">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA188">
         <v>2.12</v>
@@ -30998,16 +30998,16 @@
         <v>1.66</v>
       </c>
       <c r="AC188">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD188">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE188">
         <v>1.05</v>
       </c>
       <c r="AF188">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG188">
         <v>1.91</v>
@@ -31119,19 +31119,19 @@
         <v>1.98</v>
       </c>
       <c r="O189">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="P189">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q189">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R189">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S189">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T189">
         <v>3.04</v>
@@ -31140,7 +31140,7 @@
         <v>2.83</v>
       </c>
       <c r="V189">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W189">
         <v>1.06</v>
@@ -31149,31 +31149,31 @@
         <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z189">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA189">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB189">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC189">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="AD189">
         <v>1.33</v>
       </c>
       <c r="AE189">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF189">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG189">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK189">
         <v>1.8</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>3.26</v>
+        <v>2.6</v>
       </c>
       <c r="O200">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P200">
         <v>2.18</v>
       </c>
       <c r="Q200">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R200">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S200">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T200">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="U200">
         <v>3.05</v>
       </c>
       <c r="V200">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W200">
         <v>1.02</v>
       </c>
       <c r="X200">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y200">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z200">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA200">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB200">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC200">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AD200">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE200">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF200">
         <v>1.85</v>
       </c>
       <c r="AG200">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -33081,55 +33081,55 @@
         <v>0</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>10.6</v>
+        <v>13.3</v>
       </c>
       <c r="O203">
-        <v>6.49</v>
+        <v>6.1</v>
       </c>
       <c r="P203">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Q203">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="R203">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S203">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T203">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="U203">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="V203">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W203">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X203">
         <v>1.01</v>
       </c>
       <c r="Y203">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z203">
-        <v>5.5</v>
+        <v>6.14</v>
       </c>
       <c r="AA203">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AB203">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC203">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD203">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE203">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF203">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG203">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK203">
         <v>1.05</v>
@@ -33570,7 +33570,7 @@
         <v>0</v>
       </c>
       <c r="Q204">
-        <v>4.11</v>
+        <v>3.94</v>
       </c>
       <c r="R204">
         <v>2.01</v>
@@ -33579,7 +33579,7 @@
         <v>1.4</v>
       </c>
       <c r="T204">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U204">
         <v>2.88</v>
@@ -33600,25 +33600,25 @@
         <v>2.92</v>
       </c>
       <c r="AA204">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB204">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC204">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD204">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE204">
         <v>1.05</v>
       </c>
       <c r="AF204">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG204">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.26</v>
+        <v>1.59</v>
       </c>
       <c r="AK204">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q205">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="R205">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="S205">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T205">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="U205">
-        <v>2.84</v>
+        <v>3.08</v>
       </c>
       <c r="V205">
+        <v>1.29</v>
+      </c>
+      <c r="W205">
+        <v>1.02</v>
+      </c>
+      <c r="X205">
+        <v>1.03</v>
+      </c>
+      <c r="Y205">
         <v>1.34</v>
       </c>
-      <c r="W205">
-        <v>1.05</v>
-      </c>
-      <c r="X205">
-        <v>1.02</v>
-      </c>
-      <c r="Y205">
-        <v>1.31</v>
-      </c>
       <c r="Z205">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="AA205">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AB205">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC205">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AD205">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE205">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF205">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AG205">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK205">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O206">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P206">
+        <v>0</v>
+      </c>
+      <c r="Q206">
+        <v>2.41</v>
+      </c>
+      <c r="R206">
+        <v>2.02</v>
+      </c>
+      <c r="S206">
+        <v>1.4</v>
+      </c>
+      <c r="T206">
+        <v>2.75</v>
+      </c>
+      <c r="U206">
         <v>3</v>
       </c>
-      <c r="Q206">
-        <v>2.9</v>
-      </c>
-      <c r="R206">
-        <v>1.92</v>
-      </c>
-      <c r="S206">
-        <v>1.44</v>
-      </c>
-      <c r="T206">
-        <v>2.46</v>
-      </c>
-      <c r="U206">
-        <v>3.08</v>
-      </c>
       <c r="V206">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W206">
+        <v>1.05</v>
+      </c>
+      <c r="X206">
         <v>1.02</v>
       </c>
-      <c r="X206">
-        <v>1.03</v>
-      </c>
       <c r="Y206">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z206">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AA206">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AB206">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC206">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AD206">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE206">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF206">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG206">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK206">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O213">
         <v>6.7</v>
       </c>
       <c r="P213">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q213">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R213">
         <v>2.96</v>
       </c>
       <c r="S213">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T213">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U213">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V213">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W213">
         <v>1.13</v>
       </c>
       <c r="X213">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z213">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA213">
         <v>1.44</v>
       </c>
       <c r="AB213">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AC213">
         <v>2.15</v>
       </c>
       <c r="AD213">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE213">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF213">
         <v>2.08</v>
       </c>
       <c r="AG213">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK213">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35200,55 +35200,55 @@
         <v>0</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35363,7 +35363,7 @@
         <v>2.75</v>
       </c>
       <c r="Q215">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="R215">
         <v>1.92</v>
@@ -35381,37 +35381,37 @@
         <v>1.28</v>
       </c>
       <c r="W215">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X215">
         <v>1.02</v>
       </c>
       <c r="Y215">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z215">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA215">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AB215">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC215">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AD215">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE215">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF215">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG215">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK215">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O216">
         <v>3.1</v>
       </c>
       <c r="P216">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q216">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R216">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S216">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T216">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U216">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="V216">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W216">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X216">
+        <v>1.04</v>
+      </c>
+      <c r="Y216">
+        <v>1.37</v>
+      </c>
+      <c r="Z216">
+        <v>2.66</v>
+      </c>
+      <c r="AA216">
+        <v>2.21</v>
+      </c>
+      <c r="AB216">
+        <v>1.58</v>
+      </c>
+      <c r="AC216">
+        <v>3.96</v>
+      </c>
+      <c r="AD216">
+        <v>1.17</v>
+      </c>
+      <c r="AE216">
         <v>1.02</v>
       </c>
-      <c r="Y216">
-        <v>1.32</v>
-      </c>
-      <c r="Z216">
-        <v>2.88</v>
-      </c>
-      <c r="AA216">
-        <v>2.04</v>
-      </c>
-      <c r="AB216">
-        <v>1.68</v>
-      </c>
-      <c r="AC216">
-        <v>3.5</v>
-      </c>
-      <c r="AD216">
-        <v>1.22</v>
-      </c>
-      <c r="AE216">
-        <v>1.04</v>
-      </c>
       <c r="AF216">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AG216">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK216">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35689,55 +35689,55 @@
         <v>6.25</v>
       </c>
       <c r="Q217">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="R217">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="S217">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T217">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="U217">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V217">
         <v>1.36</v>
       </c>
       <c r="W217">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X217">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y217">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z217">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AA217">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB217">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AC217">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AD217">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE217">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF217">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG217">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK217">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35855,13 +35855,13 @@
         <v>2</v>
       </c>
       <c r="R218">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="S218">
         <v>1.19</v>
       </c>
       <c r="T218">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U218">
         <v>2</v>
@@ -35873,16 +35873,16 @@
         <v>1.14</v>
       </c>
       <c r="X218">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z218">
         <v>5.5</v>
       </c>
       <c r="AA218">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB218">
         <v>2.62</v>
@@ -35894,13 +35894,13 @@
         <v>1.69</v>
       </c>
       <c r="AE218">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF218">
         <v>1.44</v>
       </c>
       <c r="AG218">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK218">
         <v>2.1</v>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK220">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36371,7 +36371,7 @@
         <v>3.42</v>
       </c>
       <c r="AA221">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB221">
         <v>1.88</v>
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="O224">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="P224">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="O227">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="P227">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
       </c>
       <c r="R227">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S227">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T227">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="U227">
-        <v>2.39</v>
+        <v>3.07</v>
       </c>
       <c r="V227">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W227">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X227">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y227">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z227">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AA227">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB227">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AC227">
-        <v>2.48</v>
+        <v>3.24</v>
       </c>
       <c r="AD227">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AE227">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF227">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG227">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK227">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="O228">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="P228">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="Q228">
         <v>2.63</v>
       </c>
       <c r="R228">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S228">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T228">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U228">
-        <v>3.07</v>
+        <v>2.39</v>
       </c>
       <c r="V228">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W228">
+        <v>1.09</v>
+      </c>
+      <c r="X228">
         <v>1.04</v>
       </c>
-      <c r="X228">
-        <v>1.01</v>
-      </c>
       <c r="Y228">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z228">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA228">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AB228">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AC228">
-        <v>3.24</v>
+        <v>2.48</v>
       </c>
       <c r="AD228">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE228">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF228">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG228">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK228">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O231">
         <v>3.7</v>
       </c>
       <c r="P231">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="Q231">
         <v>2.58</v>
@@ -37983,43 +37983,43 @@
         <v>3.8</v>
       </c>
       <c r="U231">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V231">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W231">
         <v>1.14</v>
       </c>
       <c r="X231">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y231">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z231">
         <v>4.75</v>
       </c>
       <c r="AA231">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB231">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AC231">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AD231">
         <v>1.52</v>
       </c>
       <c r="AE231">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF231">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG231">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AK231">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38297,55 +38297,55 @@
         <v>0</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q248">
         <v>2.28</v>
@@ -40905,7 +40905,7 @@
         <v>0</v>
       </c>
       <c r="Q249">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R249">
         <v>2.3</v>
@@ -40917,7 +40917,7 @@
         <v>3.1</v>
       </c>
       <c r="U249">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V249">
         <v>1.44</v>
@@ -40938,22 +40938,22 @@
         <v>1.8</v>
       </c>
       <c r="AB249">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC249">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD249">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE249">
         <v>1.1</v>
       </c>
       <c r="AF249">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG249">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         </is>
       </c>
       <c r="N250">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O250">
         <v>3.2</v>
@@ -41068,22 +41068,22 @@
         <v>2.15</v>
       </c>
       <c r="Q250">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R250">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S250">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T250">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="U250">
         <v>2.77</v>
       </c>
       <c r="V250">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W250">
         <v>1.06</v>
@@ -41092,31 +41092,31 @@
         <v>1.01</v>
       </c>
       <c r="Y250">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z250">
         <v>3.3</v>
       </c>
       <c r="AA250">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB250">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC250">
-        <v>3.05</v>
+        <v>3.49</v>
       </c>
       <c r="AD250">
         <v>1.29</v>
       </c>
       <c r="AE250">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF250">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG250">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AK250">
         <v>1.33</v>
@@ -41711,31 +41711,31 @@
         </is>
       </c>
       <c r="N254">
-        <v>9</v>
+        <v>8.85</v>
       </c>
       <c r="O254">
-        <v>5.53</v>
+        <v>5.57</v>
       </c>
       <c r="P254">
         <v>1.28</v>
       </c>
       <c r="Q254">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="R254">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="S254">
         <v>1.19</v>
       </c>
       <c r="T254">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="U254">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="V254">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W254">
         <v>1.16</v>
@@ -41744,31 +41744,31 @@
         <v>1.01</v>
       </c>
       <c r="Y254">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z254">
-        <v>5.65</v>
+        <v>6.25</v>
       </c>
       <c r="AA254">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB254">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AC254">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD254">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE254">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF254">
         <v>1.65</v>
       </c>
       <c r="AG254">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK254">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41874,19 +41874,19 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O255">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="P255">
-        <v>4.67</v>
+        <v>4.72</v>
       </c>
       <c r="Q255">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="R255">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S255">
         <v>1.28</v>
@@ -41895,28 +41895,28 @@
         <v>3.18</v>
       </c>
       <c r="U255">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="V255">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W255">
         <v>1.09</v>
       </c>
       <c r="X255">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y255">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z255">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="AA255">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB255">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC255">
         <v>2.46</v>
@@ -41925,13 +41925,13 @@
         <v>1.43</v>
       </c>
       <c r="AE255">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF255">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG255">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>1.22</v>
       </c>
       <c r="AK255">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O261">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="P261">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -44808,19 +44808,19 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="O273">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P273">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q273">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R273">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S273">
         <v>1.33</v>
@@ -44835,7 +44835,7 @@
         <v>1.42</v>
       </c>
       <c r="W273">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X273">
         <v>1</v>
@@ -44850,7 +44850,7 @@
         <v>1.75</v>
       </c>
       <c r="AB273">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC273">
         <v>3</v>
@@ -44862,7 +44862,7 @@
         <v>1.11</v>
       </c>
       <c r="AF273">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG273">
         <v>1.83</v>
@@ -44881,7 +44881,7 @@
         <v>1.19</v>
       </c>
       <c r="AK273">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O277">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P277">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="Q277">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R277">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S277">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T277">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="U277">
-        <v>2.55</v>
+        <v>2.93</v>
       </c>
       <c r="V277">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W277">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X277">
         <v>1.04</v>
       </c>
       <c r="Y277">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z277">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA277">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AB277">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC277">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD277">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE277">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF277">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG277">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AK277">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O278">
+        <v>3.55</v>
+      </c>
+      <c r="P278">
+        <v>2.44</v>
+      </c>
+      <c r="Q278">
+        <v>3.2</v>
+      </c>
+      <c r="R278">
+        <v>2.3</v>
+      </c>
+      <c r="S278">
+        <v>1.33</v>
+      </c>
+      <c r="T278">
         <v>3.3</v>
       </c>
-      <c r="P278">
-        <v>2.72</v>
-      </c>
-      <c r="Q278">
-        <v>3.1</v>
-      </c>
-      <c r="R278">
-        <v>2.1</v>
-      </c>
-      <c r="S278">
-        <v>1.45</v>
-      </c>
-      <c r="T278">
-        <v>2.74</v>
-      </c>
       <c r="U278">
-        <v>2.93</v>
+        <v>2.55</v>
       </c>
       <c r="V278">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W278">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X278">
         <v>1.04</v>
       </c>
       <c r="Y278">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z278">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA278">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB278">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC278">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD278">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE278">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF278">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG278">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AK278">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="O281">
-        <v>6.95</v>
+        <v>6.2</v>
       </c>
       <c r="P281">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O282">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P282">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46441,10 +46441,10 @@
         <v>2.35</v>
       </c>
       <c r="O283">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P283">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q283">
         <v>3.06</v>
@@ -46453,28 +46453,28 @@
         <v>1.94</v>
       </c>
       <c r="S283">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T283">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U283">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="V283">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W283">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X283">
         <v>1.03</v>
       </c>
       <c r="Y283">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z283">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA283">
         <v>2.04</v>
@@ -46616,19 +46616,19 @@
         <v>2.01</v>
       </c>
       <c r="S284">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T284">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="U284">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="V284">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W284">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X284">
         <v>1.02</v>
@@ -46640,10 +46640,10 @@
         <v>3.28</v>
       </c>
       <c r="AA284">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB284">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC284">
         <v>3.2</v>
@@ -46785,13 +46785,13 @@
         <v>2.47</v>
       </c>
       <c r="U285">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V285">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W285">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X285">
         <v>1.02</v>
@@ -46834,7 +46834,7 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AK285">
         <v>1.4</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47455,10 +47455,10 @@
         <v>0</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC289">
         <v>0</v>
@@ -48433,10 +48433,10 @@
         <v>0</v>
       </c>
       <c r="AA295">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB295">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC295">
         <v>0</v>
@@ -52001,7 +52001,7 @@
         <v>4.33</v>
       </c>
       <c r="U317">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="V317">
         <v>1.78</v>
@@ -52031,13 +52031,13 @@
         <v>1.86</v>
       </c>
       <c r="AE317">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF317">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG317">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>6.25</v>
       </c>
       <c r="AA319">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB319">
         <v>3.1</v>
@@ -52469,13 +52469,13 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O320">
         <v>4</v>
       </c>
       <c r="P320">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="Q320">
         <v>2.25</v>
@@ -52662,7 +52662,7 @@
         <v>1.11</v>
       </c>
       <c r="X321">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y321">
         <v>1.18</v>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK321">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,80 +53936,80 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.99</v>
+        <v>4.05</v>
       </c>
       <c r="O329">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P329">
-        <v>3.3</v>
+        <v>1.71</v>
       </c>
       <c r="Q329">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="R329">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="S329">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="T329">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U329">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="V329">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W329">
+        <v>1.1</v>
+      </c>
+      <c r="X329">
         <v>1.05</v>
       </c>
-      <c r="X329">
-        <v>1.03</v>
-      </c>
       <c r="Y329">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="Z329">
-        <v>2.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA329">
-        <v>2.23</v>
+        <v>1.81</v>
       </c>
       <c r="AB329">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="AC329">
-        <v>4.18</v>
+        <v>2.97</v>
       </c>
       <c r="AD329">
+        <v>1.37</v>
+      </c>
+      <c r="AE329">
+        <v>1.13</v>
+      </c>
+      <c r="AF329">
+        <v>1.75</v>
+      </c>
+      <c r="AG329">
+        <v>1.95</v>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ329">
+        <v>1.25</v>
+      </c>
+      <c r="AK329">
         <v>1.17</v>
-      </c>
-      <c r="AE329">
-        <v>1.01</v>
-      </c>
-      <c r="AF329">
-        <v>1.97</v>
-      </c>
-      <c r="AG329">
-        <v>1.73</v>
-      </c>
-      <c r="AH329" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI329" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ329">
-        <v>1.33</v>
-      </c>
-      <c r="AK329">
-        <v>1.7</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G330">
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>4.05</v>
+        <v>1.99</v>
       </c>
       <c r="O330">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P330">
-        <v>1.71</v>
+        <v>3.3</v>
       </c>
       <c r="Q330">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="R330">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="S330">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="T330">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U330">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="V330">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W330">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X330">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y330">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="Z330">
-        <v>3.54</v>
+        <v>2.7</v>
       </c>
       <c r="AA330">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="AB330">
-        <v>1.98</v>
+        <v>1.59</v>
       </c>
       <c r="AC330">
-        <v>2.97</v>
+        <v>4.18</v>
       </c>
       <c r="AD330">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AE330">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AF330">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AG330">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK330">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54443,7 +54443,7 @@
         <v>1.18</v>
       </c>
       <c r="T332">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U332">
         <v>2</v>
@@ -54458,7 +54458,7 @@
         <v>1.01</v>
       </c>
       <c r="Y332">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z332">
         <v>6.5</v>
@@ -54482,7 +54482,7 @@
         <v>1.33</v>
       </c>
       <c r="AG332">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
@@ -54495,7 +54495,7 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK332">
         <v>1.95</v>
@@ -54600,7 +54600,7 @@
         <v>2.5</v>
       </c>
       <c r="R333">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S333">
         <v>1.25</v>
@@ -54658,7 +54658,7 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK333">
         <v>1.73</v>
@@ -54760,10 +54760,10 @@
         <v>1.57</v>
       </c>
       <c r="Q334">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R334">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="S334">
         <v>1.22</v>
@@ -54772,10 +54772,10 @@
         <v>4</v>
       </c>
       <c r="U334">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V334">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W334">
         <v>1.15</v>
@@ -54784,7 +54784,7 @@
         <v>1.03</v>
       </c>
       <c r="Y334">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z334">
         <v>5</v>
@@ -54796,13 +54796,13 @@
         <v>2.5</v>
       </c>
       <c r="AC334">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD334">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE334">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF334">
         <v>1.5</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,64 +55077,64 @@
         </is>
       </c>
       <c r="N336">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="O336">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P336">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="Q336">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="R336">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S336">
         <v>1.25</v>
       </c>
       <c r="T336">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U336">
         <v>2.25</v>
       </c>
       <c r="V336">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W336">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X336">
         <v>1.03</v>
       </c>
       <c r="Y336">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z336">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA336">
         <v>1.57</v>
       </c>
       <c r="AB336">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC336">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AD336">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AE336">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF336">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG336">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK336">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,65 +55240,65 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="O337">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P337">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="Q337">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="R337">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S337">
         <v>1.25</v>
       </c>
       <c r="T337">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U337">
         <v>2.25</v>
       </c>
       <c r="V337">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W337">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X337">
         <v>1.03</v>
       </c>
       <c r="Y337">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z337">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA337">
         <v>1.57</v>
       </c>
       <c r="AB337">
+        <v>2.35</v>
+      </c>
+      <c r="AC337">
+        <v>2.43</v>
+      </c>
+      <c r="AD337">
+        <v>1.54</v>
+      </c>
+      <c r="AE337">
+        <v>1.2</v>
+      </c>
+      <c r="AF337">
+        <v>1.55</v>
+      </c>
+      <c r="AG337">
         <v>2.25</v>
       </c>
-      <c r="AC337">
-        <v>2.5</v>
-      </c>
-      <c r="AD337">
-        <v>1.44</v>
-      </c>
-      <c r="AE337">
-        <v>1.21</v>
-      </c>
-      <c r="AF337">
-        <v>1.57</v>
-      </c>
-      <c r="AG337">
-        <v>2.3</v>
-      </c>
       <c r="AH337" t="inlineStr">
         <is>
           <t>[]</t>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK337">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,64 +55403,64 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="O338">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="P338">
-        <v>3.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q338">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R338">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="S338">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="T338">
-        <v>2.52</v>
+        <v>3.26</v>
       </c>
       <c r="U338">
-        <v>3.18</v>
+        <v>2.42</v>
       </c>
       <c r="V338">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="W338">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X338">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y338">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="Z338">
-        <v>2.75</v>
+        <v>3.78</v>
       </c>
       <c r="AA338">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="AB338">
+        <v>2.02</v>
+      </c>
+      <c r="AC338">
+        <v>2.83</v>
+      </c>
+      <c r="AD338">
+        <v>1.33</v>
+      </c>
+      <c r="AE338">
+        <v>1.08</v>
+      </c>
+      <c r="AF338">
         <v>1.6</v>
       </c>
-      <c r="AC338">
-        <v>4.52</v>
-      </c>
-      <c r="AD338">
-        <v>1.21</v>
-      </c>
-      <c r="AE338">
-        <v>1.02</v>
-      </c>
-      <c r="AF338">
-        <v>2</v>
-      </c>
       <c r="AG338">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>1.22</v>
       </c>
       <c r="AK338">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,25 +55566,25 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="O339">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P339">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q339">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="R339">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="S339">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T339">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U339">
         <v>2.62</v>
@@ -55593,37 +55593,37 @@
         <v>1.4</v>
       </c>
       <c r="W339">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X339">
         <v>1.01</v>
       </c>
       <c r="Y339">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z339">
-        <v>3.57</v>
+        <v>3.28</v>
       </c>
       <c r="AA339">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB339">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC339">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="AD339">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE339">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF339">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AG339">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK339">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,52 +55729,52 @@
         </is>
       </c>
       <c r="N340">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="O340">
         <v>3.35</v>
       </c>
       <c r="P340">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q340">
+        <v>2.94</v>
+      </c>
+      <c r="R340">
+        <v>2.23</v>
+      </c>
+      <c r="S340">
+        <v>1.33</v>
+      </c>
+      <c r="T340">
+        <v>2.9</v>
+      </c>
+      <c r="U340">
         <v>2.62</v>
       </c>
-      <c r="R340">
-        <v>2.28</v>
-      </c>
-      <c r="S340">
+      <c r="V340">
+        <v>1.4</v>
+      </c>
+      <c r="W340">
+        <v>1.06</v>
+      </c>
+      <c r="X340">
+        <v>1.01</v>
+      </c>
+      <c r="Y340">
         <v>1.27</v>
       </c>
-      <c r="T340">
-        <v>3.26</v>
-      </c>
-      <c r="U340">
-        <v>2.42</v>
-      </c>
-      <c r="V340">
-        <v>1.47</v>
-      </c>
-      <c r="W340">
-        <v>1.08</v>
-      </c>
-      <c r="X340">
-        <v>1.03</v>
-      </c>
-      <c r="Y340">
-        <v>1.25</v>
-      </c>
       <c r="Z340">
-        <v>3.78</v>
+        <v>3.57</v>
       </c>
       <c r="AA340">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB340">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AC340">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="AD340">
         <v>1.33</v>
@@ -55783,10 +55783,10 @@
         <v>1.08</v>
       </c>
       <c r="AF340">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG340">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK340">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,65 +55892,65 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O341">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P341">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Q341">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R341">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="S341">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="T341">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="U341">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="V341">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W341">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X341">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y341">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="Z341">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AA341">
-        <v>1.89</v>
+        <v>2.29</v>
       </c>
       <c r="AB341">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AC341">
-        <v>3.04</v>
+        <v>4.52</v>
       </c>
       <c r="AD341">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AE341">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AF341">
+        <v>2</v>
+      </c>
+      <c r="AG341">
         <v>1.71</v>
       </c>
-      <c r="AG341">
-        <v>2</v>
-      </c>
       <c r="AH341" t="inlineStr">
         <is>
           <t>[]</t>
@@ -55962,10 +55962,10 @@
         </is>
       </c>
       <c r="AJ341">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK341">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,64 +56055,64 @@
         </is>
       </c>
       <c r="N342">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O342">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P342">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="Q342">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R342">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S342">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T342">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U342">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V342">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W342">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X342">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y342">
         <v>1.17</v>
       </c>
       <c r="Z342">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA342">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AB342">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AC342">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AD342">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE342">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF342">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG342">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AH342" t="inlineStr">
         <is>
@@ -56125,10 +56125,10 @@
         </is>
       </c>
       <c r="AJ342">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK342">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,34 +56218,34 @@
         </is>
       </c>
       <c r="N343">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="O343">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P343">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="Q343">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R343">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S343">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T343">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U343">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V343">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W343">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X343">
         <v>1.03</v>
@@ -56254,44 +56254,44 @@
         <v>1.17</v>
       </c>
       <c r="Z343">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA343">
+        <v>1.62</v>
+      </c>
+      <c r="AB343">
+        <v>2.2</v>
+      </c>
+      <c r="AC343">
+        <v>2.5</v>
+      </c>
+      <c r="AD343">
+        <v>1.44</v>
+      </c>
+      <c r="AE343">
+        <v>1.18</v>
+      </c>
+      <c r="AF343">
         <v>1.53</v>
       </c>
-      <c r="AB343">
+      <c r="AG343">
         <v>2.4</v>
       </c>
-      <c r="AC343">
-        <v>2.35</v>
-      </c>
-      <c r="AD343">
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ343">
+        <v>1.29</v>
+      </c>
+      <c r="AK343">
         <v>1.53</v>
-      </c>
-      <c r="AE343">
-        <v>1.22</v>
-      </c>
-      <c r="AF343">
-        <v>1.44</v>
-      </c>
-      <c r="AG343">
-        <v>2.51</v>
-      </c>
-      <c r="AH343" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI343" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ343">
-        <v>1.33</v>
-      </c>
-      <c r="AK343">
-        <v>1.77</v>
       </c>
       <c r="AL343">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R2">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="S2">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="U2">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
         <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="AA2">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB2">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q4">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="R4">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="S4">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="U4">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z4">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="AA4">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>3.08</v>
+        <v>3.52</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -7701,7 +7701,7 @@
         <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,65 +7807,65 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P46">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
+        <v>2.99</v>
+      </c>
+      <c r="R46">
+        <v>2.38</v>
+      </c>
+      <c r="S46">
+        <v>1.27</v>
+      </c>
+      <c r="T46">
+        <v>3.42</v>
+      </c>
+      <c r="U46">
+        <v>2.24</v>
+      </c>
+      <c r="V46">
+        <v>1.58</v>
+      </c>
+      <c r="W46">
+        <v>1.11</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.2</v>
+      </c>
+      <c r="Z46">
+        <v>4.89</v>
+      </c>
+      <c r="AA46">
+        <v>1.6</v>
+      </c>
+      <c r="AB46">
+        <v>2.3</v>
+      </c>
+      <c r="AC46">
+        <v>2.55</v>
+      </c>
+      <c r="AD46">
+        <v>1.47</v>
+      </c>
+      <c r="AE46">
+        <v>1.15</v>
+      </c>
+      <c r="AF46">
+        <v>1.5</v>
+      </c>
+      <c r="AG46">
         <v>2.45</v>
       </c>
-      <c r="R46">
-        <v>2.25</v>
-      </c>
-      <c r="S46">
-        <v>1.36</v>
-      </c>
-      <c r="T46">
-        <v>2.82</v>
-      </c>
-      <c r="U46">
-        <v>2.59</v>
-      </c>
-      <c r="V46">
-        <v>1.48</v>
-      </c>
-      <c r="W46">
-        <v>1.07</v>
-      </c>
-      <c r="X46">
-        <v>1.04</v>
-      </c>
-      <c r="Y46">
-        <v>1.26</v>
-      </c>
-      <c r="Z46">
-        <v>3.8</v>
-      </c>
-      <c r="AA46">
-        <v>1.75</v>
-      </c>
-      <c r="AB46">
-        <v>1.95</v>
-      </c>
-      <c r="AC46">
-        <v>2.9</v>
-      </c>
-      <c r="AD46">
-        <v>1.36</v>
-      </c>
-      <c r="AE46">
-        <v>1.1</v>
-      </c>
-      <c r="AF46">
-        <v>1.66</v>
-      </c>
-      <c r="AG46">
-        <v>2.08</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="O47">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
+        <v>3.5</v>
+      </c>
+      <c r="Q47">
+        <v>2.45</v>
+      </c>
+      <c r="R47">
+        <v>2.25</v>
+      </c>
+      <c r="S47">
+        <v>1.29</v>
+      </c>
+      <c r="T47">
+        <v>3.3</v>
+      </c>
+      <c r="U47">
         <v>2.6</v>
       </c>
-      <c r="Q47">
-        <v>2.99</v>
-      </c>
-      <c r="R47">
-        <v>2.38</v>
-      </c>
-      <c r="S47">
-        <v>1.27</v>
-      </c>
-      <c r="T47">
-        <v>3.42</v>
-      </c>
-      <c r="U47">
-        <v>2.25</v>
-      </c>
       <c r="V47">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.89</v>
+        <v>3.8</v>
       </c>
       <c r="AA47">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB47">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AC47">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AD47">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG47">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK47">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O50">
         <v>3.35</v>
       </c>
       <c r="P50">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q50">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R50">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="S50">
+        <v>1.39</v>
+      </c>
+      <c r="T50">
+        <v>2.73</v>
+      </c>
+      <c r="U50">
+        <v>2.95</v>
+      </c>
+      <c r="V50">
         <v>1.33</v>
       </c>
-      <c r="T50">
-        <v>3.1</v>
-      </c>
-      <c r="U50">
-        <v>2.5</v>
-      </c>
-      <c r="V50">
-        <v>1.45</v>
-      </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y50">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z50">
-        <v>3.98</v>
+        <v>2.94</v>
       </c>
       <c r="AA50">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AB50">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC50">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="AD50">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O51">
         <v>3.35</v>
       </c>
       <c r="P51">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q51">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R51">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="S51">
+        <v>1.33</v>
+      </c>
+      <c r="T51">
+        <v>3.1</v>
+      </c>
+      <c r="U51">
+        <v>2.5</v>
+      </c>
+      <c r="V51">
+        <v>1.45</v>
+      </c>
+      <c r="W51">
+        <v>1.07</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="Y51">
+        <v>1.22</v>
+      </c>
+      <c r="Z51">
+        <v>3.98</v>
+      </c>
+      <c r="AA51">
+        <v>1.78</v>
+      </c>
+      <c r="AB51">
+        <v>2</v>
+      </c>
+      <c r="AC51">
+        <v>2.76</v>
+      </c>
+      <c r="AD51">
         <v>1.39</v>
       </c>
-      <c r="T51">
-        <v>2.73</v>
-      </c>
-      <c r="U51">
-        <v>2.95</v>
-      </c>
-      <c r="V51">
-        <v>1.33</v>
-      </c>
-      <c r="W51">
-        <v>1.04</v>
-      </c>
-      <c r="X51">
-        <v>1.06</v>
-      </c>
-      <c r="Y51">
-        <v>1.36</v>
-      </c>
-      <c r="Z51">
-        <v>2.94</v>
-      </c>
-      <c r="AA51">
-        <v>2.1</v>
-      </c>
-      <c r="AB51">
-        <v>1.7</v>
-      </c>
-      <c r="AC51">
-        <v>3.76</v>
-      </c>
-      <c r="AD51">
-        <v>1.25</v>
-      </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AK51">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="O59">
         <v>3.5</v>
       </c>
       <c r="P59">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="Q59">
-        <v>2.63</v>
+        <v>2.37</v>
       </c>
       <c r="R59">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="S59">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U59">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="V59">
+        <v>1.58</v>
+      </c>
+      <c r="W59">
+        <v>1.11</v>
+      </c>
+      <c r="X59">
+        <v>1.03</v>
+      </c>
+      <c r="Y59">
+        <v>1.1</v>
+      </c>
+      <c r="Z59">
+        <v>5</v>
+      </c>
+      <c r="AA59">
         <v>1.47</v>
       </c>
-      <c r="W59">
-        <v>1.1</v>
-      </c>
-      <c r="X59">
-        <v>1.04</v>
-      </c>
-      <c r="Y59">
-        <v>1.17</v>
-      </c>
-      <c r="Z59">
-        <v>3.3</v>
-      </c>
-      <c r="AA59">
-        <v>1.53</v>
-      </c>
       <c r="AB59">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AC59">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD59">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE59">
         <v>1.22</v>
       </c>
       <c r="AF59">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AG59">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.87</v>
+        <v>2.7</v>
       </c>
       <c r="O60">
         <v>3.5</v>
       </c>
       <c r="P60">
-        <v>3.21</v>
+        <v>2.15</v>
       </c>
       <c r="Q60">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="R60">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S60">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U60">
         <v>2.22</v>
       </c>
       <c r="V60">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W60">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X60">
         <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
         <v>5</v>
       </c>
       <c r="AA60">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB60">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC60">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="AD60">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE60">
         <v>1.22</v>
       </c>
       <c r="AF60">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AG60">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O61">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P61">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q61">
         <v>3</v>
       </c>
       <c r="R61">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S61">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T61">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="U61">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="V61">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
         <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AA61">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AB61">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AC61">
-        <v>2.21</v>
+        <v>2.83</v>
       </c>
       <c r="AD61">
+        <v>1.38</v>
+      </c>
+      <c r="AE61">
+        <v>1.12</v>
+      </c>
+      <c r="AF61">
         <v>1.62</v>
       </c>
-      <c r="AE61">
-        <v>1.22</v>
-      </c>
-      <c r="AF61">
-        <v>1.43</v>
-      </c>
       <c r="AG61">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.29</v>
       </c>
       <c r="AK61">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="O62">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P62">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q62">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R62">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S62">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U62">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="V62">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z62">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA62">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB62">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="AC62">
-        <v>2.83</v>
+        <v>2.32</v>
       </c>
       <c r="AD62">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF62">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG62">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O63">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q63">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="R63">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="U63">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="V63">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z63">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA63">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB63">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="AC63">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD63">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE63">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG63">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="O112">
-        <v>6.9</v>
+        <v>3.9</v>
       </c>
       <c r="P112">
-        <v>9.75</v>
+        <v>2.69</v>
       </c>
       <c r="Q112">
-        <v>1.59</v>
+        <v>2.7</v>
       </c>
       <c r="R112">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="S112">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T112">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U112">
         <v>2.02</v>
       </c>
       <c r="V112">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="W112">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z112">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA112">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB112">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AC112">
+        <v>1.85</v>
+      </c>
+      <c r="AD112">
         <v>1.82</v>
       </c>
-      <c r="AD112">
-        <v>1.94</v>
-      </c>
       <c r="AE112">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF112">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AG112">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AK112">
-        <v>4.15</v>
+        <v>1.55</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="O113">
-        <v>3.9</v>
+        <v>6.9</v>
       </c>
       <c r="P113">
-        <v>2.69</v>
+        <v>9.75</v>
       </c>
       <c r="Q113">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="R113">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="S113">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T113">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U113">
         <v>2.02</v>
       </c>
       <c r="V113">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="W113">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z113">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA113">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB113">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AC113">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD113">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AE113">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF113">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AG113">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="AK113">
-        <v>1.55</v>
+        <v>4.15</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
+        <v>1.88</v>
+      </c>
+      <c r="O117">
+        <v>3.7</v>
+      </c>
+      <c r="P117">
+        <v>3.9</v>
+      </c>
+      <c r="Q117">
         <v>2.3</v>
       </c>
-      <c r="O117">
-        <v>3.5</v>
-      </c>
-      <c r="P117">
-        <v>2.6</v>
-      </c>
-      <c r="Q117">
-        <v>2.98</v>
-      </c>
       <c r="R117">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S117">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T117">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="U117">
-        <v>2.3</v>
+        <v>2.86</v>
       </c>
       <c r="V117">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W117">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X117">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z117">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA117">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AB117">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC117">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AD117">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE117">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF117">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AG117">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AK117">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O118">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P118">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q118">
+        <v>2.98</v>
+      </c>
+      <c r="R118">
+        <v>2.22</v>
+      </c>
+      <c r="S118">
+        <v>1.32</v>
+      </c>
+      <c r="T118">
+        <v>3.5</v>
+      </c>
+      <c r="U118">
         <v>2.3</v>
       </c>
-      <c r="R118">
-        <v>2.2</v>
-      </c>
-      <c r="S118">
-        <v>1.33</v>
-      </c>
-      <c r="T118">
-        <v>3.05</v>
-      </c>
-      <c r="U118">
-        <v>2.86</v>
-      </c>
       <c r="V118">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W118">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y118">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z118">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA118">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AB118">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC118">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AD118">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE118">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF118">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AG118">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AK118">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,40 +21825,40 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="O132">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P132">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q132">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="R132">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S132">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T132">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U132">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V132">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W132">
+        <v>1.07</v>
+      </c>
+      <c r="X132">
         <v>1.05</v>
       </c>
-      <c r="X132">
-        <v>1</v>
-      </c>
       <c r="Y132">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z132">
         <v>3.6</v>
@@ -21867,19 +21867,19 @@
         <v>1.83</v>
       </c>
       <c r="AB132">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC132">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD132">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE132">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF132">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG132">
         <v>2.05</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK132">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O133">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P133">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="Q133">
-        <v>3.52</v>
+        <v>2.89</v>
       </c>
       <c r="R133">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="S133">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T133">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U133">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="V133">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W133">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X133">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y133">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z133">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA133">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AB133">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC133">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="AD133">
         <v>1.33</v>
       </c>
       <c r="AE133">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF133">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG133">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK133">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O134">
+        <v>3.1</v>
+      </c>
+      <c r="P134">
+        <v>2.65</v>
+      </c>
+      <c r="Q134">
+        <v>3.01</v>
+      </c>
+      <c r="R134">
+        <v>1.95</v>
+      </c>
+      <c r="S134">
+        <v>1.46</v>
+      </c>
+      <c r="T134">
+        <v>2.75</v>
+      </c>
+      <c r="U134">
         <v>3.25</v>
       </c>
-      <c r="P134">
-        <v>3</v>
-      </c>
-      <c r="Q134">
-        <v>2.89</v>
-      </c>
-      <c r="R134">
-        <v>2.24</v>
-      </c>
-      <c r="S134">
-        <v>1.37</v>
-      </c>
-      <c r="T134">
-        <v>2.81</v>
-      </c>
-      <c r="U134">
-        <v>2.81</v>
-      </c>
       <c r="V134">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W134">
         <v>1.05</v>
       </c>
       <c r="X134">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y134">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="Z134">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA134">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="AB134">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AC134">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="AD134">
+        <v>1.16</v>
+      </c>
+      <c r="AE134">
+        <v>1.06</v>
+      </c>
+      <c r="AF134">
+        <v>1.85</v>
+      </c>
+      <c r="AG134">
+        <v>1.8</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
         <v>1.33</v>
       </c>
-      <c r="AE134">
-        <v>1.07</v>
-      </c>
-      <c r="AF134">
-        <v>1.7</v>
-      </c>
-      <c r="AG134">
-        <v>2</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.24</v>
-      </c>
       <c r="AK134">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="O135">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P135">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="Q135">
-        <v>3.01</v>
+        <v>2</v>
       </c>
       <c r="R135">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="S135">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="T135">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="U135">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="V135">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="W135">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X135">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="Z135">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA135">
-        <v>2.16</v>
+        <v>1.61</v>
       </c>
       <c r="AB135">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC135">
-        <v>4.2</v>
+        <v>2.43</v>
       </c>
       <c r="AD135">
-        <v>1.16</v>
+        <v>1.5</v>
       </c>
       <c r="AE135">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF135">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG135">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK135">
-        <v>1.44</v>
+        <v>2.31</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,80 +22477,80 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="O136">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="P136">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="Q136">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="R136">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S136">
+        <v>1.33</v>
+      </c>
+      <c r="T136">
+        <v>2.88</v>
+      </c>
+      <c r="U136">
+        <v>2.62</v>
+      </c>
+      <c r="V136">
+        <v>1.44</v>
+      </c>
+      <c r="W136">
+        <v>1.05</v>
+      </c>
+      <c r="X136">
+        <v>1</v>
+      </c>
+      <c r="Y136">
+        <v>1.22</v>
+      </c>
+      <c r="Z136">
+        <v>3.6</v>
+      </c>
+      <c r="AA136">
+        <v>1.83</v>
+      </c>
+      <c r="AB136">
+        <v>1.97</v>
+      </c>
+      <c r="AC136">
+        <v>3</v>
+      </c>
+      <c r="AD136">
+        <v>1.34</v>
+      </c>
+      <c r="AE136">
+        <v>1.12</v>
+      </c>
+      <c r="AF136">
+        <v>1.7</v>
+      </c>
+      <c r="AG136">
+        <v>2.05</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ136">
         <v>1.29</v>
       </c>
-      <c r="T136">
-        <v>3.44</v>
-      </c>
-      <c r="U136">
-        <v>2.45</v>
-      </c>
-      <c r="V136">
-        <v>1.54</v>
-      </c>
-      <c r="W136">
-        <v>1.13</v>
-      </c>
-      <c r="X136">
-        <v>1.01</v>
-      </c>
-      <c r="Y136">
-        <v>1.2</v>
-      </c>
-      <c r="Z136">
-        <v>4.3</v>
-      </c>
-      <c r="AA136">
-        <v>1.61</v>
-      </c>
-      <c r="AB136">
-        <v>2.25</v>
-      </c>
-      <c r="AC136">
-        <v>2.43</v>
-      </c>
-      <c r="AD136">
-        <v>1.5</v>
-      </c>
-      <c r="AE136">
-        <v>1.15</v>
-      </c>
-      <c r="AF136">
-        <v>1.62</v>
-      </c>
-      <c r="AG136">
-        <v>2.1</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>1.19</v>
-      </c>
       <c r="AK136">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O142">
         <v>3.5</v>
@@ -23464,10 +23464,10 @@
         <v>3.1</v>
       </c>
       <c r="Q142">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R142">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S142">
         <v>1.33</v>
@@ -23485,7 +23485,7 @@
         <v>1.08</v>
       </c>
       <c r="X142">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y142">
         <v>1.28</v>
@@ -23500,13 +23500,13 @@
         <v>1.94</v>
       </c>
       <c r="AC142">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD142">
         <v>1.31</v>
       </c>
       <c r="AE142">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF142">
         <v>1.65</v>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK142">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23627,22 +23627,22 @@
         <v>2.9</v>
       </c>
       <c r="Q143">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R143">
         <v>2.2</v>
       </c>
       <c r="S143">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T143">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="U143">
         <v>2.75</v>
       </c>
       <c r="V143">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W143">
         <v>1.06</v>
@@ -23657,10 +23657,10 @@
         <v>3.77</v>
       </c>
       <c r="AA143">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB143">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC143">
         <v>3.1</v>
@@ -23669,7 +23669,7 @@
         <v>1.36</v>
       </c>
       <c r="AE143">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF143">
         <v>1.65</v>
@@ -23793,7 +23793,7 @@
         <v>2.8</v>
       </c>
       <c r="R144">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S144">
         <v>1.36</v>
@@ -23814,13 +23814,13 @@
         <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z144">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA144">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB144">
         <v>1.89</v>
@@ -23835,7 +23835,7 @@
         <v>1.11</v>
       </c>
       <c r="AF144">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG144">
         <v>2.1</v>
@@ -23854,7 +23854,7 @@
         <v>1.3</v>
       </c>
       <c r="AK144">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,16 +23944,16 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O145">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="P145">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q145">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="R145">
         <v>2.4</v>
@@ -23968,7 +23968,7 @@
         <v>2.35</v>
       </c>
       <c r="V145">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W145">
         <v>1.11</v>
@@ -23995,10 +23995,10 @@
         <v>1.49</v>
       </c>
       <c r="AE145">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF145">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG145">
         <v>2.3</v>
@@ -24017,7 +24017,7 @@
         <v>1.22</v>
       </c>
       <c r="AK145">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.57</v>
+        <v>2.87</v>
       </c>
       <c r="O146">
+        <v>3.48</v>
+      </c>
+      <c r="P146">
+        <v>2.38</v>
+      </c>
+      <c r="Q146">
+        <v>3.25</v>
+      </c>
+      <c r="R146">
+        <v>2.11</v>
+      </c>
+      <c r="S146">
+        <v>1.3</v>
+      </c>
+      <c r="T146">
         <v>3.2</v>
       </c>
-      <c r="P146">
-        <v>2.8</v>
-      </c>
-      <c r="Q146">
-        <v>3.1</v>
-      </c>
-      <c r="R146">
-        <v>2</v>
-      </c>
-      <c r="S146">
-        <v>1.46</v>
-      </c>
-      <c r="T146">
+      <c r="U146">
         <v>2.53</v>
       </c>
-      <c r="U146">
-        <v>3.1</v>
-      </c>
       <c r="V146">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W146">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y146">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="Z146">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA146">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AB146">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AC146">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="AD146">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AE146">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AG146">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>1.33</v>
       </c>
       <c r="AK146">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24276,7 +24276,7 @@
         <v>4</v>
       </c>
       <c r="P147">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="Q147">
         <v>2.05</v>
@@ -24288,16 +24288,16 @@
         <v>1.29</v>
       </c>
       <c r="T147">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U147">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V147">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W147">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X147">
         <v>1.01</v>
@@ -24306,7 +24306,7 @@
         <v>1.2</v>
       </c>
       <c r="Z147">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA147">
         <v>1.61</v>
@@ -24321,13 +24321,13 @@
         <v>1.5</v>
       </c>
       <c r="AE147">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF147">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG147">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O148">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P148">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="Q148">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="R148">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S148">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="T148">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="U148">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="V148">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W148">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X148">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y148">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Z148">
-        <v>3.44</v>
+        <v>2.8</v>
       </c>
       <c r="AA148">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AB148">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AC148">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="AD148">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AE148">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF148">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AG148">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK148">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O151">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="P151">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="Q151">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="R151">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="S151">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T151">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U151">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="V151">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W151">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X151">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z151">
-        <v>3.52</v>
+        <v>4.48</v>
       </c>
       <c r="AA151">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AB151">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AC151">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AD151">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AE151">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF151">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG151">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="O152">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P152">
-        <v>4.3</v>
+        <v>3.57</v>
       </c>
       <c r="Q152">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="R152">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T152">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="U152">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="V152">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W152">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X152">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z152">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="AA152">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AB152">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="AC152">
-        <v>2.27</v>
+        <v>2.68</v>
       </c>
       <c r="AD152">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AE152">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AF152">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AG152">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK152">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O153">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="P153">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="Q153">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="R153">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="S153">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T153">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U153">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="V153">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W153">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X153">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z153">
-        <v>4.48</v>
+        <v>3.52</v>
       </c>
       <c r="AA153">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB153">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC153">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AD153">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AE153">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF153">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG153">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
+        <v>3.05</v>
+      </c>
+      <c r="O154">
+        <v>3.45</v>
+      </c>
+      <c r="P154">
+        <v>2.1</v>
+      </c>
+      <c r="Q154">
+        <v>3.6</v>
+      </c>
+      <c r="R154">
+        <v>2.23</v>
+      </c>
+      <c r="S154">
+        <v>1.33</v>
+      </c>
+      <c r="T154">
+        <v>3</v>
+      </c>
+      <c r="U154">
         <v>2.45</v>
       </c>
-      <c r="O154">
-        <v>3.4</v>
-      </c>
-      <c r="P154">
-        <v>2.58</v>
-      </c>
-      <c r="Q154">
-        <v>2.85</v>
-      </c>
-      <c r="R154">
-        <v>2.1</v>
-      </c>
-      <c r="S154">
-        <v>1.36</v>
-      </c>
-      <c r="T154">
-        <v>2.9</v>
-      </c>
-      <c r="U154">
-        <v>2.75</v>
-      </c>
       <c r="V154">
+        <v>1.48</v>
+      </c>
+      <c r="W154">
+        <v>1.07</v>
+      </c>
+      <c r="X154">
+        <v>1.04</v>
+      </c>
+      <c r="Y154">
+        <v>1.23</v>
+      </c>
+      <c r="Z154">
+        <v>3.8</v>
+      </c>
+      <c r="AA154">
+        <v>1.7</v>
+      </c>
+      <c r="AB154">
+        <v>2.05</v>
+      </c>
+      <c r="AC154">
+        <v>2.86</v>
+      </c>
+      <c r="AD154">
         <v>1.4</v>
       </c>
-      <c r="W154">
-        <v>1.05</v>
-      </c>
-      <c r="X154">
-        <v>1.01</v>
-      </c>
-      <c r="Y154">
-        <v>1.29</v>
-      </c>
-      <c r="Z154">
-        <v>3.4</v>
-      </c>
-      <c r="AA154">
-        <v>1.91</v>
-      </c>
-      <c r="AB154">
-        <v>1.83</v>
-      </c>
-      <c r="AC154">
-        <v>3.39</v>
-      </c>
-      <c r="AD154">
-        <v>1.31</v>
-      </c>
       <c r="AE154">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF154">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG154">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK154">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,80 +25574,80 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="O155">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P155">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q155">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="R155">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="S155">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T155">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="U155">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="V155">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W155">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X155">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y155">
+        <v>1.14</v>
+      </c>
+      <c r="Z155">
+        <v>4.4</v>
+      </c>
+      <c r="AA155">
+        <v>1.53</v>
+      </c>
+      <c r="AB155">
+        <v>2.45</v>
+      </c>
+      <c r="AC155">
+        <v>2.28</v>
+      </c>
+      <c r="AD155">
+        <v>1.55</v>
+      </c>
+      <c r="AE155">
+        <v>1.2</v>
+      </c>
+      <c r="AF155">
+        <v>1.48</v>
+      </c>
+      <c r="AG155">
+        <v>2.4</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
         <v>1.22</v>
       </c>
-      <c r="Z155">
-        <v>3.45</v>
-      </c>
-      <c r="AA155">
-        <v>1.71</v>
-      </c>
-      <c r="AB155">
-        <v>1.98</v>
-      </c>
-      <c r="AC155">
-        <v>2.68</v>
-      </c>
-      <c r="AD155">
-        <v>1.35</v>
-      </c>
-      <c r="AE155">
-        <v>1.14</v>
-      </c>
-      <c r="AF155">
-        <v>1.72</v>
-      </c>
-      <c r="AG155">
-        <v>2</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>1.17</v>
-      </c>
       <c r="AK155">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="O156">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P156">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q156">
-        <v>3.6</v>
+        <v>2.09</v>
       </c>
       <c r="R156">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="S156">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T156">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="U156">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="V156">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W156">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X156">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y156">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z156">
-        <v>3.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA156">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AB156">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC156">
-        <v>2.86</v>
+        <v>2.27</v>
       </c>
       <c r="AD156">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE156">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AF156">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG156">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.22</v>
       </c>
       <c r="AK156">
-        <v>1.28</v>
+        <v>1.99</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="O157">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P157">
+        <v>2.58</v>
+      </c>
+      <c r="Q157">
+        <v>2.85</v>
+      </c>
+      <c r="R157">
+        <v>2.1</v>
+      </c>
+      <c r="S157">
+        <v>1.36</v>
+      </c>
+      <c r="T157">
+        <v>2.9</v>
+      </c>
+      <c r="U157">
+        <v>2.75</v>
+      </c>
+      <c r="V157">
+        <v>1.4</v>
+      </c>
+      <c r="W157">
+        <v>1.05</v>
+      </c>
+      <c r="X157">
+        <v>1.01</v>
+      </c>
+      <c r="Y157">
+        <v>1.29</v>
+      </c>
+      <c r="Z157">
         <v>3.4</v>
       </c>
-      <c r="Q157">
-        <v>2.5</v>
-      </c>
-      <c r="R157">
-        <v>2.47</v>
-      </c>
-      <c r="S157">
-        <v>1.25</v>
-      </c>
-      <c r="T157">
-        <v>3.5</v>
-      </c>
-      <c r="U157">
-        <v>2.22</v>
-      </c>
-      <c r="V157">
-        <v>1.6</v>
-      </c>
-      <c r="W157">
-        <v>1.13</v>
-      </c>
-      <c r="X157">
-        <v>1.03</v>
-      </c>
-      <c r="Y157">
-        <v>1.14</v>
-      </c>
-      <c r="Z157">
-        <v>4.4</v>
-      </c>
       <c r="AA157">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AB157">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AC157">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="AD157">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AE157">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF157">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AG157">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK157">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O160">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P160">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q160">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R160">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S160">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T160">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U160">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V160">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W160">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X160">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y160">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z160">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA160">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB160">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC160">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD160">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE160">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF160">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG160">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK160">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -28517,7 +28517,7 @@
         <v>2.65</v>
       </c>
       <c r="Q173">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="R173">
         <v>2.2</v>
@@ -28544,16 +28544,16 @@
         <v>1.3</v>
       </c>
       <c r="Z173">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA173">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB173">
         <v>1.75</v>
       </c>
       <c r="AC173">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD173">
         <v>1.25</v>
@@ -28562,7 +28562,7 @@
         <v>1.08</v>
       </c>
       <c r="AF173">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG173">
         <v>2</v>
@@ -28581,7 +28581,7 @@
         <v>1.33</v>
       </c>
       <c r="AK173">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,43 +38125,43 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q232">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="R232">
         <v>2</v>
       </c>
       <c r="S232">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T232">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="U232">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="V232">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W232">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X232">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y232">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z232">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA232">
         <v>2.09</v>
@@ -38170,19 +38170,19 @@
         <v>1.66</v>
       </c>
       <c r="AC232">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="AD232">
         <v>1.2</v>
       </c>
       <c r="AE232">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF232">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG232">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>1.27</v>
       </c>
       <c r="AK232">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,43 +38288,43 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O233">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P233">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q233">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="R233">
         <v>2</v>
       </c>
       <c r="S233">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T233">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="U233">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="V233">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W233">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X233">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z233">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA233">
         <v>2.09</v>
@@ -38333,19 +38333,19 @@
         <v>1.66</v>
       </c>
       <c r="AC233">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AD233">
         <v>1.2</v>
       </c>
       <c r="AE233">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF233">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG233">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>1.27</v>
       </c>
       <c r="AK233">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="O235">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P235">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="Q235">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="R235">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="S235">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="T235">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="U235">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="V235">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W235">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X235">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y235">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z235">
-        <v>3.18</v>
+        <v>4.33</v>
       </c>
       <c r="AA235">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AB235">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AC235">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AD235">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE235">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF235">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AG235">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AK235">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
+        <v>2.16</v>
+      </c>
+      <c r="O236">
         <v>3.4</v>
       </c>
-      <c r="O236">
-        <v>3.65</v>
-      </c>
       <c r="P236">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="Q236">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="R236">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S236">
+        <v>1.37</v>
+      </c>
+      <c r="T236">
+        <v>2.98</v>
+      </c>
+      <c r="U236">
+        <v>2.9</v>
+      </c>
+      <c r="V236">
+        <v>1.36</v>
+      </c>
+      <c r="W236">
+        <v>1.07</v>
+      </c>
+      <c r="X236">
+        <v>1.03</v>
+      </c>
+      <c r="Y236">
         <v>1.29</v>
       </c>
-      <c r="T236">
-        <v>3.1</v>
-      </c>
-      <c r="U236">
-        <v>2.44</v>
-      </c>
-      <c r="V236">
-        <v>1.49</v>
-      </c>
-      <c r="W236">
-        <v>1.08</v>
-      </c>
-      <c r="X236">
-        <v>1</v>
-      </c>
-      <c r="Y236">
-        <v>1.2</v>
-      </c>
       <c r="Z236">
-        <v>4.33</v>
+        <v>3.18</v>
       </c>
       <c r="AA236">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AB236">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AC236">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AD236">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE236">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF236">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AG236">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AK236">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -40084,10 +40084,10 @@
         <v>10</v>
       </c>
       <c r="O244">
-        <v>5.95</v>
+        <v>5.2</v>
       </c>
       <c r="P244">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q244">
         <v>10</v>
@@ -40111,28 +40111,28 @@
         <v>1.06</v>
       </c>
       <c r="X244">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y244">
         <v>1.25</v>
       </c>
       <c r="Z244">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="AA244">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AB244">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC244">
         <v>2.76</v>
       </c>
       <c r="AD244">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE244">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF244">
         <v>2.35</v>
@@ -42526,16 +42526,16 @@
         </is>
       </c>
       <c r="N259">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O259">
         <v>3.25</v>
       </c>
       <c r="P259">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Q259">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R259">
         <v>1.91</v>
@@ -42547,13 +42547,13 @@
         <v>2.35</v>
       </c>
       <c r="U259">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="V259">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W259">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X259">
         <v>1.1</v>
@@ -42565,7 +42565,7 @@
         <v>2.5</v>
       </c>
       <c r="AA259">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AB259">
         <v>1.44</v>
@@ -42580,10 +42580,10 @@
         <v>1.04</v>
       </c>
       <c r="AF259">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG259">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>1.26</v>
       </c>
       <c r="AK259">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42689,25 +42689,25 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O260">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P260">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="Q260">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="R260">
         <v>1.91</v>
       </c>
       <c r="S260">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="T260">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="U260">
         <v>3.75</v>
@@ -42719,22 +42719,22 @@
         <v>1.01</v>
       </c>
       <c r="X260">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y260">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z260">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AA260">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB260">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AC260">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD260">
         <v>1.11</v>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK260">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -44482,28 +44482,28 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O271">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P271">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q271">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R271">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="S271">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T271">
         <v>2.25</v>
       </c>
       <c r="U271">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="V271">
         <v>1.2</v>
@@ -44515,22 +44515,22 @@
         <v>1.08</v>
       </c>
       <c r="Y271">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Z271">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA271">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AB271">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AC271">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AD271">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE271">
         <v>1.03</v>
@@ -44539,7 +44539,7 @@
         <v>2.25</v>
       </c>
       <c r="AG271">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK271">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44645,28 +44645,28 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O272">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P272">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q272">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R272">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="S272">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="T272">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U272">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="V272">
         <v>1.22</v>
@@ -44675,25 +44675,25 @@
         <v>1.01</v>
       </c>
       <c r="X272">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y272">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Z272">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AA272">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="AB272">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AC272">
         <v>5.45</v>
       </c>
       <c r="AD272">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE272">
         <v>1.03</v>
@@ -44702,7 +44702,7 @@
         <v>2.25</v>
       </c>
       <c r="AG272">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,80 +45623,80 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O278">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P278">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="Q278">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="R278">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="S278">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="T278">
+        <v>2.63</v>
+      </c>
+      <c r="U278">
+        <v>2.9</v>
+      </c>
+      <c r="V278">
+        <v>1.37</v>
+      </c>
+      <c r="W278">
+        <v>1.06</v>
+      </c>
+      <c r="X278">
+        <v>1.07</v>
+      </c>
+      <c r="Y278">
+        <v>1.33</v>
+      </c>
+      <c r="Z278">
         <v>3.1</v>
       </c>
-      <c r="U278">
-        <v>2.55</v>
-      </c>
-      <c r="V278">
-        <v>1.43</v>
-      </c>
-      <c r="W278">
-        <v>1.11</v>
-      </c>
-      <c r="X278">
-        <v>1.04</v>
-      </c>
-      <c r="Y278">
-        <v>1.18</v>
-      </c>
-      <c r="Z278">
-        <v>4.2</v>
-      </c>
       <c r="AA278">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AB278">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="AC278">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="AD278">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE278">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF278">
+        <v>1.85</v>
+      </c>
+      <c r="AG278">
+        <v>1.89</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ278">
+        <v>1.36</v>
+      </c>
+      <c r="AK278">
         <v>1.6</v>
-      </c>
-      <c r="AG278">
-        <v>2.3</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ278">
-        <v>1.31</v>
-      </c>
-      <c r="AK278">
-        <v>1.44</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="O280">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P280">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="Q280">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="R280">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="S280">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="T280">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="U280">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="V280">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W280">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X280">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y280">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z280">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA280">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="AB280">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AC280">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
       <c r="AD280">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE280">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF280">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG280">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK280">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -47905,10 +47905,10 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O292">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P292">
         <v>3.1</v>
@@ -49055,28 +49055,28 @@
         <v>2.05</v>
       </c>
       <c r="Q299">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="R299">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S299">
         <v>1.4</v>
       </c>
       <c r="T299">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U299">
         <v>3</v>
       </c>
       <c r="V299">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W299">
         <v>1.04</v>
       </c>
       <c r="X299">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y299">
         <v>1.3</v>
@@ -49085,19 +49085,19 @@
         <v>2.99</v>
       </c>
       <c r="AA299">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AB299">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC299">
-        <v>3.73</v>
+        <v>3.54</v>
       </c>
       <c r="AD299">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE299">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF299">
         <v>1.83</v>
@@ -49698,64 +49698,64 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q303">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R303">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S303">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T303">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U303">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V303">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W303">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X303">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y303">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z303">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA303">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB303">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC303">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD303">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE303">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF303">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG303">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK303">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -52475,7 +52475,7 @@
         <v>4.28</v>
       </c>
       <c r="P320">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="Q320">
         <v>2.15</v>
@@ -52490,7 +52490,7 @@
         <v>4.33</v>
       </c>
       <c r="U320">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="V320">
         <v>1.78</v>
@@ -52505,19 +52505,19 @@
         <v>1.07</v>
       </c>
       <c r="Z320">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA320">
         <v>1.32</v>
       </c>
       <c r="AB320">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AC320">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AD320">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE320">
         <v>1.33</v>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK320">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52665,16 +52665,16 @@
         <v>1.01</v>
       </c>
       <c r="Y321">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z321">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA321">
         <v>1.4</v>
       </c>
       <c r="AB321">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AC321">
         <v>1.95</v>
@@ -52798,7 +52798,7 @@
         <v>1.8</v>
       </c>
       <c r="O322">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P322">
         <v>3.4</v>
@@ -52849,10 +52849,10 @@
         <v>1.36</v>
       </c>
       <c r="AF322">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG322">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>5.8</v>
       </c>
       <c r="AA323">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB323">
         <v>2.7</v>
@@ -53124,13 +53124,13 @@
         <v>2.05</v>
       </c>
       <c r="O324">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P324">
         <v>3</v>
       </c>
       <c r="Q324">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R324">
         <v>2.3</v>
@@ -53175,7 +53175,7 @@
         <v>1.15</v>
       </c>
       <c r="AF324">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG324">
         <v>2.38</v>
@@ -53791,13 +53791,13 @@
         <v>1.18</v>
       </c>
       <c r="T328">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U328">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V328">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W328">
         <v>1.2</v>
@@ -53812,16 +53812,16 @@
         <v>6.5</v>
       </c>
       <c r="AA328">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB328">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AC328">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD328">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE328">
         <v>1.33</v>
@@ -53987,7 +53987,7 @@
         <v>1.49</v>
       </c>
       <c r="AE329">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF329">
         <v>1.45</v>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK329">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54138,7 +54138,7 @@
         <v>5</v>
       </c>
       <c r="AA330">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB330">
         <v>2.5</v>
@@ -54153,10 +54153,10 @@
         <v>1.3</v>
       </c>
       <c r="AF330">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG330">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>1.55</v>
       </c>
       <c r="W332">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X332">
         <v>1.03</v>
@@ -54588,7 +54588,7 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O333">
         <v>3.9</v>
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,64 +54914,64 @@
         </is>
       </c>
       <c r="N335">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O335">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P335">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="Q335">
-        <v>2.59</v>
+        <v>3.03</v>
       </c>
       <c r="R335">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S335">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T335">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U335">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V335">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W335">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X335">
         <v>1.01</v>
       </c>
       <c r="Y335">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z335">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA335">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB335">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC335">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AD335">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE335">
         <v>1.08</v>
       </c>
       <c r="AF335">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG335">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK335">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,64 +55077,64 @@
         </is>
       </c>
       <c r="N336">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="O336">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P336">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="Q336">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="R336">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="S336">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="T336">
-        <v>3.05</v>
+        <v>2.41</v>
       </c>
       <c r="U336">
+        <v>3.18</v>
+      </c>
+      <c r="V336">
+        <v>1.28</v>
+      </c>
+      <c r="W336">
+        <v>1.02</v>
+      </c>
+      <c r="X336">
+        <v>1.04</v>
+      </c>
+      <c r="Y336">
+        <v>1.45</v>
+      </c>
+      <c r="Z336">
         <v>2.75</v>
       </c>
-      <c r="V336">
-        <v>1.41</v>
-      </c>
-      <c r="W336">
-        <v>1.1</v>
-      </c>
-      <c r="X336">
-        <v>1.01</v>
-      </c>
-      <c r="Y336">
-        <v>1.23</v>
-      </c>
-      <c r="Z336">
-        <v>3.42</v>
-      </c>
       <c r="AA336">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="AB336">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AC336">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="AD336">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE336">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF336">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AG336">
-        <v>2.07</v>
+        <v>1.69</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK336">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,65 +55240,65 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O337">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P337">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q337">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="R337">
+        <v>2.24</v>
+      </c>
+      <c r="S337">
+        <v>1.34</v>
+      </c>
+      <c r="T337">
+        <v>2.88</v>
+      </c>
+      <c r="U337">
+        <v>2.81</v>
+      </c>
+      <c r="V337">
+        <v>1.4</v>
+      </c>
+      <c r="W337">
+        <v>1.06</v>
+      </c>
+      <c r="X337">
+        <v>1.01</v>
+      </c>
+      <c r="Y337">
+        <v>1.25</v>
+      </c>
+      <c r="Z337">
+        <v>3.28</v>
+      </c>
+      <c r="AA337">
+        <v>1.9</v>
+      </c>
+      <c r="AB337">
+        <v>1.85</v>
+      </c>
+      <c r="AC337">
+        <v>3.04</v>
+      </c>
+      <c r="AD337">
+        <v>1.29</v>
+      </c>
+      <c r="AE337">
+        <v>1.08</v>
+      </c>
+      <c r="AF337">
+        <v>1.65</v>
+      </c>
+      <c r="AG337">
         <v>2.06</v>
       </c>
-      <c r="S337">
-        <v>1.47</v>
-      </c>
-      <c r="T337">
-        <v>2.41</v>
-      </c>
-      <c r="U337">
-        <v>3.18</v>
-      </c>
-      <c r="V337">
-        <v>1.28</v>
-      </c>
-      <c r="W337">
-        <v>1.02</v>
-      </c>
-      <c r="X337">
-        <v>1.04</v>
-      </c>
-      <c r="Y337">
-        <v>1.45</v>
-      </c>
-      <c r="Z337">
-        <v>2.75</v>
-      </c>
-      <c r="AA337">
-        <v>2.29</v>
-      </c>
-      <c r="AB337">
-        <v>1.6</v>
-      </c>
-      <c r="AC337">
-        <v>3.65</v>
-      </c>
-      <c r="AD337">
-        <v>1.21</v>
-      </c>
-      <c r="AE337">
-        <v>1.02</v>
-      </c>
-      <c r="AF337">
-        <v>2.05</v>
-      </c>
-      <c r="AG337">
-        <v>1.69</v>
-      </c>
       <c r="AH337" t="inlineStr">
         <is>
           <t>[]</t>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK337">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55442,7 +55442,7 @@
         <v>5</v>
       </c>
       <c r="AA338">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB338">
         <v>2.4</v>
@@ -55460,7 +55460,7 @@
         <v>1.45</v>
       </c>
       <c r="AG338">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>1.57</v>
       </c>
       <c r="W339">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X339">
         <v>1.03</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="R3">
+        <v>1.99</v>
+      </c>
+      <c r="S3">
+        <v>1.39</v>
+      </c>
+      <c r="T3">
+        <v>2.91</v>
+      </c>
+      <c r="U3">
+        <v>2.99</v>
+      </c>
+      <c r="V3">
+        <v>1.34</v>
+      </c>
+      <c r="W3">
+        <v>1.03</v>
+      </c>
+      <c r="X3">
+        <v>1.06</v>
+      </c>
+      <c r="Y3">
+        <v>1.27</v>
+      </c>
+      <c r="Z3">
+        <v>3.41</v>
+      </c>
+      <c r="AA3">
         <v>2.05</v>
       </c>
-      <c r="S3">
-        <v>1.4</v>
-      </c>
-      <c r="T3">
-        <v>2.75</v>
-      </c>
-      <c r="U3">
-        <v>2.8</v>
-      </c>
-      <c r="V3">
-        <v>1.4</v>
-      </c>
-      <c r="W3">
-        <v>1.06</v>
-      </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
-      <c r="Y3">
-        <v>1.3</v>
-      </c>
-      <c r="Z3">
-        <v>3.5</v>
-      </c>
-      <c r="AA3">
-        <v>1.95</v>
-      </c>
       <c r="AB3">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>3.39</v>
+        <v>3.52</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.46</v>
+        <v>2.9</v>
       </c>
       <c r="R4">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
         <v>1.03</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
+        <v>1.3</v>
+      </c>
+      <c r="Z4">
+        <v>3.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.95</v>
+      </c>
+      <c r="AB4">
+        <v>1.85</v>
+      </c>
+      <c r="AC4">
+        <v>3.39</v>
+      </c>
+      <c r="AD4">
+        <v>1.26</v>
+      </c>
+      <c r="AE4">
         <v>1.06</v>
       </c>
-      <c r="Y4">
-        <v>1.27</v>
-      </c>
-      <c r="Z4">
-        <v>3.41</v>
-      </c>
-      <c r="AA4">
-        <v>2.05</v>
-      </c>
-      <c r="AB4">
-        <v>1.75</v>
-      </c>
-      <c r="AC4">
-        <v>3.52</v>
-      </c>
-      <c r="AD4">
-        <v>1.29</v>
-      </c>
-      <c r="AE4">
-        <v>1.04</v>
-      </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG4">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>2.36</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA33">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB33">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC33">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AD33">
+        <v>1.5</v>
+      </c>
+      <c r="AE33">
+        <v>1.18</v>
+      </c>
+      <c r="AF33">
         <v>1.45</v>
       </c>
-      <c r="AE33">
-        <v>1.2</v>
-      </c>
-      <c r="AF33">
-        <v>1.55</v>
-      </c>
       <c r="AG33">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AK33">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.67</v>
+        <v>1.83</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T34">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V34">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
         <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB34">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC34">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AD34">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG34">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O50">
         <v>3.35</v>
       </c>
       <c r="P50">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q50">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R50">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="S50">
+        <v>1.33</v>
+      </c>
+      <c r="T50">
+        <v>3.1</v>
+      </c>
+      <c r="U50">
+        <v>2.5</v>
+      </c>
+      <c r="V50">
+        <v>1.45</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1</v>
+      </c>
+      <c r="Y50">
+        <v>1.22</v>
+      </c>
+      <c r="Z50">
+        <v>3.98</v>
+      </c>
+      <c r="AA50">
+        <v>1.78</v>
+      </c>
+      <c r="AB50">
+        <v>2</v>
+      </c>
+      <c r="AC50">
+        <v>2.76</v>
+      </c>
+      <c r="AD50">
         <v>1.39</v>
       </c>
-      <c r="T50">
-        <v>2.73</v>
-      </c>
-      <c r="U50">
-        <v>2.95</v>
-      </c>
-      <c r="V50">
-        <v>1.33</v>
-      </c>
-      <c r="W50">
-        <v>1.04</v>
-      </c>
-      <c r="X50">
-        <v>1.06</v>
-      </c>
-      <c r="Y50">
-        <v>1.36</v>
-      </c>
-      <c r="Z50">
-        <v>2.94</v>
-      </c>
-      <c r="AA50">
-        <v>2.1</v>
-      </c>
-      <c r="AB50">
-        <v>1.7</v>
-      </c>
-      <c r="AC50">
-        <v>3.76</v>
-      </c>
-      <c r="AD50">
-        <v>1.25</v>
-      </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O51">
         <v>3.35</v>
       </c>
       <c r="P51">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q51">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R51">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="S51">
+        <v>1.39</v>
+      </c>
+      <c r="T51">
+        <v>2.73</v>
+      </c>
+      <c r="U51">
+        <v>2.95</v>
+      </c>
+      <c r="V51">
         <v>1.33</v>
       </c>
-      <c r="T51">
-        <v>3.1</v>
-      </c>
-      <c r="U51">
-        <v>2.5</v>
-      </c>
-      <c r="V51">
-        <v>1.45</v>
-      </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>3.98</v>
+        <v>2.94</v>
       </c>
       <c r="AA51">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC51">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O62">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q62">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="R62">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="U62">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="V62">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z62">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA62">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB62">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="AC62">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD62">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE62">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG62">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
+        <v>1.75</v>
+      </c>
+      <c r="O63">
+        <v>3.9</v>
+      </c>
+      <c r="P63">
+        <v>4.1</v>
+      </c>
+      <c r="Q63">
+        <v>2.25</v>
+      </c>
+      <c r="R63">
+        <v>2.38</v>
+      </c>
+      <c r="S63">
+        <v>1.3</v>
+      </c>
+      <c r="T63">
+        <v>3.08</v>
+      </c>
+      <c r="U63">
+        <v>2.38</v>
+      </c>
+      <c r="V63">
+        <v>1.5</v>
+      </c>
+      <c r="W63">
+        <v>1.11</v>
+      </c>
+      <c r="X63">
+        <v>1.02</v>
+      </c>
+      <c r="Y63">
+        <v>1.12</v>
+      </c>
+      <c r="Z63">
+        <v>4.2</v>
+      </c>
+      <c r="AA63">
+        <v>1.67</v>
+      </c>
+      <c r="AB63">
+        <v>2.17</v>
+      </c>
+      <c r="AC63">
+        <v>2.32</v>
+      </c>
+      <c r="AD63">
+        <v>1.44</v>
+      </c>
+      <c r="AE63">
+        <v>1.2</v>
+      </c>
+      <c r="AF63">
+        <v>1.5</v>
+      </c>
+      <c r="AG63">
         <v>2.2</v>
-      </c>
-      <c r="O63">
-        <v>3.5</v>
-      </c>
-      <c r="P63">
-        <v>2.75</v>
-      </c>
-      <c r="Q63">
-        <v>2.63</v>
-      </c>
-      <c r="R63">
-        <v>2.44</v>
-      </c>
-      <c r="S63">
-        <v>1.2</v>
-      </c>
-      <c r="T63">
-        <v>3.4</v>
-      </c>
-      <c r="U63">
-        <v>2.02</v>
-      </c>
-      <c r="V63">
-        <v>1.47</v>
-      </c>
-      <c r="W63">
-        <v>1.1</v>
-      </c>
-      <c r="X63">
-        <v>1.04</v>
-      </c>
-      <c r="Y63">
-        <v>1.17</v>
-      </c>
-      <c r="Z63">
-        <v>3.3</v>
-      </c>
-      <c r="AA63">
-        <v>1.53</v>
-      </c>
-      <c r="AB63">
-        <v>2.34</v>
-      </c>
-      <c r="AC63">
-        <v>2.3</v>
-      </c>
-      <c r="AD63">
-        <v>1.55</v>
-      </c>
-      <c r="AE63">
-        <v>1.22</v>
-      </c>
-      <c r="AF63">
-        <v>1.36</v>
-      </c>
-      <c r="AG63">
-        <v>2.45</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.3</v>
+        <v>1.23</v>
       </c>
       <c r="O112">
-        <v>3.9</v>
+        <v>6.9</v>
       </c>
       <c r="P112">
-        <v>2.69</v>
+        <v>9.75</v>
       </c>
       <c r="Q112">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="R112">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="S112">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T112">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U112">
         <v>2.02</v>
       </c>
       <c r="V112">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="W112">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X112">
         <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z112">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA112">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB112">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AC112">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD112">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AE112">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF112">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AG112">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="AK112">
-        <v>1.55</v>
+        <v>4.15</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.23</v>
+        <v>2.3</v>
       </c>
       <c r="O113">
-        <v>6.9</v>
+        <v>3.9</v>
       </c>
       <c r="P113">
-        <v>9.75</v>
+        <v>2.69</v>
       </c>
       <c r="Q113">
-        <v>1.59</v>
+        <v>2.7</v>
       </c>
       <c r="R113">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="S113">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T113">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U113">
         <v>2.02</v>
       </c>
       <c r="V113">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="W113">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z113">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA113">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB113">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AC113">
+        <v>1.85</v>
+      </c>
+      <c r="AD113">
         <v>1.82</v>
       </c>
-      <c r="AD113">
-        <v>1.94</v>
-      </c>
       <c r="AE113">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF113">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AG113">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AK113">
-        <v>4.15</v>
+        <v>1.55</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.7</v>
+        <v>1.46</v>
       </c>
       <c r="O126">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P126">
-        <v>2.4</v>
+        <v>6.25</v>
       </c>
       <c r="Q126">
-        <v>3.23</v>
+        <v>1.93</v>
       </c>
       <c r="R126">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="S126">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T126">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="U126">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W126">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z126">
-        <v>2.97</v>
+        <v>3.95</v>
       </c>
       <c r="AA126">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="AB126">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AC126">
-        <v>3.65</v>
+        <v>3.06</v>
       </c>
       <c r="AD126">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE126">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF126">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AG126">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="AK126">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.46</v>
+        <v>2.7</v>
       </c>
       <c r="O127">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P127">
-        <v>6.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q127">
-        <v>1.93</v>
+        <v>3.23</v>
       </c>
       <c r="R127">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="S127">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T127">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="U127">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="V127">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z127">
-        <v>3.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA127">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AB127">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AC127">
-        <v>3.06</v>
+        <v>3.65</v>
       </c>
       <c r="AD127">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE127">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF127">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG127">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AK127">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>3.15</v>
+        <v>1.57</v>
       </c>
       <c r="O132">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P132">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="Q132">
-        <v>3.52</v>
+        <v>2</v>
       </c>
       <c r="R132">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="S132">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T132">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="U132">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V132">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="W132">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X132">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z132">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA132">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AB132">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC132">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="AD132">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE132">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF132">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG132">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK132">
-        <v>1.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,31 +21988,31 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O133">
+        <v>3.35</v>
+      </c>
+      <c r="P133">
         <v>3.25</v>
       </c>
-      <c r="P133">
-        <v>3</v>
-      </c>
       <c r="Q133">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="R133">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T133">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U133">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V133">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W133">
         <v>1.05</v>
@@ -22021,31 +22021,31 @@
         <v>1</v>
       </c>
       <c r="Y133">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z133">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA133">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB133">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AC133">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="AD133">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE133">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF133">
         <v>1.7</v>
       </c>
       <c r="AG133">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK133">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O134">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P134">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q134">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="R134">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S134">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="T134">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U134">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="V134">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W134">
         <v>1.05</v>
       </c>
       <c r="X134">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y134">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z134">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA134">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AB134">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC134">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AD134">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE134">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF134">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG134">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK134">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,65 +22314,65 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="O135">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="P135">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q135">
+        <v>2.89</v>
+      </c>
+      <c r="R135">
+        <v>2.24</v>
+      </c>
+      <c r="S135">
+        <v>1.37</v>
+      </c>
+      <c r="T135">
+        <v>2.81</v>
+      </c>
+      <c r="U135">
+        <v>2.81</v>
+      </c>
+      <c r="V135">
+        <v>1.4</v>
+      </c>
+      <c r="W135">
+        <v>1.05</v>
+      </c>
+      <c r="X135">
+        <v>1</v>
+      </c>
+      <c r="Y135">
+        <v>1.29</v>
+      </c>
+      <c r="Z135">
+        <v>3.4</v>
+      </c>
+      <c r="AA135">
+        <v>1.92</v>
+      </c>
+      <c r="AB135">
+        <v>1.84</v>
+      </c>
+      <c r="AC135">
+        <v>3.21</v>
+      </c>
+      <c r="AD135">
+        <v>1.33</v>
+      </c>
+      <c r="AE135">
+        <v>1.07</v>
+      </c>
+      <c r="AF135">
+        <v>1.7</v>
+      </c>
+      <c r="AG135">
         <v>2</v>
       </c>
-      <c r="R135">
-        <v>2.4</v>
-      </c>
-      <c r="S135">
-        <v>1.29</v>
-      </c>
-      <c r="T135">
-        <v>3.44</v>
-      </c>
-      <c r="U135">
-        <v>2.45</v>
-      </c>
-      <c r="V135">
-        <v>1.54</v>
-      </c>
-      <c r="W135">
-        <v>1.13</v>
-      </c>
-      <c r="X135">
-        <v>1.01</v>
-      </c>
-      <c r="Y135">
-        <v>1.2</v>
-      </c>
-      <c r="Z135">
-        <v>4.3</v>
-      </c>
-      <c r="AA135">
-        <v>1.61</v>
-      </c>
-      <c r="AB135">
-        <v>2.25</v>
-      </c>
-      <c r="AC135">
-        <v>2.43</v>
-      </c>
-      <c r="AD135">
-        <v>1.5</v>
-      </c>
-      <c r="AE135">
-        <v>1.15</v>
-      </c>
-      <c r="AF135">
-        <v>1.62</v>
-      </c>
-      <c r="AG135">
-        <v>2.1</v>
-      </c>
       <c r="AH135" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK135">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="O136">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P136">
+        <v>2.65</v>
+      </c>
+      <c r="Q136">
+        <v>3.01</v>
+      </c>
+      <c r="R136">
+        <v>1.95</v>
+      </c>
+      <c r="S136">
+        <v>1.46</v>
+      </c>
+      <c r="T136">
+        <v>2.75</v>
+      </c>
+      <c r="U136">
         <v>3.25</v>
       </c>
-      <c r="Q136">
-        <v>2.7</v>
-      </c>
-      <c r="R136">
-        <v>2.1</v>
-      </c>
-      <c r="S136">
-        <v>1.33</v>
-      </c>
-      <c r="T136">
-        <v>2.88</v>
-      </c>
-      <c r="U136">
-        <v>2.62</v>
-      </c>
       <c r="V136">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="W136">
         <v>1.05</v>
       </c>
       <c r="X136">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y136">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="Z136">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA136">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AB136">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="AC136">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AD136">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AE136">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF136">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG136">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK136">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O137">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q137">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="R137">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="S137">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U137">
-        <v>2.98</v>
+        <v>2.55</v>
       </c>
       <c r="V137">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W137">
+        <v>1.07</v>
+      </c>
+      <c r="X137">
         <v>1.05</v>
       </c>
-      <c r="X137">
-        <v>1</v>
-      </c>
       <c r="Y137">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z137">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AA137">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB137">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC137">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AD137">
+        <v>1.33</v>
+      </c>
+      <c r="AE137">
+        <v>1.08</v>
+      </c>
+      <c r="AF137">
+        <v>1.75</v>
+      </c>
+      <c r="AG137">
+        <v>2.05</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
         <v>1.23</v>
       </c>
-      <c r="AE137">
-        <v>1.04</v>
-      </c>
-      <c r="AF137">
-        <v>1.8</v>
-      </c>
-      <c r="AG137">
-        <v>2</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.25</v>
-      </c>
       <c r="AK137">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.87</v>
+        <v>1.66</v>
       </c>
       <c r="O146">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P146">
-        <v>2.38</v>
+        <v>4.54</v>
       </c>
       <c r="Q146">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="R146">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="S146">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T146">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U146">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="V146">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W146">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X146">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z146">
-        <v>3.44</v>
+        <v>4.4</v>
       </c>
       <c r="AA146">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB146">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AC146">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AD146">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AE146">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF146">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG146">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK146">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="O147">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P147">
-        <v>4.54</v>
+        <v>2.7</v>
       </c>
       <c r="Q147">
+        <v>3.3</v>
+      </c>
+      <c r="R147">
         <v>2.05</v>
       </c>
-      <c r="R147">
-        <v>2.5</v>
-      </c>
       <c r="S147">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="T147">
-        <v>3.8</v>
+        <v>2.53</v>
       </c>
       <c r="U147">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="V147">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W147">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X147">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y147">
+        <v>1.37</v>
+      </c>
+      <c r="Z147">
+        <v>2.8</v>
+      </c>
+      <c r="AA147">
+        <v>2.08</v>
+      </c>
+      <c r="AB147">
+        <v>1.65</v>
+      </c>
+      <c r="AC147">
+        <v>3.74</v>
+      </c>
+      <c r="AD147">
         <v>1.2</v>
       </c>
-      <c r="Z147">
-        <v>4.4</v>
-      </c>
-      <c r="AA147">
-        <v>1.61</v>
-      </c>
-      <c r="AB147">
-        <v>2.31</v>
-      </c>
-      <c r="AC147">
-        <v>2.5</v>
-      </c>
-      <c r="AD147">
-        <v>1.5</v>
-      </c>
       <c r="AE147">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF147">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AG147">
-        <v>2.18</v>
+        <v>1.86</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK147">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="O148">
+        <v>3.48</v>
+      </c>
+      <c r="P148">
+        <v>2.38</v>
+      </c>
+      <c r="Q148">
+        <v>3.25</v>
+      </c>
+      <c r="R148">
+        <v>2.11</v>
+      </c>
+      <c r="S148">
+        <v>1.3</v>
+      </c>
+      <c r="T148">
         <v>3.2</v>
       </c>
-      <c r="P148">
-        <v>2.7</v>
-      </c>
-      <c r="Q148">
-        <v>3.3</v>
-      </c>
-      <c r="R148">
-        <v>2.05</v>
-      </c>
-      <c r="S148">
-        <v>1.46</v>
-      </c>
-      <c r="T148">
+      <c r="U148">
         <v>2.53</v>
       </c>
-      <c r="U148">
-        <v>3.1</v>
-      </c>
       <c r="V148">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W148">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X148">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y148">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="Z148">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA148">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AB148">
+        <v>1.88</v>
+      </c>
+      <c r="AC148">
+        <v>3</v>
+      </c>
+      <c r="AD148">
+        <v>1.35</v>
+      </c>
+      <c r="AE148">
+        <v>1.13</v>
+      </c>
+      <c r="AF148">
         <v>1.65</v>
       </c>
-      <c r="AC148">
-        <v>3.74</v>
-      </c>
-      <c r="AD148">
-        <v>1.2</v>
-      </c>
-      <c r="AE148">
-        <v>1.04</v>
-      </c>
-      <c r="AF148">
-        <v>1.84</v>
-      </c>
       <c r="AG148">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK148">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,34 +24922,34 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="O151">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P151">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="Q151">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="R151">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="S151">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T151">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="U151">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="V151">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W151">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X151">
         <v>1.01</v>
@@ -24958,28 +24958,28 @@
         <v>1.22</v>
       </c>
       <c r="Z151">
-        <v>4.48</v>
+        <v>3.45</v>
       </c>
       <c r="AA151">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AB151">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC151">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="AD151">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AE151">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF151">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG151">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK151">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,80 +25085,80 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.71</v>
+        <v>3.05</v>
       </c>
       <c r="O152">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P152">
-        <v>3.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q152">
-        <v>2.21</v>
+        <v>3.6</v>
       </c>
       <c r="R152">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="S152">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T152">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U152">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="V152">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W152">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X152">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y152">
+        <v>1.23</v>
+      </c>
+      <c r="Z152">
+        <v>3.8</v>
+      </c>
+      <c r="AA152">
+        <v>1.7</v>
+      </c>
+      <c r="AB152">
+        <v>2.05</v>
+      </c>
+      <c r="AC152">
+        <v>2.86</v>
+      </c>
+      <c r="AD152">
+        <v>1.4</v>
+      </c>
+      <c r="AE152">
+        <v>1.13</v>
+      </c>
+      <c r="AF152">
+        <v>1.62</v>
+      </c>
+      <c r="AG152">
+        <v>2.2</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ152">
         <v>1.22</v>
       </c>
-      <c r="Z152">
-        <v>3.45</v>
-      </c>
-      <c r="AA152">
-        <v>1.71</v>
-      </c>
-      <c r="AB152">
-        <v>1.98</v>
-      </c>
-      <c r="AC152">
-        <v>2.68</v>
-      </c>
-      <c r="AD152">
-        <v>1.35</v>
-      </c>
-      <c r="AE152">
-        <v>1.14</v>
-      </c>
-      <c r="AF152">
-        <v>1.72</v>
-      </c>
-      <c r="AG152">
-        <v>2</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ152">
-        <v>1.17</v>
-      </c>
       <c r="AK152">
-        <v>2.06</v>
+        <v>1.28</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="O154">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P154">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q154">
-        <v>3.6</v>
+        <v>2.09</v>
       </c>
       <c r="R154">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="S154">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T154">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="U154">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="V154">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W154">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X154">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="Z154">
-        <v>3.8</v>
+        <v>4.85</v>
       </c>
       <c r="AA154">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="AB154">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC154">
-        <v>2.86</v>
+        <v>2.27</v>
       </c>
       <c r="AD154">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AE154">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AF154">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG154">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>1.22</v>
       </c>
       <c r="AK154">
-        <v>1.28</v>
+        <v>1.99</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O155">
+        <v>3.75</v>
+      </c>
+      <c r="P155">
         <v>3.6</v>
       </c>
-      <c r="P155">
+      <c r="Q155">
+        <v>2.35</v>
+      </c>
+      <c r="R155">
+        <v>2.28</v>
+      </c>
+      <c r="S155">
+        <v>1.29</v>
+      </c>
+      <c r="T155">
         <v>3.4</v>
       </c>
-      <c r="Q155">
-        <v>2.5</v>
-      </c>
-      <c r="R155">
-        <v>2.47</v>
-      </c>
-      <c r="S155">
-        <v>1.25</v>
-      </c>
-      <c r="T155">
-        <v>3.5</v>
-      </c>
       <c r="U155">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="V155">
+        <v>1.55</v>
+      </c>
+      <c r="W155">
+        <v>1.12</v>
+      </c>
+      <c r="X155">
+        <v>1.01</v>
+      </c>
+      <c r="Y155">
+        <v>1.22</v>
+      </c>
+      <c r="Z155">
+        <v>4.48</v>
+      </c>
+      <c r="AA155">
+        <v>1.65</v>
+      </c>
+      <c r="AB155">
+        <v>2.25</v>
+      </c>
+      <c r="AC155">
+        <v>2.65</v>
+      </c>
+      <c r="AD155">
+        <v>1.49</v>
+      </c>
+      <c r="AE155">
+        <v>1.13</v>
+      </c>
+      <c r="AF155">
         <v>1.6</v>
       </c>
-      <c r="W155">
-        <v>1.13</v>
-      </c>
-      <c r="X155">
-        <v>1.03</v>
-      </c>
-      <c r="Y155">
-        <v>1.14</v>
-      </c>
-      <c r="Z155">
-        <v>4.4</v>
-      </c>
-      <c r="AA155">
-        <v>1.53</v>
-      </c>
-      <c r="AB155">
-        <v>2.45</v>
-      </c>
-      <c r="AC155">
-        <v>2.28</v>
-      </c>
-      <c r="AD155">
-        <v>1.55</v>
-      </c>
-      <c r="AE155">
-        <v>1.2</v>
-      </c>
-      <c r="AF155">
-        <v>1.48</v>
-      </c>
       <c r="AG155">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>1.22</v>
       </c>
       <c r="AK155">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="O156">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P156">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="Q156">
-        <v>2.09</v>
+        <v>2.85</v>
       </c>
       <c r="R156">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="S156">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T156">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="U156">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="V156">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W156">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z156">
-        <v>4.85</v>
+        <v>3.4</v>
       </c>
       <c r="AA156">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AB156">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC156">
-        <v>2.27</v>
+        <v>3.39</v>
       </c>
       <c r="AD156">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AE156">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AF156">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG156">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK156">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
+        <v>2</v>
+      </c>
+      <c r="O157">
+        <v>3.6</v>
+      </c>
+      <c r="P157">
+        <v>3.4</v>
+      </c>
+      <c r="Q157">
+        <v>2.5</v>
+      </c>
+      <c r="R157">
+        <v>2.47</v>
+      </c>
+      <c r="S157">
+        <v>1.25</v>
+      </c>
+      <c r="T157">
+        <v>3.5</v>
+      </c>
+      <c r="U157">
+        <v>2.22</v>
+      </c>
+      <c r="V157">
+        <v>1.6</v>
+      </c>
+      <c r="W157">
+        <v>1.13</v>
+      </c>
+      <c r="X157">
+        <v>1.03</v>
+      </c>
+      <c r="Y157">
+        <v>1.14</v>
+      </c>
+      <c r="Z157">
+        <v>4.4</v>
+      </c>
+      <c r="AA157">
+        <v>1.53</v>
+      </c>
+      <c r="AB157">
         <v>2.45</v>
       </c>
-      <c r="O157">
-        <v>3.4</v>
-      </c>
-      <c r="P157">
-        <v>2.58</v>
-      </c>
-      <c r="Q157">
-        <v>2.85</v>
-      </c>
-      <c r="R157">
-        <v>2.1</v>
-      </c>
-      <c r="S157">
-        <v>1.36</v>
-      </c>
-      <c r="T157">
-        <v>2.9</v>
-      </c>
-      <c r="U157">
-        <v>2.75</v>
-      </c>
-      <c r="V157">
-        <v>1.4</v>
-      </c>
-      <c r="W157">
-        <v>1.05</v>
-      </c>
-      <c r="X157">
-        <v>1.01</v>
-      </c>
-      <c r="Y157">
-        <v>1.29</v>
-      </c>
-      <c r="Z157">
-        <v>3.4</v>
-      </c>
-      <c r="AA157">
-        <v>1.91</v>
-      </c>
-      <c r="AB157">
-        <v>1.83</v>
-      </c>
       <c r="AC157">
-        <v>3.39</v>
+        <v>2.28</v>
       </c>
       <c r="AD157">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AE157">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF157">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AG157">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK157">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -51986,7 +51986,7 @@
         <v>3.98</v>
       </c>
       <c r="P317">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q317">
         <v>0</v>
@@ -52469,31 +52469,31 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O320">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="P320">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q320">
         <v>2.15</v>
       </c>
       <c r="R320">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="S320">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T320">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="U320">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V320">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W320">
         <v>1.22</v>
@@ -52505,28 +52505,28 @@
         <v>1.07</v>
       </c>
       <c r="Z320">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA320">
         <v>1.32</v>
       </c>
       <c r="AB320">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AC320">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD320">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE320">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF320">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG320">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK320">
         <v>2</v>
@@ -52632,10 +52632,10 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O321">
-        <v>4.31</v>
+        <v>3.95</v>
       </c>
       <c r="P321">
         <v>3.7</v>
@@ -52650,7 +52650,7 @@
         <v>1.2</v>
       </c>
       <c r="T321">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="U321">
         <v>2</v>
@@ -52659,37 +52659,37 @@
         <v>1.73</v>
       </c>
       <c r="W321">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X321">
         <v>1.01</v>
       </c>
       <c r="Y321">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z321">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA321">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB321">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="AC321">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AD321">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AE321">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AF321">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG321">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52795,31 +52795,31 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O322">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P322">
         <v>3.4</v>
       </c>
       <c r="Q322">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R322">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="S322">
         <v>1.14</v>
       </c>
       <c r="T322">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="U322">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V322">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="W322">
         <v>1.19</v>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK322">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O323">
         <v>4</v>
       </c>
       <c r="P323">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q323">
         <v>2.25</v>
@@ -52982,7 +52982,7 @@
         <v>2</v>
       </c>
       <c r="V323">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W323">
         <v>1.18</v>
@@ -52994,7 +52994,7 @@
         <v>1.07</v>
       </c>
       <c r="Z323">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA323">
         <v>1.4</v>
@@ -53009,7 +53009,7 @@
         <v>1.8</v>
       </c>
       <c r="AE323">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF323">
         <v>1.4</v>
@@ -53130,7 +53130,7 @@
         <v>3</v>
       </c>
       <c r="Q324">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R324">
         <v>2.3</v>
@@ -53139,7 +53139,7 @@
         <v>1.28</v>
       </c>
       <c r="T324">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U324">
         <v>2.35</v>
@@ -53157,25 +53157,25 @@
         <v>1.18</v>
       </c>
       <c r="Z324">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA324">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB324">
         <v>2.2</v>
       </c>
       <c r="AC324">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD324">
         <v>1.44</v>
       </c>
       <c r="AE324">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF324">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG324">
         <v>2.38</v>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK324">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53782,10 +53782,10 @@
         <v>3.6</v>
       </c>
       <c r="Q328">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="R328">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="S328">
         <v>1.18</v>
@@ -53794,10 +53794,10 @@
         <v>4.6</v>
       </c>
       <c r="U328">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="V328">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="W328">
         <v>1.2</v>
@@ -53809,22 +53809,22 @@
         <v>1.06</v>
       </c>
       <c r="Z328">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA328">
         <v>1.36</v>
       </c>
       <c r="AB328">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC328">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD328">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE328">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF328">
         <v>1.33</v>
@@ -53843,7 +53843,7 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK328">
         <v>1.95</v>
@@ -53936,10 +53936,10 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O329">
-        <v>3.97</v>
+        <v>3.6</v>
       </c>
       <c r="P329">
         <v>3.25</v>
@@ -53960,7 +53960,7 @@
         <v>2.35</v>
       </c>
       <c r="V329">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W329">
         <v>1.13</v>
@@ -53969,13 +53969,13 @@
         <v>1.03</v>
       </c>
       <c r="Y329">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z329">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA329">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB329">
         <v>2.4</v>
@@ -53987,7 +53987,7 @@
         <v>1.49</v>
       </c>
       <c r="AE329">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF329">
         <v>1.45</v>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK329">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54117,13 +54117,13 @@
         <v>1.22</v>
       </c>
       <c r="T330">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U330">
         <v>2.07</v>
       </c>
       <c r="V330">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W330">
         <v>1.15</v>
@@ -54144,19 +54144,19 @@
         <v>2.5</v>
       </c>
       <c r="AC330">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AD330">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE330">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF330">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG330">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK330">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54425,25 +54425,25 @@
         </is>
       </c>
       <c r="N332">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O332">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P332">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q332">
         <v>2.4</v>
       </c>
       <c r="R332">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S332">
         <v>1.25</v>
       </c>
       <c r="T332">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U332">
         <v>2.25</v>
@@ -54588,7 +54588,7 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="O333">
         <v>3.9</v>
@@ -54621,7 +54621,7 @@
         <v>1.03</v>
       </c>
       <c r="Y333">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z333">
         <v>4.9</v>
@@ -54633,13 +54633,13 @@
         <v>2.35</v>
       </c>
       <c r="AC333">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AD333">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE333">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF333">
         <v>1.55</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,80 +55403,80 @@
         </is>
       </c>
       <c r="N338">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O338">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P338">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="Q338">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R338">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S338">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T338">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U338">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V338">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W338">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X338">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y338">
         <v>1.17</v>
       </c>
       <c r="Z338">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA338">
+        <v>1.54</v>
+      </c>
+      <c r="AB338">
+        <v>2.21</v>
+      </c>
+      <c r="AC338">
+        <v>2.5</v>
+      </c>
+      <c r="AD338">
+        <v>1.44</v>
+      </c>
+      <c r="AE338">
+        <v>1.18</v>
+      </c>
+      <c r="AF338">
+        <v>1.48</v>
+      </c>
+      <c r="AG338">
+        <v>2.4</v>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ338">
+        <v>1.44</v>
+      </c>
+      <c r="AK338">
         <v>1.55</v>
-      </c>
-      <c r="AB338">
-        <v>2.4</v>
-      </c>
-      <c r="AC338">
-        <v>2.32</v>
-      </c>
-      <c r="AD338">
-        <v>1.57</v>
-      </c>
-      <c r="AE338">
-        <v>1.22</v>
-      </c>
-      <c r="AF338">
-        <v>1.45</v>
-      </c>
-      <c r="AG338">
-        <v>2.55</v>
-      </c>
-      <c r="AH338" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI338" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ338">
-        <v>1.33</v>
-      </c>
-      <c r="AK338">
-        <v>1.77</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,64 +55566,64 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O339">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P339">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="Q339">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="R339">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S339">
         <v>1.25</v>
       </c>
       <c r="T339">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U339">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V339">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W339">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X339">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y339">
         <v>1.17</v>
       </c>
       <c r="Z339">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA339">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AB339">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AC339">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AD339">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AE339">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF339">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG339">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK339">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AL339">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S2">
         <v>1.37</v>
       </c>
       <c r="T2">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z2">
         <v>3.3</v>
       </c>
       <c r="AA2">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC2">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
+        <v>3.26</v>
+      </c>
+      <c r="R3">
+        <v>1.97</v>
+      </c>
+      <c r="S3">
+        <v>1.41</v>
+      </c>
+      <c r="T3">
+        <v>2.65</v>
+      </c>
+      <c r="U3">
         <v>2.9</v>
       </c>
-      <c r="R3">
-        <v>2.06</v>
-      </c>
-      <c r="S3">
-        <v>1.38</v>
-      </c>
-      <c r="T3">
-        <v>2.81</v>
-      </c>
-      <c r="U3">
-        <v>2.73</v>
-      </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
+        <v>1.08</v>
+      </c>
+      <c r="X3">
         <v>1.06</v>
-      </c>
-      <c r="X3">
-        <v>1.01</v>
       </c>
       <c r="Y3">
         <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AA3">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AB3">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="AD3">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG3">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AK3">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4">
@@ -961,77 +961,77 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
         <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
-        <v>3.46</v>
+        <v>3.04</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S4">
+        <v>1.43</v>
+      </c>
+      <c r="T4">
+        <v>2.62</v>
+      </c>
+      <c r="U4">
+        <v>2.64</v>
+      </c>
+      <c r="V4">
         <v>1.41</v>
       </c>
-      <c r="T4">
-        <v>2.84</v>
-      </c>
-      <c r="U4">
-        <v>2.99</v>
-      </c>
-      <c r="V4">
-        <v>1.36</v>
-      </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
         <v>1.28</v>
       </c>
       <c r="Z4">
-        <v>3.26</v>
+        <v>3.67</v>
       </c>
       <c r="AA4">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC4">
-        <v>3.68</v>
+        <v>3.23</v>
       </c>
       <c r="AD4">
+        <v>1.34</v>
+      </c>
+      <c r="AE4">
+        <v>1.07</v>
+      </c>
+      <c r="AF4">
+        <v>1.67</v>
+      </c>
+      <c r="AG4">
+        <v>2.1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.28</v>
-      </c>
-      <c r="AE4">
-        <v>1.11</v>
-      </c>
-      <c r="AF4">
-        <v>1.78</v>
-      </c>
-      <c r="AG4">
-        <v>1.93</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.33</v>
       </c>
       <c r="AK4">
         <v>1.41</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U16">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2950,47 +2950,47 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AA16">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC16">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="AD16">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
         <v>1.83</v>
       </c>
       <c r="AG16">
+        <v>1.86</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.27</v>
+      </c>
+      <c r="AK16">
         <v>1.91</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.22</v>
-      </c>
-      <c r="AK16">
-        <v>1.94</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="O32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q32">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="R32">
+        <v>2.38</v>
+      </c>
+      <c r="S32">
+        <v>1.26</v>
+      </c>
+      <c r="T32">
+        <v>3.45</v>
+      </c>
+      <c r="U32">
+        <v>2.44</v>
+      </c>
+      <c r="V32">
+        <v>1.56</v>
+      </c>
+      <c r="W32">
+        <v>1.11</v>
+      </c>
+      <c r="X32">
+        <v>1.03</v>
+      </c>
+      <c r="Y32">
+        <v>1.17</v>
+      </c>
+      <c r="Z32">
+        <v>4.45</v>
+      </c>
+      <c r="AA32">
+        <v>1.61</v>
+      </c>
+      <c r="AB32">
+        <v>2.25</v>
+      </c>
+      <c r="AC32">
         <v>2.45</v>
       </c>
-      <c r="S32">
-        <v>1.25</v>
-      </c>
-      <c r="T32">
-        <v>3.68</v>
-      </c>
-      <c r="U32">
-        <v>2.2</v>
-      </c>
-      <c r="V32">
-        <v>1.66</v>
-      </c>
-      <c r="W32">
-        <v>1.18</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.13</v>
-      </c>
-      <c r="Z32">
-        <v>5.25</v>
-      </c>
-      <c r="AA32">
-        <v>1.48</v>
-      </c>
-      <c r="AB32">
-        <v>2.5</v>
-      </c>
-      <c r="AC32">
-        <v>2.26</v>
-      </c>
       <c r="AD32">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE32">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.71</v>
+        <v>2.03</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="R33">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="U33">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA33">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AB33">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AC33">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AD33">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE33">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,28 +5851,28 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.93</v>
+        <v>2.71</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="S34">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="V34">
         <v>1.56</v>
@@ -5881,34 +5881,34 @@
         <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z34">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA34">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB34">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC34">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AD34">
         <v>1.52</v>
       </c>
       <c r="AE34">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG34">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="AK34">
-        <v>1.92</v>
+        <v>1.42</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>2.45</v>
+        <v>2.99</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S46">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="W46">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>3.7</v>
+        <v>4.89</v>
       </c>
       <c r="AA46">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB46">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC46">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD46">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE46">
         <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
+        <v>2.05</v>
+      </c>
+      <c r="O47">
+        <v>3.6</v>
+      </c>
+      <c r="P47">
+        <v>3.4</v>
+      </c>
+      <c r="Q47">
         <v>2.45</v>
       </c>
-      <c r="O47">
+      <c r="R47">
+        <v>2.25</v>
+      </c>
+      <c r="S47">
+        <v>1.32</v>
+      </c>
+      <c r="T47">
+        <v>3</v>
+      </c>
+      <c r="U47">
+        <v>2.41</v>
+      </c>
+      <c r="V47">
+        <v>1.5</v>
+      </c>
+      <c r="W47">
+        <v>1.09</v>
+      </c>
+      <c r="X47">
+        <v>1.04</v>
+      </c>
+      <c r="Y47">
+        <v>1.17</v>
+      </c>
+      <c r="Z47">
         <v>3.7</v>
       </c>
-      <c r="P47">
-        <v>2.6</v>
-      </c>
-      <c r="Q47">
-        <v>2.99</v>
-      </c>
-      <c r="R47">
-        <v>2.38</v>
-      </c>
-      <c r="S47">
-        <v>1.28</v>
-      </c>
-      <c r="T47">
-        <v>3.3</v>
-      </c>
-      <c r="U47">
-        <v>2.24</v>
-      </c>
-      <c r="V47">
-        <v>1.58</v>
-      </c>
-      <c r="W47">
-        <v>1.13</v>
-      </c>
-      <c r="X47">
-        <v>1.01</v>
-      </c>
-      <c r="Y47">
-        <v>1.18</v>
-      </c>
-      <c r="Z47">
-        <v>4.89</v>
-      </c>
       <c r="AA47">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB47">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC47">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD47">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
         <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AG47">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q91">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="R91">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S91">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U91">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W91">
         <v>1.1</v>
       </c>
       <c r="X91">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z91">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA91">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB91">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC91">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD91">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE91">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF91">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK91">
-        <v>1.69</v>
+        <v>2.36</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q92">
-        <v>2.05</v>
+        <v>2.69</v>
       </c>
       <c r="R92">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S92">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U92">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W92">
         <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z92">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA92">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB92">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC92">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AD92">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG92">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK92">
-        <v>2.36</v>
+        <v>1.69</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>4</v>
+        <v>1.23</v>
       </c>
       <c r="O111">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="P111">
-        <v>1.78</v>
+        <v>9</v>
       </c>
       <c r="Q111">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="R111">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="S111">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T111">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="U111">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V111">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W111">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z111">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA111">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AB111">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AC111">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AD111">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AE111">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AF111">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="AG111">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="AK111">
-        <v>1.22</v>
+        <v>3.8</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,80 +18565,80 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="O112">
+        <v>4.1</v>
+      </c>
+      <c r="P112">
+        <v>1.78</v>
+      </c>
+      <c r="Q112">
         <v>3.9</v>
       </c>
-      <c r="P112">
-        <v>2.71</v>
-      </c>
-      <c r="Q112">
-        <v>2.7</v>
-      </c>
       <c r="R112">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="S112">
         <v>1.22</v>
       </c>
       <c r="T112">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U112">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V112">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W112">
+        <v>1.2</v>
+      </c>
+      <c r="X112">
+        <v>1.02</v>
+      </c>
+      <c r="Y112">
+        <v>1.08</v>
+      </c>
+      <c r="Z112">
+        <v>7</v>
+      </c>
+      <c r="AA112">
+        <v>1.42</v>
+      </c>
+      <c r="AB112">
+        <v>2.66</v>
+      </c>
+      <c r="AC112">
+        <v>2.11</v>
+      </c>
+      <c r="AD112">
+        <v>1.84</v>
+      </c>
+      <c r="AE112">
+        <v>1.29</v>
+      </c>
+      <c r="AF112">
+        <v>1.45</v>
+      </c>
+      <c r="AG112">
+        <v>2.8</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <v>1.26</v>
+      </c>
+      <c r="AK112">
         <v>1.22</v>
-      </c>
-      <c r="X112">
-        <v>1.01</v>
-      </c>
-      <c r="Y112">
-        <v>1.07</v>
-      </c>
-      <c r="Z112">
-        <v>7.5</v>
-      </c>
-      <c r="AA112">
-        <v>1.36</v>
-      </c>
-      <c r="AB112">
-        <v>3.2</v>
-      </c>
-      <c r="AC112">
-        <v>1.85</v>
-      </c>
-      <c r="AD112">
-        <v>1.82</v>
-      </c>
-      <c r="AE112">
-        <v>1.38</v>
-      </c>
-      <c r="AF112">
-        <v>1.33</v>
-      </c>
-      <c r="AG112">
-        <v>3.3</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.43</v>
-      </c>
-      <c r="AK112">
-        <v>1.55</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.23</v>
+        <v>2.25</v>
       </c>
       <c r="O113">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="P113">
-        <v>9</v>
+        <v>2.71</v>
       </c>
       <c r="Q113">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="R113">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="S113">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="U113">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V113">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="W113">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z113">
         <v>7.5</v>
       </c>
       <c r="AA113">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB113">
         <v>3.2</v>
       </c>
       <c r="AC113">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AD113">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AE113">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF113">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AG113">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="AK113">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="O133">
         <v>3.25</v>
       </c>
       <c r="P133">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q133">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="R133">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="T133">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U133">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="V133">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="W133">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X133">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y133">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z133">
-        <v>2.79</v>
+        <v>3.08</v>
       </c>
       <c r="AA133">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AB133">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AC133">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD133">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE133">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF133">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG133">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK133">
         <v>1.44</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="O134">
         <v>3.25</v>
       </c>
       <c r="P134">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q134">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="R134">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S134">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="T134">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="U134">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="V134">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W134">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X134">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y134">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="Z134">
-        <v>3.08</v>
+        <v>2.79</v>
       </c>
       <c r="AA134">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AB134">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC134">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AD134">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE134">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF134">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG134">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK134">
         <v>1.44</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P135">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q135">
-        <v>3.52</v>
+        <v>2.63</v>
       </c>
       <c r="R135">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="S135">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T135">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="U135">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="V135">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W135">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X135">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y135">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z135">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AA135">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB135">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC135">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD135">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE135">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF135">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG135">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.57</v>
+        <v>3.15</v>
       </c>
       <c r="O136">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="Q136">
-        <v>2</v>
+        <v>3.52</v>
       </c>
       <c r="R136">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="S136">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T136">
-        <v>3.45</v>
+        <v>2.77</v>
       </c>
       <c r="U136">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="V136">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y136">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z136">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA136">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB136">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AC136">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD136">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE136">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK136">
-        <v>2.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="O137">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="P137">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="Q137">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="R137">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="S137">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T137">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="U137">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="V137">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="W137">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X137">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y137">
         <v>1.2</v>
       </c>
       <c r="Z137">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="AA137">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AB137">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="AC137">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AD137">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE137">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF137">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG137">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK137">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.67</v>
+        <v>2.87</v>
       </c>
       <c r="O146">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P146">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q146">
-        <v>2.05</v>
+        <v>3.57</v>
       </c>
       <c r="R146">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="S146">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T146">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U146">
-        <v>2.23</v>
+        <v>2.54</v>
       </c>
       <c r="V146">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z146">
-        <v>4.8</v>
+        <v>3.44</v>
       </c>
       <c r="AA146">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB146">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AC146">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="AD146">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AE146">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG146">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="AK146">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.87</v>
+        <v>1.67</v>
       </c>
       <c r="O147">
+        <v>4.1</v>
+      </c>
+      <c r="P147">
+        <v>4.5</v>
+      </c>
+      <c r="Q147">
+        <v>2.05</v>
+      </c>
+      <c r="R147">
+        <v>2.5</v>
+      </c>
+      <c r="S147">
+        <v>1.22</v>
+      </c>
+      <c r="T147">
         <v>3.4</v>
       </c>
-      <c r="P147">
-        <v>2.36</v>
-      </c>
-      <c r="Q147">
-        <v>3.57</v>
-      </c>
-      <c r="R147">
-        <v>2.11</v>
-      </c>
-      <c r="S147">
-        <v>1.3</v>
-      </c>
-      <c r="T147">
-        <v>2.88</v>
-      </c>
       <c r="U147">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="V147">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W147">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X147">
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z147">
-        <v>3.44</v>
+        <v>4.8</v>
       </c>
       <c r="AA147">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB147">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC147">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="AD147">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AE147">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF147">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG147">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AK147">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="O151">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P151">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q151">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="R151">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="S151">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T151">
+        <v>2.88</v>
+      </c>
+      <c r="U151">
+        <v>2.75</v>
+      </c>
+      <c r="V151">
+        <v>1.4</v>
+      </c>
+      <c r="W151">
+        <v>1.05</v>
+      </c>
+      <c r="X151">
+        <v>1.05</v>
+      </c>
+      <c r="Y151">
+        <v>1.31</v>
+      </c>
+      <c r="Z151">
+        <v>3.05</v>
+      </c>
+      <c r="AA151">
+        <v>1.93</v>
+      </c>
+      <c r="AB151">
+        <v>1.83</v>
+      </c>
+      <c r="AC151">
         <v>3.3</v>
       </c>
-      <c r="U151">
-        <v>2.39</v>
-      </c>
-      <c r="V151">
-        <v>1.47</v>
-      </c>
-      <c r="W151">
-        <v>1.08</v>
-      </c>
-      <c r="X151">
-        <v>1.03</v>
-      </c>
-      <c r="Y151">
-        <v>1.19</v>
-      </c>
-      <c r="Z151">
-        <v>3.78</v>
-      </c>
-      <c r="AA151">
-        <v>1.73</v>
-      </c>
-      <c r="AB151">
-        <v>2.04</v>
-      </c>
-      <c r="AC151">
-        <v>2.64</v>
-      </c>
       <c r="AD151">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE151">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF151">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG151">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="O152">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P152">
-        <v>4.03</v>
+        <v>4.3</v>
       </c>
       <c r="Q152">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="R152">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="S152">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T152">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="U152">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="V152">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W152">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X152">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y152">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z152">
-        <v>3.3</v>
+        <v>5.43</v>
       </c>
       <c r="AA152">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB152">
-        <v>1.87</v>
+        <v>2.61</v>
       </c>
       <c r="AC152">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD152">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AE152">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AF152">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG152">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK152">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="O153">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P153">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q153">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="R153">
-        <v>2.08</v>
+        <v>2.47</v>
       </c>
       <c r="S153">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="T153">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U153">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V153">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W153">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X153">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z153">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA153">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AB153">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC153">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="AD153">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE153">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF153">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG153">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK153">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="O154">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P154">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q154">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R154">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S154">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T154">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U154">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="V154">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W154">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X154">
         <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z154">
-        <v>5.43</v>
+        <v>3.78</v>
       </c>
       <c r="AA154">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AB154">
-        <v>2.61</v>
+        <v>2.04</v>
       </c>
       <c r="AC154">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="AD154">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="AE154">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AF154">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AG154">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK154">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O155">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P155">
-        <v>3.4</v>
+        <v>4.03</v>
       </c>
       <c r="Q155">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R155">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="S155">
+        <v>1.35</v>
+      </c>
+      <c r="T155">
+        <v>3</v>
+      </c>
+      <c r="U155">
+        <v>2.84</v>
+      </c>
+      <c r="V155">
+        <v>1.4</v>
+      </c>
+      <c r="W155">
+        <v>1.06</v>
+      </c>
+      <c r="X155">
+        <v>1.05</v>
+      </c>
+      <c r="Y155">
         <v>1.25</v>
       </c>
-      <c r="T155">
-        <v>3.42</v>
-      </c>
-      <c r="U155">
-        <v>2.22</v>
-      </c>
-      <c r="V155">
-        <v>1.62</v>
-      </c>
-      <c r="W155">
-        <v>1.15</v>
-      </c>
-      <c r="X155">
-        <v>1.03</v>
-      </c>
-      <c r="Y155">
-        <v>1.13</v>
-      </c>
       <c r="Z155">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA155">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AB155">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="AC155">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD155">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE155">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF155">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AG155">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK155">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="O156">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P156">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="Q156">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R156">
+        <v>2.49</v>
+      </c>
+      <c r="S156">
+        <v>1.25</v>
+      </c>
+      <c r="T156">
+        <v>3.42</v>
+      </c>
+      <c r="U156">
+        <v>2.22</v>
+      </c>
+      <c r="V156">
+        <v>1.62</v>
+      </c>
+      <c r="W156">
+        <v>1.15</v>
+      </c>
+      <c r="X156">
+        <v>1.03</v>
+      </c>
+      <c r="Y156">
+        <v>1.13</v>
+      </c>
+      <c r="Z156">
+        <v>4.9</v>
+      </c>
+      <c r="AA156">
+        <v>1.53</v>
+      </c>
+      <c r="AB156">
+        <v>2.44</v>
+      </c>
+      <c r="AC156">
         <v>2.3</v>
       </c>
-      <c r="S156">
-        <v>1.35</v>
-      </c>
-      <c r="T156">
-        <v>2.86</v>
-      </c>
-      <c r="U156">
-        <v>2.6</v>
-      </c>
-      <c r="V156">
+      <c r="AD156">
+        <v>1.57</v>
+      </c>
+      <c r="AE156">
+        <v>1.19</v>
+      </c>
+      <c r="AF156">
         <v>1.47</v>
       </c>
-      <c r="W156">
-        <v>1.07</v>
-      </c>
-      <c r="X156">
-        <v>1.02</v>
-      </c>
-      <c r="Y156">
-        <v>1.18</v>
-      </c>
-      <c r="Z156">
-        <v>4.2</v>
-      </c>
-      <c r="AA156">
-        <v>1.67</v>
-      </c>
-      <c r="AB156">
-        <v>2.15</v>
-      </c>
-      <c r="AC156">
-        <v>2.65</v>
-      </c>
-      <c r="AD156">
-        <v>1.41</v>
-      </c>
-      <c r="AE156">
-        <v>1.13</v>
-      </c>
-      <c r="AF156">
-        <v>1.61</v>
-      </c>
       <c r="AG156">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK156">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,46 +25900,46 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.79</v>
+        <v>3.05</v>
       </c>
       <c r="O157">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P157">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="Q157">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="R157">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="S157">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T157">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U157">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V157">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="W157">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X157">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z157">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA157">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB157">
         <v>2.15</v>
@@ -25948,16 +25948,16 @@
         <v>2.65</v>
       </c>
       <c r="AD157">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE157">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF157">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG157">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK157">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O205">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P205">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q205">
-        <v>2.95</v>
+        <v>3.94</v>
       </c>
       <c r="R205">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S205">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T205">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="U205">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="V205">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W205">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X205">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y205">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z205">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AA205">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB205">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC205">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AD205">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE205">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF205">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG205">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AK205">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,80 +33887,80 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q206">
-        <v>3.94</v>
+        <v>2.95</v>
       </c>
       <c r="R206">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="S206">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T206">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="U206">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="V206">
+        <v>1.27</v>
+      </c>
+      <c r="W206">
+        <v>1.01</v>
+      </c>
+      <c r="X206">
+        <v>1.04</v>
+      </c>
+      <c r="Y206">
+        <v>1.37</v>
+      </c>
+      <c r="Z206">
+        <v>2.66</v>
+      </c>
+      <c r="AA206">
+        <v>2.23</v>
+      </c>
+      <c r="AB206">
+        <v>1.57</v>
+      </c>
+      <c r="AC206">
+        <v>4.1</v>
+      </c>
+      <c r="AD206">
+        <v>1.16</v>
+      </c>
+      <c r="AE206">
+        <v>1.02</v>
+      </c>
+      <c r="AF206">
+        <v>1.9</v>
+      </c>
+      <c r="AG206">
+        <v>1.78</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ206">
         <v>1.29</v>
       </c>
-      <c r="W206">
-        <v>1.03</v>
-      </c>
-      <c r="X206">
-        <v>1.03</v>
-      </c>
-      <c r="Y206">
-        <v>1.35</v>
-      </c>
-      <c r="Z206">
-        <v>2.74</v>
-      </c>
-      <c r="AA206">
-        <v>2.2</v>
-      </c>
-      <c r="AB206">
-        <v>1.65</v>
-      </c>
-      <c r="AC206">
-        <v>3.82</v>
-      </c>
-      <c r="AD206">
-        <v>1.19</v>
-      </c>
-      <c r="AE206">
-        <v>1.03</v>
-      </c>
-      <c r="AF206">
-        <v>1.85</v>
-      </c>
-      <c r="AG206">
-        <v>1.82</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ206">
-        <v>1.52</v>
-      </c>
       <c r="AK206">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O227">
+        <v>3.25</v>
+      </c>
+      <c r="P227">
         <v>3.3</v>
-      </c>
-      <c r="P227">
-        <v>2.87</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
       </c>
       <c r="R227">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S227">
+        <v>1.41</v>
+      </c>
+      <c r="T227">
+        <v>2.69</v>
+      </c>
+      <c r="U227">
+        <v>2.89</v>
+      </c>
+      <c r="V227">
+        <v>1.36</v>
+      </c>
+      <c r="W227">
+        <v>1.04</v>
+      </c>
+      <c r="X227">
+        <v>1.01</v>
+      </c>
+      <c r="Y227">
         <v>1.33</v>
       </c>
-      <c r="T227">
-        <v>3.2</v>
-      </c>
-      <c r="U227">
-        <v>2.45</v>
-      </c>
-      <c r="V227">
-        <v>1.48</v>
-      </c>
-      <c r="W227">
-        <v>1.08</v>
-      </c>
-      <c r="X227">
-        <v>1</v>
-      </c>
-      <c r="Y227">
-        <v>1.22</v>
-      </c>
       <c r="Z227">
-        <v>4.26</v>
+        <v>3.13</v>
       </c>
       <c r="AA227">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB227">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC227">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AD227">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE227">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF227">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG227">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK227">
         <v>1.67</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O228">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P228">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="Q228">
         <v>2.63</v>
       </c>
       <c r="R228">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S228">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T228">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U228">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="V228">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W228">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X228">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y228">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z228">
-        <v>3.13</v>
+        <v>4.26</v>
       </c>
       <c r="AA228">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AB228">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC228">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="AD228">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE228">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF228">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG228">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK228">
         <v>1.67</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O279">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P279">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="Q279">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="R279">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="S279">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T279">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="U279">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="V279">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W279">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X279">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y279">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z279">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA279">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB279">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC279">
-        <v>2.58</v>
+        <v>3.48</v>
       </c>
       <c r="AD279">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE279">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF279">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG279">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AK279">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="O280">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P280">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q280">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="R280">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="S280">
+        <v>1.3</v>
+      </c>
+      <c r="T280">
+        <v>3.25</v>
+      </c>
+      <c r="U280">
+        <v>2.4</v>
+      </c>
+      <c r="V280">
+        <v>1.54</v>
+      </c>
+      <c r="W280">
+        <v>1.11</v>
+      </c>
+      <c r="X280">
+        <v>1.02</v>
+      </c>
+      <c r="Y280">
+        <v>1.18</v>
+      </c>
+      <c r="Z280">
+        <v>4.2</v>
+      </c>
+      <c r="AA280">
+        <v>1.66</v>
+      </c>
+      <c r="AB280">
+        <v>2.2</v>
+      </c>
+      <c r="AC280">
+        <v>2.58</v>
+      </c>
+      <c r="AD280">
         <v>1.44</v>
       </c>
-      <c r="T280">
-        <v>2.77</v>
-      </c>
-      <c r="U280">
-        <v>2.82</v>
-      </c>
-      <c r="V280">
-        <v>1.36</v>
-      </c>
-      <c r="W280">
-        <v>1.06</v>
-      </c>
-      <c r="X280">
-        <v>1.04</v>
-      </c>
-      <c r="Y280">
-        <v>1.33</v>
-      </c>
-      <c r="Z280">
-        <v>3.1</v>
-      </c>
-      <c r="AA280">
-        <v>2.1</v>
-      </c>
-      <c r="AB280">
-        <v>1.72</v>
-      </c>
-      <c r="AC280">
-        <v>3.48</v>
-      </c>
-      <c r="AD280">
-        <v>1.25</v>
-      </c>
       <c r="AE280">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF280">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG280">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AK280">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AL280">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3">
@@ -804,58 +804,58 @@
         <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q3">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="R3">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
+        <v>1.43</v>
+      </c>
+      <c r="T3">
+        <v>2.62</v>
+      </c>
+      <c r="U3">
+        <v>2.64</v>
+      </c>
+      <c r="V3">
         <v>1.41</v>
       </c>
-      <c r="T3">
-        <v>2.65</v>
-      </c>
-      <c r="U3">
-        <v>2.9</v>
-      </c>
-      <c r="V3">
+      <c r="W3">
+        <v>1.04</v>
+      </c>
+      <c r="X3">
+        <v>1.05</v>
+      </c>
+      <c r="Y3">
+        <v>1.28</v>
+      </c>
+      <c r="Z3">
+        <v>3.67</v>
+      </c>
+      <c r="AA3">
+        <v>1.99</v>
+      </c>
+      <c r="AB3">
+        <v>1.86</v>
+      </c>
+      <c r="AC3">
+        <v>3.23</v>
+      </c>
+      <c r="AD3">
         <v>1.34</v>
       </c>
-      <c r="W3">
-        <v>1.08</v>
-      </c>
-      <c r="X3">
-        <v>1.06</v>
-      </c>
-      <c r="Y3">
-        <v>1.3</v>
-      </c>
-      <c r="Z3">
-        <v>3.2</v>
-      </c>
-      <c r="AA3">
-        <v>2.04</v>
-      </c>
-      <c r="AB3">
-        <v>1.78</v>
-      </c>
-      <c r="AC3">
-        <v>3.6</v>
-      </c>
-      <c r="AD3">
-        <v>1.23</v>
-      </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AK3">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4">
@@ -967,58 +967,58 @@
         <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="R4">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S4">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U4">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
+        <v>1.06</v>
+      </c>
+      <c r="Y4">
+        <v>1.3</v>
+      </c>
+      <c r="Z4">
+        <v>3.2</v>
+      </c>
+      <c r="AA4">
+        <v>2.04</v>
+      </c>
+      <c r="AB4">
+        <v>1.78</v>
+      </c>
+      <c r="AC4">
+        <v>3.6</v>
+      </c>
+      <c r="AD4">
+        <v>1.23</v>
+      </c>
+      <c r="AE4">
         <v>1.04</v>
       </c>
-      <c r="X4">
-        <v>1.05</v>
-      </c>
-      <c r="Y4">
-        <v>1.28</v>
-      </c>
-      <c r="Z4">
-        <v>3.67</v>
-      </c>
-      <c r="AA4">
-        <v>1.99</v>
-      </c>
-      <c r="AB4">
-        <v>1.86</v>
-      </c>
-      <c r="AC4">
-        <v>3.23</v>
-      </c>
-      <c r="AD4">
-        <v>1.34</v>
-      </c>
-      <c r="AE4">
-        <v>1.07</v>
-      </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AK4">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,65 +5688,65 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.03</v>
+        <v>2.71</v>
       </c>
       <c r="O33">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q33">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V33">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
+        <v>1.11</v>
+      </c>
+      <c r="X33">
+        <v>1.04</v>
+      </c>
+      <c r="Y33">
+        <v>1.15</v>
+      </c>
+      <c r="Z33">
+        <v>4.4</v>
+      </c>
+      <c r="AA33">
+        <v>1.59</v>
+      </c>
+      <c r="AB33">
+        <v>2.23</v>
+      </c>
+      <c r="AC33">
+        <v>2.31</v>
+      </c>
+      <c r="AD33">
+        <v>1.52</v>
+      </c>
+      <c r="AE33">
         <v>1.18</v>
       </c>
-      <c r="X33">
-        <v>1.02</v>
-      </c>
-      <c r="Y33">
-        <v>1.13</v>
-      </c>
-      <c r="Z33">
-        <v>5.25</v>
-      </c>
-      <c r="AA33">
-        <v>1.48</v>
-      </c>
-      <c r="AB33">
+      <c r="AF33">
+        <v>1.45</v>
+      </c>
+      <c r="AG33">
         <v>2.5</v>
       </c>
-      <c r="AC33">
-        <v>2.26</v>
-      </c>
-      <c r="AD33">
-        <v>1.57</v>
-      </c>
-      <c r="AE33">
-        <v>1.22</v>
-      </c>
-      <c r="AF33">
-        <v>1.44</v>
-      </c>
-      <c r="AG33">
-        <v>2.6</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AK33">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.71</v>
+        <v>2.03</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P34">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="R34">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="U34">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V34">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA34">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AB34">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="AC34">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AD34">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="O50">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="Q50">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S50">
+        <v>1.35</v>
+      </c>
+      <c r="T50">
+        <v>2.82</v>
+      </c>
+      <c r="U50">
+        <v>2.59</v>
+      </c>
+      <c r="V50">
+        <v>1.45</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>1.22</v>
+      </c>
+      <c r="Z50">
+        <v>3.98</v>
+      </c>
+      <c r="AA50">
+        <v>1.78</v>
+      </c>
+      <c r="AB50">
+        <v>2</v>
+      </c>
+      <c r="AC50">
+        <v>2.76</v>
+      </c>
+      <c r="AD50">
         <v>1.39</v>
       </c>
-      <c r="T50">
-        <v>2.54</v>
-      </c>
-      <c r="U50">
-        <v>2.95</v>
-      </c>
-      <c r="V50">
-        <v>1.35</v>
-      </c>
-      <c r="W50">
-        <v>1.05</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.31</v>
-      </c>
-      <c r="Z50">
-        <v>2.94</v>
-      </c>
-      <c r="AA50">
-        <v>2.1</v>
-      </c>
-      <c r="AB50">
-        <v>1.69</v>
-      </c>
-      <c r="AC50">
-        <v>3.8</v>
-      </c>
-      <c r="AD50">
-        <v>1.24</v>
-      </c>
       <c r="AE50">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AK50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="O51">
+        <v>3.32</v>
+      </c>
+      <c r="P51">
+        <v>2.28</v>
+      </c>
+      <c r="Q51">
         <v>3.5</v>
       </c>
-      <c r="P51">
-        <v>2.55</v>
-      </c>
-      <c r="Q51">
-        <v>2.89</v>
-      </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
+        <v>1.39</v>
+      </c>
+      <c r="T51">
+        <v>2.54</v>
+      </c>
+      <c r="U51">
+        <v>2.95</v>
+      </c>
+      <c r="V51">
         <v>1.35</v>
       </c>
-      <c r="T51">
-        <v>2.82</v>
-      </c>
-      <c r="U51">
-        <v>2.59</v>
-      </c>
-      <c r="V51">
-        <v>1.45</v>
-      </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z51">
-        <v>3.98</v>
+        <v>2.94</v>
       </c>
       <c r="AA51">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AC51">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,58 +10252,58 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="O61">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="P61">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="Q61">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="R61">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="S61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T61">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U61">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V61">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W61">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="AA61">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="AB61">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="AC61">
-        <v>2.83</v>
+        <v>2.32</v>
       </c>
       <c r="AD61">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE61">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF61">
         <v>1.62</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,65 +10415,65 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P62">
+        <v>2.45</v>
+      </c>
+      <c r="Q62">
+        <v>3.1</v>
+      </c>
+      <c r="R62">
+        <v>2.29</v>
+      </c>
+      <c r="S62">
+        <v>1.33</v>
+      </c>
+      <c r="T62">
+        <v>3.1</v>
+      </c>
+      <c r="U62">
+        <v>2.5</v>
+      </c>
+      <c r="V62">
+        <v>1.44</v>
+      </c>
+      <c r="W62">
+        <v>1.1</v>
+      </c>
+      <c r="X62">
+        <v>1.04</v>
+      </c>
+      <c r="Y62">
+        <v>1.22</v>
+      </c>
+      <c r="Z62">
+        <v>3.78</v>
+      </c>
+      <c r="AA62">
+        <v>1.77</v>
+      </c>
+      <c r="AB62">
+        <v>2.01</v>
+      </c>
+      <c r="AC62">
+        <v>2.83</v>
+      </c>
+      <c r="AD62">
+        <v>1.38</v>
+      </c>
+      <c r="AE62">
+        <v>1.15</v>
+      </c>
+      <c r="AF62">
+        <v>1.62</v>
+      </c>
+      <c r="AG62">
         <v>2.15</v>
       </c>
-      <c r="Q62">
-        <v>3.15</v>
-      </c>
-      <c r="R62">
-        <v>2.32</v>
-      </c>
-      <c r="S62">
-        <v>1.22</v>
-      </c>
-      <c r="T62">
-        <v>3.75</v>
-      </c>
-      <c r="U62">
-        <v>2.2</v>
-      </c>
-      <c r="V62">
-        <v>1.62</v>
-      </c>
-      <c r="W62">
-        <v>1.17</v>
-      </c>
-      <c r="X62">
-        <v>1.03</v>
-      </c>
-      <c r="Y62">
-        <v>1.12</v>
-      </c>
-      <c r="Z62">
-        <v>4.8</v>
-      </c>
-      <c r="AA62">
-        <v>1.46</v>
-      </c>
-      <c r="AB62">
-        <v>2.4</v>
-      </c>
-      <c r="AC62">
-        <v>2.21</v>
-      </c>
-      <c r="AD62">
-        <v>1.6</v>
-      </c>
-      <c r="AE62">
-        <v>1.21</v>
-      </c>
-      <c r="AF62">
-        <v>1.43</v>
-      </c>
-      <c r="AG62">
-        <v>2.59</v>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK62">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="O63">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="Q63">
-        <v>2.14</v>
+        <v>3.15</v>
       </c>
       <c r="R63">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="U63">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="V63">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W63">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
         <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA63">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AB63">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AC63">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AD63">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AE63">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF63">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AG63">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.21</v>
       </c>
       <c r="AK63">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.23</v>
+        <v>4</v>
       </c>
       <c r="O111">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="P111">
-        <v>9</v>
+        <v>1.78</v>
       </c>
       <c r="Q111">
-        <v>1.57</v>
+        <v>3.9</v>
       </c>
       <c r="R111">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="S111">
+        <v>1.22</v>
+      </c>
+      <c r="T111">
+        <v>4.05</v>
+      </c>
+      <c r="U111">
+        <v>2</v>
+      </c>
+      <c r="V111">
+        <v>1.78</v>
+      </c>
+      <c r="W111">
         <v>1.2</v>
       </c>
-      <c r="T111">
-        <v>4.7</v>
-      </c>
-      <c r="U111">
-        <v>2.02</v>
-      </c>
-      <c r="V111">
-        <v>1.85</v>
-      </c>
-      <c r="W111">
-        <v>1.24</v>
-      </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z111">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA111">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AB111">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AC111">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AD111">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AE111">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AF111">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="AG111">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="AK111">
-        <v>3.8</v>
+        <v>1.22</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="O112">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P112">
-        <v>1.78</v>
+        <v>2.71</v>
       </c>
       <c r="Q112">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="R112">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="S112">
         <v>1.22</v>
       </c>
       <c r="T112">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U112">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="V112">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W112">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z112">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA112">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB112">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="AC112">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AD112">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AE112">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AF112">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AG112">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AK112">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.25</v>
+        <v>1.23</v>
       </c>
       <c r="O113">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="P113">
-        <v>2.71</v>
+        <v>9</v>
       </c>
       <c r="Q113">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="R113">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="S113">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T113">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="U113">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V113">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="W113">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X113">
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z113">
         <v>7.5</v>
       </c>
       <c r="AA113">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB113">
         <v>3.2</v>
       </c>
       <c r="AC113">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD113">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AE113">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF113">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AG113">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.43</v>
+        <v>1.06</v>
       </c>
       <c r="AK113">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="O132">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="P132">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="Q132">
-        <v>2.81</v>
+        <v>2</v>
       </c>
       <c r="R132">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S132">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T132">
-        <v>2.81</v>
+        <v>3.45</v>
       </c>
       <c r="U132">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="V132">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="W132">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X132">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z132">
-        <v>3.61</v>
+        <v>4.35</v>
       </c>
       <c r="AA132">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB132">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AC132">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD132">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE132">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF132">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG132">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK132">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="O133">
         <v>3.25</v>
       </c>
       <c r="P133">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q133">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="R133">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S133">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="T133">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="U133">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="V133">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W133">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X133">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y133">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="Z133">
-        <v>3.08</v>
+        <v>2.79</v>
       </c>
       <c r="AA133">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AB133">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AC133">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AD133">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE133">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF133">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG133">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK133">
         <v>1.44</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O134">
         <v>3.25</v>
       </c>
       <c r="P134">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="Q134">
-        <v>3.01</v>
+        <v>2.81</v>
       </c>
       <c r="R134">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="S134">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="T134">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U134">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="V134">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W134">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X134">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y134">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="Z134">
-        <v>2.79</v>
+        <v>3.61</v>
       </c>
       <c r="AA134">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AB134">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AC134">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AD134">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE134">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF134">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AG134">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.57</v>
+        <v>2.47</v>
       </c>
       <c r="O137">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P137">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="Q137">
+        <v>3</v>
+      </c>
+      <c r="R137">
+        <v>2.1</v>
+      </c>
+      <c r="S137">
+        <v>1.39</v>
+      </c>
+      <c r="T137">
+        <v>2.73</v>
+      </c>
+      <c r="U137">
+        <v>2.9</v>
+      </c>
+      <c r="V137">
+        <v>1.35</v>
+      </c>
+      <c r="W137">
+        <v>1.03</v>
+      </c>
+      <c r="X137">
+        <v>1.04</v>
+      </c>
+      <c r="Y137">
+        <v>1.31</v>
+      </c>
+      <c r="Z137">
+        <v>3.08</v>
+      </c>
+      <c r="AA137">
+        <v>2.02</v>
+      </c>
+      <c r="AB137">
+        <v>1.78</v>
+      </c>
+      <c r="AC137">
+        <v>3.75</v>
+      </c>
+      <c r="AD137">
+        <v>1.25</v>
+      </c>
+      <c r="AE137">
+        <v>1.08</v>
+      </c>
+      <c r="AF137">
+        <v>1.75</v>
+      </c>
+      <c r="AG137">
         <v>2</v>
       </c>
-      <c r="R137">
-        <v>2.4</v>
-      </c>
-      <c r="S137">
-        <v>1.25</v>
-      </c>
-      <c r="T137">
-        <v>3.45</v>
-      </c>
-      <c r="U137">
-        <v>2.21</v>
-      </c>
-      <c r="V137">
-        <v>1.61</v>
-      </c>
-      <c r="W137">
-        <v>1.14</v>
-      </c>
-      <c r="X137">
-        <v>1.03</v>
-      </c>
-      <c r="Y137">
-        <v>1.2</v>
-      </c>
-      <c r="Z137">
-        <v>4.35</v>
-      </c>
-      <c r="AA137">
-        <v>1.58</v>
-      </c>
-      <c r="AB137">
-        <v>2.31</v>
-      </c>
-      <c r="AC137">
-        <v>2.5</v>
-      </c>
-      <c r="AD137">
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>1.33</v>
+      </c>
+      <c r="AK137">
         <v>1.44</v>
-      </c>
-      <c r="AE137">
-        <v>1.17</v>
-      </c>
-      <c r="AF137">
-        <v>1.65</v>
-      </c>
-      <c r="AG137">
-        <v>2.14</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.19</v>
-      </c>
-      <c r="AK137">
-        <v>2.33</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>2.87</v>
+        <v>1.67</v>
       </c>
       <c r="O146">
+        <v>4.1</v>
+      </c>
+      <c r="P146">
+        <v>4.5</v>
+      </c>
+      <c r="Q146">
+        <v>2.05</v>
+      </c>
+      <c r="R146">
+        <v>2.5</v>
+      </c>
+      <c r="S146">
+        <v>1.22</v>
+      </c>
+      <c r="T146">
         <v>3.4</v>
       </c>
-      <c r="P146">
-        <v>2.36</v>
-      </c>
-      <c r="Q146">
-        <v>3.57</v>
-      </c>
-      <c r="R146">
-        <v>2.11</v>
-      </c>
-      <c r="S146">
-        <v>1.3</v>
-      </c>
-      <c r="T146">
-        <v>2.88</v>
-      </c>
       <c r="U146">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="V146">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W146">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X146">
         <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z146">
-        <v>3.44</v>
+        <v>4.8</v>
       </c>
       <c r="AA146">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB146">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC146">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="AD146">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AE146">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF146">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG146">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AK146">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="O147">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="P147">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q147">
-        <v>2.05</v>
+        <v>3.48</v>
       </c>
       <c r="R147">
+        <v>1.96</v>
+      </c>
+      <c r="S147">
+        <v>1.47</v>
+      </c>
+      <c r="T147">
         <v>2.5</v>
       </c>
-      <c r="S147">
+      <c r="U147">
+        <v>3.1</v>
+      </c>
+      <c r="V147">
+        <v>1.32</v>
+      </c>
+      <c r="W147">
+        <v>1.04</v>
+      </c>
+      <c r="X147">
+        <v>1.06</v>
+      </c>
+      <c r="Y147">
+        <v>1.36</v>
+      </c>
+      <c r="Z147">
+        <v>2.9</v>
+      </c>
+      <c r="AA147">
+        <v>2.15</v>
+      </c>
+      <c r="AB147">
+        <v>1.65</v>
+      </c>
+      <c r="AC147">
+        <v>3.9</v>
+      </c>
+      <c r="AD147">
         <v>1.22</v>
       </c>
-      <c r="T147">
-        <v>3.4</v>
-      </c>
-      <c r="U147">
-        <v>2.23</v>
-      </c>
-      <c r="V147">
-        <v>1.61</v>
-      </c>
-      <c r="W147">
-        <v>1.14</v>
-      </c>
-      <c r="X147">
-        <v>1.01</v>
-      </c>
-      <c r="Y147">
-        <v>1.2</v>
-      </c>
-      <c r="Z147">
-        <v>4.8</v>
-      </c>
-      <c r="AA147">
-        <v>1.61</v>
-      </c>
-      <c r="AB147">
-        <v>2.3</v>
-      </c>
-      <c r="AC147">
-        <v>2.5</v>
-      </c>
-      <c r="AD147">
-        <v>1.48</v>
-      </c>
       <c r="AE147">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF147">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG147">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="AK147">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,65 +24433,65 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="O148">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P148">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q148">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="R148">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="S148">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="T148">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U148">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="V148">
+        <v>1.44</v>
+      </c>
+      <c r="W148">
+        <v>1.06</v>
+      </c>
+      <c r="X148">
+        <v>1.01</v>
+      </c>
+      <c r="Y148">
+        <v>1.23</v>
+      </c>
+      <c r="Z148">
+        <v>3.44</v>
+      </c>
+      <c r="AA148">
+        <v>1.8</v>
+      </c>
+      <c r="AB148">
+        <v>1.88</v>
+      </c>
+      <c r="AC148">
+        <v>3.12</v>
+      </c>
+      <c r="AD148">
         <v>1.32</v>
       </c>
-      <c r="W148">
-        <v>1.04</v>
-      </c>
-      <c r="X148">
-        <v>1.06</v>
-      </c>
-      <c r="Y148">
-        <v>1.36</v>
-      </c>
-      <c r="Z148">
-        <v>2.9</v>
-      </c>
-      <c r="AA148">
+      <c r="AE148">
+        <v>1.13</v>
+      </c>
+      <c r="AF148">
+        <v>1.65</v>
+      </c>
+      <c r="AG148">
         <v>2.15</v>
       </c>
-      <c r="AB148">
-        <v>1.65</v>
-      </c>
-      <c r="AC148">
-        <v>3.9</v>
-      </c>
-      <c r="AD148">
-        <v>1.22</v>
-      </c>
-      <c r="AE148">
-        <v>1.04</v>
-      </c>
-      <c r="AF148">
-        <v>1.83</v>
-      </c>
-      <c r="AG148">
-        <v>1.91</v>
-      </c>
       <c r="AH148" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AK148">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="O151">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P151">
-        <v>2.6</v>
+        <v>4.03</v>
       </c>
       <c r="Q151">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="R151">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="S151">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T151">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U151">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="V151">
         <v>1.4</v>
       </c>
       <c r="W151">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X151">
         <v>1.05</v>
       </c>
       <c r="Y151">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z151">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA151">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB151">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC151">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD151">
         <v>1.3</v>
       </c>
       <c r="AE151">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF151">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG151">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK151">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,80 +25085,80 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O152">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P152">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q152">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R152">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S152">
         <v>1.25</v>
       </c>
       <c r="T152">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U152">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V152">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W152">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X152">
         <v>1.03</v>
       </c>
       <c r="Y152">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z152">
-        <v>5.43</v>
+        <v>4.9</v>
       </c>
       <c r="AA152">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB152">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="AC152">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AD152">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE152">
+        <v>1.19</v>
+      </c>
+      <c r="AF152">
+        <v>1.47</v>
+      </c>
+      <c r="AG152">
+        <v>2.43</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ152">
         <v>1.26</v>
       </c>
-      <c r="AF152">
-        <v>1.53</v>
-      </c>
-      <c r="AG152">
-        <v>2.3</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ152">
-        <v>1.17</v>
-      </c>
       <c r="AK152">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O153">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P153">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q153">
+        <v>2.3</v>
+      </c>
+      <c r="R153">
         <v>2.35</v>
       </c>
-      <c r="R153">
-        <v>2.47</v>
-      </c>
       <c r="S153">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T153">
         <v>3.3</v>
       </c>
       <c r="U153">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="V153">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="W153">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X153">
         <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z153">
-        <v>4.33</v>
+        <v>3.78</v>
       </c>
       <c r="AA153">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AB153">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC153">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="AD153">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE153">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF153">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG153">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK153">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O154">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P154">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q154">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R154">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S154">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T154">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U154">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="V154">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="W154">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X154">
         <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z154">
-        <v>3.78</v>
+        <v>5.43</v>
       </c>
       <c r="AA154">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AB154">
-        <v>2.04</v>
+        <v>2.61</v>
       </c>
       <c r="AC154">
-        <v>2.64</v>
+        <v>2.23</v>
       </c>
       <c r="AD154">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="AE154">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AF154">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AG154">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK154">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,80 +25574,80 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.85</v>
+        <v>3.05</v>
       </c>
       <c r="O155">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P155">
-        <v>4.03</v>
+        <v>2</v>
       </c>
       <c r="Q155">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="R155">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S155">
         <v>1.35</v>
       </c>
       <c r="T155">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U155">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="V155">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W155">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X155">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y155">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z155">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA155">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB155">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC155">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AD155">
+        <v>1.41</v>
+      </c>
+      <c r="AE155">
+        <v>1.13</v>
+      </c>
+      <c r="AF155">
+        <v>1.61</v>
+      </c>
+      <c r="AG155">
+        <v>2.2</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
         <v>1.3</v>
       </c>
-      <c r="AE155">
-        <v>1.11</v>
-      </c>
-      <c r="AF155">
-        <v>1.73</v>
-      </c>
-      <c r="AG155">
-        <v>2.05</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>1.22</v>
-      </c>
       <c r="AK155">
-        <v>1.83</v>
+        <v>1.28</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O156">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P156">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q156">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="R156">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="S156">
+        <v>1.37</v>
+      </c>
+      <c r="T156">
+        <v>2.88</v>
+      </c>
+      <c r="U156">
+        <v>2.75</v>
+      </c>
+      <c r="V156">
+        <v>1.4</v>
+      </c>
+      <c r="W156">
+        <v>1.05</v>
+      </c>
+      <c r="X156">
+        <v>1.05</v>
+      </c>
+      <c r="Y156">
+        <v>1.31</v>
+      </c>
+      <c r="Z156">
+        <v>3.05</v>
+      </c>
+      <c r="AA156">
+        <v>1.93</v>
+      </c>
+      <c r="AB156">
+        <v>1.83</v>
+      </c>
+      <c r="AC156">
+        <v>3.3</v>
+      </c>
+      <c r="AD156">
+        <v>1.3</v>
+      </c>
+      <c r="AE156">
+        <v>1.1</v>
+      </c>
+      <c r="AF156">
+        <v>1.7</v>
+      </c>
+      <c r="AG156">
+        <v>2.01</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
         <v>1.25</v>
       </c>
-      <c r="T156">
-        <v>3.42</v>
-      </c>
-      <c r="U156">
-        <v>2.22</v>
-      </c>
-      <c r="V156">
-        <v>1.62</v>
-      </c>
-      <c r="W156">
-        <v>1.15</v>
-      </c>
-      <c r="X156">
-        <v>1.03</v>
-      </c>
-      <c r="Y156">
-        <v>1.13</v>
-      </c>
-      <c r="Z156">
-        <v>4.9</v>
-      </c>
-      <c r="AA156">
-        <v>1.53</v>
-      </c>
-      <c r="AB156">
-        <v>2.44</v>
-      </c>
-      <c r="AC156">
-        <v>2.3</v>
-      </c>
-      <c r="AD156">
-        <v>1.57</v>
-      </c>
-      <c r="AE156">
-        <v>1.19</v>
-      </c>
-      <c r="AF156">
-        <v>1.47</v>
-      </c>
-      <c r="AG156">
-        <v>2.43</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.26</v>
-      </c>
       <c r="AK156">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,46 +25900,46 @@
         </is>
       </c>
       <c r="N157">
-        <v>3.05</v>
+        <v>1.79</v>
       </c>
       <c r="O157">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P157">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="Q157">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="R157">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S157">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="T157">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="U157">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V157">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W157">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z157">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA157">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB157">
         <v>2.15</v>
@@ -25948,16 +25948,16 @@
         <v>2.65</v>
       </c>
       <c r="AD157">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE157">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF157">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG157">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK157">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O227">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P227">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="Q227">
         <v>2.63</v>
       </c>
       <c r="R227">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S227">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T227">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="U227">
-        <v>2.89</v>
+        <v>2.45</v>
       </c>
       <c r="V227">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W227">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X227">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y227">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z227">
-        <v>3.13</v>
+        <v>4.26</v>
       </c>
       <c r="AA227">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AB227">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC227">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="AD227">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE227">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF227">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG227">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK227">
         <v>1.67</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O228">
+        <v>3.25</v>
+      </c>
+      <c r="P228">
         <v>3.3</v>
-      </c>
-      <c r="P228">
-        <v>2.87</v>
       </c>
       <c r="Q228">
         <v>2.63</v>
       </c>
       <c r="R228">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S228">
+        <v>1.41</v>
+      </c>
+      <c r="T228">
+        <v>2.69</v>
+      </c>
+      <c r="U228">
+        <v>2.89</v>
+      </c>
+      <c r="V228">
+        <v>1.36</v>
+      </c>
+      <c r="W228">
+        <v>1.04</v>
+      </c>
+      <c r="X228">
+        <v>1.01</v>
+      </c>
+      <c r="Y228">
         <v>1.33</v>
       </c>
-      <c r="T228">
-        <v>3.2</v>
-      </c>
-      <c r="U228">
-        <v>2.45</v>
-      </c>
-      <c r="V228">
-        <v>1.48</v>
-      </c>
-      <c r="W228">
-        <v>1.08</v>
-      </c>
-      <c r="X228">
-        <v>1</v>
-      </c>
-      <c r="Y228">
-        <v>1.22</v>
-      </c>
       <c r="Z228">
-        <v>4.26</v>
+        <v>3.13</v>
       </c>
       <c r="AA228">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB228">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC228">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AD228">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE228">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF228">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG228">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK228">
         <v>1.67</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
+        <v>3.12</v>
+      </c>
+      <c r="O246">
         <v>3.15</v>
       </c>
-      <c r="O246">
-        <v>3.4</v>
-      </c>
       <c r="P246">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="O279">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P279">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q279">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="R279">
-        <v>2.05</v>
+        <v>2.43</v>
       </c>
       <c r="S279">
+        <v>1.3</v>
+      </c>
+      <c r="T279">
+        <v>3.25</v>
+      </c>
+      <c r="U279">
+        <v>2.4</v>
+      </c>
+      <c r="V279">
+        <v>1.54</v>
+      </c>
+      <c r="W279">
+        <v>1.11</v>
+      </c>
+      <c r="X279">
+        <v>1.02</v>
+      </c>
+      <c r="Y279">
+        <v>1.18</v>
+      </c>
+      <c r="Z279">
+        <v>4.2</v>
+      </c>
+      <c r="AA279">
+        <v>1.66</v>
+      </c>
+      <c r="AB279">
+        <v>2.2</v>
+      </c>
+      <c r="AC279">
+        <v>2.58</v>
+      </c>
+      <c r="AD279">
         <v>1.44</v>
       </c>
-      <c r="T279">
-        <v>2.77</v>
-      </c>
-      <c r="U279">
-        <v>2.82</v>
-      </c>
-      <c r="V279">
-        <v>1.36</v>
-      </c>
-      <c r="W279">
-        <v>1.06</v>
-      </c>
-      <c r="X279">
-        <v>1.04</v>
-      </c>
-      <c r="Y279">
-        <v>1.33</v>
-      </c>
-      <c r="Z279">
-        <v>3.1</v>
-      </c>
-      <c r="AA279">
-        <v>2.1</v>
-      </c>
-      <c r="AB279">
-        <v>1.72</v>
-      </c>
-      <c r="AC279">
-        <v>3.48</v>
-      </c>
-      <c r="AD279">
-        <v>1.25</v>
-      </c>
       <c r="AE279">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF279">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG279">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AK279">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O280">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P280">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="Q280">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="R280">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="S280">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T280">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="U280">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="V280">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W280">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X280">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y280">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z280">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA280">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB280">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC280">
-        <v>2.58</v>
+        <v>3.48</v>
       </c>
       <c r="AD280">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE280">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF280">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG280">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AK280">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G314">
@@ -51491,64 +51491,64 @@
         </is>
       </c>
       <c r="N314">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="O314">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P314">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q314">
+        <v>2.07</v>
+      </c>
+      <c r="R314">
+        <v>2.51</v>
+      </c>
+      <c r="S314">
+        <v>1.27</v>
+      </c>
+      <c r="T314">
+        <v>3.25</v>
+      </c>
+      <c r="U314">
+        <v>2.27</v>
+      </c>
+      <c r="V314">
+        <v>1.53</v>
+      </c>
+      <c r="W314">
+        <v>1.1</v>
+      </c>
+      <c r="X314">
+        <v>1.03</v>
+      </c>
+      <c r="Y314">
+        <v>1.19</v>
+      </c>
+      <c r="Z314">
+        <v>4.44</v>
+      </c>
+      <c r="AA314">
+        <v>1.65</v>
+      </c>
+      <c r="AB314">
         <v>2.28</v>
       </c>
-      <c r="R314">
-        <v>2.28</v>
-      </c>
-      <c r="S314">
-        <v>1.36</v>
-      </c>
-      <c r="T314">
-        <v>2.88</v>
-      </c>
-      <c r="U314">
-        <v>2.7</v>
-      </c>
-      <c r="V314">
-        <v>1.38</v>
-      </c>
-      <c r="W314">
-        <v>1.04</v>
-      </c>
-      <c r="X314">
-        <v>1.01</v>
-      </c>
-      <c r="Y314">
-        <v>1.28</v>
-      </c>
-      <c r="Z314">
-        <v>3.42</v>
-      </c>
-      <c r="AA314">
-        <v>1.9</v>
-      </c>
-      <c r="AB314">
-        <v>1.88</v>
-      </c>
       <c r="AC314">
-        <v>2.85</v>
+        <v>2.51</v>
       </c>
       <c r="AD314">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="AE314">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF314">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG314">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK314">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,64 +51654,64 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="O315">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P315">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q315">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="R315">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="S315">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T315">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U315">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="V315">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="W315">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X315">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y315">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z315">
-        <v>4.44</v>
+        <v>3.42</v>
       </c>
       <c r="AA315">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB315">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="AC315">
-        <v>2.51</v>
+        <v>2.85</v>
       </c>
       <c r="AD315">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AE315">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF315">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG315">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK315">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -52481,7 +52481,7 @@
         <v>2.15</v>
       </c>
       <c r="R320">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S320">
         <v>1.18</v>
@@ -52496,13 +52496,13 @@
         <v>1.73</v>
       </c>
       <c r="W320">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X320">
         <v>1.01</v>
       </c>
       <c r="Y320">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z320">
         <v>7.5</v>
@@ -52514,19 +52514,19 @@
         <v>2.88</v>
       </c>
       <c r="AC320">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AD320">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE320">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF320">
         <v>1.4</v>
       </c>
       <c r="AG320">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,7 +52539,7 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK320">
         <v>1.88</v>
@@ -52635,16 +52635,16 @@
         <v>1.87</v>
       </c>
       <c r="O321">
-        <v>4.12</v>
+        <v>3.7</v>
       </c>
       <c r="P321">
         <v>3.4</v>
       </c>
       <c r="Q321">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="R321">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S321">
         <v>1.19</v>
@@ -52653,7 +52653,7 @@
         <v>4</v>
       </c>
       <c r="U321">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V321">
         <v>1.72</v>
@@ -52665,7 +52665,7 @@
         <v>1.02</v>
       </c>
       <c r="Y321">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z321">
         <v>5.65</v>
@@ -52674,16 +52674,16 @@
         <v>1.4</v>
       </c>
       <c r="AB321">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC321">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AD321">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AE321">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AF321">
         <v>1.44</v>
@@ -52795,7 +52795,7 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O322">
         <v>4.26</v>
@@ -52813,13 +52813,13 @@
         <v>1.18</v>
       </c>
       <c r="T322">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="U322">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V322">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W322">
         <v>1.22</v>
@@ -52831,28 +52831,28 @@
         <v>1.11</v>
       </c>
       <c r="Z322">
-        <v>6</v>
+        <v>6.62</v>
       </c>
       <c r="AA322">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB322">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AC322">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AD322">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE322">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF322">
         <v>1.33</v>
       </c>
       <c r="AG322">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK322">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52976,46 +52976,46 @@
         <v>1.2</v>
       </c>
       <c r="T323">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U323">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="V323">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="W323">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X323">
         <v>1.02</v>
       </c>
       <c r="Y323">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z323">
-        <v>5.7</v>
+        <v>6.28</v>
       </c>
       <c r="AA323">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB323">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="AC323">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AD323">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="AE323">
         <v>1.29</v>
       </c>
       <c r="AF323">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG323">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>1.2</v>
       </c>
       <c r="AK323">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53124,10 +53124,10 @@
         <v>2.3</v>
       </c>
       <c r="O324">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="P324">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q324">
         <v>2.55</v>
@@ -53136,16 +53136,16 @@
         <v>2.3</v>
       </c>
       <c r="S324">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T324">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U324">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="V324">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W324">
         <v>1.12</v>
@@ -53154,16 +53154,16 @@
         <v>1.01</v>
       </c>
       <c r="Y324">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z324">
         <v>4.2</v>
       </c>
       <c r="AA324">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB324">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC324">
         <v>2.55</v>
@@ -53194,7 +53194,7 @@
         <v>1.22</v>
       </c>
       <c r="AK324">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53773,7 +53773,7 @@
         </is>
       </c>
       <c r="N328">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O328">
         <v>3.95</v>
@@ -53794,7 +53794,7 @@
         <v>4.33</v>
       </c>
       <c r="U328">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V328">
         <v>1.76</v>
@@ -53806,13 +53806,13 @@
         <v>1.01</v>
       </c>
       <c r="Y328">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z328">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA328">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB328">
         <v>2.85</v>
@@ -53827,7 +53827,7 @@
         <v>1.33</v>
       </c>
       <c r="AF328">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG328">
         <v>2.8</v>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK328">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53957,7 +53957,7 @@
         <v>3.8</v>
       </c>
       <c r="U329">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V329">
         <v>1.6</v>
@@ -53990,7 +53990,7 @@
         <v>1.18</v>
       </c>
       <c r="AF329">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG329">
         <v>2.5</v>
@@ -54009,7 +54009,7 @@
         <v>1.26</v>
       </c>
       <c r="AK329">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54117,10 +54117,10 @@
         <v>1.22</v>
       </c>
       <c r="T330">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="U330">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V330">
         <v>1.64</v>
@@ -54150,7 +54150,7 @@
         <v>1.62</v>
       </c>
       <c r="AE330">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF330">
         <v>1.53</v>
@@ -54169,7 +54169,7 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.22</v>
+        <v>2.31</v>
       </c>
       <c r="AK330">
         <v>1.18</v>
@@ -54443,7 +54443,7 @@
         <v>1.25</v>
       </c>
       <c r="T332">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U332">
         <v>2.25</v>
@@ -54476,7 +54476,7 @@
         <v>1.51</v>
       </c>
       <c r="AE332">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF332">
         <v>1.57</v>
@@ -54600,16 +54600,16 @@
         <v>2.2</v>
       </c>
       <c r="R333">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S333">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T333">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U333">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V333">
         <v>1.51</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,64 +55403,64 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O338">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P338">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="Q338">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="R338">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S338">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T338">
         <v>3.5</v>
       </c>
       <c r="U338">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V338">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W338">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X338">
         <v>1.03</v>
       </c>
       <c r="Y338">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z338">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA338">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AB338">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AC338">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AD338">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AE338">
         <v>1.18</v>
       </c>
       <c r="AF338">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG338">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,10 +55473,10 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK338">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,64 +55566,64 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O339">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P339">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q339">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="R339">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S339">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T339">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U339">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V339">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W339">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X339">
         <v>1.03</v>
       </c>
       <c r="Y339">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z339">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA339">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AB339">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AC339">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AD339">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE339">
         <v>1.18</v>
       </c>
       <c r="AF339">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG339">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK339">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AL339">
         <v>0</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.1</v>
+        <v>1.58</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
+        <v>4.65</v>
+      </c>
+      <c r="Q27">
         <v>2.05</v>
       </c>
-      <c r="Q27">
-        <v>3.26</v>
-      </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
         <v>1.12</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z27">
-        <v>4.05</v>
+        <v>5.4</v>
       </c>
       <c r="AA27">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
       <c r="AC27">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="AD27">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AE27">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.33</v>
+        <v>2.35</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.65</v>
+        <v>2.05</v>
       </c>
       <c r="Q28">
-        <v>2.05</v>
+        <v>3.26</v>
       </c>
       <c r="R28">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="U28">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W28">
         <v>1.12</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z28">
-        <v>5.4</v>
+        <v>4.05</v>
       </c>
       <c r="AA28">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AB28">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="AC28">
+        <v>2.65</v>
+      </c>
+      <c r="AD28">
+        <v>1.45</v>
+      </c>
+      <c r="AE28">
+        <v>1.14</v>
+      </c>
+      <c r="AF28">
+        <v>1.62</v>
+      </c>
+      <c r="AG28">
         <v>2.28</v>
       </c>
-      <c r="AD28">
-        <v>1.64</v>
-      </c>
-      <c r="AE28">
-        <v>1.22</v>
-      </c>
-      <c r="AF28">
-        <v>1.53</v>
-      </c>
-      <c r="AG28">
-        <v>2.3</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>2.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="U33">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V33">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z33">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB33">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC33">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AD33">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W34">
         <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB34">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AD34">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG34">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="O50">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
+        <v>1.33</v>
+      </c>
+      <c r="T50">
+        <v>3.1</v>
+      </c>
+      <c r="U50">
+        <v>2.6</v>
+      </c>
+      <c r="V50">
+        <v>1.44</v>
+      </c>
+      <c r="W50">
+        <v>1.06</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>1.25</v>
+      </c>
+      <c r="Z50">
+        <v>3.98</v>
+      </c>
+      <c r="AA50">
+        <v>1.77</v>
+      </c>
+      <c r="AB50">
+        <v>2.01</v>
+      </c>
+      <c r="AC50">
+        <v>2.76</v>
+      </c>
+      <c r="AD50">
         <v>1.39</v>
       </c>
-      <c r="T50">
-        <v>2.73</v>
-      </c>
-      <c r="U50">
-        <v>2.95</v>
-      </c>
-      <c r="V50">
-        <v>1.35</v>
-      </c>
-      <c r="W50">
-        <v>1.04</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.31</v>
-      </c>
-      <c r="Z50">
-        <v>2.94</v>
-      </c>
-      <c r="AA50">
-        <v>2.05</v>
-      </c>
-      <c r="AB50">
-        <v>1.69</v>
-      </c>
-      <c r="AC50">
-        <v>3.78</v>
-      </c>
-      <c r="AD50">
-        <v>1.25</v>
-      </c>
       <c r="AE50">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="O51">
+        <v>3.26</v>
+      </c>
+      <c r="P51">
+        <v>2.4</v>
+      </c>
+      <c r="Q51">
         <v>3.5</v>
       </c>
-      <c r="P51">
-        <v>2.6</v>
-      </c>
-      <c r="Q51">
-        <v>2.89</v>
-      </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
+        <v>1.39</v>
+      </c>
+      <c r="T51">
+        <v>2.73</v>
+      </c>
+      <c r="U51">
+        <v>2.95</v>
+      </c>
+      <c r="V51">
+        <v>1.35</v>
+      </c>
+      <c r="W51">
+        <v>1.04</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
+        <v>1.31</v>
+      </c>
+      <c r="Z51">
+        <v>2.94</v>
+      </c>
+      <c r="AA51">
+        <v>2.05</v>
+      </c>
+      <c r="AB51">
+        <v>1.69</v>
+      </c>
+      <c r="AC51">
+        <v>3.78</v>
+      </c>
+      <c r="AD51">
+        <v>1.25</v>
+      </c>
+      <c r="AE51">
+        <v>1.02</v>
+      </c>
+      <c r="AF51">
+        <v>1.83</v>
+      </c>
+      <c r="AG51">
+        <v>1.91</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.3</v>
+      </c>
+      <c r="AK51">
         <v>1.33</v>
-      </c>
-      <c r="T51">
-        <v>3.1</v>
-      </c>
-      <c r="U51">
-        <v>2.6</v>
-      </c>
-      <c r="V51">
-        <v>1.44</v>
-      </c>
-      <c r="W51">
-        <v>1.06</v>
-      </c>
-      <c r="X51">
-        <v>1.03</v>
-      </c>
-      <c r="Y51">
-        <v>1.25</v>
-      </c>
-      <c r="Z51">
-        <v>3.98</v>
-      </c>
-      <c r="AA51">
-        <v>1.77</v>
-      </c>
-      <c r="AB51">
-        <v>2.01</v>
-      </c>
-      <c r="AC51">
-        <v>2.76</v>
-      </c>
-      <c r="AD51">
-        <v>1.39</v>
-      </c>
-      <c r="AE51">
-        <v>1.14</v>
-      </c>
-      <c r="AF51">
-        <v>1.62</v>
-      </c>
-      <c r="AG51">
-        <v>2.3</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.38</v>
-      </c>
-      <c r="AK51">
-        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,65 +10415,65 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P62">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q62">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R62">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T62">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="U62">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V62">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA62">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AB62">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC62">
+        <v>2.83</v>
+      </c>
+      <c r="AD62">
+        <v>1.38</v>
+      </c>
+      <c r="AE62">
+        <v>1.09</v>
+      </c>
+      <c r="AF62">
+        <v>1.59</v>
+      </c>
+      <c r="AG62">
         <v>2.19</v>
       </c>
-      <c r="AD62">
-        <v>1.6</v>
-      </c>
-      <c r="AE62">
-        <v>1.22</v>
-      </c>
-      <c r="AF62">
-        <v>1.43</v>
-      </c>
-      <c r="AG62">
-        <v>2.62</v>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK62">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q63">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R63">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S63">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="U63">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V63">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X63">
         <v>1.03</v>
       </c>
       <c r="Y63">
+        <v>1.11</v>
+      </c>
+      <c r="Z63">
+        <v>4.8</v>
+      </c>
+      <c r="AA63">
+        <v>1.46</v>
+      </c>
+      <c r="AB63">
+        <v>2.4</v>
+      </c>
+      <c r="AC63">
+        <v>2.19</v>
+      </c>
+      <c r="AD63">
+        <v>1.6</v>
+      </c>
+      <c r="AE63">
         <v>1.22</v>
       </c>
-      <c r="Z63">
-        <v>3.75</v>
-      </c>
-      <c r="AA63">
-        <v>1.75</v>
-      </c>
-      <c r="AB63">
-        <v>1.95</v>
-      </c>
-      <c r="AC63">
-        <v>2.83</v>
-      </c>
-      <c r="AD63">
-        <v>1.38</v>
-      </c>
-      <c r="AE63">
-        <v>1.09</v>
-      </c>
       <c r="AF63">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="AG63">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK63">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="O87">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="P87">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q87">
-        <v>5.19</v>
+        <v>2.65</v>
       </c>
       <c r="R87">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="S87">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="T87">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="U87">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="V87">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W87">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X87">
         <v>1.06</v>
       </c>
       <c r="Y87">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="Z87">
+        <v>2.55</v>
+      </c>
+      <c r="AA87">
+        <v>2.62</v>
+      </c>
+      <c r="AB87">
+        <v>1.44</v>
+      </c>
+      <c r="AC87">
+        <v>4.8</v>
+      </c>
+      <c r="AD87">
+        <v>1.12</v>
+      </c>
+      <c r="AE87">
+        <v>1.03</v>
+      </c>
+      <c r="AF87">
         <v>2.05</v>
       </c>
-      <c r="AA87">
-        <v>3.15</v>
-      </c>
-      <c r="AB87">
-        <v>1.37</v>
-      </c>
-      <c r="AC87">
-        <v>5.5</v>
-      </c>
-      <c r="AD87">
-        <v>1.08</v>
-      </c>
-      <c r="AE87">
-        <v>1.02</v>
-      </c>
-      <c r="AF87">
-        <v>2.23</v>
-      </c>
       <c r="AG87">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AK87">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="O88">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P88">
-        <v>3.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q88">
-        <v>2.65</v>
+        <v>5.19</v>
       </c>
       <c r="R88">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="S88">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="T88">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="U88">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="V88">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X88">
         <v>1.06</v>
       </c>
       <c r="Y88">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="Z88">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AA88">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="AB88">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC88">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AD88">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE88">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF88">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AG88">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AK88">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -17282,7 +17282,7 @@
         <v>3.2</v>
       </c>
       <c r="U104">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V104">
         <v>1.44</v>
@@ -17297,25 +17297,25 @@
         <v>1.19</v>
       </c>
       <c r="Z104">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA104">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB104">
         <v>2.08</v>
       </c>
       <c r="AC104">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD104">
         <v>1.4</v>
       </c>
       <c r="AE104">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF104">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG104">
         <v>2.2</v>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK104">
         <v>1.44</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O105">
         <v>3.35</v>
@@ -17436,7 +17436,7 @@
         <v>2.4</v>
       </c>
       <c r="R105">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S105">
         <v>1.37</v>
@@ -17445,7 +17445,7 @@
         <v>2.96</v>
       </c>
       <c r="U105">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V105">
         <v>1.36</v>
@@ -17460,7 +17460,7 @@
         <v>1.29</v>
       </c>
       <c r="Z105">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="AA105">
         <v>1.95</v>
@@ -17469,13 +17469,13 @@
         <v>1.79</v>
       </c>
       <c r="AC105">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD105">
         <v>1.31</v>
       </c>
       <c r="AE105">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF105">
         <v>1.75</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17590,7 +17590,7 @@
         <v>1.97</v>
       </c>
       <c r="O106">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P106">
         <v>3.4</v>
@@ -17599,10 +17599,10 @@
         <v>2.5</v>
       </c>
       <c r="R106">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S106">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T106">
         <v>3.08</v>
@@ -17623,28 +17623,28 @@
         <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AA106">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB106">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC106">
         <v>2.9</v>
       </c>
       <c r="AD106">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE106">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF106">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG106">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.68</v>
+        <v>1.23</v>
       </c>
       <c r="O112">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="P112">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q112">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="R112">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="S112">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T112">
-        <v>3.45</v>
+        <v>4.55</v>
       </c>
       <c r="U112">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="V112">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="W112">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X112">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z112">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA112">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AB112">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="AC112">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AD112">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="AE112">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AF112">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AG112">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK112">
-        <v>2.1</v>
+        <v>3.64</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="O113">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="P113">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="Q113">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="R113">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="S113">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="T113">
-        <v>4.55</v>
+        <v>3.45</v>
       </c>
       <c r="U113">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="V113">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="W113">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="Z113">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA113">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AB113">
-        <v>2.87</v>
+        <v>2.33</v>
       </c>
       <c r="AC113">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AD113">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="AE113">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AF113">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AG113">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AK113">
-        <v>3.64</v>
+        <v>2.1</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O117">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q117">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="R117">
+        <v>2.26</v>
+      </c>
+      <c r="S117">
+        <v>1.28</v>
+      </c>
+      <c r="T117">
+        <v>3.5</v>
+      </c>
+      <c r="U117">
         <v>2.3</v>
       </c>
-      <c r="S117">
-        <v>1.32</v>
-      </c>
-      <c r="T117">
-        <v>3.1</v>
-      </c>
-      <c r="U117">
-        <v>2.6</v>
-      </c>
       <c r="V117">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W117">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>3.86</v>
+        <v>4.7</v>
       </c>
       <c r="AA117">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB117">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AC117">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD117">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE117">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF117">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
+        <v>1.88</v>
+      </c>
+      <c r="O118">
+        <v>3.7</v>
+      </c>
+      <c r="P118">
+        <v>3.8</v>
+      </c>
+      <c r="Q118">
+        <v>2.4</v>
+      </c>
+      <c r="R118">
         <v>2.3</v>
       </c>
-      <c r="O118">
-        <v>3.3</v>
-      </c>
-      <c r="P118">
-        <v>2.62</v>
-      </c>
-      <c r="Q118">
-        <v>2.98</v>
-      </c>
-      <c r="R118">
-        <v>2.26</v>
-      </c>
       <c r="S118">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T118">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U118">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V118">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W118">
+        <v>1.09</v>
+      </c>
+      <c r="X118">
+        <v>1.02</v>
+      </c>
+      <c r="Y118">
+        <v>1.22</v>
+      </c>
+      <c r="Z118">
+        <v>3.86</v>
+      </c>
+      <c r="AA118">
+        <v>1.8</v>
+      </c>
+      <c r="AB118">
+        <v>2</v>
+      </c>
+      <c r="AC118">
+        <v>3</v>
+      </c>
+      <c r="AD118">
+        <v>1.36</v>
+      </c>
+      <c r="AE118">
         <v>1.11</v>
       </c>
-      <c r="X118">
-        <v>1.04</v>
-      </c>
-      <c r="Y118">
-        <v>1.18</v>
-      </c>
-      <c r="Z118">
-        <v>4.7</v>
-      </c>
-      <c r="AA118">
-        <v>1.61</v>
-      </c>
-      <c r="AB118">
-        <v>2.28</v>
-      </c>
-      <c r="AC118">
-        <v>2.63</v>
-      </c>
-      <c r="AD118">
-        <v>1.44</v>
-      </c>
-      <c r="AE118">
-        <v>1.14</v>
-      </c>
       <c r="AF118">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AG118">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="O132">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P132">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q132">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="R132">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S132">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="T132">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="U132">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="V132">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="W132">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X132">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y132">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z132">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA132">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AB132">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC132">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="AD132">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE132">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF132">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG132">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK132">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,61 +21988,61 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="O133">
         <v>3.25</v>
       </c>
       <c r="P133">
+        <v>2.55</v>
+      </c>
+      <c r="Q133">
         <v>3</v>
       </c>
-      <c r="Q133">
-        <v>2.81</v>
-      </c>
       <c r="R133">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="S133">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T133">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U133">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="V133">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W133">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X133">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y133">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z133">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AA133">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AB133">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC133">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD133">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE133">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF133">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG133">
         <v>2</v>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK133">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="O134">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="P134">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="Q134">
-        <v>3.32</v>
+        <v>2.05</v>
       </c>
       <c r="R134">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S134">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="T134">
-        <v>2.5</v>
+        <v>3.36</v>
       </c>
       <c r="U134">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="V134">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="W134">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X134">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="Z134">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA134">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AB134">
+        <v>2.12</v>
+      </c>
+      <c r="AC134">
+        <v>2.33</v>
+      </c>
+      <c r="AD134">
+        <v>1.42</v>
+      </c>
+      <c r="AE134">
+        <v>1.14</v>
+      </c>
+      <c r="AF134">
         <v>1.62</v>
       </c>
-      <c r="AC134">
-        <v>4.2</v>
-      </c>
-      <c r="AD134">
-        <v>1.2</v>
-      </c>
-      <c r="AE134">
-        <v>1.06</v>
-      </c>
-      <c r="AF134">
-        <v>1.87</v>
-      </c>
       <c r="AG134">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK134">
-        <v>1.39</v>
+        <v>2.25</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O135">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P135">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q135">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="R135">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S135">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T135">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="U135">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V135">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W135">
+        <v>1.07</v>
+      </c>
+      <c r="X135">
+        <v>1</v>
+      </c>
+      <c r="Y135">
+        <v>1.28</v>
+      </c>
+      <c r="Z135">
+        <v>3.4</v>
+      </c>
+      <c r="AA135">
+        <v>1.93</v>
+      </c>
+      <c r="AB135">
+        <v>1.85</v>
+      </c>
+      <c r="AC135">
+        <v>3.2</v>
+      </c>
+      <c r="AD135">
+        <v>1.25</v>
+      </c>
+      <c r="AE135">
         <v>1.06</v>
       </c>
-      <c r="X135">
-        <v>1.04</v>
-      </c>
-      <c r="Y135">
-        <v>1.2</v>
-      </c>
-      <c r="Z135">
-        <v>3.45</v>
-      </c>
-      <c r="AA135">
-        <v>1.8</v>
-      </c>
-      <c r="AB135">
-        <v>1.96</v>
-      </c>
-      <c r="AC135">
-        <v>2.88</v>
-      </c>
-      <c r="AD135">
-        <v>1.36</v>
-      </c>
-      <c r="AE135">
-        <v>1.08</v>
-      </c>
       <c r="AF135">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG135">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.57</v>
+        <v>3.15</v>
       </c>
       <c r="O136">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="Q136">
-        <v>2.05</v>
+        <v>3.52</v>
       </c>
       <c r="R136">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S136">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="T136">
-        <v>3.36</v>
+        <v>3.07</v>
       </c>
       <c r="U136">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="V136">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X136">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y136">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z136">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA136">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AB136">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AC136">
-        <v>2.33</v>
+        <v>2.97</v>
       </c>
       <c r="AD136">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE136">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK136">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="O137">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P137">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="Q137">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="R137">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S137">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="T137">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="U137">
+        <v>2.6</v>
+      </c>
+      <c r="V137">
+        <v>1.46</v>
+      </c>
+      <c r="W137">
+        <v>1.06</v>
+      </c>
+      <c r="X137">
+        <v>1.04</v>
+      </c>
+      <c r="Y137">
+        <v>1.2</v>
+      </c>
+      <c r="Z137">
+        <v>3.45</v>
+      </c>
+      <c r="AA137">
+        <v>1.8</v>
+      </c>
+      <c r="AB137">
+        <v>1.96</v>
+      </c>
+      <c r="AC137">
         <v>2.88</v>
       </c>
-      <c r="V137">
-        <v>1.37</v>
-      </c>
-      <c r="W137">
+      <c r="AD137">
+        <v>1.36</v>
+      </c>
+      <c r="AE137">
         <v>1.08</v>
       </c>
-      <c r="X137">
-        <v>1.06</v>
-      </c>
-      <c r="Y137">
-        <v>1.32</v>
-      </c>
-      <c r="Z137">
-        <v>3</v>
-      </c>
-      <c r="AA137">
-        <v>2.02</v>
-      </c>
-      <c r="AB137">
-        <v>1.76</v>
-      </c>
-      <c r="AC137">
-        <v>3.6</v>
-      </c>
-      <c r="AD137">
-        <v>1.23</v>
-      </c>
-      <c r="AE137">
-        <v>1.04</v>
-      </c>
       <c r="AF137">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG137">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK137">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="O147">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P147">
-        <v>4.54</v>
+        <v>2.36</v>
       </c>
       <c r="Q147">
-        <v>2.05</v>
+        <v>3.35</v>
       </c>
       <c r="R147">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S147">
+        <v>1.39</v>
+      </c>
+      <c r="T147">
+        <v>2.77</v>
+      </c>
+      <c r="U147">
+        <v>2.69</v>
+      </c>
+      <c r="V147">
+        <v>1.41</v>
+      </c>
+      <c r="W147">
+        <v>1.06</v>
+      </c>
+      <c r="X147">
+        <v>1.04</v>
+      </c>
+      <c r="Y147">
         <v>1.25</v>
       </c>
-      <c r="T147">
-        <v>3.8</v>
-      </c>
-      <c r="U147">
-        <v>2.36</v>
-      </c>
-      <c r="V147">
-        <v>1.57</v>
-      </c>
-      <c r="W147">
-        <v>1.14</v>
-      </c>
-      <c r="X147">
-        <v>1.01</v>
-      </c>
-      <c r="Y147">
-        <v>1.2</v>
-      </c>
       <c r="Z147">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA147">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB147">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC147">
-        <v>2.48</v>
+        <v>2.95</v>
       </c>
       <c r="AD147">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE147">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF147">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG147">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AK147">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,80 +24433,80 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="O148">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="P148">
+        <v>4.54</v>
+      </c>
+      <c r="Q148">
+        <v>2.05</v>
+      </c>
+      <c r="R148">
+        <v>2.5</v>
+      </c>
+      <c r="S148">
+        <v>1.25</v>
+      </c>
+      <c r="T148">
+        <v>3.8</v>
+      </c>
+      <c r="U148">
         <v>2.36</v>
       </c>
-      <c r="Q148">
-        <v>3.35</v>
-      </c>
-      <c r="R148">
+      <c r="V148">
+        <v>1.57</v>
+      </c>
+      <c r="W148">
+        <v>1.14</v>
+      </c>
+      <c r="X148">
+        <v>1.01</v>
+      </c>
+      <c r="Y148">
+        <v>1.2</v>
+      </c>
+      <c r="Z148">
+        <v>4.5</v>
+      </c>
+      <c r="AA148">
+        <v>1.61</v>
+      </c>
+      <c r="AB148">
+        <v>2.3</v>
+      </c>
+      <c r="AC148">
+        <v>2.48</v>
+      </c>
+      <c r="AD148">
+        <v>1.5</v>
+      </c>
+      <c r="AE148">
+        <v>1.21</v>
+      </c>
+      <c r="AF148">
+        <v>1.62</v>
+      </c>
+      <c r="AG148">
+        <v>2.2</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ148">
+        <v>1.22</v>
+      </c>
+      <c r="AK148">
         <v>2.1</v>
-      </c>
-      <c r="S148">
-        <v>1.39</v>
-      </c>
-      <c r="T148">
-        <v>2.77</v>
-      </c>
-      <c r="U148">
-        <v>2.69</v>
-      </c>
-      <c r="V148">
-        <v>1.41</v>
-      </c>
-      <c r="W148">
-        <v>1.06</v>
-      </c>
-      <c r="X148">
-        <v>1.04</v>
-      </c>
-      <c r="Y148">
-        <v>1.25</v>
-      </c>
-      <c r="Z148">
-        <v>3.5</v>
-      </c>
-      <c r="AA148">
-        <v>1.9</v>
-      </c>
-      <c r="AB148">
-        <v>1.9</v>
-      </c>
-      <c r="AC148">
-        <v>2.95</v>
-      </c>
-      <c r="AD148">
-        <v>1.33</v>
-      </c>
-      <c r="AE148">
-        <v>1.08</v>
-      </c>
-      <c r="AF148">
-        <v>1.66</v>
-      </c>
-      <c r="AG148">
-        <v>2.15</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ148">
-        <v>1.49</v>
-      </c>
-      <c r="AK148">
-        <v>1.4</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,64 +24922,64 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="O151">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P151">
-        <v>4.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q151">
+        <v>3.5</v>
+      </c>
+      <c r="R151">
         <v>2.3</v>
-      </c>
-      <c r="R151">
-        <v>2.34</v>
       </c>
       <c r="S151">
         <v>1.35</v>
       </c>
       <c r="T151">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="U151">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V151">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W151">
         <v>1.07</v>
       </c>
       <c r="X151">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y151">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z151">
-        <v>3.74</v>
+        <v>4.09</v>
       </c>
       <c r="AA151">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB151">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC151">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AD151">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE151">
         <v>1.13</v>
       </c>
       <c r="AF151">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AG151">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK151">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,80 +25085,80 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.53</v>
+        <v>2.61</v>
       </c>
       <c r="O152">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="P152">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q152">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="R152">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="S152">
+        <v>1.37</v>
+      </c>
+      <c r="T152">
+        <v>2.88</v>
+      </c>
+      <c r="U152">
+        <v>2.75</v>
+      </c>
+      <c r="V152">
+        <v>1.41</v>
+      </c>
+      <c r="W152">
+        <v>1.08</v>
+      </c>
+      <c r="X152">
+        <v>1.05</v>
+      </c>
+      <c r="Y152">
+        <v>1.28</v>
+      </c>
+      <c r="Z152">
+        <v>3.3</v>
+      </c>
+      <c r="AA152">
+        <v>1.99</v>
+      </c>
+      <c r="AB152">
+        <v>1.83</v>
+      </c>
+      <c r="AC152">
+        <v>3.3</v>
+      </c>
+      <c r="AD152">
+        <v>1.3</v>
+      </c>
+      <c r="AE152">
+        <v>1.1</v>
+      </c>
+      <c r="AF152">
+        <v>1.7</v>
+      </c>
+      <c r="AG152">
+        <v>2.04</v>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ152">
         <v>1.25</v>
       </c>
-      <c r="T152">
-        <v>3.7</v>
-      </c>
-      <c r="U152">
-        <v>2.2</v>
-      </c>
-      <c r="V152">
-        <v>1.58</v>
-      </c>
-      <c r="W152">
-        <v>1.14</v>
-      </c>
-      <c r="X152">
-        <v>1.03</v>
-      </c>
-      <c r="Y152">
-        <v>1.13</v>
-      </c>
-      <c r="Z152">
-        <v>5.05</v>
-      </c>
-      <c r="AA152">
-        <v>1.5</v>
-      </c>
-      <c r="AB152">
-        <v>2.45</v>
-      </c>
-      <c r="AC152">
-        <v>2.25</v>
-      </c>
-      <c r="AD152">
-        <v>1.64</v>
-      </c>
-      <c r="AE152">
-        <v>1.26</v>
-      </c>
-      <c r="AF152">
-        <v>1.53</v>
-      </c>
-      <c r="AG152">
-        <v>2.3</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ152">
-        <v>1.17</v>
-      </c>
       <c r="AK152">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,64 +25248,64 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="O153">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P153">
-        <v>3.98</v>
+        <v>4.3</v>
       </c>
       <c r="Q153">
+        <v>2.1</v>
+      </c>
+      <c r="R153">
         <v>2.4</v>
       </c>
-      <c r="R153">
-        <v>2.31</v>
-      </c>
       <c r="S153">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T153">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="U153">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="V153">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W153">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X153">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z153">
-        <v>3.8</v>
+        <v>5.05</v>
       </c>
       <c r="AA153">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AB153">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AC153">
-        <v>2.94</v>
+        <v>2.25</v>
       </c>
       <c r="AD153">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AE153">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AF153">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG153">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK153">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O154">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P154">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="Q154">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R154">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S154">
+        <v>1.33</v>
+      </c>
+      <c r="T154">
+        <v>3.11</v>
+      </c>
+      <c r="U154">
+        <v>2.75</v>
+      </c>
+      <c r="V154">
+        <v>1.42</v>
+      </c>
+      <c r="W154">
+        <v>1.07</v>
+      </c>
+      <c r="X154">
+        <v>1.05</v>
+      </c>
+      <c r="Y154">
         <v>1.25</v>
       </c>
-      <c r="T154">
+      <c r="Z154">
         <v>3.8</v>
       </c>
-      <c r="U154">
-        <v>2.22</v>
-      </c>
-      <c r="V154">
-        <v>1.62</v>
-      </c>
-      <c r="W154">
-        <v>1.15</v>
-      </c>
-      <c r="X154">
-        <v>1.03</v>
-      </c>
-      <c r="Y154">
-        <v>1.13</v>
-      </c>
-      <c r="Z154">
-        <v>4.9</v>
-      </c>
       <c r="AA154">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="AB154">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="AC154">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="AD154">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AE154">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF154">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AG154">
-        <v>2.43</v>
+        <v>2.01</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK154">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>3</v>
+        <v>1.94</v>
       </c>
       <c r="O155">
+        <v>3.65</v>
+      </c>
+      <c r="P155">
         <v>3.4</v>
       </c>
-      <c r="P155">
-        <v>2.02</v>
-      </c>
       <c r="Q155">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R155">
+        <v>2.28</v>
+      </c>
+      <c r="S155">
+        <v>1.25</v>
+      </c>
+      <c r="T155">
+        <v>3.8</v>
+      </c>
+      <c r="U155">
+        <v>2.22</v>
+      </c>
+      <c r="V155">
+        <v>1.62</v>
+      </c>
+      <c r="W155">
+        <v>1.15</v>
+      </c>
+      <c r="X155">
+        <v>1.03</v>
+      </c>
+      <c r="Y155">
+        <v>1.13</v>
+      </c>
+      <c r="Z155">
+        <v>4.9</v>
+      </c>
+      <c r="AA155">
+        <v>1.51</v>
+      </c>
+      <c r="AB155">
+        <v>2.44</v>
+      </c>
+      <c r="AC155">
         <v>2.3</v>
       </c>
-      <c r="S155">
-        <v>1.35</v>
-      </c>
-      <c r="T155">
-        <v>2.86</v>
-      </c>
-      <c r="U155">
-        <v>2.44</v>
-      </c>
-      <c r="V155">
+      <c r="AD155">
+        <v>1.55</v>
+      </c>
+      <c r="AE155">
+        <v>1.22</v>
+      </c>
+      <c r="AF155">
         <v>1.47</v>
       </c>
-      <c r="W155">
-        <v>1.07</v>
-      </c>
-      <c r="X155">
-        <v>1.02</v>
-      </c>
-      <c r="Y155">
-        <v>1.23</v>
-      </c>
-      <c r="Z155">
-        <v>4.09</v>
-      </c>
-      <c r="AA155">
-        <v>1.67</v>
-      </c>
-      <c r="AB155">
-        <v>2.15</v>
-      </c>
-      <c r="AC155">
-        <v>2.88</v>
-      </c>
-      <c r="AD155">
-        <v>1.4</v>
-      </c>
-      <c r="AE155">
-        <v>1.13</v>
-      </c>
-      <c r="AF155">
-        <v>1.61</v>
-      </c>
       <c r="AG155">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK155">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.61</v>
+        <v>1.8</v>
       </c>
       <c r="O157">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P157">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q157">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R157">
-        <v>2.07</v>
+        <v>2.34</v>
       </c>
       <c r="S157">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T157">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U157">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="V157">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W157">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X157">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z157">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA157">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="AB157">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AC157">
-        <v>3.3</v>
+        <v>2.64</v>
       </c>
       <c r="AD157">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE157">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF157">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG157">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK157">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q205">
-        <v>3.86</v>
+        <v>3.01</v>
       </c>
       <c r="R205">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="S205">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T205">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U205">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V205">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W205">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X205">
         <v>1.04</v>
       </c>
       <c r="Y205">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Z205">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="AA205">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AB205">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC205">
-        <v>3.74</v>
+        <v>4.15</v>
       </c>
       <c r="AD205">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE205">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF205">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG205">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AK205">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O206">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P206">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q206">
-        <v>3.01</v>
+        <v>3.86</v>
       </c>
       <c r="R206">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="S206">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T206">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U206">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="V206">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W206">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X206">
         <v>1.04</v>
       </c>
       <c r="Y206">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="Z206">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AA206">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB206">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC206">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="AD206">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE206">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF206">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG206">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AK206">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="O235">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P235">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="Q235">
-        <v>3.47</v>
+        <v>2.7</v>
       </c>
       <c r="R235">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="S235">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T235">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="U235">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="V235">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W235">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X235">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y235">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z235">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="AA235">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AB235">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC235">
-        <v>2.63</v>
+        <v>3.18</v>
       </c>
       <c r="AD235">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AE235">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF235">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AG235">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK235">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,80 +38777,80 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="O236">
+        <v>3.7</v>
+      </c>
+      <c r="P236">
+        <v>2</v>
+      </c>
+      <c r="Q236">
+        <v>3.47</v>
+      </c>
+      <c r="R236">
+        <v>2.19</v>
+      </c>
+      <c r="S236">
+        <v>1.3</v>
+      </c>
+      <c r="T236">
         <v>3.3</v>
       </c>
-      <c r="P236">
-        <v>3.2</v>
-      </c>
-      <c r="Q236">
-        <v>2.7</v>
-      </c>
-      <c r="R236">
-        <v>2.06</v>
-      </c>
-      <c r="S236">
-        <v>1.41</v>
-      </c>
-      <c r="T236">
+      <c r="U236">
+        <v>2.41</v>
+      </c>
+      <c r="V236">
+        <v>1.51</v>
+      </c>
+      <c r="W236">
+        <v>1.1</v>
+      </c>
+      <c r="X236">
+        <v>1.04</v>
+      </c>
+      <c r="Y236">
+        <v>1.2</v>
+      </c>
+      <c r="Z236">
+        <v>4.4</v>
+      </c>
+      <c r="AA236">
+        <v>1.66</v>
+      </c>
+      <c r="AB236">
+        <v>2.1</v>
+      </c>
+      <c r="AC236">
         <v>2.63</v>
       </c>
-      <c r="U236">
-        <v>2.7</v>
-      </c>
-      <c r="V236">
-        <v>1.41</v>
-      </c>
-      <c r="W236">
-        <v>1.07</v>
-      </c>
-      <c r="X236">
-        <v>1.03</v>
-      </c>
-      <c r="Y236">
+      <c r="AD236">
+        <v>1.48</v>
+      </c>
+      <c r="AE236">
+        <v>1.14</v>
+      </c>
+      <c r="AF236">
+        <v>1.56</v>
+      </c>
+      <c r="AG236">
+        <v>2.24</v>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ236">
+        <v>1.3</v>
+      </c>
+      <c r="AK236">
         <v>1.29</v>
-      </c>
-      <c r="Z236">
-        <v>3</v>
-      </c>
-      <c r="AA236">
-        <v>1.95</v>
-      </c>
-      <c r="AB236">
-        <v>1.85</v>
-      </c>
-      <c r="AC236">
-        <v>3.18</v>
-      </c>
-      <c r="AD236">
-        <v>1.21</v>
-      </c>
-      <c r="AE236">
-        <v>1.07</v>
-      </c>
-      <c r="AF236">
-        <v>1.74</v>
-      </c>
-      <c r="AG236">
-        <v>1.98</v>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ236">
-        <v>1.25</v>
-      </c>
-      <c r="AK236">
-        <v>1.62</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,80 +45786,80 @@
         </is>
       </c>
       <c r="N279">
+        <v>2.57</v>
+      </c>
+      <c r="O279">
+        <v>3.55</v>
+      </c>
+      <c r="P279">
+        <v>2.44</v>
+      </c>
+      <c r="Q279">
+        <v>3.2</v>
+      </c>
+      <c r="R279">
         <v>2.3</v>
       </c>
-      <c r="O279">
-        <v>3.3</v>
-      </c>
-      <c r="P279">
-        <v>3.1</v>
-      </c>
-      <c r="Q279">
-        <v>2.76</v>
-      </c>
-      <c r="R279">
-        <v>2.02</v>
-      </c>
       <c r="S279">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T279">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U279">
-        <v>3.08</v>
+        <v>2.49</v>
       </c>
       <c r="V279">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="W279">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X279">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y279">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z279">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="AA279">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AB279">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC279">
-        <v>3.48</v>
+        <v>2.7</v>
       </c>
       <c r="AD279">
+        <v>1.49</v>
+      </c>
+      <c r="AE279">
+        <v>1.18</v>
+      </c>
+      <c r="AF279">
+        <v>1.6</v>
+      </c>
+      <c r="AG279">
+        <v>2.38</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ279">
         <v>1.25</v>
       </c>
-      <c r="AE279">
-        <v>1.07</v>
-      </c>
-      <c r="AF279">
-        <v>1.85</v>
-      </c>
-      <c r="AG279">
-        <v>1.93</v>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ279">
-        <v>1.35</v>
-      </c>
       <c r="AK279">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="O280">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P280">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="Q280">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="R280">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="S280">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="T280">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U280">
-        <v>2.49</v>
+        <v>3.08</v>
       </c>
       <c r="V280">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="W280">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X280">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y280">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z280">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA280">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AB280">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC280">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD280">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AE280">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF280">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG280">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK280">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -51980,13 +51980,13 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O317">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="P317">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q317">
         <v>0</v>
@@ -52019,10 +52019,10 @@
         <v>0</v>
       </c>
       <c r="AA317">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB317">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC317">
         <v>0</v>
@@ -52469,25 +52469,25 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O320">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P320">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q320">
         <v>2.15</v>
       </c>
       <c r="R320">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="S320">
         <v>1.18</v>
       </c>
       <c r="T320">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U320">
         <v>2</v>
@@ -52508,22 +52508,22 @@
         <v>7.5</v>
       </c>
       <c r="AA320">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB320">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC320">
         <v>1.92</v>
       </c>
       <c r="AD320">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AE320">
         <v>1.36</v>
       </c>
       <c r="AF320">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG320">
         <v>2.9</v>
@@ -52539,7 +52539,7 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK320">
         <v>1.85</v>
@@ -52635,28 +52635,28 @@
         <v>1.84</v>
       </c>
       <c r="O321">
-        <v>3.95</v>
+        <v>4.12</v>
       </c>
       <c r="P321">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q321">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="R321">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S321">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T321">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U321">
         <v>1.97</v>
       </c>
       <c r="V321">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W321">
         <v>1.18</v>
@@ -52665,31 +52665,31 @@
         <v>1.01</v>
       </c>
       <c r="Y321">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z321">
-        <v>5.65</v>
+        <v>6.28</v>
       </c>
       <c r="AA321">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB321">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AC321">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AD321">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE321">
         <v>1.34</v>
       </c>
       <c r="AF321">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG321">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O322">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="P322">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q322">
         <v>2.55</v>
@@ -52819,7 +52819,7 @@
         <v>2.33</v>
       </c>
       <c r="V322">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W322">
         <v>1.12</v>
@@ -52834,13 +52834,13 @@
         <v>4.5</v>
       </c>
       <c r="AA322">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB322">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC322">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="AD322">
         <v>1.5</v>
@@ -52849,10 +52849,10 @@
         <v>1.17</v>
       </c>
       <c r="AF322">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AG322">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O323">
         <v>3.75</v>
@@ -52967,10 +52967,10 @@
         <v>3.2</v>
       </c>
       <c r="Q323">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="R323">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="S323">
         <v>1.18</v>
@@ -52979,10 +52979,10 @@
         <v>4.05</v>
       </c>
       <c r="U323">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V323">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="W323">
         <v>1.22</v>
@@ -52997,16 +52997,16 @@
         <v>6.62</v>
       </c>
       <c r="AA323">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB323">
         <v>2.85</v>
       </c>
       <c r="AC323">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AD323">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AE323">
         <v>1.31</v>
@@ -53015,7 +53015,7 @@
         <v>1.33</v>
       </c>
       <c r="AG323">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK323">
         <v>1.86</v>
@@ -53121,10 +53121,10 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O324">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P324">
         <v>3.7</v>
@@ -53139,13 +53139,13 @@
         <v>1.22</v>
       </c>
       <c r="T324">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="U324">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V324">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="W324">
         <v>1.18</v>
@@ -53157,19 +53157,19 @@
         <v>1.12</v>
       </c>
       <c r="Z324">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
       <c r="AA324">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB324">
         <v>2.8</v>
       </c>
       <c r="AC324">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AD324">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE324">
         <v>1.29</v>
@@ -53178,7 +53178,7 @@
         <v>1.4</v>
       </c>
       <c r="AG324">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>1.2</v>
       </c>
       <c r="AK324">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53773,19 +53773,19 @@
         </is>
       </c>
       <c r="N328">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="O328">
-        <v>3.9</v>
+        <v>4.26</v>
       </c>
       <c r="P328">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q328">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R328">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S328">
         <v>1.2</v>
@@ -53794,10 +53794,10 @@
         <v>4.33</v>
       </c>
       <c r="U328">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="V328">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W328">
         <v>1.18</v>
@@ -53806,10 +53806,10 @@
         <v>1.01</v>
       </c>
       <c r="Y328">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z328">
-        <v>6.43</v>
+        <v>6.56</v>
       </c>
       <c r="AA328">
         <v>1.4</v>
@@ -53818,10 +53818,10 @@
         <v>2.85</v>
       </c>
       <c r="AC328">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD328">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AE328">
         <v>1.33</v>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK328">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="O329">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="P329">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q329">
         <v>2.45</v>
@@ -53951,7 +53951,7 @@
         <v>2.45</v>
       </c>
       <c r="S329">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T329">
         <v>3.8</v>
@@ -53960,22 +53960,22 @@
         <v>2.17</v>
       </c>
       <c r="V329">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W329">
         <v>1.13</v>
       </c>
       <c r="X329">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y329">
         <v>1.17</v>
       </c>
       <c r="Z329">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA329">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB329">
         <v>2.35</v>
@@ -53987,10 +53987,10 @@
         <v>1.5</v>
       </c>
       <c r="AE329">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF329">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG329">
         <v>2.5</v>
@@ -54006,7 +54006,7 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK329">
         <v>1.66</v>
@@ -54105,25 +54105,25 @@
         <v>4</v>
       </c>
       <c r="P330">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q330">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="R330">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="S330">
         <v>1.22</v>
       </c>
       <c r="T330">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="U330">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V330">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W330">
         <v>1.18</v>
@@ -54132,10 +54132,10 @@
         <v>1.03</v>
       </c>
       <c r="Y330">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z330">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA330">
         <v>1.5</v>
@@ -54147,13 +54147,13 @@
         <v>2.2</v>
       </c>
       <c r="AD330">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE330">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF330">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG330">
         <v>2.45</v>
@@ -54169,7 +54169,7 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>1.22</v>
+        <v>2.22</v>
       </c>
       <c r="AK330">
         <v>1.18</v>
@@ -54425,31 +54425,31 @@
         </is>
       </c>
       <c r="N332">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="O332">
         <v>3.4</v>
       </c>
       <c r="P332">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="Q332">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="R332">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="S332">
         <v>1.25</v>
       </c>
       <c r="T332">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U332">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="V332">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W332">
         <v>1.11</v>
@@ -54464,16 +54464,16 @@
         <v>4.4</v>
       </c>
       <c r="AA332">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB332">
         <v>2.2</v>
       </c>
       <c r="AC332">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AD332">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE332">
         <v>1.2</v>
@@ -54498,7 +54498,7 @@
         <v>1.22</v>
       </c>
       <c r="AK332">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL332">
         <v>0</v>
@@ -54588,16 +54588,16 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O333">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="P333">
         <v>4.2</v>
       </c>
       <c r="Q333">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="R333">
         <v>2.35</v>
@@ -54612,7 +54612,7 @@
         <v>2.38</v>
       </c>
       <c r="V333">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W333">
         <v>1.11</v>
@@ -55430,7 +55430,7 @@
         <v>1.6</v>
       </c>
       <c r="W338">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X338">
         <v>1.03</v>
@@ -55451,7 +55451,7 @@
         <v>2.37</v>
       </c>
       <c r="AD338">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE338">
         <v>1.21</v>
@@ -55473,10 +55473,10 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK338">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55572,10 +55572,10 @@
         <v>3.4</v>
       </c>
       <c r="P339">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q339">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="R339">
         <v>2.18</v>
@@ -55587,7 +55587,7 @@
         <v>3.45</v>
       </c>
       <c r="U339">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="V339">
         <v>1.5</v>
@@ -55596,25 +55596,25 @@
         <v>1.12</v>
       </c>
       <c r="X339">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y339">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z339">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA339">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB339">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC339">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD339">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AE339">
         <v>1.18</v>
@@ -55636,7 +55636,7 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK339">
         <v>1.5</v>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -1453,7 +1453,7 @@
         <v>2.2</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
         <v>2.95</v>
@@ -1622,10 +1622,10 @@
         <v>2.2</v>
       </c>
       <c r="Q8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
         <v>1.35</v>
@@ -1640,7 +1640,7 @@
         <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.03</v>
@@ -1664,7 +1664,7 @@
         <v>1.3</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
         <v>1.67</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="O12">
         <v>3.4</v>
@@ -2277,13 +2277,13 @@
         <v>3.86</v>
       </c>
       <c r="R12">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="S12">
         <v>1.28</v>
       </c>
       <c r="T12">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
         <v>2.25</v>
@@ -2292,7 +2292,7 @@
         <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,28 +2301,28 @@
         <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA12">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB12">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AC12">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AD12">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE12">
         <v>1.17</v>
       </c>
       <c r="AF12">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2760,13 +2760,13 @@
         <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q15">
         <v>3.35</v>
       </c>
       <c r="R15">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S15">
         <v>1.45</v>
@@ -2793,16 +2793,16 @@
         <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="AB15">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE15">
         <v>1.04</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O25">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q25">
         <v>4</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
         <v>1.29</v>
@@ -4432,10 +4432,10 @@
         <v>2.72</v>
       </c>
       <c r="AD25">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
         <v>1.67</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="O26">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>2.05</v>
+        <v>3.99</v>
       </c>
       <c r="Q26">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="U26">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="V26">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="AD26">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.34</v>
+        <v>1.95</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="O27">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P27">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q27">
+        <v>2.07</v>
+      </c>
+      <c r="R27">
+        <v>2.5</v>
+      </c>
+      <c r="S27">
+        <v>1.22</v>
+      </c>
+      <c r="T27">
+        <v>3.55</v>
+      </c>
+      <c r="U27">
+        <v>2.2</v>
+      </c>
+      <c r="V27">
+        <v>1.6</v>
+      </c>
+      <c r="W27">
+        <v>1.12</v>
+      </c>
+      <c r="X27">
+        <v>1.03</v>
+      </c>
+      <c r="Y27">
+        <v>1.1</v>
+      </c>
+      <c r="Z27">
+        <v>5.4</v>
+      </c>
+      <c r="AA27">
+        <v>1.44</v>
+      </c>
+      <c r="AB27">
+        <v>2.44</v>
+      </c>
+      <c r="AC27">
         <v>2.25</v>
       </c>
-      <c r="R27">
-        <v>2.17</v>
-      </c>
-      <c r="S27">
-        <v>1.35</v>
-      </c>
-      <c r="T27">
-        <v>3.13</v>
-      </c>
-      <c r="U27">
-        <v>2.65</v>
-      </c>
-      <c r="V27">
-        <v>1.42</v>
-      </c>
-      <c r="W27">
-        <v>1.07</v>
-      </c>
-      <c r="X27">
-        <v>1.04</v>
-      </c>
-      <c r="Y27">
-        <v>1.25</v>
-      </c>
-      <c r="Z27">
-        <v>3.6</v>
-      </c>
-      <c r="AA27">
-        <v>1.85</v>
-      </c>
-      <c r="AB27">
-        <v>1.95</v>
-      </c>
-      <c r="AC27">
-        <v>2.94</v>
-      </c>
       <c r="AD27">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK27">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,61 +4873,61 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q28">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="R28">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="U28">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V28">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W28">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="AC28">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AD28">
+        <v>1.43</v>
+      </c>
+      <c r="AE28">
+        <v>1.14</v>
+      </c>
+      <c r="AF28">
         <v>1.62</v>
-      </c>
-      <c r="AE28">
-        <v>1.22</v>
-      </c>
-      <c r="AF28">
-        <v>1.57</v>
       </c>
       <c r="AG28">
         <v>2.3</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="AK28">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5358,17 +5358,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q31">
         <v>2.38</v>
@@ -5377,7 +5377,7 @@
         <v>2.1</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
         <v>3</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.86</v>
+        <v>2.7</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="Q33">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U33">
         <v>2.25</v>
@@ -5715,37 +5715,37 @@
         <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="AA33">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC33">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AD33">
+        <v>1.55</v>
+      </c>
+      <c r="AE33">
+        <v>1.15</v>
+      </c>
+      <c r="AF33">
         <v>1.46</v>
       </c>
-      <c r="AE33">
-        <v>1.21</v>
-      </c>
-      <c r="AF33">
-        <v>1.53</v>
-      </c>
       <c r="AG33">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T34">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
         <v>2.25</v>
@@ -5878,37 +5878,37 @@
         <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
         <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB34">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC34">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AD34">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF34">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="P48">
-        <v>4.05</v>
+        <v>6.18</v>
       </c>
       <c r="Q48">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="R48">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="T48">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="V48">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AB48">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>3.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD48">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE48">
+        <v>1.16</v>
+      </c>
+      <c r="AF48">
+        <v>1.7</v>
+      </c>
+      <c r="AG48">
+        <v>1.99</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.06</v>
       </c>
-      <c r="AF48">
-        <v>1.76</v>
-      </c>
-      <c r="AG48">
-        <v>1.88</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.21</v>
-      </c>
       <c r="AK48">
-        <v>1.94</v>
+        <v>2.49</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="O49">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="P49">
-        <v>6.18</v>
+        <v>4.05</v>
       </c>
       <c r="Q49">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="S49">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="U49">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AA49">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AB49">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AC49">
-        <v>2.33</v>
+        <v>3.08</v>
       </c>
       <c r="AD49">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE49">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF49">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG49">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>2.49</v>
+        <v>1.94</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8944,17 +8944,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q53">
         <v>2.93</v>
@@ -8990,7 +8990,7 @@
         <v>1.61</v>
       </c>
       <c r="AB53">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AC53">
         <v>2.45</v>
@@ -8999,7 +8999,7 @@
         <v>1.52</v>
       </c>
       <c r="AE53">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF53">
         <v>1.51</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK69">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="O110">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P110">
-        <v>2.67</v>
+        <v>1.67</v>
       </c>
       <c r="Q110">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="R110">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S110">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T110">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U110">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="V110">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="W110">
         <v>1.2</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z110">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="AA110">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB110">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AC110">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AD110">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AE110">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AF110">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG110">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK110">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,34 +18565,34 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.23</v>
+        <v>2.35</v>
       </c>
       <c r="O112">
-        <v>6.75</v>
+        <v>4.1</v>
       </c>
       <c r="P112">
-        <v>10.66</v>
+        <v>2.67</v>
       </c>
       <c r="Q112">
-        <v>1.59</v>
+        <v>2.7</v>
       </c>
       <c r="R112">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="S112">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T112">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U112">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V112">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="W112">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X112">
         <v>1.01</v>
@@ -18601,28 +18601,28 @@
         <v>1.05</v>
       </c>
       <c r="Z112">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="AA112">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB112">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AC112">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AD112">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE112">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AF112">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AG112">
-        <v>1.97</v>
+        <v>3.3</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK112">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>4</v>
+        <v>1.23</v>
       </c>
       <c r="O113">
-        <v>4.05</v>
+        <v>6.75</v>
       </c>
       <c r="P113">
-        <v>1.67</v>
+        <v>10.66</v>
       </c>
       <c r="Q113">
-        <v>4</v>
+        <v>1.59</v>
       </c>
       <c r="R113">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S113">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T113">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U113">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="V113">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W113">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z113">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA113">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB113">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="AC113">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AD113">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE113">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF113">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG113">
-        <v>2.77</v>
+        <v>1.97</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AK113">
-        <v>1.25</v>
+        <v>3.9</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="O117">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P117">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="Q117">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="R117">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T117">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U117">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V117">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W117">
+        <v>1.09</v>
+      </c>
+      <c r="X117">
+        <v>1.02</v>
+      </c>
+      <c r="Y117">
+        <v>1.22</v>
+      </c>
+      <c r="Z117">
+        <v>3.8</v>
+      </c>
+      <c r="AA117">
+        <v>1.8</v>
+      </c>
+      <c r="AB117">
+        <v>2</v>
+      </c>
+      <c r="AC117">
+        <v>3</v>
+      </c>
+      <c r="AD117">
+        <v>1.36</v>
+      </c>
+      <c r="AE117">
         <v>1.11</v>
       </c>
-      <c r="X117">
-        <v>1.03</v>
-      </c>
-      <c r="Y117">
-        <v>1.18</v>
-      </c>
-      <c r="Z117">
-        <v>4.5</v>
-      </c>
-      <c r="AA117">
-        <v>1.61</v>
-      </c>
-      <c r="AB117">
-        <v>2.21</v>
-      </c>
-      <c r="AC117">
-        <v>2.63</v>
-      </c>
-      <c r="AD117">
-        <v>1.44</v>
-      </c>
-      <c r="AE117">
-        <v>1.18</v>
-      </c>
       <c r="AF117">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AG117">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK117">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="O118">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P118">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q118">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="R118">
+        <v>2.24</v>
+      </c>
+      <c r="S118">
+        <v>1.28</v>
+      </c>
+      <c r="T118">
+        <v>3.5</v>
+      </c>
+      <c r="U118">
         <v>2.3</v>
       </c>
-      <c r="S118">
-        <v>1.35</v>
-      </c>
-      <c r="T118">
-        <v>3.1</v>
-      </c>
-      <c r="U118">
-        <v>2.6</v>
-      </c>
       <c r="V118">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W118">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y118">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z118">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA118">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB118">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AC118">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD118">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE118">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF118">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AG118">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK118">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="O132">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="P132">
-        <v>4.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q132">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="R132">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="S132">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="T132">
+        <v>2.72</v>
+      </c>
+      <c r="U132">
+        <v>2.59</v>
+      </c>
+      <c r="V132">
+        <v>1.41</v>
+      </c>
+      <c r="W132">
+        <v>1.07</v>
+      </c>
+      <c r="X132">
+        <v>1</v>
+      </c>
+      <c r="Y132">
+        <v>1.24</v>
+      </c>
+      <c r="Z132">
         <v>3.5</v>
       </c>
-      <c r="U132">
-        <v>2.25</v>
-      </c>
-      <c r="V132">
-        <v>1.55</v>
-      </c>
-      <c r="W132">
-        <v>1.12</v>
-      </c>
-      <c r="X132">
-        <v>1.02</v>
-      </c>
-      <c r="Y132">
-        <v>1.2</v>
-      </c>
-      <c r="Z132">
-        <v>4.33</v>
-      </c>
       <c r="AA132">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AB132">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="AC132">
-        <v>2.54</v>
+        <v>3.4</v>
       </c>
       <c r="AD132">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AE132">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AF132">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG132">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
+        <v>2.58</v>
+      </c>
+      <c r="O133">
+        <v>3.2</v>
+      </c>
+      <c r="P133">
+        <v>2.5</v>
+      </c>
+      <c r="Q133">
+        <v>3</v>
+      </c>
+      <c r="R133">
         <v>2.1</v>
       </c>
-      <c r="O133">
-        <v>3.4</v>
-      </c>
-      <c r="P133">
-        <v>3.14</v>
-      </c>
-      <c r="Q133">
-        <v>2.7</v>
-      </c>
-      <c r="R133">
-        <v>2.23</v>
-      </c>
       <c r="S133">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T133">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="U133">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="V133">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W133">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X133">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y133">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z133">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AA133">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB133">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC133">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD133">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE133">
         <v>1.08</v>
       </c>
       <c r="AF133">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG133">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK133">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,80 +22151,80 @@
         </is>
       </c>
       <c r="N134">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O134">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P134">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q134">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R134">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S134">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="T134">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="U134">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="V134">
+        <v>1.3</v>
+      </c>
+      <c r="W134">
+        <v>1.04</v>
+      </c>
+      <c r="X134">
+        <v>1.02</v>
+      </c>
+      <c r="Y134">
+        <v>1.36</v>
+      </c>
+      <c r="Z134">
+        <v>2.7</v>
+      </c>
+      <c r="AA134">
+        <v>2.17</v>
+      </c>
+      <c r="AB134">
+        <v>1.59</v>
+      </c>
+      <c r="AC134">
+        <v>4.2</v>
+      </c>
+      <c r="AD134">
+        <v>1.2</v>
+      </c>
+      <c r="AE134">
+        <v>1.06</v>
+      </c>
+      <c r="AF134">
+        <v>1.9</v>
+      </c>
+      <c r="AG134">
+        <v>1.91</v>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ134">
+        <v>1.33</v>
+      </c>
+      <c r="AK134">
         <v>1.44</v>
-      </c>
-      <c r="W134">
-        <v>1.1</v>
-      </c>
-      <c r="X134">
-        <v>1.05</v>
-      </c>
-      <c r="Y134">
-        <v>1.22</v>
-      </c>
-      <c r="Z134">
-        <v>3.5</v>
-      </c>
-      <c r="AA134">
-        <v>1.85</v>
-      </c>
-      <c r="AB134">
-        <v>1.9</v>
-      </c>
-      <c r="AC134">
-        <v>3.2</v>
-      </c>
-      <c r="AD134">
-        <v>1.33</v>
-      </c>
-      <c r="AE134">
-        <v>1.07</v>
-      </c>
-      <c r="AF134">
-        <v>1.67</v>
-      </c>
-      <c r="AG134">
-        <v>2</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>1.59</v>
-      </c>
-      <c r="AK134">
-        <v>1.29</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,80 +22314,80 @@
         </is>
       </c>
       <c r="N135">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="O135">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P135">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q135">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="R135">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S135">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="T135">
-        <v>2.5</v>
+        <v>3.07</v>
       </c>
       <c r="U135">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="V135">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W135">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y135">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z135">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA135">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB135">
+        <v>1.9</v>
+      </c>
+      <c r="AC135">
+        <v>3.2</v>
+      </c>
+      <c r="AD135">
+        <v>1.33</v>
+      </c>
+      <c r="AE135">
+        <v>1.07</v>
+      </c>
+      <c r="AF135">
+        <v>1.67</v>
+      </c>
+      <c r="AG135">
+        <v>2</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
         <v>1.59</v>
       </c>
-      <c r="AC135">
-        <v>4.2</v>
-      </c>
-      <c r="AD135">
-        <v>1.2</v>
-      </c>
-      <c r="AE135">
-        <v>1.06</v>
-      </c>
-      <c r="AF135">
-        <v>1.9</v>
-      </c>
-      <c r="AG135">
-        <v>1.91</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>1.33</v>
-      </c>
       <c r="AK135">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O136">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P136">
+        <v>3.14</v>
+      </c>
+      <c r="Q136">
+        <v>2.7</v>
+      </c>
+      <c r="R136">
+        <v>2.23</v>
+      </c>
+      <c r="S136">
+        <v>1.32</v>
+      </c>
+      <c r="T136">
         <v>3.05</v>
       </c>
-      <c r="Q136">
-        <v>2.74</v>
-      </c>
-      <c r="R136">
-        <v>2.05</v>
-      </c>
-      <c r="S136">
-        <v>1.38</v>
-      </c>
-      <c r="T136">
-        <v>2.72</v>
-      </c>
       <c r="U136">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V136">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X136">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y136">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z136">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA136">
+        <v>1.87</v>
+      </c>
+      <c r="AB136">
         <v>1.93</v>
       </c>
-      <c r="AB136">
-        <v>1.84</v>
-      </c>
       <c r="AC136">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD136">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AE136">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF136">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG136">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.58</v>
+        <v>1.57</v>
       </c>
       <c r="O137">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="P137">
-        <v>2.5</v>
+        <v>4.15</v>
       </c>
       <c r="Q137">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="R137">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S137">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="T137">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U137">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="V137">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="Z137">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AA137">
-        <v>2.03</v>
+        <v>1.58</v>
       </c>
       <c r="AB137">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AC137">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="AD137">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AE137">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AF137">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG137">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK137">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,65 +25248,65 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.82</v>
+        <v>3.42</v>
       </c>
       <c r="O153">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="P153">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q153">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="R153">
+        <v>2.3</v>
+      </c>
+      <c r="S153">
+        <v>1.32</v>
+      </c>
+      <c r="T153">
+        <v>2.86</v>
+      </c>
+      <c r="U153">
+        <v>2.6</v>
+      </c>
+      <c r="V153">
+        <v>1.47</v>
+      </c>
+      <c r="W153">
+        <v>1.07</v>
+      </c>
+      <c r="X153">
+        <v>1.02</v>
+      </c>
+      <c r="Y153">
+        <v>1.19</v>
+      </c>
+      <c r="Z153">
+        <v>3.82</v>
+      </c>
+      <c r="AA153">
+        <v>1.67</v>
+      </c>
+      <c r="AB153">
+        <v>2.15</v>
+      </c>
+      <c r="AC153">
+        <v>2.71</v>
+      </c>
+      <c r="AD153">
+        <v>1.4</v>
+      </c>
+      <c r="AE153">
+        <v>1.13</v>
+      </c>
+      <c r="AF153">
+        <v>1.62</v>
+      </c>
+      <c r="AG153">
         <v>2.2</v>
       </c>
-      <c r="S153">
-        <v>1.33</v>
-      </c>
-      <c r="T153">
-        <v>2.89</v>
-      </c>
-      <c r="U153">
-        <v>2.75</v>
-      </c>
-      <c r="V153">
-        <v>1.43</v>
-      </c>
-      <c r="W153">
-        <v>1.1</v>
-      </c>
-      <c r="X153">
-        <v>1.05</v>
-      </c>
-      <c r="Y153">
-        <v>1.27</v>
-      </c>
-      <c r="Z153">
-        <v>3.25</v>
-      </c>
-      <c r="AA153">
-        <v>1.84</v>
-      </c>
-      <c r="AB153">
-        <v>1.93</v>
-      </c>
-      <c r="AC153">
-        <v>2.94</v>
-      </c>
-      <c r="AD153">
-        <v>1.31</v>
-      </c>
-      <c r="AE153">
-        <v>1.11</v>
-      </c>
-      <c r="AF153">
-        <v>1.73</v>
-      </c>
-      <c r="AG153">
-        <v>2.01</v>
-      </c>
       <c r="AH153" t="inlineStr">
         <is>
           <t>[]</t>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AK153">
-        <v>1.92</v>
+        <v>1.29</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,80 +25411,80 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.53</v>
+        <v>1.82</v>
       </c>
       <c r="O154">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P154">
-        <v>2.52</v>
+        <v>3.75</v>
       </c>
       <c r="Q154">
-        <v>2.99</v>
+        <v>2.36</v>
       </c>
       <c r="R154">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="S154">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T154">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U154">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V154">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W154">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X154">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z154">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA154">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB154">
+        <v>2.15</v>
+      </c>
+      <c r="AC154">
+        <v>2.65</v>
+      </c>
+      <c r="AD154">
+        <v>1.44</v>
+      </c>
+      <c r="AE154">
+        <v>1.13</v>
+      </c>
+      <c r="AF154">
+        <v>1.6</v>
+      </c>
+      <c r="AG154">
+        <v>2.25</v>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ154">
+        <v>1.22</v>
+      </c>
+      <c r="AK154">
         <v>1.83</v>
-      </c>
-      <c r="AC154">
-        <v>3.3</v>
-      </c>
-      <c r="AD154">
-        <v>1.3</v>
-      </c>
-      <c r="AE154">
-        <v>1.1</v>
-      </c>
-      <c r="AF154">
-        <v>1.7</v>
-      </c>
-      <c r="AG154">
-        <v>2.05</v>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ154">
-        <v>1.25</v>
-      </c>
-      <c r="AK154">
-        <v>1.46</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,65 +25574,65 @@
         </is>
       </c>
       <c r="N155">
-        <v>3.42</v>
+        <v>1.61</v>
       </c>
       <c r="O155">
-        <v>3.48</v>
+        <v>3.95</v>
       </c>
       <c r="P155">
-        <v>2.05</v>
+        <v>4.25</v>
       </c>
       <c r="Q155">
+        <v>2.1</v>
+      </c>
+      <c r="R155">
+        <v>2.4</v>
+      </c>
+      <c r="S155">
+        <v>1.25</v>
+      </c>
+      <c r="T155">
         <v>3.5</v>
       </c>
-      <c r="R155">
+      <c r="U155">
+        <v>2.15</v>
+      </c>
+      <c r="V155">
+        <v>1.61</v>
+      </c>
+      <c r="W155">
+        <v>1.14</v>
+      </c>
+      <c r="X155">
+        <v>1.03</v>
+      </c>
+      <c r="Y155">
+        <v>1.13</v>
+      </c>
+      <c r="Z155">
+        <v>5.5</v>
+      </c>
+      <c r="AA155">
+        <v>1.5</v>
+      </c>
+      <c r="AB155">
+        <v>2.55</v>
+      </c>
+      <c r="AC155">
+        <v>2.25</v>
+      </c>
+      <c r="AD155">
+        <v>1.62</v>
+      </c>
+      <c r="AE155">
+        <v>1.22</v>
+      </c>
+      <c r="AF155">
+        <v>1.53</v>
+      </c>
+      <c r="AG155">
         <v>2.3</v>
       </c>
-      <c r="S155">
-        <v>1.32</v>
-      </c>
-      <c r="T155">
-        <v>2.86</v>
-      </c>
-      <c r="U155">
-        <v>2.6</v>
-      </c>
-      <c r="V155">
-        <v>1.47</v>
-      </c>
-      <c r="W155">
-        <v>1.07</v>
-      </c>
-      <c r="X155">
-        <v>1.02</v>
-      </c>
-      <c r="Y155">
-        <v>1.19</v>
-      </c>
-      <c r="Z155">
-        <v>3.82</v>
-      </c>
-      <c r="AA155">
-        <v>1.67</v>
-      </c>
-      <c r="AB155">
-        <v>2.15</v>
-      </c>
-      <c r="AC155">
-        <v>2.71</v>
-      </c>
-      <c r="AD155">
-        <v>1.4</v>
-      </c>
-      <c r="AE155">
-        <v>1.13</v>
-      </c>
-      <c r="AF155">
-        <v>1.62</v>
-      </c>
-      <c r="AG155">
-        <v>2.2</v>
-      </c>
       <c r="AH155" t="inlineStr">
         <is>
           <t>[]</t>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="AK155">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G156">
@@ -25740,61 +25740,61 @@
         <v>1.82</v>
       </c>
       <c r="O156">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P156">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q156">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R156">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S156">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T156">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U156">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="V156">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W156">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y156">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z156">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AA156">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AB156">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AC156">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="AD156">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AE156">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF156">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG156">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.22</v>
       </c>
       <c r="AK156">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.61</v>
+        <v>2.53</v>
       </c>
       <c r="O157">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="P157">
-        <v>4.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q157">
-        <v>2.1</v>
+        <v>2.99</v>
       </c>
       <c r="R157">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="S157">
+        <v>1.37</v>
+      </c>
+      <c r="T157">
+        <v>2.88</v>
+      </c>
+      <c r="U157">
+        <v>2.75</v>
+      </c>
+      <c r="V157">
+        <v>1.42</v>
+      </c>
+      <c r="W157">
+        <v>1.06</v>
+      </c>
+      <c r="X157">
+        <v>1.05</v>
+      </c>
+      <c r="Y157">
+        <v>1.28</v>
+      </c>
+      <c r="Z157">
+        <v>3.3</v>
+      </c>
+      <c r="AA157">
+        <v>2</v>
+      </c>
+      <c r="AB157">
+        <v>1.83</v>
+      </c>
+      <c r="AC157">
+        <v>3.3</v>
+      </c>
+      <c r="AD157">
+        <v>1.3</v>
+      </c>
+      <c r="AE157">
+        <v>1.1</v>
+      </c>
+      <c r="AF157">
+        <v>1.7</v>
+      </c>
+      <c r="AG157">
+        <v>2.05</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>1.25</v>
       </c>
-      <c r="T157">
-        <v>3.5</v>
-      </c>
-      <c r="U157">
-        <v>2.15</v>
-      </c>
-      <c r="V157">
-        <v>1.61</v>
-      </c>
-      <c r="W157">
-        <v>1.14</v>
-      </c>
-      <c r="X157">
-        <v>1.03</v>
-      </c>
-      <c r="Y157">
-        <v>1.13</v>
-      </c>
-      <c r="Z157">
-        <v>5.5</v>
-      </c>
-      <c r="AA157">
-        <v>1.5</v>
-      </c>
-      <c r="AB157">
-        <v>2.55</v>
-      </c>
-      <c r="AC157">
-        <v>2.25</v>
-      </c>
-      <c r="AD157">
-        <v>1.62</v>
-      </c>
-      <c r="AE157">
-        <v>1.22</v>
-      </c>
-      <c r="AF157">
-        <v>1.53</v>
-      </c>
-      <c r="AG157">
-        <v>2.3</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.17</v>
-      </c>
       <c r="AK157">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,80 +28834,80 @@
         </is>
       </c>
       <c r="N175">
+        <v>1.67</v>
+      </c>
+      <c r="O175">
+        <v>3.8</v>
+      </c>
+      <c r="P175">
+        <v>3.88</v>
+      </c>
+      <c r="Q175">
         <v>2.2</v>
       </c>
-      <c r="O175">
-        <v>3.2</v>
-      </c>
-      <c r="P175">
-        <v>2.83</v>
-      </c>
-      <c r="Q175">
-        <v>3</v>
-      </c>
       <c r="R175">
+        <v>2.3</v>
+      </c>
+      <c r="S175">
+        <v>1.29</v>
+      </c>
+      <c r="T175">
+        <v>3.3</v>
+      </c>
+      <c r="U175">
+        <v>2.4</v>
+      </c>
+      <c r="V175">
+        <v>1.5</v>
+      </c>
+      <c r="W175">
+        <v>1.08</v>
+      </c>
+      <c r="X175">
+        <v>1.02</v>
+      </c>
+      <c r="Y175">
+        <v>1.18</v>
+      </c>
+      <c r="Z175">
+        <v>4.2</v>
+      </c>
+      <c r="AA175">
+        <v>1.63</v>
+      </c>
+      <c r="AB175">
+        <v>2.13</v>
+      </c>
+      <c r="AC175">
+        <v>2.63</v>
+      </c>
+      <c r="AD175">
+        <v>1.44</v>
+      </c>
+      <c r="AE175">
+        <v>1.14</v>
+      </c>
+      <c r="AF175">
+        <v>1.61</v>
+      </c>
+      <c r="AG175">
+        <v>2.09</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ175">
+        <v>1.22</v>
+      </c>
+      <c r="AK175">
         <v>2.1</v>
-      </c>
-      <c r="S175">
-        <v>1.36</v>
-      </c>
-      <c r="T175">
-        <v>2.66</v>
-      </c>
-      <c r="U175">
-        <v>2.75</v>
-      </c>
-      <c r="V175">
-        <v>1.36</v>
-      </c>
-      <c r="W175">
-        <v>1.06</v>
-      </c>
-      <c r="X175">
-        <v>1.03</v>
-      </c>
-      <c r="Y175">
-        <v>1.26</v>
-      </c>
-      <c r="Z175">
-        <v>3.2</v>
-      </c>
-      <c r="AA175">
-        <v>1.89</v>
-      </c>
-      <c r="AB175">
-        <v>1.8</v>
-      </c>
-      <c r="AC175">
-        <v>3.14</v>
-      </c>
-      <c r="AD175">
-        <v>1.27</v>
-      </c>
-      <c r="AE175">
-        <v>1.06</v>
-      </c>
-      <c r="AF175">
-        <v>1.7</v>
-      </c>
-      <c r="AG175">
-        <v>2</v>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ175">
-        <v>1.25</v>
-      </c>
-      <c r="AK175">
-        <v>1.57</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="O176">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P176">
-        <v>3.88</v>
+        <v>2.83</v>
       </c>
       <c r="Q176">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="R176">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S176">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T176">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="U176">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V176">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W176">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X176">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y176">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z176">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA176">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AB176">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AC176">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="AD176">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE176">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF176">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG176">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK176">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -31626,7 +31626,7 @@
         <v>2.88</v>
       </c>
       <c r="U192">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V192">
         <v>1.4</v>
@@ -31641,19 +31641,19 @@
         <v>1.3</v>
       </c>
       <c r="Z192">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA192">
         <v>2.02</v>
       </c>
       <c r="AB192">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC192">
         <v>3.5</v>
       </c>
       <c r="AD192">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE192">
         <v>1.11</v>
@@ -42218,7 +42218,7 @@
         <v>1.33</v>
       </c>
       <c r="T257">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U257">
         <v>2.75</v>
@@ -42239,10 +42239,10 @@
         <v>3.2</v>
       </c>
       <c r="AA257">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB257">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AC257">
         <v>3.2</v>
@@ -50912,7 +50912,7 @@
         <v>1.3</v>
       </c>
       <c r="AK310">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="O311">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P311">
-        <v>1.41</v>
+        <v>2</v>
       </c>
       <c r="Q311">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="R311">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S311">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T311">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U311">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V311">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W311">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X311">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y311">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z311">
-        <v>4.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA311">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AB311">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AC311">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="AD311">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE311">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF311">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG311">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK311">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,64 +51165,64 @@
         </is>
       </c>
       <c r="N312">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="O312">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P312">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q312">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="R312">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S312">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T312">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U312">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V312">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W312">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X312">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y312">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="Z312">
-        <v>3.14</v>
+        <v>5.27</v>
       </c>
       <c r="AA312">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB312">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="AC312">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD312">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="AE312">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AF312">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AG312">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK312">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>3.19</v>
+        <v>1.7</v>
       </c>
       <c r="O313">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P313">
-        <v>1.85</v>
+        <v>4.25</v>
       </c>
       <c r="Q313">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="R313">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S313">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T313">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="U313">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="V313">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W313">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X313">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y313">
+        <v>1.23</v>
+      </c>
+      <c r="Z313">
+        <v>3.42</v>
+      </c>
+      <c r="AA313">
+        <v>1.9</v>
+      </c>
+      <c r="AB313">
+        <v>1.88</v>
+      </c>
+      <c r="AC313">
+        <v>3.21</v>
+      </c>
+      <c r="AD313">
+        <v>1.32</v>
+      </c>
+      <c r="AE313">
         <v>1.11</v>
       </c>
-      <c r="Z313">
-        <v>5.27</v>
-      </c>
-      <c r="AA313">
-        <v>1.53</v>
-      </c>
-      <c r="AB313">
-        <v>2.37</v>
-      </c>
-      <c r="AC313">
-        <v>2.27</v>
-      </c>
-      <c r="AD313">
-        <v>1.61</v>
-      </c>
-      <c r="AE313">
-        <v>1.21</v>
-      </c>
       <c r="AF313">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="AG313">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK313">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,80 +51654,80 @@
         </is>
       </c>
       <c r="N315">
-        <v>1.7</v>
+        <v>4.15</v>
       </c>
       <c r="O315">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P315">
-        <v>4.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q315">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="R315">
+        <v>2.4</v>
+      </c>
+      <c r="S315">
+        <v>1.25</v>
+      </c>
+      <c r="T315">
+        <v>3.4</v>
+      </c>
+      <c r="U315">
+        <v>2.52</v>
+      </c>
+      <c r="V315">
+        <v>1.54</v>
+      </c>
+      <c r="W315">
+        <v>1.12</v>
+      </c>
+      <c r="X315">
+        <v>1.02</v>
+      </c>
+      <c r="Y315">
+        <v>1.16</v>
+      </c>
+      <c r="Z315">
+        <v>4.05</v>
+      </c>
+      <c r="AA315">
+        <v>1.54</v>
+      </c>
+      <c r="AB315">
         <v>2.2</v>
       </c>
-      <c r="S315">
-        <v>1.36</v>
-      </c>
-      <c r="T315">
-        <v>3</v>
-      </c>
-      <c r="U315">
-        <v>2.83</v>
-      </c>
-      <c r="V315">
-        <v>1.4</v>
-      </c>
-      <c r="W315">
-        <v>1.04</v>
-      </c>
-      <c r="X315">
-        <v>1.01</v>
-      </c>
-      <c r="Y315">
-        <v>1.23</v>
-      </c>
-      <c r="Z315">
-        <v>3.42</v>
-      </c>
-      <c r="AA315">
-        <v>1.9</v>
-      </c>
-      <c r="AB315">
-        <v>1.88</v>
-      </c>
       <c r="AC315">
-        <v>3.21</v>
+        <v>2.49</v>
       </c>
       <c r="AD315">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE315">
+        <v>1.16</v>
+      </c>
+      <c r="AF315">
+        <v>1.67</v>
+      </c>
+      <c r="AG315">
+        <v>2.23</v>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ315">
+        <v>1.17</v>
+      </c>
+      <c r="AK315">
         <v>1.11</v>
-      </c>
-      <c r="AF315">
-        <v>1.72</v>
-      </c>
-      <c r="AG315">
-        <v>1.96</v>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ315">
-        <v>1.12</v>
-      </c>
-      <c r="AK315">
-        <v>1.86</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51844,13 +51844,13 @@
         <v>1.47</v>
       </c>
       <c r="W316">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X316">
         <v>1.04</v>
       </c>
       <c r="Y316">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z316">
         <v>3.9</v>
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G332">
@@ -54425,31 +54425,31 @@
         </is>
       </c>
       <c r="N332">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="O332">
-        <v>3.5</v>
+        <v>4.06</v>
       </c>
       <c r="P332">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q332">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="R332">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S332">
         <v>1.28</v>
       </c>
       <c r="T332">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U332">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="V332">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W332">
         <v>1.11</v>
@@ -54458,47 +54458,47 @@
         <v>1.03</v>
       </c>
       <c r="Y332">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z332">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA332">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB332">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AC332">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD332">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE332">
+        <v>1.18</v>
+      </c>
+      <c r="AF332">
+        <v>1.55</v>
+      </c>
+      <c r="AG332">
+        <v>2.25</v>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ332">
         <v>1.2</v>
       </c>
-      <c r="AF332">
-        <v>1.57</v>
-      </c>
-      <c r="AG332">
-        <v>2.3</v>
-      </c>
-      <c r="AH332" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI332" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ332">
-        <v>1.25</v>
-      </c>
       <c r="AK332">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AL332">
         <v>0</v>
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G333">
@@ -54588,31 +54588,31 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="O333">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
       <c r="P333">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q333">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="R333">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S333">
         <v>1.28</v>
       </c>
       <c r="T333">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U333">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="V333">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W333">
         <v>1.11</v>
@@ -54621,31 +54621,31 @@
         <v>1.03</v>
       </c>
       <c r="Y333">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z333">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA333">
+        <v>1.66</v>
+      </c>
+      <c r="AB333">
+        <v>2.13</v>
+      </c>
+      <c r="AC333">
+        <v>2.55</v>
+      </c>
+      <c r="AD333">
+        <v>1.51</v>
+      </c>
+      <c r="AE333">
+        <v>1.2</v>
+      </c>
+      <c r="AF333">
         <v>1.57</v>
       </c>
-      <c r="AB333">
-        <v>2.35</v>
-      </c>
-      <c r="AC333">
-        <v>2.63</v>
-      </c>
-      <c r="AD333">
-        <v>1.44</v>
-      </c>
-      <c r="AE333">
-        <v>1.18</v>
-      </c>
-      <c r="AF333">
-        <v>1.55</v>
-      </c>
       <c r="AG333">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
@@ -54658,10 +54658,10 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK333">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AL333">
         <v>0</v>
@@ -54769,10 +54769,10 @@
         <v>1.3</v>
       </c>
       <c r="T334">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U334">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V334">
         <v>1.44</v>
@@ -54793,13 +54793,13 @@
         <v>1.75</v>
       </c>
       <c r="AB334">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC334">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD334">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE334">
         <v>1.09</v>
@@ -54824,7 +54824,7 @@
         <v>1.22</v>
       </c>
       <c r="AK334">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL334">
         <v>0</v>
@@ -55131,10 +55131,10 @@
         <v>1.12</v>
       </c>
       <c r="AF336">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG336">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>

--- a/jogos_2026-09-12.xlsx
+++ b/jogos_2026-09-12.xlsx
@@ -1450,43 +1450,43 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA7">
         <v>1.9</v>
@@ -1495,19 +1495,19 @@
         <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="Q26">
+        <v>2.07</v>
+      </c>
+      <c r="R26">
+        <v>2.5</v>
+      </c>
+      <c r="S26">
+        <v>1.22</v>
+      </c>
+      <c r="T26">
+        <v>3.55</v>
+      </c>
+      <c r="U26">
+        <v>2.2</v>
+      </c>
+      <c r="V26">
+        <v>1.6</v>
+      </c>
+      <c r="W26">
+        <v>1.12</v>
+      </c>
+      <c r="X26">
+        <v>1.03</v>
+      </c>
+      <c r="Y26">
+        <v>1.1</v>
+      </c>
+      <c r="Z26">
+        <v>5.4</v>
+      </c>
+      <c r="AA26">
+        <v>1.44</v>
+      </c>
+      <c r="AB26">
+        <v>2.44</v>
+      </c>
+      <c r="AC26">
         <v>2.25</v>
       </c>
-      <c r="R26">
-        <v>2.16</v>
-      </c>
-      <c r="S26">
-        <v>1.36</v>
-      </c>
-      <c r="T26">
-        <v>3.11</v>
-      </c>
-      <c r="U26">
-        <v>2.65</v>
-      </c>
-      <c r="V26">
-        <v>1.42</v>
-      </c>
-      <c r="W26">
-        <v>1.07</v>
-      </c>
-      <c r="X26">
-        <v>1.02</v>
-      </c>
-      <c r="Y26">
-        <v>1.25</v>
-      </c>
-      <c r="Z26">
-        <v>3.6</v>
-      </c>
-      <c r="AA26">
-        <v>1.85</v>
-      </c>
-      <c r="AB26">
-        <v>1.95</v>
-      </c>
-      <c r="AC26">
-        <v>2.99</v>
-      </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK26">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="O27">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="Q27">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="R27">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>3.55</v>
+        <v>3.11</v>
       </c>
       <c r="U27">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="V27">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA27">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="AC27">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="AD27">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG27">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5199,34 +5199,34 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O30">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="Q30">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="R30">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T30">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U30">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1.02</v>
@@ -5235,13 +5235,13 @@
         <v>1.29</v>
       </c>
       <c r="Z30">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA30">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB30">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC30">
         <v>3.3</v>
@@ -5253,7 +5253,7 @@
         <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG30">
         <v>2</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>2.35</v>
+        <v>3.35</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T33">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
         <v>2.25</v>
@@ -5715,37 +5715,37 @@
         <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.17</v>
       </c>
       <c r="Z33">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB33">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC33">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AD33">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE33">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF33">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.86</v>
+        <v>2.7</v>
       </c>
       <c r="O34">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3.35</v>
+        <v>2.35</v>
       </c>
       <c r="Q34">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
         <v>2.25</v>
@@ -5878,37 +5878,37 @@
         <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
         <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="AA34">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB34">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC34">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AD34">
+        <v>1.55</v>
+      </c>
+      <c r="AE34">
+        <v>1.15</v>
+      </c>
+      <c r="AF34">
         <v>1.46</v>
       </c>
-      <c r="AE34">
-        <v>1.21</v>
-      </c>
-      <c r="AF34">
-        <v>1.53</v>
-      </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6026,7 +6026,7 @@
         <v>3.24</v>
       </c>
       <c r="R35">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
         <v>1.31</v>
@@ -6068,7 +6068,7 @@
         <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG35">
         <v>2.15</v>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="O40">
         <v>3.45</v>
       </c>
       <c r="P40">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="Q40">
         <v>2.25</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S40">
         <v>1.33</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
+        <v>2.09</v>
+      </c>
+      <c r="O46">
+        <v>3.4</v>
+      </c>
+      <c r="P46">
+        <v>3.3</v>
+      </c>
+      <c r="Q46">
         <v>2.45</v>
-      </c>
-      <c r="O46">
-        <v>3.7</v>
-      </c>
-      <c r="P46">
-        <v>2.44</v>
-      </c>
-      <c r="Q46">
-        <v>2.88</v>
       </c>
       <c r="R46">
         <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U46">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V46">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W46">
+        <v>1.08</v>
+      </c>
+      <c r="X46">
+        <v>1.04</v>
+      </c>
+      <c r="Y46">
+        <v>1.22</v>
+      </c>
+      <c r="Z46">
+        <v>3.54</v>
+      </c>
+      <c r="AA46">
+        <v>1.8</v>
+      </c>
+      <c r="AB46">
+        <v>1.91</v>
+      </c>
+      <c r="AC46">
+        <v>3.17</v>
+      </c>
+      <c r="AD46">
+        <v>1.35</v>
+      </c>
+      <c r="AE46">
         <v>1.13</v>
       </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>1.18</v>
-      </c>
-      <c r="Z46">
-        <v>4.4</v>
-      </c>
-      <c r="AA46">
-        <v>1.59</v>
-      </c>
-      <c r="AB46">
-        <v>2.37</v>
-      </c>
-      <c r="AC46">
-        <v>2.34</v>
-      </c>
-      <c r="AD46">
-        <v>1.5</v>
-      </c>
-      <c r="AE46">
-        <v>1.17</v>
-      </c>
       <c r="AF46">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG46">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK46">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q47">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R47">
         <v>2.25</v>
       </c>
       <c r="S47">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="T47">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="AA47">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AB47">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="AC47">
-        <v>3.17</v>
+        <v>2.34</v>
       </c>
       <c r="AD47">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="O48">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>6.18</v>
+        <v>4.05</v>
       </c>
       <c r="Q48">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="S48">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="T48">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="U48">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="V48">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z48">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AA48">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AB48">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AC48">
-        <v>2.33</v>
+        <v>3.08</v>
       </c>
       <c r="AD48">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE48">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF48">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG48">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AK48">
-        <v>2.49</v>
+        <v>1.94</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="O49">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="P49">
-        <v>4.05</v>
+        <v>6.18</v>
       </c>
       <c r="Q49">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="R49">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="V49">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z49">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AB49">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AC49">
-        <v>3.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD49">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE49">
+        <v>1.16</v>
+      </c>
+      <c r="AF49">
+        <v>1.7</v>
+      </c>
+      <c r="AG49">
+        <v>1.99</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.06</v>
       </c>
-      <c r="AF49">
-        <v>1.76</v>
-      </c>
-      <c r="AG49">
-        <v>1.88</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.21</v>
-      </c>
       <c r="AK49">
-        <v>1.94</v>
+        <v>2.49</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="O50">
+        <v>3.25</v>
+      </c>
+      <c r="P50">
+        <v>2.28</v>
+      </c>
+      <c r="Q50">
         <v>3.5</v>
       </c>
-      <c r="P50">
-        <v>2.6</v>
-      </c>
-      <c r="Q50">
-        <v>2.89</v>
-      </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S50">
+        <v>1.39</v>
+      </c>
+      <c r="T50">
+        <v>2.74</v>
+      </c>
+      <c r="U50">
+        <v>2.95</v>
+      </c>
+      <c r="V50">
+        <v>1.35</v>
+      </c>
+      <c r="W50">
+        <v>1.05</v>
+      </c>
+      <c r="X50">
+        <v>1.06</v>
+      </c>
+      <c r="Y50">
+        <v>1.31</v>
+      </c>
+      <c r="Z50">
+        <v>2.94</v>
+      </c>
+      <c r="AA50">
+        <v>2.05</v>
+      </c>
+      <c r="AB50">
+        <v>1.7</v>
+      </c>
+      <c r="AC50">
+        <v>4.1</v>
+      </c>
+      <c r="AD50">
+        <v>1.22</v>
+      </c>
+      <c r="AE50">
+        <v>1.07</v>
+      </c>
+      <c r="AF50">
+        <v>1.83</v>
+      </c>
+      <c r="AG50">
+        <v>1.91</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.3</v>
+      </c>
+      <c r="AK50">
         <v>1.33</v>
-      </c>
-      <c r="T50">
-        <v>3.1</v>
-      </c>
-      <c r="U50">
-        <v>2.6</v>
-      </c>
-      <c r="V50">
-        <v>1.48</v>
-      </c>
-      <c r="W50">
-        <v>1.11</v>
-      </c>
-      <c r="X50">
-        <v>1.03</v>
-      </c>
-      <c r="Y50">
-        <v>1.24</v>
-      </c>
-      <c r="Z50">
-        <v>4.02</v>
-      </c>
-      <c r="AA50">
-        <v>1.78</v>
-      </c>
-      <c r="AB50">
-        <v>2</v>
-      </c>
-      <c r="AC50">
-        <v>2.76</v>
-      </c>
-      <c r="AD50">
-        <v>1.4</v>
-      </c>
-      <c r="AE50">
-        <v>1.1</v>
-      </c>
-      <c r="AF50">
-        <v>1.62</v>
-      </c>
-      <c r="AG50">
-        <v>2.3</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.38</v>
-      </c>
-      <c r="AK50">
-        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="Q51">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="R51">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="V51">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z51">
-        <v>2.94</v>
+        <v>4.02</v>
       </c>
       <c r="AA51">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AB51">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC51">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>0</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P62">
+        <v>2.45</v>
+      </c>
+      <c r="Q62">
+        <v>3.1</v>
+      </c>
+      <c r="R62">
         <v>2.15</v>
       </c>
-      <c r="Q62">
-        <v>3.15</v>
-      </c>
-      <c r="R62">
-        <v>2.32</v>
-      </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T62">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="U62">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V62">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z62">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AB62">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AC62">
-        <v>2.21</v>
+        <v>2.83</v>
       </c>
       <c r="AD62">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AE62">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AG62">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK62">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q63">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R63">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S63">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="U63">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V63">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z63">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA63">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AC63">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="AD63">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE63">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="AG63">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK63">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P66">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q66">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R66">
+        <v>2.1</v>
+      </c>
+      <c r="S66">
+        <v>1.3</v>
+      </c>
+      <c r="T66">
+        <v>3.04</v>
+      </c>
+      <c r="U66">
+        <v>2.61</v>
+      </c>
+      <c r="V66">
+        <v>1.41</v>
+      </c>
+      <c r="W66">
+        <v>1.06</v>
+      </c>
+      <c r="X66">
+        <v>1.03</v>
+      </c>
+      <c r="Y66">
+        <v>1.22</v>
+      </c>
+      <c r="Z66">
+        <v>3.5</v>
+      </c>
+      <c r="AA66">
         <v>2.05</v>
       </c>
-      <c r="S66">
-        <v>1.38</v>
-      </c>
-      <c r="T66">
-        <v>2.67</v>
-      </c>
-      <c r="U66">
-        <v>2.75</v>
-      </c>
-      <c r="V66">
-        <v>1.32</v>
-      </c>
-      <c r="W66">
-        <v>1.05</v>
-      </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.28</v>
-      </c>
-      <c r="Z66">
-        <v>3.08</v>
-      </c>
-      <c r="AA66">
-        <v>1.98</v>
-      </c>
       <c r="AB66">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC66">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD66">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG66">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11583,7 +11583,7 @@
         <v>1.36</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
         <v>1.04</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q91">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="R91">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S91">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T91">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U91">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V91">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W91">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y91">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z91">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA91">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AB91">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AC91">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AD91">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF91">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>2.22</v>
+        <v>1.69</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="R92">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T92">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U92">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V92">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W92">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z92">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA92">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AB92">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AC92">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AD92">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF92">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG92">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK92">
-        <v>1.69</v>
+        <v>2.22</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -17098,65 +17098,65 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O103">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P103">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q103">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="R103">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="S103">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T103">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U103">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="V103">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W103">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X103">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z103">
-        <v>2.66</v>
+        <v>3.01</v>
       </c>
       <c r="AA103">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB103">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC103">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD103">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE103">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF103">
+        <v>1.81</v>
+      </c>
+      <c r="AG103">
         <v>1.86</v>
       </c>
-      <c r="AG103">
-        <v>1.81</v>
-      </c>
       <c r="AH103" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AK103">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17285,7 +17285,7 @@
         <v>2.28</v>
       </c>
       <c r="V104">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W104">
         <v>1.08</v>
@@ -17439,13 +17439,13 @@
         <v>2.03</v>
       </c>
       <c r="S105">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T105">
         <v>2.88</v>
       </c>
       <c r="U105">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="V105">
         <v>1.36</v>
@@ -17460,7 +17460,7 @@
         <v>1.29</v>
       </c>
       <c r="Z105">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="AA105">
         <v>1.95</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="O117">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P117">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q117">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="R117">
+        <v>2.24</v>
+      </c>
+      <c r="S117">
+        <v>1.28</v>
+      </c>
+      <c r="T117">
+        <v>3.5</v>
+      </c>
+      <c r="U117">
         <v>2.3</v>
       </c>
-      <c r="S117">
-        <v>1.35</v>
-      </c>
-      <c r="T117">
-        <v>3.1</v>
-      </c>
-      <c r="U117">
-        <v>2.6</v>
-      </c>
       <c r="V117">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W117">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA117">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB117">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AC117">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD117">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE117">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF117">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="O118">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P118">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="Q118">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="R118">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S118">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T118">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U118">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V118">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W118">
+        <v>1.09</v>
+      </c>
+      <c r="X118">
+        <v>1.02</v>
+      </c>
+      <c r="Y118">
+        <v>1.22</v>
+      </c>
+      <c r="Z118">
+        <v>3.8</v>
+      </c>
+      <c r="AA118">
+        <v>1.8</v>
+      </c>
+      <c r="AB118">
+        <v>2</v>
+      </c>
+      <c r="AC118">
+        <v>3</v>
+      </c>
+      <c r="AD118">
+        <v>1.36</v>
+      </c>
+      <c r="AE118">
         <v>1.11</v>
       </c>
-      <c r="X118">
-        <v>1.03</v>
-      </c>
-      <c r="Y118">
-        <v>1.18</v>
-      </c>
-      <c r="Z118">
-        <v>4.5</v>
-      </c>
-      <c r="AA118">
-        <v>1.61</v>
-      </c>
-      <c r="AB118">
-        <v>2.21</v>
-      </c>
-      <c r="AC118">
-        <v>2.63</v>
-      </c>
-      <c r="AD118">
-        <v>1.44</v>
-      </c>
-      <c r="AE118">
-        <v>1.18</v>
-      </c>
       <c r="AF118">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AG118">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          